--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5228,10 +5231,10 @@
         <v>10594.3</v>
       </c>
       <c r="E57" t="n">
-        <v>10650.44</v>
+        <v>10650.4</v>
       </c>
       <c r="F57" t="n">
-        <v>-180.66</v>
+        <v>-180.7</v>
       </c>
       <c r="G57" s="5" t="n">
         <v>-0.0167</v>
@@ -5299,31 +5302,115 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10650.92</v>
+      </c>
+      <c r="C58" t="n">
+        <v>10734.85</v>
+      </c>
+      <c r="D58" t="n">
+        <v>10650.92</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>83.93000000000001</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10320.3</v>
+      </c>
+      <c r="J58" t="n">
+        <v>10335.95</v>
+      </c>
+      <c r="K58" t="n">
+        <v>10513.4</v>
+      </c>
+      <c r="L58" t="n">
+        <v>10690.85</v>
+      </c>
+      <c r="M58" t="n">
+        <v>10787.4</v>
+      </c>
+      <c r="N58" t="n">
+        <v>10883.95</v>
+      </c>
+      <c r="O58" t="n">
+        <v>11142.3</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I58" s="13" t="n">
-        <v>10320.3</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>10336.01</v>
-      </c>
-      <c r="K58" s="13" t="n">
-        <v>10513.44</v>
-      </c>
-      <c r="L58" s="13" t="n">
-        <v>10690.87</v>
-      </c>
-      <c r="M58" s="13" t="n">
-        <v>10787.44</v>
-      </c>
-      <c r="N58" s="13" t="n">
-        <v>10884.01</v>
-      </c>
-      <c r="O58" s="13" t="n">
-        <v>11142.3</v>
+      <c r="I59" s="14" t="n">
+        <v>10566.99</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>10818.78</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -669,25 +666,25 @@
         <v>230.6</v>
       </c>
       <c r="I2" t="n">
-        <v>8964.299999999999</v>
+        <v>9016.700000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>9000.629999999999</v>
+        <v>9020.280000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>9074.450000000001</v>
+        <v>9087.549999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>9148.280000000001</v>
+        <v>9154.83</v>
       </c>
       <c r="M2" t="n">
-        <v>9203.35</v>
+        <v>9190.25</v>
       </c>
       <c r="N2" t="n">
-        <v>9258.43</v>
+        <v>9225.67</v>
       </c>
       <c r="O2" t="n">
-        <v>9351</v>
+        <v>9324.799999999999</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5308,25 +5305,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10650.92</v>
+        <v>10650.9</v>
       </c>
       <c r="C58" t="n">
-        <v>10734.85</v>
+        <v>10734.9</v>
       </c>
       <c r="D58" t="n">
-        <v>10650.92</v>
+        <v>10650.9</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>10697.6</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>47.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0044</v>
       </c>
       <c r="H58" t="n">
-        <v>83.93000000000001</v>
+        <v>84</v>
       </c>
       <c r="I58" t="n">
         <v>10320.3</v>
@@ -5349,10 +5346,8 @@
       <c r="O58" t="n">
         <v>11142.3</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5360,9 +5355,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5381,36 +5376,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="14" t="n">
-        <v>10566.99</v>
-      </c>
-      <c r="J59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="14" t="n">
-        <v>10818.78</v>
+      <c r="I59" s="13" t="n">
+        <v>10566.9</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>10615.95</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>10655.6</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>10695.25</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>10739.6</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>10783.95</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>10818.9</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -5311,19 +5311,19 @@
         <v>10734.9</v>
       </c>
       <c r="D58" t="n">
-        <v>10650.9</v>
+        <v>10586.39</v>
       </c>
       <c r="E58" t="n">
-        <v>10697.6</v>
+        <v>10658.13</v>
       </c>
       <c r="F58" t="n">
-        <v>47.2</v>
+        <v>7.73</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0007</v>
       </c>
       <c r="H58" t="n">
-        <v>84</v>
+        <v>148.51</v>
       </c>
       <c r="I58" t="n">
         <v>10320.3</v>
@@ -5355,9 +5355,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -5387,25 +5387,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>10566.9</v>
+        <v>10437.88</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>10615.95</v>
+        <v>10508.36</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>10655.6</v>
+        <v>10583.87</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>10695.25</v>
+        <v>10659.39</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>10739.6</v>
+        <v>10732.39</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>10783.95</v>
+        <v>10805.38</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>10818.9</v>
+        <v>10883.41</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>230.6</v>
       </c>
       <c r="I2" t="n">
-        <v>9016.700000000001</v>
+        <v>9036.9</v>
       </c>
       <c r="J2" t="n">
-        <v>9020.280000000001</v>
+        <v>9027.85</v>
       </c>
       <c r="K2" t="n">
-        <v>9087.549999999999</v>
+        <v>9092.6</v>
       </c>
       <c r="L2" t="n">
-        <v>9154.83</v>
+        <v>9157.35</v>
       </c>
       <c r="M2" t="n">
-        <v>9190.25</v>
+        <v>9185.200000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>9225.67</v>
+        <v>9213.049999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>9324.799999999999</v>
+        <v>9314.700000000001</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -720,7 +720,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -5315,19 +5315,19 @@
         <v>10734.9</v>
       </c>
       <c r="D58" t="n">
-        <v>10586.39</v>
+        <v>10586.4</v>
       </c>
       <c r="E58" t="n">
-        <v>10658.13</v>
+        <v>10658.1</v>
       </c>
       <c r="F58" t="n">
-        <v>7.73</v>
+        <v>7.7</v>
       </c>
       <c r="G58" s="5" t="n">
         <v>0.0007</v>
       </c>
       <c r="H58" t="n">
-        <v>148.51</v>
+        <v>148.5</v>
       </c>
       <c r="I58" t="n">
         <v>10320.3</v>
@@ -5391,25 +5391,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>10437.88</v>
+        <v>10437.9</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>10508.36</v>
+        <v>10508.32</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>10583.87</v>
+        <v>10583.85</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>10659.39</v>
+        <v>10659.38</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>10732.39</v>
+        <v>10732.35</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>10805.38</v>
+        <v>10805.32</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>10883.41</v>
+        <v>10883.4</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -5312,22 +5312,22 @@
         <v>10650.9</v>
       </c>
       <c r="C58" t="n">
-        <v>10734.9</v>
+        <v>10735.34</v>
       </c>
       <c r="D58" t="n">
         <v>10586.4</v>
       </c>
       <c r="E58" t="n">
-        <v>10658.1</v>
+        <v>10688.47</v>
       </c>
       <c r="F58" t="n">
-        <v>7.7</v>
+        <v>38.07</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0036</v>
       </c>
       <c r="H58" t="n">
-        <v>148.5</v>
+        <v>148.94</v>
       </c>
       <c r="I58" t="n">
         <v>10320.3</v>
@@ -5391,25 +5391,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>10437.9</v>
+        <v>10437.46</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>10508.32</v>
+        <v>10553.33</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>10583.85</v>
+        <v>10614</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>10659.38</v>
+        <v>10674.67</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>10732.35</v>
+        <v>10762.94</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>10805.32</v>
+        <v>10851.21</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>10883.4</v>
+        <v>10884.28</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -5312,22 +5312,22 @@
         <v>10650.9</v>
       </c>
       <c r="C58" t="n">
-        <v>10735.34</v>
+        <v>10823</v>
       </c>
       <c r="D58" t="n">
         <v>10586.4</v>
       </c>
       <c r="E58" t="n">
-        <v>10688.47</v>
+        <v>10816.14</v>
       </c>
       <c r="F58" t="n">
-        <v>38.07</v>
+        <v>165.74</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0036</v>
+        <v>0.0156</v>
       </c>
       <c r="H58" t="n">
-        <v>148.94</v>
+        <v>236.6</v>
       </c>
       <c r="I58" t="n">
         <v>10320.3</v>
@@ -5359,13 +5359,15 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5391,25 +5393,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>10437.46</v>
+        <v>10349.8</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>10553.33</v>
+        <v>10635.26</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>10614</v>
+        <v>10697.84</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>10674.67</v>
+        <v>10760.42</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>10762.94</v>
+        <v>10934.44</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>10851.21</v>
+        <v>11108.46</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>10884.28</v>
+        <v>11059.6</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5386,34 +5379,6 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>10349.8</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>10635.26</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>10697.84</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>10760.42</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>10934.44</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>11108.46</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>11059.6</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9138.9</v>
+        <v>9321.4</v>
       </c>
       <c r="C2" t="n">
-        <v>9357.5</v>
+        <v>9325.9</v>
       </c>
       <c r="D2" t="n">
-        <v>9126.9</v>
+        <v>9179.200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9321.4</v>
+        <v>9187.299999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>182.5</v>
+        <v>-134.1</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.02</v>
+        <v>-0.0144</v>
       </c>
       <c r="H2" t="n">
-        <v>230.6</v>
+        <v>146.7</v>
       </c>
       <c r="I2" t="n">
-        <v>9036.9</v>
+        <v>8896.299999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>9027.85</v>
+        <v>9130.4</v>
       </c>
       <c r="K2" t="n">
-        <v>9092.6</v>
+        <v>9206.1</v>
       </c>
       <c r="L2" t="n">
-        <v>9157.35</v>
+        <v>9281.799999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>9185.200000000001</v>
+        <v>9436.700000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>9213.049999999999</v>
+        <v>9591.6</v>
       </c>
       <c r="O2" t="n">
-        <v>9314.700000000001</v>
+        <v>9588.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,28 +685,24 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -715,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9321.4</v>
+        <v>9187.299999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>9325.9</v>
+        <v>9253.5</v>
       </c>
       <c r="D3" t="n">
-        <v>9179.200000000001</v>
+        <v>9107.4</v>
       </c>
       <c r="E3" t="n">
-        <v>9187.299999999999</v>
+        <v>9208.200000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-134.1</v>
+        <v>20.9</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0144</v>
+        <v>0.0023</v>
       </c>
       <c r="H3" t="n">
-        <v>146.7</v>
+        <v>146.1</v>
       </c>
       <c r="I3" t="n">
-        <v>8896.299999999999</v>
+        <v>9032.5</v>
       </c>
       <c r="J3" t="n">
-        <v>9130.4</v>
+        <v>9007.969999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>9206.1</v>
+        <v>9113.950000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>9281.799999999999</v>
+        <v>9219.93</v>
       </c>
       <c r="M3" t="n">
-        <v>9436.700000000001</v>
+        <v>9260.65</v>
       </c>
       <c r="N3" t="n">
-        <v>9591.6</v>
+        <v>9301.370000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>9588.1</v>
+        <v>9472.6</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -775,12 +771,12 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -806,50 +802,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9187.299999999999</v>
+        <v>9208.200000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>9253.5</v>
+        <v>9340.700000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>9107.4</v>
+        <v>9190.6</v>
       </c>
       <c r="E4" t="n">
-        <v>9208.200000000001</v>
+        <v>9283.299999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>20.9</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>146.1</v>
+        <v>150.1</v>
       </c>
       <c r="I4" t="n">
-        <v>9032.5</v>
+        <v>8961.299999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>9007.969999999999</v>
+        <v>9075.98</v>
       </c>
       <c r="K4" t="n">
-        <v>9113.950000000001</v>
+        <v>9135.15</v>
       </c>
       <c r="L4" t="n">
-        <v>9219.93</v>
+        <v>9194.33</v>
       </c>
       <c r="M4" t="n">
-        <v>9260.65</v>
+        <v>9281.25</v>
       </c>
       <c r="N4" t="n">
-        <v>9301.370000000001</v>
+        <v>9368.17</v>
       </c>
       <c r="O4" t="n">
-        <v>9472.6</v>
+        <v>9399.6</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -857,18 +853,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -881,59 +877,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9208.200000000001</v>
+        <v>9283.299999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>9340.700000000001</v>
+        <v>9314.4</v>
       </c>
       <c r="D5" t="n">
-        <v>9190.6</v>
+        <v>9195.700000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>9283.299999999999</v>
+        <v>9216.700000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>75.09999999999999</v>
+        <v>-66.59999999999999</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0072</v>
       </c>
       <c r="H5" t="n">
-        <v>150.1</v>
+        <v>118.7</v>
       </c>
       <c r="I5" t="n">
-        <v>8961.299999999999</v>
+        <v>9040.5</v>
       </c>
       <c r="J5" t="n">
-        <v>9075.98</v>
+        <v>9142.02</v>
       </c>
       <c r="K5" t="n">
-        <v>9135.15</v>
+        <v>9208.25</v>
       </c>
       <c r="L5" t="n">
-        <v>9194.33</v>
+        <v>9274.469999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>9281.25</v>
+        <v>9358.35</v>
       </c>
       <c r="N5" t="n">
-        <v>9368.17</v>
+        <v>9442.23</v>
       </c>
       <c r="O5" t="n">
-        <v>9399.6</v>
+        <v>9490.799999999999</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -941,18 +933,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -965,55 +957,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9283.299999999999</v>
+        <v>9216.700000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>9314.4</v>
+        <v>9292.1</v>
       </c>
       <c r="D6" t="n">
-        <v>9195.700000000001</v>
+        <v>9177.1</v>
       </c>
       <c r="E6" t="n">
-        <v>9216.700000000001</v>
+        <v>9284.799999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-66.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.0074</v>
       </c>
       <c r="H6" t="n">
-        <v>118.7</v>
+        <v>115</v>
       </c>
       <c r="I6" t="n">
-        <v>9040.5</v>
+        <v>9077</v>
       </c>
       <c r="J6" t="n">
-        <v>9142.02</v>
+        <v>9078.82</v>
       </c>
       <c r="K6" t="n">
-        <v>9208.25</v>
+        <v>9157.35</v>
       </c>
       <c r="L6" t="n">
-        <v>9274.469999999999</v>
+        <v>9235.879999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>9358.35</v>
+        <v>9276.049999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>9442.23</v>
+        <v>9316.23</v>
       </c>
       <c r="O6" t="n">
-        <v>9490.799999999999</v>
+        <v>9433.1</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,18 +1017,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1054,50 +1050,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9216.700000000001</v>
+        <v>9284.799999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>9292.1</v>
+        <v>9494.6</v>
       </c>
       <c r="D7" t="n">
-        <v>9177.1</v>
+        <v>9266.299999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>9284.799999999999</v>
+        <v>9491.299999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>68.09999999999999</v>
+        <v>206.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0222</v>
       </c>
       <c r="H7" t="n">
-        <v>115</v>
+        <v>228.3</v>
       </c>
       <c r="I7" t="n">
-        <v>9077</v>
+        <v>9062.1</v>
       </c>
       <c r="J7" t="n">
-        <v>9078.82</v>
+        <v>9194.9</v>
       </c>
       <c r="K7" t="n">
-        <v>9157.35</v>
+        <v>9227.299999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>9235.879999999999</v>
+        <v>9259.700000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>9276.049999999999</v>
+        <v>9342.299999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>9316.23</v>
+        <v>9424.9</v>
       </c>
       <c r="O7" t="n">
-        <v>9433.1</v>
+        <v>9407.1</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1108,80 +1104,80 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9284.799999999999</v>
+        <v>9491.200000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>9494.6</v>
+        <v>9577.1</v>
       </c>
       <c r="D8" t="n">
-        <v>9266.299999999999</v>
+        <v>9414.6</v>
       </c>
       <c r="E8" t="n">
-        <v>9491.299999999999</v>
+        <v>9427.5</v>
       </c>
       <c r="F8" t="n">
-        <v>206.5</v>
+        <v>-63.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0067</v>
       </c>
       <c r="H8" t="n">
-        <v>228.3</v>
+        <v>162.5</v>
       </c>
       <c r="I8" t="n">
-        <v>9062.1</v>
+        <v>9038</v>
       </c>
       <c r="J8" t="n">
-        <v>9194.9</v>
+        <v>9318.43</v>
       </c>
       <c r="K8" t="n">
-        <v>9227.299999999999</v>
+        <v>9377.15</v>
       </c>
       <c r="L8" t="n">
-        <v>9259.700000000001</v>
+        <v>9435.870000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>9342.299999999999</v>
+        <v>9605.450000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>9424.9</v>
+        <v>9775.02</v>
       </c>
       <c r="O8" t="n">
-        <v>9407.1</v>
+        <v>9722.9</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1194,78 +1190,76 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9491.200000000001</v>
+        <v>9427.5</v>
       </c>
       <c r="C9" t="n">
-        <v>9577.1</v>
+        <v>9474.299999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>9414.6</v>
+        <v>9276.9</v>
       </c>
       <c r="E9" t="n">
-        <v>9427.5</v>
+        <v>9354.6</v>
       </c>
       <c r="F9" t="n">
-        <v>-63.8</v>
+        <v>-72.90000000000001</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0067</v>
+        <v>-0.0077</v>
       </c>
       <c r="H9" t="n">
-        <v>162.5</v>
+        <v>197.4</v>
       </c>
       <c r="I9" t="n">
-        <v>9038</v>
+        <v>9252.1</v>
       </c>
       <c r="J9" t="n">
-        <v>9318.43</v>
+        <v>9230.83</v>
       </c>
       <c r="K9" t="n">
-        <v>9377.15</v>
+        <v>9346.25</v>
       </c>
       <c r="L9" t="n">
-        <v>9435.870000000001</v>
+        <v>9461.67</v>
       </c>
       <c r="M9" t="n">
-        <v>9605.450000000001</v>
+        <v>9508.75</v>
       </c>
       <c r="N9" t="n">
-        <v>9775.02</v>
+        <v>9555.83</v>
       </c>
       <c r="O9" t="n">
-        <v>9722.9</v>
+        <v>9739.6</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,12 +1267,14 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1297,57 +1293,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9427.5</v>
+        <v>9354.5</v>
       </c>
       <c r="C10" t="n">
-        <v>9474.299999999999</v>
+        <v>9645.6</v>
       </c>
       <c r="D10" t="n">
-        <v>9276.9</v>
+        <v>9354.5</v>
       </c>
       <c r="E10" t="n">
-        <v>9354.6</v>
+        <v>9645.6</v>
       </c>
       <c r="F10" t="n">
-        <v>-72.90000000000001</v>
+        <v>291</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0311</v>
       </c>
       <c r="H10" t="n">
-        <v>197.4</v>
+        <v>291.1</v>
       </c>
       <c r="I10" t="n">
-        <v>9252.1</v>
+        <v>9079.5</v>
       </c>
       <c r="J10" t="n">
-        <v>9230.83</v>
+        <v>9146.700000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>9346.25</v>
+        <v>9255.9</v>
       </c>
       <c r="L10" t="n">
-        <v>9461.67</v>
+        <v>9365.1</v>
       </c>
       <c r="M10" t="n">
-        <v>9508.75</v>
+        <v>9453.299999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>9555.83</v>
+        <v>9541.5</v>
       </c>
       <c r="O10" t="n">
-        <v>9739.6</v>
+        <v>9671.700000000001</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1355,83 +1351,83 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
-      </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9354.5</v>
+        <v>9645.6</v>
       </c>
       <c r="C11" t="n">
-        <v>9645.6</v>
+        <v>9787.6</v>
       </c>
       <c r="D11" t="n">
-        <v>9354.5</v>
+        <v>9632.799999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>9645.6</v>
+        <v>9717.299999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>291</v>
+        <v>71.7</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0311</v>
+        <v>0.0074</v>
       </c>
       <c r="H11" t="n">
-        <v>291.1</v>
+        <v>154.8</v>
       </c>
       <c r="I11" t="n">
-        <v>9079.5</v>
+        <v>9063.4</v>
       </c>
       <c r="J11" t="n">
-        <v>9146.700000000001</v>
+        <v>9427.27</v>
       </c>
       <c r="K11" t="n">
-        <v>9255.9</v>
+        <v>9500.049999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>9365.1</v>
+        <v>9572.82</v>
       </c>
       <c r="M11" t="n">
-        <v>9453.299999999999</v>
+        <v>9791.15</v>
       </c>
       <c r="N11" t="n">
-        <v>9541.5</v>
+        <v>10009.47</v>
       </c>
       <c r="O11" t="n">
-        <v>9671.700000000001</v>
+        <v>9936.700000000001</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1442,25 +1438,21 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
@@ -1472,50 +1464,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9645.6</v>
+        <v>9717.299999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>9787.6</v>
+        <v>9786.799999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>9632.799999999999</v>
+        <v>9574.200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>9717.299999999999</v>
+        <v>9682.6</v>
       </c>
       <c r="F12" t="n">
-        <v>71.7</v>
+        <v>-34.7</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0036</v>
       </c>
       <c r="H12" t="n">
-        <v>154.8</v>
+        <v>212.6</v>
       </c>
       <c r="I12" t="n">
-        <v>9063.4</v>
+        <v>9478</v>
       </c>
       <c r="J12" t="n">
-        <v>9427.27</v>
+        <v>9566.049999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>9500.049999999999</v>
+        <v>9639.9</v>
       </c>
       <c r="L12" t="n">
-        <v>9572.82</v>
+        <v>9713.75</v>
       </c>
       <c r="M12" t="n">
-        <v>9791.15</v>
+        <v>9794.700000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>10009.47</v>
+        <v>9875.65</v>
       </c>
       <c r="O12" t="n">
-        <v>9936.700000000001</v>
+        <v>9942.4</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1523,18 +1515,18 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1547,55 +1539,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9717.299999999999</v>
+        <v>9682.6</v>
       </c>
       <c r="C13" t="n">
-        <v>9786.799999999999</v>
+        <v>9930.1</v>
       </c>
       <c r="D13" t="n">
-        <v>9574.200000000001</v>
+        <v>9610.5</v>
       </c>
       <c r="E13" t="n">
-        <v>9682.6</v>
+        <v>9698.4</v>
       </c>
       <c r="F13" t="n">
-        <v>-34.7</v>
+        <v>15.8</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0016</v>
       </c>
       <c r="H13" t="n">
-        <v>212.6</v>
+        <v>319.6</v>
       </c>
       <c r="I13" t="n">
-        <v>9478</v>
+        <v>9361.6</v>
       </c>
       <c r="J13" t="n">
-        <v>9566.049999999999</v>
+        <v>9471.049999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>9639.9</v>
+        <v>9576.299999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>9713.75</v>
+        <v>9681.549999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>9794.700000000001</v>
+        <v>9788.9</v>
       </c>
       <c r="N13" t="n">
-        <v>9875.65</v>
+        <v>9896.25</v>
       </c>
       <c r="O13" t="n">
-        <v>9942.4</v>
+        <v>9999.4</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1603,21 +1599,23 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1627,59 +1625,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9682.6</v>
+        <v>9698.4</v>
       </c>
       <c r="C14" t="n">
-        <v>9930.1</v>
+        <v>9707.700000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>9610.5</v>
+        <v>9423.9</v>
       </c>
       <c r="E14" t="n">
-        <v>9698.4</v>
+        <v>9539.700000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>15.8</v>
+        <v>-158.7</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0164</v>
       </c>
       <c r="H14" t="n">
-        <v>319.6</v>
+        <v>283.8</v>
       </c>
       <c r="I14" t="n">
-        <v>9361.6</v>
+        <v>9290.9</v>
       </c>
       <c r="J14" t="n">
-        <v>9471.049999999999</v>
+        <v>9342.85</v>
       </c>
       <c r="K14" t="n">
-        <v>9576.299999999999</v>
+        <v>9538.6</v>
       </c>
       <c r="L14" t="n">
-        <v>9681.549999999999</v>
+        <v>9734.35</v>
       </c>
       <c r="M14" t="n">
-        <v>9788.9</v>
+        <v>9858.200000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>9896.25</v>
+        <v>9982.049999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>9999.4</v>
+        <v>10249.7</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1687,23 +1681,21 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1713,55 +1705,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9698.4</v>
+        <v>9539.700000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>9707.700000000001</v>
+        <v>9740.200000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>9423.9</v>
+        <v>9521.5</v>
       </c>
       <c r="E15" t="n">
-        <v>9539.700000000001</v>
+        <v>9720.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-158.7</v>
+        <v>180.8</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.019</v>
       </c>
       <c r="H15" t="n">
-        <v>283.8</v>
+        <v>218.7</v>
       </c>
       <c r="I15" t="n">
-        <v>9290.9</v>
+        <v>9140.1</v>
       </c>
       <c r="J15" t="n">
-        <v>9342.85</v>
+        <v>9242.85</v>
       </c>
       <c r="K15" t="n">
-        <v>9538.6</v>
+        <v>9397.799999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>9734.35</v>
+        <v>9552.75</v>
       </c>
       <c r="M15" t="n">
-        <v>9858.200000000001</v>
+        <v>9681.6</v>
       </c>
       <c r="N15" t="n">
-        <v>9982.049999999999</v>
+        <v>9810.450000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>10249.7</v>
+        <v>9991.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1769,19 +1765,19 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1793,59 +1789,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9539.700000000001</v>
+        <v>9720.6</v>
       </c>
       <c r="C16" t="n">
-        <v>9740.200000000001</v>
+        <v>9744.799999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>9521.5</v>
+        <v>9667</v>
       </c>
       <c r="E16" t="n">
-        <v>9720.5</v>
+        <v>9667</v>
       </c>
       <c r="F16" t="n">
-        <v>180.8</v>
+        <v>-53.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.019</v>
+        <v>-0.0055</v>
       </c>
       <c r="H16" t="n">
-        <v>218.7</v>
+        <v>77.8</v>
       </c>
       <c r="I16" t="n">
-        <v>9140.1</v>
+        <v>9302.799999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>9242.85</v>
+        <v>9546.620000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>9397.799999999999</v>
+        <v>9611.15</v>
       </c>
       <c r="L16" t="n">
-        <v>9552.75</v>
+        <v>9675.68</v>
       </c>
       <c r="M16" t="n">
-        <v>9681.6</v>
+        <v>9829.85</v>
       </c>
       <c r="N16" t="n">
-        <v>9810.450000000001</v>
+        <v>9984.030000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>9991.5</v>
+        <v>9958.9</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1858,13 +1850,11 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1877,55 +1867,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9720.6</v>
+        <v>9667.1</v>
       </c>
       <c r="C17" t="n">
-        <v>9744.799999999999</v>
+        <v>9761.5</v>
       </c>
       <c r="D17" t="n">
-        <v>9667</v>
+        <v>9622.700000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>9667</v>
+        <v>9649</v>
       </c>
       <c r="F17" t="n">
-        <v>-53.5</v>
+        <v>-18</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0019</v>
       </c>
       <c r="H17" t="n">
-        <v>77.8</v>
+        <v>138.8</v>
       </c>
       <c r="I17" t="n">
-        <v>9302.799999999999</v>
+        <v>9589.200000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>9546.620000000001</v>
+        <v>9569.75</v>
       </c>
       <c r="K17" t="n">
-        <v>9611.15</v>
+        <v>9628.1</v>
       </c>
       <c r="L17" t="n">
-        <v>9675.68</v>
+        <v>9686.450000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>9829.85</v>
+        <v>9705.9</v>
       </c>
       <c r="N17" t="n">
-        <v>9984.030000000001</v>
+        <v>9725.35</v>
       </c>
       <c r="O17" t="n">
-        <v>9958.9</v>
+        <v>9822.6</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1933,19 +1927,25 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1957,57 +1957,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9667.1</v>
+        <v>9649</v>
       </c>
       <c r="C18" t="n">
-        <v>9761.5</v>
+        <v>9903.1</v>
       </c>
       <c r="D18" t="n">
-        <v>9622.700000000001</v>
+        <v>9649</v>
       </c>
       <c r="E18" t="n">
-        <v>9649</v>
+        <v>9897.4</v>
       </c>
       <c r="F18" t="n">
-        <v>-18</v>
+        <v>248.4</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0257</v>
       </c>
       <c r="H18" t="n">
-        <v>138.8</v>
+        <v>254.1</v>
       </c>
       <c r="I18" t="n">
-        <v>9589.200000000001</v>
+        <v>9483.9</v>
       </c>
       <c r="J18" t="n">
-        <v>9569.75</v>
+        <v>9488.65</v>
       </c>
       <c r="K18" t="n">
-        <v>9628.1</v>
+        <v>9579.6</v>
       </c>
       <c r="L18" t="n">
-        <v>9686.450000000001</v>
+        <v>9670.549999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>9705.9</v>
+        <v>9718.4</v>
       </c>
       <c r="N18" t="n">
-        <v>9725.35</v>
+        <v>9766.25</v>
       </c>
       <c r="O18" t="n">
-        <v>9822.6</v>
+        <v>9900.299999999999</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2015,87 +2015,83 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9649</v>
+        <v>9897.4</v>
       </c>
       <c r="C19" t="n">
-        <v>9903.1</v>
+        <v>9901.5</v>
       </c>
       <c r="D19" t="n">
-        <v>9649</v>
+        <v>9829.4</v>
       </c>
       <c r="E19" t="n">
-        <v>9897.4</v>
+        <v>9870.700000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>248.4</v>
+        <v>-26.7</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0257</v>
+        <v>-0.0027</v>
       </c>
       <c r="H19" t="n">
-        <v>254.1</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>9483.9</v>
+        <v>9394.9</v>
       </c>
       <c r="J19" t="n">
-        <v>9488.65</v>
+        <v>9703.98</v>
       </c>
       <c r="K19" t="n">
-        <v>9579.6</v>
+        <v>9770.35</v>
       </c>
       <c r="L19" t="n">
-        <v>9670.549999999999</v>
+        <v>9836.73</v>
       </c>
       <c r="M19" t="n">
-        <v>9718.4</v>
+        <v>10024.45</v>
       </c>
       <c r="N19" t="n">
-        <v>9766.25</v>
+        <v>10212.18</v>
       </c>
       <c r="O19" t="n">
-        <v>9900.299999999999</v>
+        <v>10157.2</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2106,80 +2102,78 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9897.4</v>
+        <v>9870.700000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>9901.5</v>
+        <v>10046.3</v>
       </c>
       <c r="D20" t="n">
-        <v>9829.4</v>
+        <v>9858.5</v>
       </c>
       <c r="E20" t="n">
-        <v>9870.700000000001</v>
+        <v>9951.1</v>
       </c>
       <c r="F20" t="n">
-        <v>-26.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0081</v>
       </c>
       <c r="H20" t="n">
-        <v>72.09999999999999</v>
+        <v>187.8</v>
       </c>
       <c r="I20" t="n">
-        <v>9394.9</v>
+        <v>9757.299999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>9703.98</v>
+        <v>9801.23</v>
       </c>
       <c r="K20" t="n">
-        <v>9770.35</v>
+        <v>9834.65</v>
       </c>
       <c r="L20" t="n">
-        <v>9836.73</v>
+        <v>9868.08</v>
       </c>
       <c r="M20" t="n">
-        <v>10024.45</v>
+        <v>9906.75</v>
       </c>
       <c r="N20" t="n">
-        <v>10212.18</v>
+        <v>9945.42</v>
       </c>
       <c r="O20" t="n">
-        <v>10157.2</v>
+        <v>9973.6</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2190,78 +2184,80 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9870.700000000001</v>
+        <v>9951.5</v>
       </c>
       <c r="C21" t="n">
-        <v>10046.3</v>
+        <v>10158.4</v>
       </c>
       <c r="D21" t="n">
-        <v>9858.5</v>
+        <v>9951.5</v>
       </c>
       <c r="E21" t="n">
-        <v>9951.1</v>
+        <v>10124.6</v>
       </c>
       <c r="F21" t="n">
-        <v>80.40000000000001</v>
+        <v>173.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0081</v>
+        <v>0.0174</v>
       </c>
       <c r="H21" t="n">
-        <v>187.8</v>
+        <v>206.9</v>
       </c>
       <c r="I21" t="n">
-        <v>9757.299999999999</v>
+        <v>9670.700000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>9801.23</v>
+        <v>9762.65</v>
       </c>
       <c r="K21" t="n">
-        <v>9834.65</v>
+        <v>9857.200000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>9868.08</v>
+        <v>9951.75</v>
       </c>
       <c r="M21" t="n">
-        <v>9906.75</v>
+        <v>10045</v>
       </c>
       <c r="N21" t="n">
-        <v>9945.42</v>
+        <v>10138.25</v>
       </c>
       <c r="O21" t="n">
-        <v>9973.6</v>
+        <v>10234.1</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2272,7 +2268,7 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2287,10 +2283,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2302,50 +2296,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9951.5</v>
+        <v>10124.5</v>
       </c>
       <c r="C22" t="n">
-        <v>10158.4</v>
+        <v>10257.8</v>
       </c>
       <c r="D22" t="n">
-        <v>9951.5</v>
+        <v>10089.9</v>
       </c>
       <c r="E22" t="n">
-        <v>10124.6</v>
+        <v>10235.3</v>
       </c>
       <c r="F22" t="n">
-        <v>173.5</v>
+        <v>110.7</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0174</v>
+        <v>0.0109</v>
       </c>
       <c r="H22" t="n">
-        <v>206.9</v>
+        <v>167.9</v>
       </c>
       <c r="I22" t="n">
-        <v>9670.700000000001</v>
+        <v>9744.6</v>
       </c>
       <c r="J22" t="n">
-        <v>9762.65</v>
+        <v>9952.52</v>
       </c>
       <c r="K22" t="n">
-        <v>9857.200000000001</v>
+        <v>10021.15</v>
       </c>
       <c r="L22" t="n">
-        <v>9951.75</v>
+        <v>10089.77</v>
       </c>
       <c r="M22" t="n">
-        <v>10045</v>
+        <v>10228.05</v>
       </c>
       <c r="N22" t="n">
-        <v>10138.25</v>
+        <v>10366.32</v>
       </c>
       <c r="O22" t="n">
-        <v>10234.1</v>
+        <v>10365.3</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2356,20 +2350,18 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2384,69 +2376,71 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10124.5</v>
+        <v>10235.3</v>
       </c>
       <c r="C23" t="n">
-        <v>10257.8</v>
+        <v>10235.3</v>
       </c>
       <c r="D23" t="n">
-        <v>10089.9</v>
+        <v>10050.2</v>
       </c>
       <c r="E23" t="n">
-        <v>10235.3</v>
+        <v>10143.4</v>
       </c>
       <c r="F23" t="n">
-        <v>110.7</v>
+        <v>-91.90000000000001</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>167.9</v>
+        <v>185.1</v>
       </c>
       <c r="I23" t="n">
-        <v>9744.6</v>
+        <v>9922</v>
       </c>
       <c r="J23" t="n">
-        <v>9952.52</v>
+        <v>10098.13</v>
       </c>
       <c r="K23" t="n">
-        <v>10021.15</v>
+        <v>10151.35</v>
       </c>
       <c r="L23" t="n">
-        <v>10089.77</v>
+        <v>10204.57</v>
       </c>
       <c r="M23" t="n">
-        <v>10228.05</v>
+        <v>10319.25</v>
       </c>
       <c r="N23" t="n">
-        <v>10366.32</v>
+        <v>10433.92</v>
       </c>
       <c r="O23" t="n">
-        <v>10365.3</v>
+        <v>10425.7</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2459,77 +2453,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10235.3</v>
+        <v>10143.1</v>
       </c>
       <c r="C24" t="n">
-        <v>10235.3</v>
+        <v>10277.7</v>
       </c>
       <c r="D24" t="n">
-        <v>10050.2</v>
+        <v>10125.3</v>
       </c>
       <c r="E24" t="n">
-        <v>10143.4</v>
+        <v>10223.5</v>
       </c>
       <c r="F24" t="n">
-        <v>-91.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>185.1</v>
+        <v>152.4</v>
       </c>
       <c r="I24" t="n">
-        <v>9922</v>
+        <v>9865.1</v>
       </c>
       <c r="J24" t="n">
-        <v>10098.13</v>
+        <v>9958.629999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>10151.35</v>
+        <v>10050.85</v>
       </c>
       <c r="L24" t="n">
-        <v>10204.57</v>
+        <v>10143.08</v>
       </c>
       <c r="M24" t="n">
-        <v>10319.25</v>
+        <v>10235.95</v>
       </c>
       <c r="N24" t="n">
-        <v>10433.92</v>
+        <v>10328.83</v>
       </c>
       <c r="O24" t="n">
-        <v>10425.7</v>
+        <v>10420.4</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2541,59 +2537,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10143.1</v>
+        <v>10223.7</v>
       </c>
       <c r="C25" t="n">
-        <v>10277.7</v>
+        <v>10481.5</v>
       </c>
       <c r="D25" t="n">
-        <v>10125.3</v>
+        <v>10145.4</v>
       </c>
       <c r="E25" t="n">
-        <v>10223.5</v>
+        <v>10369.8</v>
       </c>
       <c r="F25" t="n">
-        <v>80.09999999999999</v>
+        <v>146.3</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0143</v>
       </c>
       <c r="H25" t="n">
-        <v>152.4</v>
+        <v>336.1</v>
       </c>
       <c r="I25" t="n">
-        <v>9865.1</v>
+        <v>9972.9</v>
       </c>
       <c r="J25" t="n">
-        <v>9958.629999999999</v>
+        <v>10082.1</v>
       </c>
       <c r="K25" t="n">
-        <v>10050.85</v>
+        <v>10147.3</v>
       </c>
       <c r="L25" t="n">
-        <v>10143.08</v>
+        <v>10212.5</v>
       </c>
       <c r="M25" t="n">
-        <v>10235.95</v>
+        <v>10299.7</v>
       </c>
       <c r="N25" t="n">
-        <v>10328.83</v>
+        <v>10386.9</v>
       </c>
       <c r="O25" t="n">
-        <v>10420.4</v>
+        <v>10430.1</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2601,24 +2593,30 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -2630,50 +2628,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10223.7</v>
+        <v>10369.8</v>
       </c>
       <c r="C26" t="n">
-        <v>10481.5</v>
+        <v>10535.8</v>
       </c>
       <c r="D26" t="n">
-        <v>10145.4</v>
+        <v>10316</v>
       </c>
       <c r="E26" t="n">
-        <v>10369.8</v>
+        <v>10446.4</v>
       </c>
       <c r="F26" t="n">
-        <v>146.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0074</v>
       </c>
       <c r="H26" t="n">
-        <v>336.1</v>
+        <v>219.8</v>
       </c>
       <c r="I26" t="n">
-        <v>9972.9</v>
+        <v>9809.299999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>10082.1</v>
+        <v>10061.88</v>
       </c>
       <c r="K26" t="n">
-        <v>10147.3</v>
+        <v>10201.75</v>
       </c>
       <c r="L26" t="n">
-        <v>10212.5</v>
+        <v>10341.62</v>
       </c>
       <c r="M26" t="n">
-        <v>10299.7</v>
+        <v>10537.85</v>
       </c>
       <c r="N26" t="n">
-        <v>10386.9</v>
+        <v>10734.07</v>
       </c>
       <c r="O26" t="n">
-        <v>10430.1</v>
+        <v>10817.6</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2681,30 +2679,24 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
@@ -2716,50 +2708,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10369.8</v>
+        <v>10446.3</v>
       </c>
       <c r="C27" t="n">
-        <v>10535.8</v>
+        <v>10745.8</v>
       </c>
       <c r="D27" t="n">
-        <v>10316</v>
+        <v>10446.3</v>
       </c>
       <c r="E27" t="n">
-        <v>10446.4</v>
+        <v>10686.9</v>
       </c>
       <c r="F27" t="n">
-        <v>76.59999999999999</v>
+        <v>240.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.023</v>
       </c>
       <c r="H27" t="n">
-        <v>219.8</v>
+        <v>299.5</v>
       </c>
       <c r="I27" t="n">
-        <v>9809.299999999999</v>
+        <v>10096.2</v>
       </c>
       <c r="J27" t="n">
-        <v>10061.88</v>
+        <v>10236.85</v>
       </c>
       <c r="K27" t="n">
-        <v>10201.75</v>
+        <v>10336.5</v>
       </c>
       <c r="L27" t="n">
-        <v>10341.62</v>
+        <v>10436.15</v>
       </c>
       <c r="M27" t="n">
-        <v>10537.85</v>
+        <v>10556.3</v>
       </c>
       <c r="N27" t="n">
-        <v>10734.07</v>
+        <v>10676.45</v>
       </c>
       <c r="O27" t="n">
-        <v>10817.6</v>
+        <v>10755.6</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2770,18 +2762,20 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2796,50 +2790,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10446.3</v>
+        <v>10686.8</v>
       </c>
       <c r="C28" t="n">
-        <v>10745.8</v>
+        <v>10934.9</v>
       </c>
       <c r="D28" t="n">
-        <v>10446.3</v>
+        <v>10645.8</v>
       </c>
       <c r="E28" t="n">
-        <v>10686.9</v>
+        <v>10910.6</v>
       </c>
       <c r="F28" t="n">
-        <v>240.5</v>
+        <v>223.7</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0209</v>
       </c>
       <c r="H28" t="n">
-        <v>299.5</v>
+        <v>289.1</v>
       </c>
       <c r="I28" t="n">
-        <v>10096.2</v>
+        <v>10146.8</v>
       </c>
       <c r="J28" t="n">
-        <v>10236.85</v>
+        <v>10432.83</v>
       </c>
       <c r="K28" t="n">
-        <v>10336.5</v>
+        <v>10537.15</v>
       </c>
       <c r="L28" t="n">
-        <v>10436.15</v>
+        <v>10641.48</v>
       </c>
       <c r="M28" t="n">
-        <v>10556.3</v>
+        <v>10836.65</v>
       </c>
       <c r="N28" t="n">
-        <v>10676.45</v>
+        <v>11031.83</v>
       </c>
       <c r="O28" t="n">
-        <v>10755.6</v>
+        <v>11045.3</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2850,20 +2844,18 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2878,69 +2870,73 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10686.8</v>
+        <v>10911</v>
       </c>
       <c r="C29" t="n">
-        <v>10934.9</v>
+        <v>10911</v>
       </c>
       <c r="D29" t="n">
-        <v>10645.8</v>
+        <v>10234.5</v>
       </c>
       <c r="E29" t="n">
-        <v>10910.6</v>
+        <v>10284.8</v>
       </c>
       <c r="F29" t="n">
-        <v>223.7</v>
+        <v>-625.8</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0574</v>
       </c>
       <c r="H29" t="n">
-        <v>289.1</v>
+        <v>676.5</v>
       </c>
       <c r="I29" t="n">
-        <v>10146.8</v>
+        <v>10356.7</v>
       </c>
       <c r="J29" t="n">
-        <v>10432.83</v>
+        <v>10681.62</v>
       </c>
       <c r="K29" t="n">
-        <v>10537.15</v>
+        <v>10766.05</v>
       </c>
       <c r="L29" t="n">
-        <v>10641.48</v>
+        <v>10850.47</v>
       </c>
       <c r="M29" t="n">
-        <v>10836.65</v>
+        <v>11055.15</v>
       </c>
       <c r="N29" t="n">
-        <v>11031.83</v>
+        <v>11259.82</v>
       </c>
       <c r="O29" t="n">
-        <v>11045.3</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+        <v>11224</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2948,9 +2944,9 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -2958,69 +2954,63 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10911</v>
+        <v>10285</v>
       </c>
       <c r="C30" t="n">
-        <v>10911</v>
+        <v>10447.5</v>
       </c>
       <c r="D30" t="n">
-        <v>10234.5</v>
+        <v>10082</v>
       </c>
       <c r="E30" t="n">
-        <v>10284.8</v>
+        <v>10261.2</v>
       </c>
       <c r="F30" t="n">
-        <v>-625.8</v>
+        <v>-23.6</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0574</v>
+        <v>-0.0023</v>
       </c>
       <c r="H30" t="n">
-        <v>676.5</v>
+        <v>365.5</v>
       </c>
       <c r="I30" t="n">
-        <v>10356.7</v>
+        <v>9558</v>
       </c>
       <c r="J30" t="n">
-        <v>10681.62</v>
+        <v>9464.32</v>
       </c>
       <c r="K30" t="n">
-        <v>10766.05</v>
+        <v>9946.549999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>10850.47</v>
+        <v>10428.77</v>
       </c>
       <c r="M30" t="n">
-        <v>11055.15</v>
+        <v>10623.05</v>
       </c>
       <c r="N30" t="n">
-        <v>11259.82</v>
+        <v>10817.32</v>
       </c>
       <c r="O30" t="n">
-        <v>11224</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>11587.5</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3042,67 +3032,73 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10285</v>
+        <v>10261.1</v>
       </c>
       <c r="C31" t="n">
-        <v>10447.5</v>
+        <v>10447.7</v>
       </c>
       <c r="D31" t="n">
-        <v>10082</v>
+        <v>9915.700000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>10261.2</v>
+        <v>9918.299999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>-23.6</v>
+        <v>-342.9</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0334</v>
       </c>
       <c r="H31" t="n">
-        <v>365.5</v>
+        <v>532</v>
       </c>
       <c r="I31" t="n">
-        <v>9558</v>
+        <v>9716.5</v>
       </c>
       <c r="J31" t="n">
-        <v>9464.32</v>
+        <v>9893.93</v>
       </c>
       <c r="K31" t="n">
-        <v>9946.549999999999</v>
+        <v>10078.45</v>
       </c>
       <c r="L31" t="n">
-        <v>10428.77</v>
+        <v>10262.98</v>
       </c>
       <c r="M31" t="n">
-        <v>10623.05</v>
+        <v>10443.95</v>
       </c>
       <c r="N31" t="n">
-        <v>10817.32</v>
+        <v>10624.93</v>
       </c>
       <c r="O31" t="n">
-        <v>11587.5</v>
+        <v>10813</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3115,78 +3111,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10261.1</v>
+        <v>9918.5</v>
       </c>
       <c r="C32" t="n">
-        <v>10447.7</v>
+        <v>10118.2</v>
       </c>
       <c r="D32" t="n">
-        <v>9915.700000000001</v>
+        <v>9670.5</v>
       </c>
       <c r="E32" t="n">
-        <v>9918.299999999999</v>
+        <v>9967.4</v>
       </c>
       <c r="F32" t="n">
-        <v>-342.9</v>
+        <v>49.1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0334</v>
+        <v>0.005</v>
       </c>
       <c r="H32" t="n">
-        <v>532</v>
+        <v>447.7</v>
       </c>
       <c r="I32" t="n">
-        <v>9716.5</v>
+        <v>9383.700000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>9893.93</v>
+        <v>9254.6</v>
       </c>
       <c r="K32" t="n">
-        <v>10078.45</v>
+        <v>9652.299999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>10262.98</v>
+        <v>10050</v>
       </c>
       <c r="M32" t="n">
-        <v>10443.95</v>
+        <v>10184.3</v>
       </c>
       <c r="N32" t="n">
-        <v>10624.93</v>
+        <v>10318.6</v>
       </c>
       <c r="O32" t="n">
-        <v>10813</v>
+        <v>10979.7</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3208,50 +3202,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9918.5</v>
+        <v>9967.5</v>
       </c>
       <c r="C33" t="n">
-        <v>10118.2</v>
+        <v>10465.2</v>
       </c>
       <c r="D33" t="n">
-        <v>9670.5</v>
+        <v>9958.1</v>
       </c>
       <c r="E33" t="n">
-        <v>9967.4</v>
+        <v>10436.3</v>
       </c>
       <c r="F33" t="n">
-        <v>49.1</v>
+        <v>468.9</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.005</v>
+        <v>0.047</v>
       </c>
       <c r="H33" t="n">
-        <v>447.7</v>
+        <v>507.1</v>
       </c>
       <c r="I33" t="n">
-        <v>9383.700000000001</v>
+        <v>9222.799999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>9254.6</v>
+        <v>9556.23</v>
       </c>
       <c r="K33" t="n">
-        <v>9652.299999999999</v>
+        <v>9743.549999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>10050</v>
+        <v>9930.879999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>10184.3</v>
+        <v>10191.25</v>
       </c>
       <c r="N33" t="n">
-        <v>10318.6</v>
+        <v>10451.63</v>
       </c>
       <c r="O33" t="n">
-        <v>10979.7</v>
+        <v>10565.9</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3264,14 +3258,18 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3283,57 +3281,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9967.5</v>
+        <v>10436.2</v>
       </c>
       <c r="C34" t="n">
-        <v>10465.2</v>
+        <v>10687.9</v>
       </c>
       <c r="D34" t="n">
-        <v>9958.1</v>
+        <v>10330.9</v>
       </c>
       <c r="E34" t="n">
-        <v>10436.3</v>
+        <v>10600.5</v>
       </c>
       <c r="F34" t="n">
-        <v>468.9</v>
+        <v>164.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.047</v>
+        <v>0.0157</v>
       </c>
       <c r="H34" t="n">
-        <v>507.1</v>
+        <v>357</v>
       </c>
       <c r="I34" t="n">
-        <v>9222.799999999999</v>
+        <v>9451</v>
       </c>
       <c r="J34" t="n">
-        <v>9556.23</v>
+        <v>10041.52</v>
       </c>
       <c r="K34" t="n">
-        <v>9743.549999999999</v>
+        <v>10182.75</v>
       </c>
       <c r="L34" t="n">
-        <v>9930.879999999999</v>
+        <v>10323.97</v>
       </c>
       <c r="M34" t="n">
-        <v>10191.25</v>
+        <v>10689.85</v>
       </c>
       <c r="N34" t="n">
-        <v>10451.63</v>
+        <v>11055.73</v>
       </c>
       <c r="O34" t="n">
-        <v>10565.9</v>
+        <v>10972.3</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3344,20 +3342,18 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3376,50 +3372,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10436.2</v>
+        <v>10601.5</v>
       </c>
       <c r="C35" t="n">
-        <v>10687.9</v>
+        <v>10667.6</v>
       </c>
       <c r="D35" t="n">
-        <v>10330.9</v>
+        <v>10528.6</v>
       </c>
       <c r="E35" t="n">
-        <v>10600.5</v>
+        <v>10667.6</v>
       </c>
       <c r="F35" t="n">
-        <v>164.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0063</v>
       </c>
       <c r="H35" t="n">
-        <v>357</v>
+        <v>139</v>
       </c>
       <c r="I35" t="n">
-        <v>9451</v>
+        <v>9973.9</v>
       </c>
       <c r="J35" t="n">
-        <v>10041.52</v>
+        <v>10289.05</v>
       </c>
       <c r="K35" t="n">
-        <v>10182.75</v>
+        <v>10422</v>
       </c>
       <c r="L35" t="n">
-        <v>10323.97</v>
+        <v>10554.95</v>
       </c>
       <c r="M35" t="n">
-        <v>10689.85</v>
+        <v>10779</v>
       </c>
       <c r="N35" t="n">
-        <v>11055.73</v>
+        <v>11003.05</v>
       </c>
       <c r="O35" t="n">
-        <v>10972.3</v>
+        <v>11044.9</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3430,7 +3426,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3453,76 +3449,80 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10601.5</v>
+        <v>10668.4</v>
       </c>
       <c r="C36" t="n">
-        <v>10667.6</v>
+        <v>10683.7</v>
       </c>
       <c r="D36" t="n">
-        <v>10528.6</v>
+        <v>10361.5</v>
       </c>
       <c r="E36" t="n">
-        <v>10667.6</v>
+        <v>10379.1</v>
       </c>
       <c r="F36" t="n">
-        <v>67.09999999999999</v>
+        <v>-288.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0063</v>
+        <v>-0.027</v>
       </c>
       <c r="H36" t="n">
-        <v>139</v>
+        <v>322.2</v>
       </c>
       <c r="I36" t="n">
-        <v>9973.9</v>
+        <v>10389.6</v>
       </c>
       <c r="J36" t="n">
-        <v>10289.05</v>
+        <v>10563.35</v>
       </c>
       <c r="K36" t="n">
-        <v>10422</v>
+        <v>10598.1</v>
       </c>
       <c r="L36" t="n">
-        <v>10554.95</v>
+        <v>10632.85</v>
       </c>
       <c r="M36" t="n">
-        <v>10779</v>
+        <v>10737.1</v>
       </c>
       <c r="N36" t="n">
-        <v>11003.05</v>
+        <v>10841.35</v>
       </c>
       <c r="O36" t="n">
-        <v>11044.9</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+        <v>10806.6</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3537,76 +3537,72 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10668.4</v>
+        <v>10378.5</v>
       </c>
       <c r="C37" t="n">
-        <v>10683.7</v>
+        <v>10410.8</v>
       </c>
       <c r="D37" t="n">
-        <v>10361.5</v>
+        <v>10188.7</v>
       </c>
       <c r="E37" t="n">
-        <v>10379.1</v>
+        <v>10363.9</v>
       </c>
       <c r="F37" t="n">
-        <v>-288.5</v>
+        <v>-15.2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.0015</v>
       </c>
       <c r="H37" t="n">
-        <v>322.2</v>
+        <v>222.1</v>
       </c>
       <c r="I37" t="n">
-        <v>10389.6</v>
+        <v>10039.3</v>
       </c>
       <c r="J37" t="n">
-        <v>10563.35</v>
+        <v>9985.15</v>
       </c>
       <c r="K37" t="n">
-        <v>10598.1</v>
+        <v>10218</v>
       </c>
       <c r="L37" t="n">
-        <v>10632.85</v>
+        <v>10450.85</v>
       </c>
       <c r="M37" t="n">
-        <v>10737.1</v>
+        <v>10540.2</v>
       </c>
       <c r="N37" t="n">
-        <v>10841.35</v>
+        <v>10629.55</v>
       </c>
       <c r="O37" t="n">
-        <v>10806.6</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
+        <v>11005.9</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3623,79 +3619,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10378.5</v>
+        <v>10365.4</v>
       </c>
       <c r="C38" t="n">
-        <v>10410.8</v>
+        <v>10488.2</v>
       </c>
       <c r="D38" t="n">
-        <v>10188.7</v>
+        <v>10164.3</v>
       </c>
       <c r="E38" t="n">
-        <v>10363.9</v>
+        <v>10233.1</v>
       </c>
       <c r="F38" t="n">
-        <v>-15.2</v>
+        <v>-130.8</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0126</v>
       </c>
       <c r="H38" t="n">
-        <v>222.1</v>
+        <v>323.9</v>
       </c>
       <c r="I38" t="n">
-        <v>10039.3</v>
+        <v>9966.6</v>
       </c>
       <c r="J38" t="n">
-        <v>9985.15</v>
+        <v>10173.88</v>
       </c>
       <c r="K38" t="n">
-        <v>10218</v>
+        <v>10252.85</v>
       </c>
       <c r="L38" t="n">
-        <v>10450.85</v>
+        <v>10331.83</v>
       </c>
       <c r="M38" t="n">
-        <v>10540.2</v>
+        <v>10474.95</v>
       </c>
       <c r="N38" t="n">
-        <v>10629.55</v>
+        <v>10618.08</v>
       </c>
       <c r="O38" t="n">
-        <v>11005.9</v>
+        <v>10632.9</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3707,78 +3703,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10365.4</v>
+        <v>10233.6</v>
       </c>
       <c r="C39" t="n">
-        <v>10488.2</v>
+        <v>10375.7</v>
       </c>
       <c r="D39" t="n">
-        <v>10164.3</v>
+        <v>10152.1</v>
       </c>
       <c r="E39" t="n">
-        <v>10233.1</v>
+        <v>10195.4</v>
       </c>
       <c r="F39" t="n">
-        <v>-130.8</v>
+        <v>-37.7</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0037</v>
       </c>
       <c r="H39" t="n">
-        <v>323.9</v>
+        <v>223.6</v>
       </c>
       <c r="I39" t="n">
-        <v>9966.6</v>
+        <v>9840.4</v>
       </c>
       <c r="J39" t="n">
-        <v>10173.88</v>
+        <v>9862.620000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>10252.85</v>
+        <v>10071.15</v>
       </c>
       <c r="L39" t="n">
-        <v>10331.83</v>
+        <v>10279.67</v>
       </c>
       <c r="M39" t="n">
-        <v>10474.95</v>
+        <v>10395.05</v>
       </c>
       <c r="N39" t="n">
-        <v>10618.08</v>
+        <v>10510.42</v>
       </c>
       <c r="O39" t="n">
-        <v>10632.9</v>
+        <v>10812.1</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3791,59 +3785,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10233.6</v>
+        <v>10194.8</v>
       </c>
       <c r="C40" t="n">
-        <v>10375.7</v>
+        <v>10497.2</v>
       </c>
       <c r="D40" t="n">
-        <v>10152.1</v>
+        <v>10151.5</v>
       </c>
       <c r="E40" t="n">
-        <v>10195.4</v>
+        <v>10466.3</v>
       </c>
       <c r="F40" t="n">
-        <v>-37.7</v>
+        <v>270.9</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0266</v>
       </c>
       <c r="H40" t="n">
-        <v>223.6</v>
+        <v>345.7</v>
       </c>
       <c r="I40" t="n">
-        <v>9840.4</v>
+        <v>9928.5</v>
       </c>
       <c r="J40" t="n">
-        <v>9862.620000000001</v>
+        <v>9937.549999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>10071.15</v>
+        <v>10083.6</v>
       </c>
       <c r="L40" t="n">
-        <v>10279.67</v>
+        <v>10229.65</v>
       </c>
       <c r="M40" t="n">
-        <v>10395.05</v>
+        <v>10307.2</v>
       </c>
       <c r="N40" t="n">
-        <v>10510.42</v>
+        <v>10384.75</v>
       </c>
       <c r="O40" t="n">
-        <v>10812.1</v>
+        <v>10599.3</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3856,72 +3846,80 @@
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="W40" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10194.8</v>
+        <v>10465.6</v>
       </c>
       <c r="C41" t="n">
-        <v>10497.2</v>
+        <v>10557.2</v>
       </c>
       <c r="D41" t="n">
-        <v>10151.5</v>
+        <v>10381.2</v>
       </c>
       <c r="E41" t="n">
-        <v>10466.3</v>
+        <v>10409.3</v>
       </c>
       <c r="F41" t="n">
-        <v>270.9</v>
+        <v>-57</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0266</v>
+        <v>-0.0054</v>
       </c>
       <c r="H41" t="n">
-        <v>345.7</v>
+        <v>176</v>
       </c>
       <c r="I41" t="n">
-        <v>9928.5</v>
+        <v>9805.799999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>9937.549999999999</v>
+        <v>10191.57</v>
       </c>
       <c r="K41" t="n">
-        <v>10083.6</v>
+        <v>10293.45</v>
       </c>
       <c r="L41" t="n">
-        <v>10229.65</v>
+        <v>10395.32</v>
       </c>
       <c r="M41" t="n">
-        <v>10307.2</v>
+        <v>10639.15</v>
       </c>
       <c r="N41" t="n">
-        <v>10384.75</v>
+        <v>10882.97</v>
       </c>
       <c r="O41" t="n">
-        <v>10599.3</v>
+        <v>10842.9</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3932,20 +3930,16 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3964,50 +3958,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10465.6</v>
+        <v>10409.3</v>
       </c>
       <c r="C42" t="n">
-        <v>10557.2</v>
+        <v>10415.7</v>
       </c>
       <c r="D42" t="n">
-        <v>10381.2</v>
+        <v>10238.6</v>
       </c>
       <c r="E42" t="n">
-        <v>10409.3</v>
+        <v>10368.1</v>
       </c>
       <c r="F42" t="n">
-        <v>-57</v>
+        <v>-41.2</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.004</v>
       </c>
       <c r="H42" t="n">
-        <v>176</v>
+        <v>177.1</v>
       </c>
       <c r="I42" t="n">
-        <v>9805.799999999999</v>
+        <v>10205.2</v>
       </c>
       <c r="J42" t="n">
-        <v>10191.57</v>
+        <v>10203.35</v>
       </c>
       <c r="K42" t="n">
-        <v>10293.45</v>
+        <v>10321.3</v>
       </c>
       <c r="L42" t="n">
-        <v>10395.32</v>
+        <v>10439.25</v>
       </c>
       <c r="M42" t="n">
-        <v>10639.15</v>
+        <v>10497.3</v>
       </c>
       <c r="N42" t="n">
-        <v>10882.97</v>
+        <v>10555.35</v>
       </c>
       <c r="O42" t="n">
-        <v>10842.9</v>
+        <v>10733.2</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4015,12 +4009,14 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4039,77 +4035,81 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10409.3</v>
+        <v>10369.1</v>
       </c>
       <c r="C43" t="n">
-        <v>10415.7</v>
+        <v>10471.7</v>
       </c>
       <c r="D43" t="n">
-        <v>10238.6</v>
+        <v>10127.6</v>
       </c>
       <c r="E43" t="n">
-        <v>10368.1</v>
+        <v>10471.7</v>
       </c>
       <c r="F43" t="n">
-        <v>-41.2</v>
+        <v>103.6</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.01</v>
       </c>
       <c r="H43" t="n">
-        <v>177.1</v>
+        <v>344.1</v>
       </c>
       <c r="I43" t="n">
-        <v>10205.2</v>
+        <v>10061.5</v>
       </c>
       <c r="J43" t="n">
-        <v>10203.35</v>
+        <v>10211.47</v>
       </c>
       <c r="K43" t="n">
-        <v>10321.3</v>
+        <v>10279.55</v>
       </c>
       <c r="L43" t="n">
-        <v>10439.25</v>
+        <v>10347.62</v>
       </c>
       <c r="M43" t="n">
-        <v>10497.3</v>
+        <v>10456.65</v>
       </c>
       <c r="N43" t="n">
-        <v>10555.35</v>
+        <v>10565.68</v>
       </c>
       <c r="O43" t="n">
-        <v>10733.2</v>
+        <v>10592.8</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4123,80 +4123,74 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10369.1</v>
+        <v>10471.4</v>
       </c>
       <c r="C44" t="n">
-        <v>10471.7</v>
+        <v>10570.1</v>
       </c>
       <c r="D44" t="n">
-        <v>10127.6</v>
+        <v>10352.9</v>
       </c>
       <c r="E44" t="n">
-        <v>10471.7</v>
+        <v>10363.3</v>
       </c>
       <c r="F44" t="n">
-        <v>103.6</v>
+        <v>-108.4</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0104</v>
       </c>
       <c r="H44" t="n">
-        <v>344.1</v>
+        <v>217.2</v>
       </c>
       <c r="I44" t="n">
-        <v>10061.5</v>
+        <v>9783.5</v>
       </c>
       <c r="J44" t="n">
-        <v>10211.47</v>
+        <v>10213.62</v>
       </c>
       <c r="K44" t="n">
-        <v>10279.55</v>
+        <v>10299.65</v>
       </c>
       <c r="L44" t="n">
-        <v>10347.62</v>
+        <v>10385.68</v>
       </c>
       <c r="M44" t="n">
-        <v>10456.65</v>
+        <v>10643.75</v>
       </c>
       <c r="N44" t="n">
-        <v>10565.68</v>
+        <v>10901.83</v>
       </c>
       <c r="O44" t="n">
-        <v>10592.8</v>
+        <v>10815.8</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4218,50 +4212,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10471.4</v>
+        <v>10363.6</v>
       </c>
       <c r="C45" t="n">
-        <v>10570.1</v>
+        <v>10575.3</v>
       </c>
       <c r="D45" t="n">
-        <v>10352.9</v>
+        <v>10332.4</v>
       </c>
       <c r="E45" t="n">
-        <v>10363.3</v>
+        <v>10508</v>
       </c>
       <c r="F45" t="n">
-        <v>-108.4</v>
+        <v>144.7</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.014</v>
       </c>
       <c r="H45" t="n">
-        <v>217.2</v>
+        <v>242.9</v>
       </c>
       <c r="I45" t="n">
-        <v>9783.5</v>
+        <v>10135.7</v>
       </c>
       <c r="J45" t="n">
-        <v>10213.62</v>
+        <v>10097</v>
       </c>
       <c r="K45" t="n">
-        <v>10299.65</v>
+        <v>10254.7</v>
       </c>
       <c r="L45" t="n">
-        <v>10385.68</v>
+        <v>10412.4</v>
       </c>
       <c r="M45" t="n">
-        <v>10643.75</v>
+        <v>10471.9</v>
       </c>
       <c r="N45" t="n">
-        <v>10901.83</v>
+        <v>10531.4</v>
       </c>
       <c r="O45" t="n">
-        <v>10815.8</v>
+        <v>10787.3</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4274,14 +4268,18 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4300,50 +4298,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10363.6</v>
+        <v>10507.8</v>
       </c>
       <c r="C46" t="n">
-        <v>10575.3</v>
+        <v>10701.3</v>
       </c>
       <c r="D46" t="n">
-        <v>10332.4</v>
+        <v>10429.2</v>
       </c>
       <c r="E46" t="n">
-        <v>10508</v>
+        <v>10679</v>
       </c>
       <c r="F46" t="n">
-        <v>144.7</v>
+        <v>171</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0163</v>
       </c>
       <c r="H46" t="n">
-        <v>242.9</v>
+        <v>272.1</v>
       </c>
       <c r="I46" t="n">
-        <v>10135.7</v>
+        <v>10089.5</v>
       </c>
       <c r="J46" t="n">
-        <v>10097</v>
+        <v>10292.18</v>
       </c>
       <c r="K46" t="n">
-        <v>10254.7</v>
+        <v>10386.55</v>
       </c>
       <c r="L46" t="n">
-        <v>10412.4</v>
+        <v>10480.93</v>
       </c>
       <c r="M46" t="n">
-        <v>10471.9</v>
+        <v>10629.45</v>
       </c>
       <c r="N46" t="n">
-        <v>10531.4</v>
+        <v>10777.97</v>
       </c>
       <c r="O46" t="n">
-        <v>10787.3</v>
+        <v>10818.2</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4354,21 +4352,19 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
@@ -4377,78 +4373,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10507.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C47" t="n">
-        <v>10701.3</v>
+        <v>10747</v>
       </c>
       <c r="D47" t="n">
-        <v>10429.2</v>
+        <v>10397.5</v>
       </c>
       <c r="E47" t="n">
-        <v>10679</v>
+        <v>10497.3</v>
       </c>
       <c r="F47" t="n">
-        <v>171</v>
+        <v>-181.7</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.017</v>
       </c>
       <c r="H47" t="n">
-        <v>272.1</v>
+        <v>349.5</v>
       </c>
       <c r="I47" t="n">
-        <v>10089.5</v>
+        <v>10157.1</v>
       </c>
       <c r="J47" t="n">
-        <v>10292.18</v>
+        <v>10463.78</v>
       </c>
       <c r="K47" t="n">
-        <v>10386.55</v>
+        <v>10542.95</v>
       </c>
       <c r="L47" t="n">
-        <v>10480.93</v>
+        <v>10622.12</v>
       </c>
       <c r="M47" t="n">
-        <v>10629.45</v>
+        <v>10815.05</v>
       </c>
       <c r="N47" t="n">
-        <v>10777.97</v>
+        <v>11007.97</v>
       </c>
       <c r="O47" t="n">
-        <v>10818.2</v>
+        <v>10973.4</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4461,72 +4455,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10679.4</v>
+        <v>10498.1</v>
       </c>
       <c r="C48" t="n">
-        <v>10747</v>
+        <v>10623.7</v>
       </c>
       <c r="D48" t="n">
-        <v>10397.5</v>
+        <v>10423</v>
       </c>
       <c r="E48" t="n">
-        <v>10497.3</v>
+        <v>10600.4</v>
       </c>
       <c r="F48" t="n">
-        <v>-181.7</v>
+        <v>103.1</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.017</v>
+        <v>0.0098</v>
       </c>
       <c r="H48" t="n">
-        <v>349.5</v>
+        <v>200.7</v>
       </c>
       <c r="I48" t="n">
-        <v>10157.1</v>
+        <v>10048</v>
       </c>
       <c r="J48" t="n">
-        <v>10463.78</v>
+        <v>10110.32</v>
       </c>
       <c r="K48" t="n">
-        <v>10542.95</v>
+        <v>10322.55</v>
       </c>
       <c r="L48" t="n">
-        <v>10622.12</v>
+        <v>10534.77</v>
       </c>
       <c r="M48" t="n">
-        <v>10815.05</v>
+        <v>10672.05</v>
       </c>
       <c r="N48" t="n">
-        <v>11007.97</v>
+        <v>10809.32</v>
       </c>
       <c r="O48" t="n">
-        <v>10973.4</v>
+        <v>11096.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4545,57 +4539,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10498.1</v>
+        <v>10600.3</v>
       </c>
       <c r="C49" t="n">
-        <v>10623.7</v>
+        <v>10763.4</v>
       </c>
       <c r="D49" t="n">
-        <v>10423</v>
+        <v>10483.1</v>
       </c>
       <c r="E49" t="n">
-        <v>10600.4</v>
+        <v>10736.2</v>
       </c>
       <c r="F49" t="n">
-        <v>103.1</v>
+        <v>135.8</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0128</v>
       </c>
       <c r="H49" t="n">
-        <v>200.7</v>
+        <v>280.3</v>
       </c>
       <c r="I49" t="n">
-        <v>10048</v>
+        <v>10222.3</v>
       </c>
       <c r="J49" t="n">
-        <v>10110.32</v>
+        <v>10438.23</v>
       </c>
       <c r="K49" t="n">
-        <v>10322.55</v>
+        <v>10500.05</v>
       </c>
       <c r="L49" t="n">
-        <v>10534.77</v>
+        <v>10561.88</v>
       </c>
       <c r="M49" t="n">
-        <v>10672.05</v>
+        <v>10700.75</v>
       </c>
       <c r="N49" t="n">
-        <v>10809.32</v>
+        <v>10839.63</v>
       </c>
       <c r="O49" t="n">
-        <v>11096.5</v>
+        <v>10824.4</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4603,16 +4597,20 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4625,59 +4623,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10600.3</v>
+        <v>10736.1</v>
       </c>
       <c r="C50" t="n">
-        <v>10763.4</v>
+        <v>10989.5</v>
       </c>
       <c r="D50" t="n">
-        <v>10483.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E50" t="n">
-        <v>10736.2</v>
+        <v>10868.1</v>
       </c>
       <c r="F50" t="n">
-        <v>135.8</v>
+        <v>131.9</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0123</v>
       </c>
       <c r="H50" t="n">
-        <v>280.3</v>
+        <v>253.4</v>
       </c>
       <c r="I50" t="n">
-        <v>10222.3</v>
+        <v>10202.8</v>
       </c>
       <c r="J50" t="n">
-        <v>10438.23</v>
+        <v>10512.37</v>
       </c>
       <c r="K50" t="n">
-        <v>10500.05</v>
+        <v>10596.05</v>
       </c>
       <c r="L50" t="n">
-        <v>10561.88</v>
+        <v>10679.73</v>
       </c>
       <c r="M50" t="n">
-        <v>10700.75</v>
+        <v>10876.35</v>
       </c>
       <c r="N50" t="n">
-        <v>10839.63</v>
+        <v>11072.98</v>
       </c>
       <c r="O50" t="n">
-        <v>10824.4</v>
+        <v>11043.7</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4685,12 +4679,10 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4716,50 +4708,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10736.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C51" t="n">
-        <v>10989.5</v>
+        <v>10959.9</v>
       </c>
       <c r="D51" t="n">
-        <v>10736.1</v>
+        <v>10832.5</v>
       </c>
       <c r="E51" t="n">
-        <v>10868.1</v>
+        <v>10901.1</v>
       </c>
       <c r="F51" t="n">
-        <v>131.9</v>
+        <v>33</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0123</v>
+        <v>0.003</v>
       </c>
       <c r="H51" t="n">
-        <v>253.4</v>
+        <v>127.4</v>
       </c>
       <c r="I51" t="n">
-        <v>10202.8</v>
+        <v>10482.7</v>
       </c>
       <c r="J51" t="n">
-        <v>10512.37</v>
+        <v>10617.35</v>
       </c>
       <c r="K51" t="n">
-        <v>10596.05</v>
+        <v>10741.4</v>
       </c>
       <c r="L51" t="n">
-        <v>10679.73</v>
+        <v>10865.45</v>
       </c>
       <c r="M51" t="n">
-        <v>10876.35</v>
+        <v>10994.8</v>
       </c>
       <c r="N51" t="n">
-        <v>11072.98</v>
+        <v>11124.15</v>
       </c>
       <c r="O51" t="n">
-        <v>11043.7</v>
+        <v>11242.9</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4770,15 +4762,13 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4791,68 +4781,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10868.1</v>
+        <v>10901.1</v>
       </c>
       <c r="C52" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D52" t="n">
-        <v>10832.5</v>
+        <v>10723.7</v>
       </c>
       <c r="E52" t="n">
-        <v>10901.1</v>
+        <v>10750.1</v>
       </c>
       <c r="F52" t="n">
-        <v>33</v>
+        <v>-151</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0139</v>
       </c>
       <c r="H52" t="n">
-        <v>127.4</v>
+        <v>187.2</v>
       </c>
       <c r="I52" t="n">
-        <v>10482.7</v>
+        <v>10705.1</v>
       </c>
       <c r="J52" t="n">
-        <v>10617.35</v>
+        <v>10776.15</v>
       </c>
       <c r="K52" t="n">
-        <v>10741.4</v>
+        <v>10837.4</v>
       </c>
       <c r="L52" t="n">
-        <v>10865.45</v>
+        <v>10898.65</v>
       </c>
       <c r="M52" t="n">
-        <v>10994.8</v>
+        <v>10964.8</v>
       </c>
       <c r="N52" t="n">
-        <v>11124.15</v>
+        <v>11030.95</v>
       </c>
       <c r="O52" t="n">
-        <v>11242.9</v>
+        <v>11087.3</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4864,86 +4862,80 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10901.1</v>
+        <v>10750</v>
       </c>
       <c r="C53" t="n">
-        <v>10910.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D53" t="n">
-        <v>10723.7</v>
+        <v>10684.4</v>
       </c>
       <c r="E53" t="n">
-        <v>10750.1</v>
+        <v>10816.6</v>
       </c>
       <c r="F53" t="n">
-        <v>-151</v>
+        <v>66.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0139</v>
+        <v>0.0062</v>
       </c>
       <c r="H53" t="n">
-        <v>187.2</v>
+        <v>147.2</v>
       </c>
       <c r="I53" t="n">
-        <v>10705.1</v>
+        <v>10536.5</v>
       </c>
       <c r="J53" t="n">
-        <v>10776.15</v>
+        <v>10529.3</v>
       </c>
       <c r="K53" t="n">
-        <v>10837.4</v>
+        <v>10656.5</v>
       </c>
       <c r="L53" t="n">
-        <v>10898.65</v>
+        <v>10783.7</v>
       </c>
       <c r="M53" t="n">
-        <v>10964.8</v>
+        <v>10843.7</v>
       </c>
       <c r="N53" t="n">
-        <v>11030.95</v>
+        <v>10903.7</v>
       </c>
       <c r="O53" t="n">
-        <v>11087.3</v>
+        <v>11098.1</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4955,55 +4947,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10750</v>
+        <v>10816.3</v>
       </c>
       <c r="C54" t="n">
-        <v>10831.6</v>
+        <v>10920.5</v>
       </c>
       <c r="D54" t="n">
-        <v>10684.4</v>
+        <v>10772.6</v>
       </c>
       <c r="E54" t="n">
-        <v>10816.6</v>
+        <v>10824.3</v>
       </c>
       <c r="F54" t="n">
-        <v>66.5</v>
+        <v>7.7</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0007</v>
       </c>
       <c r="H54" t="n">
-        <v>147.2</v>
+        <v>147.9</v>
       </c>
       <c r="I54" t="n">
-        <v>10536.5</v>
+        <v>10537.2</v>
       </c>
       <c r="J54" t="n">
-        <v>10529.3</v>
+        <v>10698.7</v>
       </c>
       <c r="K54" t="n">
-        <v>10656.5</v>
+        <v>10743</v>
       </c>
       <c r="L54" t="n">
-        <v>10783.7</v>
+        <v>10787.3</v>
       </c>
       <c r="M54" t="n">
-        <v>10843.7</v>
+        <v>10890.2</v>
       </c>
       <c r="N54" t="n">
-        <v>10903.7</v>
+        <v>10993.1</v>
       </c>
       <c r="O54" t="n">
-        <v>11098.1</v>
+        <v>10978.8</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5014,14 +5010,14 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U54" s="8" t="n">
@@ -5037,57 +5033,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10816.3</v>
+        <v>10824.6</v>
       </c>
       <c r="C55" t="n">
-        <v>10920.5</v>
+        <v>10866.8</v>
       </c>
       <c r="D55" t="n">
-        <v>10772.6</v>
+        <v>10689.6</v>
       </c>
       <c r="E55" t="n">
-        <v>10824.3</v>
+        <v>10831.1</v>
       </c>
       <c r="F55" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>147.9</v>
+        <v>177.2</v>
       </c>
       <c r="I55" t="n">
-        <v>10537.2</v>
+        <v>10624.7</v>
       </c>
       <c r="J55" t="n">
-        <v>10698.7</v>
+        <v>10665.27</v>
       </c>
       <c r="K55" t="n">
-        <v>10743</v>
+        <v>10750.35</v>
       </c>
       <c r="L55" t="n">
-        <v>10787.3</v>
+        <v>10835.42</v>
       </c>
       <c r="M55" t="n">
-        <v>10890.2</v>
+        <v>10898.25</v>
       </c>
       <c r="N55" t="n">
-        <v>10993.1</v>
+        <v>10961.08</v>
       </c>
       <c r="O55" t="n">
-        <v>10978.8</v>
+        <v>11068.4</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5095,18 +5091,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5121,72 +5117,74 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10824.6</v>
+        <v>10831</v>
       </c>
       <c r="C56" t="n">
-        <v>10866.8</v>
+        <v>10868.3</v>
       </c>
       <c r="D56" t="n">
-        <v>10689.6</v>
+        <v>10594.3</v>
       </c>
       <c r="E56" t="n">
-        <v>10831.1</v>
+        <v>10650.4</v>
       </c>
       <c r="F56" t="n">
-        <v>6.8</v>
+        <v>-180.7</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0167</v>
       </c>
       <c r="H56" t="n">
-        <v>177.2</v>
+        <v>274</v>
       </c>
       <c r="I56" t="n">
-        <v>10624.7</v>
+        <v>10512.4</v>
       </c>
       <c r="J56" t="n">
-        <v>10665.27</v>
+        <v>10680.35</v>
       </c>
       <c r="K56" t="n">
-        <v>10750.35</v>
+        <v>10742.5</v>
       </c>
       <c r="L56" t="n">
-        <v>10835.42</v>
+        <v>10804.65</v>
       </c>
       <c r="M56" t="n">
-        <v>10898.25</v>
+        <v>10919.7</v>
       </c>
       <c r="N56" t="n">
-        <v>10961.08</v>
+        <v>11034.75</v>
       </c>
       <c r="O56" t="n">
-        <v>11068.4</v>
+        <v>11044</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5212,72 +5210,70 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10831</v>
+        <v>10650.9</v>
       </c>
       <c r="C57" t="n">
-        <v>10868.3</v>
+        <v>10823</v>
       </c>
       <c r="D57" t="n">
-        <v>10594.3</v>
+        <v>10586.4</v>
       </c>
       <c r="E57" t="n">
-        <v>10650.4</v>
+        <v>10659.13</v>
       </c>
       <c r="F57" t="n">
-        <v>-180.7</v>
+        <v>8.73</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0167</v>
+        <v>0.0008</v>
       </c>
       <c r="H57" t="n">
-        <v>274</v>
+        <v>236.6</v>
       </c>
       <c r="I57" t="n">
-        <v>10512.4</v>
+        <v>10320.3</v>
       </c>
       <c r="J57" t="n">
-        <v>10680.35</v>
+        <v>10335.95</v>
       </c>
       <c r="K57" t="n">
-        <v>10742.5</v>
+        <v>10513.4</v>
       </c>
       <c r="L57" t="n">
-        <v>10804.65</v>
+        <v>10690.85</v>
       </c>
       <c r="M57" t="n">
-        <v>10919.7</v>
+        <v>10787.4</v>
       </c>
       <c r="N57" t="n">
-        <v>11034.75</v>
+        <v>10883.95</v>
       </c>
       <c r="O57" t="n">
-        <v>11044</v>
+        <v>11142.3</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5290,90 +5286,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>10650.9</v>
-      </c>
-      <c r="C58" t="n">
-        <v>10823</v>
-      </c>
-      <c r="D58" t="n">
-        <v>10586.4</v>
-      </c>
-      <c r="E58" t="n">
-        <v>10816.14</v>
-      </c>
-      <c r="F58" t="n">
-        <v>165.74</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0156</v>
-      </c>
-      <c r="H58" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="I58" t="n">
-        <v>10320.3</v>
-      </c>
-      <c r="J58" t="n">
-        <v>10335.95</v>
-      </c>
-      <c r="K58" t="n">
-        <v>10513.4</v>
-      </c>
-      <c r="L58" t="n">
-        <v>10690.85</v>
-      </c>
-      <c r="M58" t="n">
-        <v>10787.4</v>
-      </c>
-      <c r="N58" t="n">
-        <v>10883.95</v>
-      </c>
-      <c r="O58" t="n">
-        <v>11142.3</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5223,10 +5226,10 @@
         <v>10586.4</v>
       </c>
       <c r="E57" t="n">
-        <v>10659.13</v>
+        <v>10659.1</v>
       </c>
       <c r="F57" t="n">
-        <v>8.73</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G57" s="5" t="n">
         <v>0.0008</v>
@@ -5286,6 +5289,90 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10659.09</v>
+      </c>
+      <c r="C58" t="n">
+        <v>10774.66</v>
+      </c>
+      <c r="D58" t="n">
+        <v>10656.7</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>117.96</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10349.8</v>
+      </c>
+      <c r="J58" t="n">
+        <v>10399.7</v>
+      </c>
+      <c r="K58" t="n">
+        <v>10540.8</v>
+      </c>
+      <c r="L58" t="n">
+        <v>10681.9</v>
+      </c>
+      <c r="M58" t="n">
+        <v>10777.4</v>
+      </c>
+      <c r="N58" t="n">
+        <v>10872.9</v>
+      </c>
+      <c r="O58" t="n">
+        <v>11059.6</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>146.7</v>
       </c>
       <c r="I2" t="n">
-        <v>8896.299999999999</v>
+        <v>8952.1</v>
       </c>
       <c r="J2" t="n">
-        <v>9130.4</v>
+        <v>9151.33</v>
       </c>
       <c r="K2" t="n">
-        <v>9206.1</v>
+        <v>9220.049999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>9281.799999999999</v>
+        <v>9288.780000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>9436.700000000001</v>
+        <v>9422.75</v>
       </c>
       <c r="N2" t="n">
-        <v>9591.6</v>
+        <v>9556.73</v>
       </c>
       <c r="O2" t="n">
-        <v>9588.1</v>
+        <v>9560.200000000001</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5301,25 +5298,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10659.09</v>
+        <v>10659.1</v>
       </c>
       <c r="C58" t="n">
-        <v>10774.66</v>
+        <v>10774.7</v>
       </c>
       <c r="D58" t="n">
         <v>10656.7</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>10739</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>79.90000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0075</v>
       </c>
       <c r="H58" t="n">
-        <v>117.96</v>
+        <v>118</v>
       </c>
       <c r="I58" t="n">
         <v>10349.8</v>
@@ -5342,25 +5339,25 @@
       <c r="O58" t="n">
         <v>11059.6</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5374,7 +5371,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -5307,13 +5307,13 @@
         <v>10656.7</v>
       </c>
       <c r="E58" t="n">
-        <v>10739</v>
+        <v>10708.33</v>
       </c>
       <c r="F58" t="n">
-        <v>79.90000000000001</v>
+        <v>49.23</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0075</v>
+        <v>0.0046</v>
       </c>
       <c r="H58" t="n">
         <v>118</v>
@@ -5350,13 +5350,11 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -659,35 +659,37 @@
         <v>146.7</v>
       </c>
       <c r="I2" t="n">
-        <v>8952.1</v>
+        <v>8976.1</v>
       </c>
       <c r="J2" t="n">
-        <v>9151.33</v>
+        <v>9160.33</v>
       </c>
       <c r="K2" t="n">
-        <v>9220.049999999999</v>
+        <v>9226.049999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>9288.780000000001</v>
+        <v>9291.780000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>9422.75</v>
+        <v>9416.75</v>
       </c>
       <c r="N2" t="n">
-        <v>9556.73</v>
+        <v>9541.73</v>
       </c>
       <c r="O2" t="n">
-        <v>9560.200000000001</v>
+        <v>9548.200000000001</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -5309,13 +5309,13 @@
         <v>10656.7</v>
       </c>
       <c r="E58" t="n">
-        <v>10708.33</v>
+        <v>10739</v>
       </c>
       <c r="F58" t="n">
-        <v>49.23</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.0075</v>
       </c>
       <c r="H58" t="n">
         <v>118</v>
@@ -5352,11 +5352,13 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -5309,13 +5309,13 @@
         <v>10656.7</v>
       </c>
       <c r="E58" t="n">
-        <v>10739</v>
+        <v>10705.26</v>
       </c>
       <c r="F58" t="n">
-        <v>79.90000000000001</v>
+        <v>46.16</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0075</v>
+        <v>0.0043</v>
       </c>
       <c r="H58" t="n">
         <v>118</v>
@@ -5352,13 +5352,11 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,32 +659,34 @@
         <v>146.7</v>
       </c>
       <c r="I2" t="n">
-        <v>8976.1</v>
+        <v>9157.5</v>
       </c>
       <c r="J2" t="n">
-        <v>9160.33</v>
+        <v>9228.35</v>
       </c>
       <c r="K2" t="n">
-        <v>9226.049999999999</v>
+        <v>9271.4</v>
       </c>
       <c r="L2" t="n">
-        <v>9291.780000000001</v>
+        <v>9314.450000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>9416.75</v>
+        <v>9371.4</v>
       </c>
       <c r="N2" t="n">
-        <v>9541.73</v>
+        <v>9428.35</v>
       </c>
       <c r="O2" t="n">
-        <v>9548.200000000001</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>9457.5</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -708,14 +710,10 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -792,12 +790,12 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -876,10 +874,14 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -956,12 +958,12 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1042,12 @@
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1128,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1204,7 +1206,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1288,7 +1290,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1376,7 +1378,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1456,7 +1458,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1536,7 +1538,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1622,7 +1624,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1702,7 +1704,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1786,7 +1788,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1864,7 +1866,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1952,7 +1954,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2040,7 +2042,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2118,7 +2120,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2206,7 +2208,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2288,7 +2290,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2368,7 +2370,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2450,7 +2452,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2534,7 +2536,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2620,7 +2622,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2700,7 +2702,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2782,7 +2784,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2862,7 +2864,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2946,7 +2948,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3024,7 +3026,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3108,7 +3110,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3190,7 +3192,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3276,7 +3278,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3360,7 +3362,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3444,7 +3446,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3532,7 +3534,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3616,7 +3618,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3700,7 +3702,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3782,7 +3784,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3864,7 +3866,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3946,7 +3948,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4030,7 +4032,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4118,7 +4120,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4200,7 +4202,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4286,7 +4288,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4370,7 +4372,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4452,7 +4454,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4534,7 +4536,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4620,7 +4622,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4700,7 +4702,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4778,7 +4780,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4864,7 +4866,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4944,7 +4946,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5028,7 +5030,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5112,7 +5114,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5198,7 +5200,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5282,7 +5284,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5309,13 +5311,13 @@
         <v>10656.7</v>
       </c>
       <c r="E58" t="n">
-        <v>10705.26</v>
+        <v>10679.99</v>
       </c>
       <c r="F58" t="n">
-        <v>46.16</v>
+        <v>20.89</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.002</v>
       </c>
       <c r="H58" t="n">
         <v>118</v>
@@ -5350,9 +5352,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5364,7 +5366,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,69 +634,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9321.4</v>
+        <v>9187.299999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>9325.9</v>
+        <v>9253.5</v>
       </c>
       <c r="D2" t="n">
-        <v>9179.200000000001</v>
+        <v>9107.4</v>
       </c>
       <c r="E2" t="n">
-        <v>9187.299999999999</v>
+        <v>9208.200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-134.1</v>
+        <v>20.9</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0144</v>
+        <v>0.0023</v>
       </c>
       <c r="H2" t="n">
-        <v>146.7</v>
+        <v>146.1</v>
       </c>
       <c r="I2" t="n">
-        <v>9157.5</v>
+        <v>9032.5</v>
       </c>
       <c r="J2" t="n">
-        <v>9228.35</v>
+        <v>9007.969999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>9271.4</v>
+        <v>9113.950000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>9314.450000000001</v>
+        <v>9219.93</v>
       </c>
       <c r="M2" t="n">
-        <v>9371.4</v>
+        <v>9260.65</v>
       </c>
       <c r="N2" t="n">
-        <v>9428.35</v>
+        <v>9301.370000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>9457.5</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
+        <v>9472.6</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -710,58 +706,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9187.299999999999</v>
+        <v>9208.200000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>9253.5</v>
+        <v>9340.700000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>9107.4</v>
+        <v>9190.6</v>
       </c>
       <c r="E3" t="n">
-        <v>9208.200000000001</v>
+        <v>9283.299999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>20.9</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>146.1</v>
+        <v>150.1</v>
       </c>
       <c r="I3" t="n">
-        <v>9032.5</v>
+        <v>8961.299999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>9007.969999999999</v>
+        <v>9075.98</v>
       </c>
       <c r="K3" t="n">
-        <v>9113.950000000001</v>
+        <v>9135.15</v>
       </c>
       <c r="L3" t="n">
-        <v>9219.93</v>
+        <v>9194.33</v>
       </c>
       <c r="M3" t="n">
-        <v>9260.65</v>
+        <v>9281.25</v>
       </c>
       <c r="N3" t="n">
-        <v>9301.370000000001</v>
+        <v>9368.17</v>
       </c>
       <c r="O3" t="n">
-        <v>9472.6</v>
+        <v>9399.6</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,18 +769,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -790,62 +790,58 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9208.200000000001</v>
+        <v>9283.299999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>9340.700000000001</v>
+        <v>9314.4</v>
       </c>
       <c r="D4" t="n">
-        <v>9190.6</v>
+        <v>9195.700000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>9283.299999999999</v>
+        <v>9216.700000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>75.09999999999999</v>
+        <v>-66.59999999999999</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0072</v>
       </c>
       <c r="H4" t="n">
-        <v>150.1</v>
+        <v>118.7</v>
       </c>
       <c r="I4" t="n">
-        <v>8961.299999999999</v>
+        <v>9040.5</v>
       </c>
       <c r="J4" t="n">
-        <v>9075.98</v>
+        <v>9142.02</v>
       </c>
       <c r="K4" t="n">
-        <v>9135.15</v>
+        <v>9208.25</v>
       </c>
       <c r="L4" t="n">
-        <v>9194.33</v>
+        <v>9274.469999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>9281.25</v>
+        <v>9358.35</v>
       </c>
       <c r="N4" t="n">
-        <v>9368.17</v>
+        <v>9442.23</v>
       </c>
       <c r="O4" t="n">
-        <v>9399.6</v>
+        <v>9490.799999999999</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,19 +849,19 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -874,62 +870,62 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9283.299999999999</v>
+        <v>9216.700000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>9314.4</v>
+        <v>9292.1</v>
       </c>
       <c r="D5" t="n">
-        <v>9195.700000000001</v>
+        <v>9177.1</v>
       </c>
       <c r="E5" t="n">
-        <v>9216.700000000001</v>
+        <v>9284.799999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-66.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.0074</v>
       </c>
       <c r="H5" t="n">
-        <v>118.7</v>
+        <v>115</v>
       </c>
       <c r="I5" t="n">
-        <v>9040.5</v>
+        <v>9077</v>
       </c>
       <c r="J5" t="n">
-        <v>9142.02</v>
+        <v>9078.82</v>
       </c>
       <c r="K5" t="n">
-        <v>9208.25</v>
+        <v>9157.35</v>
       </c>
       <c r="L5" t="n">
-        <v>9274.469999999999</v>
+        <v>9235.879999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>9358.35</v>
+        <v>9276.049999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>9442.23</v>
+        <v>9316.23</v>
       </c>
       <c r="O5" t="n">
-        <v>9490.799999999999</v>
+        <v>9433.1</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -937,19 +933,19 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -958,62 +954,62 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9216.700000000001</v>
+        <v>9284.799999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>9292.1</v>
+        <v>9494.6</v>
       </c>
       <c r="D6" t="n">
-        <v>9177.1</v>
+        <v>9266.299999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>9284.799999999999</v>
+        <v>9491.299999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>68.09999999999999</v>
+        <v>206.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0222</v>
       </c>
       <c r="H6" t="n">
-        <v>115</v>
+        <v>228.3</v>
       </c>
       <c r="I6" t="n">
-        <v>9077</v>
+        <v>9062.1</v>
       </c>
       <c r="J6" t="n">
-        <v>9078.82</v>
+        <v>9194.9</v>
       </c>
       <c r="K6" t="n">
-        <v>9157.35</v>
+        <v>9227.299999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>9235.879999999999</v>
+        <v>9259.700000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>9276.049999999999</v>
+        <v>9342.299999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>9316.23</v>
+        <v>9424.9</v>
       </c>
       <c r="O6" t="n">
-        <v>9433.1</v>
+        <v>9407.1</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1031,73 +1027,73 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9284.799999999999</v>
+        <v>9491.200000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>9494.6</v>
+        <v>9577.1</v>
       </c>
       <c r="D7" t="n">
-        <v>9266.299999999999</v>
+        <v>9414.6</v>
       </c>
       <c r="E7" t="n">
-        <v>9491.299999999999</v>
+        <v>9427.5</v>
       </c>
       <c r="F7" t="n">
-        <v>206.5</v>
+        <v>-63.8</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0067</v>
       </c>
       <c r="H7" t="n">
-        <v>228.3</v>
+        <v>162.5</v>
       </c>
       <c r="I7" t="n">
-        <v>9062.1</v>
+        <v>9038</v>
       </c>
       <c r="J7" t="n">
-        <v>9194.9</v>
+        <v>9318.43</v>
       </c>
       <c r="K7" t="n">
-        <v>9227.299999999999</v>
+        <v>9377.15</v>
       </c>
       <c r="L7" t="n">
-        <v>9259.700000000001</v>
+        <v>9435.870000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>9342.299999999999</v>
+        <v>9605.450000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>9424.9</v>
+        <v>9775.02</v>
       </c>
       <c r="O7" t="n">
-        <v>9407.1</v>
+        <v>9722.9</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1108,80 +1104,78 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9491.200000000001</v>
+        <v>9427.5</v>
       </c>
       <c r="C8" t="n">
-        <v>9577.1</v>
+        <v>9474.299999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>9414.6</v>
+        <v>9276.9</v>
       </c>
       <c r="E8" t="n">
-        <v>9427.5</v>
+        <v>9354.6</v>
       </c>
       <c r="F8" t="n">
-        <v>-63.8</v>
+        <v>-72.90000000000001</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0067</v>
+        <v>-0.0077</v>
       </c>
       <c r="H8" t="n">
-        <v>162.5</v>
+        <v>197.4</v>
       </c>
       <c r="I8" t="n">
-        <v>9038</v>
+        <v>9252.1</v>
       </c>
       <c r="J8" t="n">
-        <v>9318.43</v>
+        <v>9230.83</v>
       </c>
       <c r="K8" t="n">
-        <v>9377.15</v>
+        <v>9346.25</v>
       </c>
       <c r="L8" t="n">
-        <v>9435.870000000001</v>
+        <v>9461.67</v>
       </c>
       <c r="M8" t="n">
-        <v>9605.450000000001</v>
+        <v>9508.75</v>
       </c>
       <c r="N8" t="n">
-        <v>9775.02</v>
+        <v>9555.83</v>
       </c>
       <c r="O8" t="n">
-        <v>9722.9</v>
+        <v>9739.6</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1189,12 +1183,14 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1206,64 +1202,64 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9427.5</v>
+        <v>9354.5</v>
       </c>
       <c r="C9" t="n">
-        <v>9474.299999999999</v>
+        <v>9645.6</v>
       </c>
       <c r="D9" t="n">
-        <v>9276.9</v>
+        <v>9354.5</v>
       </c>
       <c r="E9" t="n">
-        <v>9354.6</v>
+        <v>9645.6</v>
       </c>
       <c r="F9" t="n">
-        <v>-72.90000000000001</v>
+        <v>291</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0311</v>
       </c>
       <c r="H9" t="n">
-        <v>197.4</v>
+        <v>291.1</v>
       </c>
       <c r="I9" t="n">
-        <v>9252.1</v>
+        <v>9079.5</v>
       </c>
       <c r="J9" t="n">
-        <v>9230.83</v>
+        <v>9146.700000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>9346.25</v>
+        <v>9255.9</v>
       </c>
       <c r="L9" t="n">
-        <v>9461.67</v>
+        <v>9365.1</v>
       </c>
       <c r="M9" t="n">
-        <v>9508.75</v>
+        <v>9453.299999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>9555.83</v>
+        <v>9541.5</v>
       </c>
       <c r="O9" t="n">
-        <v>9739.6</v>
+        <v>9671.700000000001</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,83 +1267,83 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9354.5</v>
+        <v>9645.6</v>
       </c>
       <c r="C10" t="n">
-        <v>9645.6</v>
+        <v>9787.6</v>
       </c>
       <c r="D10" t="n">
-        <v>9354.5</v>
+        <v>9632.799999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>9645.6</v>
+        <v>9717.299999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>291</v>
+        <v>71.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0311</v>
+        <v>0.0074</v>
       </c>
       <c r="H10" t="n">
-        <v>291.1</v>
+        <v>154.8</v>
       </c>
       <c r="I10" t="n">
-        <v>9079.5</v>
+        <v>9063.4</v>
       </c>
       <c r="J10" t="n">
-        <v>9146.700000000001</v>
+        <v>9427.27</v>
       </c>
       <c r="K10" t="n">
-        <v>9255.9</v>
+        <v>9500.049999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>9365.1</v>
+        <v>9572.82</v>
       </c>
       <c r="M10" t="n">
-        <v>9453.299999999999</v>
+        <v>9791.15</v>
       </c>
       <c r="N10" t="n">
-        <v>9541.5</v>
+        <v>10009.47</v>
       </c>
       <c r="O10" t="n">
-        <v>9671.700000000001</v>
+        <v>9936.700000000001</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1365,20 +1361,16 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1388,50 +1380,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9645.6</v>
+        <v>9717.299999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>9787.6</v>
+        <v>9786.799999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>9632.799999999999</v>
+        <v>9574.200000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>9717.299999999999</v>
+        <v>9682.6</v>
       </c>
       <c r="F11" t="n">
-        <v>71.7</v>
+        <v>-34.7</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0036</v>
       </c>
       <c r="H11" t="n">
-        <v>154.8</v>
+        <v>212.6</v>
       </c>
       <c r="I11" t="n">
-        <v>9063.4</v>
+        <v>9478</v>
       </c>
       <c r="J11" t="n">
-        <v>9427.27</v>
+        <v>9566.049999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>9500.049999999999</v>
+        <v>9639.9</v>
       </c>
       <c r="L11" t="n">
-        <v>9572.82</v>
+        <v>9713.75</v>
       </c>
       <c r="M11" t="n">
-        <v>9791.15</v>
+        <v>9794.700000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>10009.47</v>
+        <v>9875.65</v>
       </c>
       <c r="O11" t="n">
-        <v>9936.700000000001</v>
+        <v>9942.4</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1439,18 +1431,18 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1458,60 +1450,64 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9717.299999999999</v>
+        <v>9682.6</v>
       </c>
       <c r="C12" t="n">
-        <v>9786.799999999999</v>
+        <v>9930.1</v>
       </c>
       <c r="D12" t="n">
-        <v>9574.200000000001</v>
+        <v>9610.5</v>
       </c>
       <c r="E12" t="n">
-        <v>9682.6</v>
+        <v>9698.4</v>
       </c>
       <c r="F12" t="n">
-        <v>-34.7</v>
+        <v>15.8</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0016</v>
       </c>
       <c r="H12" t="n">
-        <v>212.6</v>
+        <v>319.6</v>
       </c>
       <c r="I12" t="n">
-        <v>9478</v>
+        <v>9361.6</v>
       </c>
       <c r="J12" t="n">
-        <v>9566.049999999999</v>
+        <v>9471.049999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>9639.9</v>
+        <v>9576.299999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>9713.75</v>
+        <v>9681.549999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>9794.700000000001</v>
+        <v>9788.9</v>
       </c>
       <c r="N12" t="n">
-        <v>9875.65</v>
+        <v>9896.25</v>
       </c>
       <c r="O12" t="n">
-        <v>9942.4</v>
+        <v>9999.4</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1519,83 +1515,81 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9682.6</v>
+        <v>9698.4</v>
       </c>
       <c r="C13" t="n">
-        <v>9930.1</v>
+        <v>9707.700000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>9610.5</v>
+        <v>9423.9</v>
       </c>
       <c r="E13" t="n">
-        <v>9698.4</v>
+        <v>9539.700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>15.8</v>
+        <v>-158.7</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0164</v>
       </c>
       <c r="H13" t="n">
-        <v>319.6</v>
+        <v>283.8</v>
       </c>
       <c r="I13" t="n">
-        <v>9361.6</v>
+        <v>9290.9</v>
       </c>
       <c r="J13" t="n">
-        <v>9471.049999999999</v>
+        <v>9342.85</v>
       </c>
       <c r="K13" t="n">
-        <v>9576.299999999999</v>
+        <v>9538.6</v>
       </c>
       <c r="L13" t="n">
-        <v>9681.549999999999</v>
+        <v>9734.35</v>
       </c>
       <c r="M13" t="n">
-        <v>9788.9</v>
+        <v>9858.200000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>9896.25</v>
+        <v>9982.049999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>9999.4</v>
+        <v>10249.7</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1603,81 +1597,83 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9698.4</v>
+        <v>9539.700000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>9707.700000000001</v>
+        <v>9740.200000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>9423.9</v>
+        <v>9521.5</v>
       </c>
       <c r="E14" t="n">
-        <v>9539.700000000001</v>
+        <v>9720.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-158.7</v>
+        <v>180.8</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.019</v>
       </c>
       <c r="H14" t="n">
-        <v>283.8</v>
+        <v>218.7</v>
       </c>
       <c r="I14" t="n">
-        <v>9290.9</v>
+        <v>9140.1</v>
       </c>
       <c r="J14" t="n">
-        <v>9342.85</v>
+        <v>9242.85</v>
       </c>
       <c r="K14" t="n">
-        <v>9538.6</v>
+        <v>9397.799999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>9734.35</v>
+        <v>9552.75</v>
       </c>
       <c r="M14" t="n">
-        <v>9858.200000000001</v>
+        <v>9681.6</v>
       </c>
       <c r="N14" t="n">
-        <v>9982.049999999999</v>
+        <v>9810.450000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>10249.7</v>
+        <v>9991.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1685,83 +1681,79 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9539.700000000001</v>
+        <v>9720.6</v>
       </c>
       <c r="C15" t="n">
-        <v>9740.200000000001</v>
+        <v>9744.799999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>9521.5</v>
+        <v>9667</v>
       </c>
       <c r="E15" t="n">
-        <v>9720.5</v>
+        <v>9667</v>
       </c>
       <c r="F15" t="n">
-        <v>180.8</v>
+        <v>-53.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.019</v>
+        <v>-0.0055</v>
       </c>
       <c r="H15" t="n">
-        <v>218.7</v>
+        <v>77.8</v>
       </c>
       <c r="I15" t="n">
-        <v>9140.1</v>
+        <v>9302.799999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>9242.85</v>
+        <v>9546.620000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>9397.799999999999</v>
+        <v>9611.15</v>
       </c>
       <c r="L15" t="n">
-        <v>9552.75</v>
+        <v>9675.68</v>
       </c>
       <c r="M15" t="n">
-        <v>9681.6</v>
+        <v>9829.85</v>
       </c>
       <c r="N15" t="n">
-        <v>9810.450000000001</v>
+        <v>9984.030000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>9991.5</v>
+        <v>9958.9</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1772,15 +1764,13 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1788,60 +1778,64 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9720.6</v>
+        <v>9667.1</v>
       </c>
       <c r="C16" t="n">
-        <v>9744.799999999999</v>
+        <v>9761.5</v>
       </c>
       <c r="D16" t="n">
-        <v>9667</v>
+        <v>9622.700000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>9667</v>
+        <v>9649</v>
       </c>
       <c r="F16" t="n">
-        <v>-53.5</v>
+        <v>-18</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0019</v>
       </c>
       <c r="H16" t="n">
-        <v>77.8</v>
+        <v>138.8</v>
       </c>
       <c r="I16" t="n">
-        <v>9302.799999999999</v>
+        <v>9589.200000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>9546.620000000001</v>
+        <v>9569.75</v>
       </c>
       <c r="K16" t="n">
-        <v>9611.15</v>
+        <v>9628.1</v>
       </c>
       <c r="L16" t="n">
-        <v>9675.68</v>
+        <v>9686.450000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>9829.85</v>
+        <v>9705.9</v>
       </c>
       <c r="N16" t="n">
-        <v>9984.030000000001</v>
+        <v>9725.35</v>
       </c>
       <c r="O16" t="n">
-        <v>9958.9</v>
+        <v>9822.6</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1849,81 +1843,87 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9667.1</v>
+        <v>9649</v>
       </c>
       <c r="C17" t="n">
-        <v>9761.5</v>
+        <v>9903.1</v>
       </c>
       <c r="D17" t="n">
-        <v>9622.700000000001</v>
+        <v>9649</v>
       </c>
       <c r="E17" t="n">
-        <v>9649</v>
+        <v>9897.4</v>
       </c>
       <c r="F17" t="n">
-        <v>-18</v>
+        <v>248.4</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0257</v>
       </c>
       <c r="H17" t="n">
-        <v>138.8</v>
+        <v>254.1</v>
       </c>
       <c r="I17" t="n">
-        <v>9589.200000000001</v>
+        <v>9483.9</v>
       </c>
       <c r="J17" t="n">
-        <v>9569.75</v>
+        <v>9488.65</v>
       </c>
       <c r="K17" t="n">
-        <v>9628.1</v>
+        <v>9579.6</v>
       </c>
       <c r="L17" t="n">
-        <v>9686.450000000001</v>
+        <v>9670.549999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>9705.9</v>
+        <v>9718.4</v>
       </c>
       <c r="N17" t="n">
-        <v>9725.35</v>
+        <v>9766.25</v>
       </c>
       <c r="O17" t="n">
-        <v>9822.6</v>
+        <v>9900.299999999999</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1931,87 +1931,83 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9649</v>
+        <v>9897.4</v>
       </c>
       <c r="C18" t="n">
-        <v>9903.1</v>
+        <v>9901.5</v>
       </c>
       <c r="D18" t="n">
-        <v>9649</v>
+        <v>9829.4</v>
       </c>
       <c r="E18" t="n">
-        <v>9897.4</v>
+        <v>9870.700000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>248.4</v>
+        <v>-26.7</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0257</v>
+        <v>-0.0027</v>
       </c>
       <c r="H18" t="n">
-        <v>254.1</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>9483.9</v>
+        <v>9394.9</v>
       </c>
       <c r="J18" t="n">
-        <v>9488.65</v>
+        <v>9703.98</v>
       </c>
       <c r="K18" t="n">
-        <v>9579.6</v>
+        <v>9770.35</v>
       </c>
       <c r="L18" t="n">
-        <v>9670.549999999999</v>
+        <v>9836.73</v>
       </c>
       <c r="M18" t="n">
-        <v>9718.4</v>
+        <v>10024.45</v>
       </c>
       <c r="N18" t="n">
-        <v>9766.25</v>
+        <v>10212.18</v>
       </c>
       <c r="O18" t="n">
-        <v>9900.299999999999</v>
+        <v>10157.2</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2024,78 +2020,76 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9897.4</v>
+        <v>9870.700000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>9901.5</v>
+        <v>10046.3</v>
       </c>
       <c r="D19" t="n">
-        <v>9829.4</v>
+        <v>9858.5</v>
       </c>
       <c r="E19" t="n">
-        <v>9870.700000000001</v>
+        <v>9951.1</v>
       </c>
       <c r="F19" t="n">
-        <v>-26.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0081</v>
       </c>
       <c r="H19" t="n">
-        <v>72.09999999999999</v>
+        <v>187.8</v>
       </c>
       <c r="I19" t="n">
-        <v>9394.9</v>
+        <v>9757.299999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>9703.98</v>
+        <v>9801.23</v>
       </c>
       <c r="K19" t="n">
-        <v>9770.35</v>
+        <v>9834.65</v>
       </c>
       <c r="L19" t="n">
-        <v>9836.73</v>
+        <v>9868.08</v>
       </c>
       <c r="M19" t="n">
-        <v>10024.45</v>
+        <v>9906.75</v>
       </c>
       <c r="N19" t="n">
-        <v>10212.18</v>
+        <v>9945.42</v>
       </c>
       <c r="O19" t="n">
-        <v>10157.2</v>
+        <v>9973.6</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2108,76 +2102,78 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9870.700000000001</v>
+        <v>9951.5</v>
       </c>
       <c r="C20" t="n">
-        <v>10046.3</v>
+        <v>10158.4</v>
       </c>
       <c r="D20" t="n">
-        <v>9858.5</v>
+        <v>9951.5</v>
       </c>
       <c r="E20" t="n">
-        <v>9951.1</v>
+        <v>10124.6</v>
       </c>
       <c r="F20" t="n">
-        <v>80.40000000000001</v>
+        <v>173.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0081</v>
+        <v>0.0174</v>
       </c>
       <c r="H20" t="n">
-        <v>187.8</v>
+        <v>206.9</v>
       </c>
       <c r="I20" t="n">
-        <v>9757.299999999999</v>
+        <v>9670.700000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>9801.23</v>
+        <v>9762.65</v>
       </c>
       <c r="K20" t="n">
-        <v>9834.65</v>
+        <v>9857.200000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>9868.08</v>
+        <v>9951.75</v>
       </c>
       <c r="M20" t="n">
-        <v>9906.75</v>
+        <v>10045</v>
       </c>
       <c r="N20" t="n">
-        <v>9945.42</v>
+        <v>10138.25</v>
       </c>
       <c r="O20" t="n">
-        <v>9973.6</v>
+        <v>10234.1</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2203,12 +2199,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2218,50 +2212,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9951.5</v>
+        <v>10124.5</v>
       </c>
       <c r="C21" t="n">
-        <v>10158.4</v>
+        <v>10257.8</v>
       </c>
       <c r="D21" t="n">
-        <v>9951.5</v>
+        <v>10089.9</v>
       </c>
       <c r="E21" t="n">
-        <v>10124.6</v>
+        <v>10235.3</v>
       </c>
       <c r="F21" t="n">
-        <v>173.5</v>
+        <v>110.7</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0174</v>
+        <v>0.0109</v>
       </c>
       <c r="H21" t="n">
-        <v>206.9</v>
+        <v>167.9</v>
       </c>
       <c r="I21" t="n">
-        <v>9670.700000000001</v>
+        <v>9744.6</v>
       </c>
       <c r="J21" t="n">
-        <v>9762.65</v>
+        <v>9952.52</v>
       </c>
       <c r="K21" t="n">
-        <v>9857.200000000001</v>
+        <v>10021.15</v>
       </c>
       <c r="L21" t="n">
-        <v>9951.75</v>
+        <v>10089.77</v>
       </c>
       <c r="M21" t="n">
-        <v>10045</v>
+        <v>10228.05</v>
       </c>
       <c r="N21" t="n">
-        <v>10138.25</v>
+        <v>10366.32</v>
       </c>
       <c r="O21" t="n">
-        <v>10234.1</v>
+        <v>10365.3</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2279,18 +2273,16 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2300,216 +2292,216 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10124.5</v>
+        <v>10235.3</v>
       </c>
       <c r="C22" t="n">
-        <v>10257.8</v>
+        <v>10235.3</v>
       </c>
       <c r="D22" t="n">
-        <v>10089.9</v>
+        <v>10050.2</v>
       </c>
       <c r="E22" t="n">
-        <v>10235.3</v>
+        <v>10143.4</v>
       </c>
       <c r="F22" t="n">
-        <v>110.7</v>
+        <v>-91.90000000000001</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>167.9</v>
+        <v>185.1</v>
       </c>
       <c r="I22" t="n">
-        <v>9744.6</v>
+        <v>9922</v>
       </c>
       <c r="J22" t="n">
-        <v>9952.52</v>
+        <v>10098.13</v>
       </c>
       <c r="K22" t="n">
-        <v>10021.15</v>
+        <v>10151.35</v>
       </c>
       <c r="L22" t="n">
-        <v>10089.77</v>
+        <v>10204.57</v>
       </c>
       <c r="M22" t="n">
-        <v>10228.05</v>
+        <v>10319.25</v>
       </c>
       <c r="N22" t="n">
-        <v>10366.32</v>
+        <v>10433.92</v>
       </c>
       <c r="O22" t="n">
-        <v>10365.3</v>
+        <v>10425.7</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10235.3</v>
+        <v>10143.1</v>
       </c>
       <c r="C23" t="n">
-        <v>10235.3</v>
+        <v>10277.7</v>
       </c>
       <c r="D23" t="n">
-        <v>10050.2</v>
+        <v>10125.3</v>
       </c>
       <c r="E23" t="n">
-        <v>10143.4</v>
+        <v>10223.5</v>
       </c>
       <c r="F23" t="n">
-        <v>-91.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>185.1</v>
+        <v>152.4</v>
       </c>
       <c r="I23" t="n">
-        <v>9922</v>
+        <v>9865.1</v>
       </c>
       <c r="J23" t="n">
-        <v>10098.13</v>
+        <v>9958.629999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>10151.35</v>
+        <v>10050.85</v>
       </c>
       <c r="L23" t="n">
-        <v>10204.57</v>
+        <v>10143.08</v>
       </c>
       <c r="M23" t="n">
-        <v>10319.25</v>
+        <v>10235.95</v>
       </c>
       <c r="N23" t="n">
-        <v>10433.92</v>
+        <v>10328.83</v>
       </c>
       <c r="O23" t="n">
-        <v>10425.7</v>
+        <v>10420.4</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10143.1</v>
+        <v>10223.7</v>
       </c>
       <c r="C24" t="n">
-        <v>10277.7</v>
+        <v>10481.5</v>
       </c>
       <c r="D24" t="n">
-        <v>10125.3</v>
+        <v>10145.4</v>
       </c>
       <c r="E24" t="n">
-        <v>10223.5</v>
+        <v>10369.8</v>
       </c>
       <c r="F24" t="n">
-        <v>80.09999999999999</v>
+        <v>146.3</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0143</v>
       </c>
       <c r="H24" t="n">
-        <v>152.4</v>
+        <v>336.1</v>
       </c>
       <c r="I24" t="n">
-        <v>9865.1</v>
+        <v>9972.9</v>
       </c>
       <c r="J24" t="n">
-        <v>9958.629999999999</v>
+        <v>10082.1</v>
       </c>
       <c r="K24" t="n">
-        <v>10050.85</v>
+        <v>10147.3</v>
       </c>
       <c r="L24" t="n">
-        <v>10143.08</v>
+        <v>10212.5</v>
       </c>
       <c r="M24" t="n">
-        <v>10235.95</v>
+        <v>10299.7</v>
       </c>
       <c r="N24" t="n">
-        <v>10328.83</v>
+        <v>10386.9</v>
       </c>
       <c r="O24" t="n">
-        <v>10420.4</v>
+        <v>10430.1</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2517,8 +2509,10 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
@@ -2527,16 +2521,20 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2546,50 +2544,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10223.7</v>
+        <v>10369.8</v>
       </c>
       <c r="C25" t="n">
-        <v>10481.5</v>
+        <v>10535.8</v>
       </c>
       <c r="D25" t="n">
-        <v>10145.4</v>
+        <v>10316</v>
       </c>
       <c r="E25" t="n">
-        <v>10369.8</v>
+        <v>10446.4</v>
       </c>
       <c r="F25" t="n">
-        <v>146.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0074</v>
       </c>
       <c r="H25" t="n">
-        <v>336.1</v>
+        <v>219.8</v>
       </c>
       <c r="I25" t="n">
-        <v>9972.9</v>
+        <v>9809.299999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>10082.1</v>
+        <v>10061.88</v>
       </c>
       <c r="K25" t="n">
-        <v>10147.3</v>
+        <v>10201.75</v>
       </c>
       <c r="L25" t="n">
-        <v>10212.5</v>
+        <v>10341.62</v>
       </c>
       <c r="M25" t="n">
-        <v>10299.7</v>
+        <v>10537.85</v>
       </c>
       <c r="N25" t="n">
-        <v>10386.9</v>
+        <v>10734.07</v>
       </c>
       <c r="O25" t="n">
-        <v>10430.1</v>
+        <v>10817.6</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2597,10 +2595,8 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
@@ -2609,20 +2605,16 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2632,50 +2624,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10369.8</v>
+        <v>10446.3</v>
       </c>
       <c r="C26" t="n">
-        <v>10535.8</v>
+        <v>10745.8</v>
       </c>
       <c r="D26" t="n">
-        <v>10316</v>
+        <v>10446.3</v>
       </c>
       <c r="E26" t="n">
-        <v>10446.4</v>
+        <v>10686.9</v>
       </c>
       <c r="F26" t="n">
-        <v>76.59999999999999</v>
+        <v>240.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.023</v>
       </c>
       <c r="H26" t="n">
-        <v>219.8</v>
+        <v>299.5</v>
       </c>
       <c r="I26" t="n">
-        <v>9809.299999999999</v>
+        <v>10096.2</v>
       </c>
       <c r="J26" t="n">
-        <v>10061.88</v>
+        <v>10236.85</v>
       </c>
       <c r="K26" t="n">
-        <v>10201.75</v>
+        <v>10336.5</v>
       </c>
       <c r="L26" t="n">
-        <v>10341.62</v>
+        <v>10436.15</v>
       </c>
       <c r="M26" t="n">
-        <v>10537.85</v>
+        <v>10556.3</v>
       </c>
       <c r="N26" t="n">
-        <v>10734.07</v>
+        <v>10676.45</v>
       </c>
       <c r="O26" t="n">
-        <v>10817.6</v>
+        <v>10755.6</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2693,16 +2685,18 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2712,50 +2706,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10446.3</v>
+        <v>10686.8</v>
       </c>
       <c r="C27" t="n">
-        <v>10745.8</v>
+        <v>10934.9</v>
       </c>
       <c r="D27" t="n">
-        <v>10446.3</v>
+        <v>10645.8</v>
       </c>
       <c r="E27" t="n">
-        <v>10686.9</v>
+        <v>10910.6</v>
       </c>
       <c r="F27" t="n">
-        <v>240.5</v>
+        <v>223.7</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0209</v>
       </c>
       <c r="H27" t="n">
-        <v>299.5</v>
+        <v>289.1</v>
       </c>
       <c r="I27" t="n">
-        <v>10096.2</v>
+        <v>10146.8</v>
       </c>
       <c r="J27" t="n">
-        <v>10236.85</v>
+        <v>10432.83</v>
       </c>
       <c r="K27" t="n">
-        <v>10336.5</v>
+        <v>10537.15</v>
       </c>
       <c r="L27" t="n">
-        <v>10436.15</v>
+        <v>10641.48</v>
       </c>
       <c r="M27" t="n">
-        <v>10556.3</v>
+        <v>10836.65</v>
       </c>
       <c r="N27" t="n">
-        <v>10676.45</v>
+        <v>11031.83</v>
       </c>
       <c r="O27" t="n">
-        <v>10755.6</v>
+        <v>11045.3</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2773,18 +2767,16 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2794,70 +2786,74 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10686.8</v>
+        <v>10911</v>
       </c>
       <c r="C28" t="n">
-        <v>10934.9</v>
+        <v>10911</v>
       </c>
       <c r="D28" t="n">
-        <v>10645.8</v>
+        <v>10234.5</v>
       </c>
       <c r="E28" t="n">
-        <v>10910.6</v>
+        <v>10284.8</v>
       </c>
       <c r="F28" t="n">
-        <v>223.7</v>
+        <v>-625.8</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0574</v>
       </c>
       <c r="H28" t="n">
-        <v>289.1</v>
+        <v>676.5</v>
       </c>
       <c r="I28" t="n">
-        <v>10146.8</v>
+        <v>10356.7</v>
       </c>
       <c r="J28" t="n">
-        <v>10432.83</v>
+        <v>10681.62</v>
       </c>
       <c r="K28" t="n">
-        <v>10537.15</v>
+        <v>10766.05</v>
       </c>
       <c r="L28" t="n">
-        <v>10641.48</v>
+        <v>10850.47</v>
       </c>
       <c r="M28" t="n">
-        <v>10836.65</v>
+        <v>11055.15</v>
       </c>
       <c r="N28" t="n">
-        <v>11031.83</v>
+        <v>11259.82</v>
       </c>
       <c r="O28" t="n">
-        <v>11045.3</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
+        <v>11224</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2866,7 +2862,7 @@
       </c>
       <c r="W28" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2874,69 +2870,63 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10911</v>
+        <v>10285</v>
       </c>
       <c r="C29" t="n">
-        <v>10911</v>
+        <v>10447.5</v>
       </c>
       <c r="D29" t="n">
-        <v>10234.5</v>
+        <v>10082</v>
       </c>
       <c r="E29" t="n">
-        <v>10284.8</v>
+        <v>10261.2</v>
       </c>
       <c r="F29" t="n">
-        <v>-625.8</v>
+        <v>-23.6</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0574</v>
+        <v>-0.0023</v>
       </c>
       <c r="H29" t="n">
-        <v>676.5</v>
+        <v>365.5</v>
       </c>
       <c r="I29" t="n">
-        <v>10356.7</v>
+        <v>9558</v>
       </c>
       <c r="J29" t="n">
-        <v>10681.62</v>
+        <v>9464.32</v>
       </c>
       <c r="K29" t="n">
-        <v>10766.05</v>
+        <v>9946.549999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>10850.47</v>
+        <v>10428.77</v>
       </c>
       <c r="M29" t="n">
-        <v>11055.15</v>
+        <v>10623.05</v>
       </c>
       <c r="N29" t="n">
-        <v>11259.82</v>
+        <v>10817.32</v>
       </c>
       <c r="O29" t="n">
-        <v>11224</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>11587.5</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2948,7 +2938,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2958,67 +2948,73 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10285</v>
+        <v>10261.1</v>
       </c>
       <c r="C30" t="n">
-        <v>10447.5</v>
+        <v>10447.7</v>
       </c>
       <c r="D30" t="n">
-        <v>10082</v>
+        <v>9915.700000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>10261.2</v>
+        <v>9918.299999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-23.6</v>
+        <v>-342.9</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0334</v>
       </c>
       <c r="H30" t="n">
-        <v>365.5</v>
+        <v>532</v>
       </c>
       <c r="I30" t="n">
-        <v>9558</v>
+        <v>9716.5</v>
       </c>
       <c r="J30" t="n">
-        <v>9464.32</v>
+        <v>9893.93</v>
       </c>
       <c r="K30" t="n">
-        <v>9946.549999999999</v>
+        <v>10078.45</v>
       </c>
       <c r="L30" t="n">
-        <v>10428.77</v>
+        <v>10262.98</v>
       </c>
       <c r="M30" t="n">
-        <v>10623.05</v>
+        <v>10443.95</v>
       </c>
       <c r="N30" t="n">
-        <v>10817.32</v>
+        <v>10624.93</v>
       </c>
       <c r="O30" t="n">
-        <v>11587.5</v>
+        <v>10813</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3026,83 +3022,81 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10261.1</v>
+        <v>9918.5</v>
       </c>
       <c r="C31" t="n">
-        <v>10447.7</v>
+        <v>10118.2</v>
       </c>
       <c r="D31" t="n">
-        <v>9915.700000000001</v>
+        <v>9670.5</v>
       </c>
       <c r="E31" t="n">
-        <v>9918.299999999999</v>
+        <v>9967.4</v>
       </c>
       <c r="F31" t="n">
-        <v>-342.9</v>
+        <v>49.1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0334</v>
+        <v>0.005</v>
       </c>
       <c r="H31" t="n">
-        <v>532</v>
+        <v>447.7</v>
       </c>
       <c r="I31" t="n">
-        <v>9716.5</v>
+        <v>9383.700000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>9893.93</v>
+        <v>9254.6</v>
       </c>
       <c r="K31" t="n">
-        <v>10078.45</v>
+        <v>9652.299999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>10262.98</v>
+        <v>10050</v>
       </c>
       <c r="M31" t="n">
-        <v>10443.95</v>
+        <v>10184.3</v>
       </c>
       <c r="N31" t="n">
-        <v>10624.93</v>
+        <v>10318.6</v>
       </c>
       <c r="O31" t="n">
-        <v>10813</v>
+        <v>10979.7</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3110,7 +3104,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3124,50 +3118,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9918.5</v>
+        <v>9967.5</v>
       </c>
       <c r="C32" t="n">
-        <v>10118.2</v>
+        <v>10465.2</v>
       </c>
       <c r="D32" t="n">
-        <v>9670.5</v>
+        <v>9958.1</v>
       </c>
       <c r="E32" t="n">
-        <v>9967.4</v>
+        <v>10436.3</v>
       </c>
       <c r="F32" t="n">
-        <v>49.1</v>
+        <v>468.9</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.005</v>
+        <v>0.047</v>
       </c>
       <c r="H32" t="n">
-        <v>447.7</v>
+        <v>507.1</v>
       </c>
       <c r="I32" t="n">
-        <v>9383.700000000001</v>
+        <v>9222.799999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>9254.6</v>
+        <v>9556.23</v>
       </c>
       <c r="K32" t="n">
-        <v>9652.299999999999</v>
+        <v>9743.549999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>10050</v>
+        <v>9930.879999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>10184.3</v>
+        <v>10191.25</v>
       </c>
       <c r="N32" t="n">
-        <v>10318.6</v>
+        <v>10451.63</v>
       </c>
       <c r="O32" t="n">
-        <v>10979.7</v>
+        <v>10565.9</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3178,78 +3172,82 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9967.5</v>
+        <v>10436.2</v>
       </c>
       <c r="C33" t="n">
-        <v>10465.2</v>
+        <v>10687.9</v>
       </c>
       <c r="D33" t="n">
-        <v>9958.1</v>
+        <v>10330.9</v>
       </c>
       <c r="E33" t="n">
-        <v>10436.3</v>
+        <v>10600.5</v>
       </c>
       <c r="F33" t="n">
-        <v>468.9</v>
+        <v>164.2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.047</v>
+        <v>0.0157</v>
       </c>
       <c r="H33" t="n">
-        <v>507.1</v>
+        <v>357</v>
       </c>
       <c r="I33" t="n">
-        <v>9222.799999999999</v>
+        <v>9451</v>
       </c>
       <c r="J33" t="n">
-        <v>9556.23</v>
+        <v>10041.52</v>
       </c>
       <c r="K33" t="n">
-        <v>9743.549999999999</v>
+        <v>10182.75</v>
       </c>
       <c r="L33" t="n">
-        <v>9930.879999999999</v>
+        <v>10323.97</v>
       </c>
       <c r="M33" t="n">
-        <v>10191.25</v>
+        <v>10689.85</v>
       </c>
       <c r="N33" t="n">
-        <v>10451.63</v>
+        <v>11055.73</v>
       </c>
       <c r="O33" t="n">
-        <v>10565.9</v>
+        <v>10972.3</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3267,18 +3265,16 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3292,50 +3288,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10436.2</v>
+        <v>10601.5</v>
       </c>
       <c r="C34" t="n">
-        <v>10687.9</v>
+        <v>10667.6</v>
       </c>
       <c r="D34" t="n">
-        <v>10330.9</v>
+        <v>10528.6</v>
       </c>
       <c r="E34" t="n">
-        <v>10600.5</v>
+        <v>10667.6</v>
       </c>
       <c r="F34" t="n">
-        <v>164.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0063</v>
       </c>
       <c r="H34" t="n">
-        <v>357</v>
+        <v>139</v>
       </c>
       <c r="I34" t="n">
-        <v>9451</v>
+        <v>9973.9</v>
       </c>
       <c r="J34" t="n">
-        <v>10041.52</v>
+        <v>10289.05</v>
       </c>
       <c r="K34" t="n">
-        <v>10182.75</v>
+        <v>10422</v>
       </c>
       <c r="L34" t="n">
-        <v>10323.97</v>
+        <v>10554.95</v>
       </c>
       <c r="M34" t="n">
-        <v>10689.85</v>
+        <v>10779</v>
       </c>
       <c r="N34" t="n">
-        <v>11055.73</v>
+        <v>11003.05</v>
       </c>
       <c r="O34" t="n">
-        <v>10972.3</v>
+        <v>11044.9</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3362,167 +3358,167 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10601.5</v>
+        <v>10668.4</v>
       </c>
       <c r="C35" t="n">
-        <v>10667.6</v>
+        <v>10683.7</v>
       </c>
       <c r="D35" t="n">
-        <v>10528.6</v>
+        <v>10361.5</v>
       </c>
       <c r="E35" t="n">
-        <v>10667.6</v>
+        <v>10379.1</v>
       </c>
       <c r="F35" t="n">
-        <v>67.09999999999999</v>
+        <v>-288.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0063</v>
+        <v>-0.027</v>
       </c>
       <c r="H35" t="n">
-        <v>139</v>
+        <v>322.2</v>
       </c>
       <c r="I35" t="n">
-        <v>9973.9</v>
+        <v>10389.6</v>
       </c>
       <c r="J35" t="n">
-        <v>10289.05</v>
+        <v>10563.35</v>
       </c>
       <c r="K35" t="n">
-        <v>10422</v>
+        <v>10598.1</v>
       </c>
       <c r="L35" t="n">
-        <v>10554.95</v>
+        <v>10632.85</v>
       </c>
       <c r="M35" t="n">
-        <v>10779</v>
+        <v>10737.1</v>
       </c>
       <c r="N35" t="n">
-        <v>11003.05</v>
+        <v>10841.35</v>
       </c>
       <c r="O35" t="n">
-        <v>11044.9</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+        <v>10806.6</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10668.4</v>
+        <v>10378.5</v>
       </c>
       <c r="C36" t="n">
-        <v>10683.7</v>
+        <v>10410.8</v>
       </c>
       <c r="D36" t="n">
-        <v>10361.5</v>
+        <v>10188.7</v>
       </c>
       <c r="E36" t="n">
-        <v>10379.1</v>
+        <v>10363.9</v>
       </c>
       <c r="F36" t="n">
-        <v>-288.5</v>
+        <v>-15.2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.0015</v>
       </c>
       <c r="H36" t="n">
-        <v>322.2</v>
+        <v>222.1</v>
       </c>
       <c r="I36" t="n">
-        <v>10389.6</v>
+        <v>10039.3</v>
       </c>
       <c r="J36" t="n">
-        <v>10563.35</v>
+        <v>9985.15</v>
       </c>
       <c r="K36" t="n">
-        <v>10598.1</v>
+        <v>10218</v>
       </c>
       <c r="L36" t="n">
-        <v>10632.85</v>
+        <v>10450.85</v>
       </c>
       <c r="M36" t="n">
-        <v>10737.1</v>
+        <v>10540.2</v>
       </c>
       <c r="N36" t="n">
-        <v>10841.35</v>
+        <v>10629.55</v>
       </c>
       <c r="O36" t="n">
-        <v>10806.6</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
+        <v>11005.9</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3534,167 +3530,165 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10378.5</v>
+        <v>10365.4</v>
       </c>
       <c r="C37" t="n">
-        <v>10410.8</v>
+        <v>10488.2</v>
       </c>
       <c r="D37" t="n">
-        <v>10188.7</v>
+        <v>10164.3</v>
       </c>
       <c r="E37" t="n">
-        <v>10363.9</v>
+        <v>10233.1</v>
       </c>
       <c r="F37" t="n">
-        <v>-15.2</v>
+        <v>-130.8</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0126</v>
       </c>
       <c r="H37" t="n">
-        <v>222.1</v>
+        <v>323.9</v>
       </c>
       <c r="I37" t="n">
-        <v>10039.3</v>
+        <v>9966.6</v>
       </c>
       <c r="J37" t="n">
-        <v>9985.15</v>
+        <v>10173.88</v>
       </c>
       <c r="K37" t="n">
-        <v>10218</v>
+        <v>10252.85</v>
       </c>
       <c r="L37" t="n">
-        <v>10450.85</v>
+        <v>10331.83</v>
       </c>
       <c r="M37" t="n">
-        <v>10540.2</v>
+        <v>10474.95</v>
       </c>
       <c r="N37" t="n">
-        <v>10629.55</v>
+        <v>10618.08</v>
       </c>
       <c r="O37" t="n">
-        <v>11005.9</v>
+        <v>10632.9</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10365.4</v>
+        <v>10233.6</v>
       </c>
       <c r="C38" t="n">
-        <v>10488.2</v>
+        <v>10375.7</v>
       </c>
       <c r="D38" t="n">
-        <v>10164.3</v>
+        <v>10152.1</v>
       </c>
       <c r="E38" t="n">
-        <v>10233.1</v>
+        <v>10195.4</v>
       </c>
       <c r="F38" t="n">
-        <v>-130.8</v>
+        <v>-37.7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0037</v>
       </c>
       <c r="H38" t="n">
-        <v>323.9</v>
+        <v>223.6</v>
       </c>
       <c r="I38" t="n">
-        <v>9966.6</v>
+        <v>9840.4</v>
       </c>
       <c r="J38" t="n">
-        <v>10173.88</v>
+        <v>9862.620000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>10252.85</v>
+        <v>10071.15</v>
       </c>
       <c r="L38" t="n">
-        <v>10331.83</v>
+        <v>10279.67</v>
       </c>
       <c r="M38" t="n">
-        <v>10474.95</v>
+        <v>10395.05</v>
       </c>
       <c r="N38" t="n">
-        <v>10618.08</v>
+        <v>10510.42</v>
       </c>
       <c r="O38" t="n">
-        <v>10632.9</v>
+        <v>10812.1</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3702,64 +3696,60 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10233.6</v>
+        <v>10194.8</v>
       </c>
       <c r="C39" t="n">
-        <v>10375.7</v>
+        <v>10497.2</v>
       </c>
       <c r="D39" t="n">
-        <v>10152.1</v>
+        <v>10151.5</v>
       </c>
       <c r="E39" t="n">
-        <v>10195.4</v>
+        <v>10466.3</v>
       </c>
       <c r="F39" t="n">
-        <v>-37.7</v>
+        <v>270.9</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0266</v>
       </c>
       <c r="H39" t="n">
-        <v>223.6</v>
+        <v>345.7</v>
       </c>
       <c r="I39" t="n">
-        <v>9840.4</v>
+        <v>9928.5</v>
       </c>
       <c r="J39" t="n">
-        <v>9862.620000000001</v>
+        <v>9937.549999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>10071.15</v>
+        <v>10083.6</v>
       </c>
       <c r="L39" t="n">
-        <v>10279.67</v>
+        <v>10229.65</v>
       </c>
       <c r="M39" t="n">
-        <v>10395.05</v>
+        <v>10307.2</v>
       </c>
       <c r="N39" t="n">
-        <v>10510.42</v>
+        <v>10384.75</v>
       </c>
       <c r="O39" t="n">
-        <v>10812.1</v>
+        <v>10599.3</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3770,74 +3760,82 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10194.8</v>
+        <v>10465.6</v>
       </c>
       <c r="C40" t="n">
-        <v>10497.2</v>
+        <v>10557.2</v>
       </c>
       <c r="D40" t="n">
-        <v>10151.5</v>
+        <v>10381.2</v>
       </c>
       <c r="E40" t="n">
-        <v>10466.3</v>
+        <v>10409.3</v>
       </c>
       <c r="F40" t="n">
-        <v>270.9</v>
+        <v>-57</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0266</v>
+        <v>-0.0054</v>
       </c>
       <c r="H40" t="n">
-        <v>345.7</v>
+        <v>176</v>
       </c>
       <c r="I40" t="n">
-        <v>9928.5</v>
+        <v>9805.799999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>9937.549999999999</v>
+        <v>10191.57</v>
       </c>
       <c r="K40" t="n">
-        <v>10083.6</v>
+        <v>10293.45</v>
       </c>
       <c r="L40" t="n">
-        <v>10229.65</v>
+        <v>10395.32</v>
       </c>
       <c r="M40" t="n">
-        <v>10307.2</v>
+        <v>10639.15</v>
       </c>
       <c r="N40" t="n">
-        <v>10384.75</v>
+        <v>10882.97</v>
       </c>
       <c r="O40" t="n">
-        <v>10599.3</v>
+        <v>10842.9</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3850,23 +3848,19 @@
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3880,50 +3874,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10465.6</v>
+        <v>10409.3</v>
       </c>
       <c r="C41" t="n">
-        <v>10557.2</v>
+        <v>10415.7</v>
       </c>
       <c r="D41" t="n">
-        <v>10381.2</v>
+        <v>10238.6</v>
       </c>
       <c r="E41" t="n">
-        <v>10409.3</v>
+        <v>10368.1</v>
       </c>
       <c r="F41" t="n">
-        <v>-57</v>
+        <v>-41.2</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.004</v>
       </c>
       <c r="H41" t="n">
-        <v>176</v>
+        <v>177.1</v>
       </c>
       <c r="I41" t="n">
-        <v>9805.799999999999</v>
+        <v>10205.2</v>
       </c>
       <c r="J41" t="n">
-        <v>10191.57</v>
+        <v>10203.35</v>
       </c>
       <c r="K41" t="n">
-        <v>10293.45</v>
+        <v>10321.3</v>
       </c>
       <c r="L41" t="n">
-        <v>10395.32</v>
+        <v>10439.25</v>
       </c>
       <c r="M41" t="n">
-        <v>10639.15</v>
+        <v>10497.3</v>
       </c>
       <c r="N41" t="n">
-        <v>10882.97</v>
+        <v>10555.35</v>
       </c>
       <c r="O41" t="n">
-        <v>10842.9</v>
+        <v>10733.2</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3931,12 +3925,14 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3948,171 +3944,169 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10409.3</v>
+        <v>10369.1</v>
       </c>
       <c r="C42" t="n">
-        <v>10415.7</v>
+        <v>10471.7</v>
       </c>
       <c r="D42" t="n">
-        <v>10238.6</v>
+        <v>10127.6</v>
       </c>
       <c r="E42" t="n">
-        <v>10368.1</v>
+        <v>10471.7</v>
       </c>
       <c r="F42" t="n">
-        <v>-41.2</v>
+        <v>103.6</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.01</v>
       </c>
       <c r="H42" t="n">
-        <v>177.1</v>
+        <v>344.1</v>
       </c>
       <c r="I42" t="n">
-        <v>10205.2</v>
+        <v>10061.5</v>
       </c>
       <c r="J42" t="n">
-        <v>10203.35</v>
+        <v>10211.47</v>
       </c>
       <c r="K42" t="n">
-        <v>10321.3</v>
+        <v>10279.55</v>
       </c>
       <c r="L42" t="n">
-        <v>10439.25</v>
+        <v>10347.62</v>
       </c>
       <c r="M42" t="n">
-        <v>10497.3</v>
+        <v>10456.65</v>
       </c>
       <c r="N42" t="n">
-        <v>10555.35</v>
+        <v>10565.68</v>
       </c>
       <c r="O42" t="n">
-        <v>10733.2</v>
+        <v>10592.8</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10369.1</v>
+        <v>10471.4</v>
       </c>
       <c r="C43" t="n">
-        <v>10471.7</v>
+        <v>10570.1</v>
       </c>
       <c r="D43" t="n">
-        <v>10127.6</v>
+        <v>10352.9</v>
       </c>
       <c r="E43" t="n">
-        <v>10471.7</v>
+        <v>10363.3</v>
       </c>
       <c r="F43" t="n">
-        <v>103.6</v>
+        <v>-108.4</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0104</v>
       </c>
       <c r="H43" t="n">
-        <v>344.1</v>
+        <v>217.2</v>
       </c>
       <c r="I43" t="n">
-        <v>10061.5</v>
+        <v>9783.5</v>
       </c>
       <c r="J43" t="n">
-        <v>10211.47</v>
+        <v>10213.62</v>
       </c>
       <c r="K43" t="n">
-        <v>10279.55</v>
+        <v>10299.65</v>
       </c>
       <c r="L43" t="n">
-        <v>10347.62</v>
+        <v>10385.68</v>
       </c>
       <c r="M43" t="n">
-        <v>10456.65</v>
+        <v>10643.75</v>
       </c>
       <c r="N43" t="n">
-        <v>10565.68</v>
+        <v>10901.83</v>
       </c>
       <c r="O43" t="n">
-        <v>10592.8</v>
+        <v>10815.8</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4120,7 +4114,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4134,50 +4128,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10471.4</v>
+        <v>10363.6</v>
       </c>
       <c r="C44" t="n">
-        <v>10570.1</v>
+        <v>10575.3</v>
       </c>
       <c r="D44" t="n">
-        <v>10352.9</v>
+        <v>10332.4</v>
       </c>
       <c r="E44" t="n">
-        <v>10363.3</v>
+        <v>10508</v>
       </c>
       <c r="F44" t="n">
-        <v>-108.4</v>
+        <v>144.7</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.014</v>
       </c>
       <c r="H44" t="n">
-        <v>217.2</v>
+        <v>242.9</v>
       </c>
       <c r="I44" t="n">
-        <v>9783.5</v>
+        <v>10135.7</v>
       </c>
       <c r="J44" t="n">
-        <v>10213.62</v>
+        <v>10097</v>
       </c>
       <c r="K44" t="n">
-        <v>10299.65</v>
+        <v>10254.7</v>
       </c>
       <c r="L44" t="n">
-        <v>10385.68</v>
+        <v>10412.4</v>
       </c>
       <c r="M44" t="n">
-        <v>10643.75</v>
+        <v>10471.9</v>
       </c>
       <c r="N44" t="n">
-        <v>10901.83</v>
+        <v>10531.4</v>
       </c>
       <c r="O44" t="n">
-        <v>10815.8</v>
+        <v>10787.3</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4188,21 +4182,25 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4216,50 +4214,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10363.6</v>
+        <v>10507.8</v>
       </c>
       <c r="C45" t="n">
-        <v>10575.3</v>
+        <v>10701.3</v>
       </c>
       <c r="D45" t="n">
-        <v>10332.4</v>
+        <v>10429.2</v>
       </c>
       <c r="E45" t="n">
-        <v>10508</v>
+        <v>10679</v>
       </c>
       <c r="F45" t="n">
-        <v>144.7</v>
+        <v>171</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0163</v>
       </c>
       <c r="H45" t="n">
-        <v>242.9</v>
+        <v>272.1</v>
       </c>
       <c r="I45" t="n">
-        <v>10135.7</v>
+        <v>10089.5</v>
       </c>
       <c r="J45" t="n">
-        <v>10097</v>
+        <v>10292.18</v>
       </c>
       <c r="K45" t="n">
-        <v>10254.7</v>
+        <v>10386.55</v>
       </c>
       <c r="L45" t="n">
-        <v>10412.4</v>
+        <v>10480.93</v>
       </c>
       <c r="M45" t="n">
-        <v>10471.9</v>
+        <v>10629.45</v>
       </c>
       <c r="N45" t="n">
-        <v>10531.4</v>
+        <v>10777.97</v>
       </c>
       <c r="O45" t="n">
-        <v>10787.3</v>
+        <v>10818.2</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4277,172 +4275,168 @@
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10507.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C46" t="n">
-        <v>10701.3</v>
+        <v>10747</v>
       </c>
       <c r="D46" t="n">
-        <v>10429.2</v>
+        <v>10397.5</v>
       </c>
       <c r="E46" t="n">
-        <v>10679</v>
+        <v>10497.3</v>
       </c>
       <c r="F46" t="n">
-        <v>171</v>
+        <v>-181.7</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.017</v>
       </c>
       <c r="H46" t="n">
-        <v>272.1</v>
+        <v>349.5</v>
       </c>
       <c r="I46" t="n">
-        <v>10089.5</v>
+        <v>10157.1</v>
       </c>
       <c r="J46" t="n">
-        <v>10292.18</v>
+        <v>10463.78</v>
       </c>
       <c r="K46" t="n">
-        <v>10386.55</v>
+        <v>10542.95</v>
       </c>
       <c r="L46" t="n">
-        <v>10480.93</v>
+        <v>10622.12</v>
       </c>
       <c r="M46" t="n">
-        <v>10629.45</v>
+        <v>10815.05</v>
       </c>
       <c r="N46" t="n">
-        <v>10777.97</v>
+        <v>11007.97</v>
       </c>
       <c r="O46" t="n">
-        <v>10818.2</v>
+        <v>10973.4</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="Q46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10679.4</v>
+        <v>10498.1</v>
       </c>
       <c r="C47" t="n">
-        <v>10747</v>
+        <v>10623.7</v>
       </c>
       <c r="D47" t="n">
-        <v>10397.5</v>
+        <v>10423</v>
       </c>
       <c r="E47" t="n">
-        <v>10497.3</v>
+        <v>10600.4</v>
       </c>
       <c r="F47" t="n">
-        <v>-181.7</v>
+        <v>103.1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.017</v>
+        <v>0.0098</v>
       </c>
       <c r="H47" t="n">
-        <v>349.5</v>
+        <v>200.7</v>
       </c>
       <c r="I47" t="n">
-        <v>10157.1</v>
+        <v>10048</v>
       </c>
       <c r="J47" t="n">
-        <v>10463.78</v>
+        <v>10110.32</v>
       </c>
       <c r="K47" t="n">
-        <v>10542.95</v>
+        <v>10322.55</v>
       </c>
       <c r="L47" t="n">
-        <v>10622.12</v>
+        <v>10534.77</v>
       </c>
       <c r="M47" t="n">
-        <v>10815.05</v>
+        <v>10672.05</v>
       </c>
       <c r="N47" t="n">
-        <v>11007.97</v>
+        <v>10809.32</v>
       </c>
       <c r="O47" t="n">
-        <v>10973.4</v>
+        <v>11096.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4454,64 +4448,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10498.1</v>
+        <v>10600.3</v>
       </c>
       <c r="C48" t="n">
-        <v>10623.7</v>
+        <v>10763.4</v>
       </c>
       <c r="D48" t="n">
-        <v>10423</v>
+        <v>10483.1</v>
       </c>
       <c r="E48" t="n">
-        <v>10600.4</v>
+        <v>10736.2</v>
       </c>
       <c r="F48" t="n">
-        <v>103.1</v>
+        <v>135.8</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0128</v>
       </c>
       <c r="H48" t="n">
-        <v>200.7</v>
+        <v>280.3</v>
       </c>
       <c r="I48" t="n">
-        <v>10048</v>
+        <v>10222.3</v>
       </c>
       <c r="J48" t="n">
-        <v>10110.32</v>
+        <v>10438.23</v>
       </c>
       <c r="K48" t="n">
-        <v>10322.55</v>
+        <v>10500.05</v>
       </c>
       <c r="L48" t="n">
-        <v>10534.77</v>
+        <v>10561.88</v>
       </c>
       <c r="M48" t="n">
-        <v>10672.05</v>
+        <v>10700.75</v>
       </c>
       <c r="N48" t="n">
-        <v>10809.32</v>
+        <v>10839.63</v>
       </c>
       <c r="O48" t="n">
-        <v>11096.5</v>
+        <v>10824.4</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4519,16 +4513,20 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4536,64 +4534,60 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10600.3</v>
+        <v>10736.1</v>
       </c>
       <c r="C49" t="n">
-        <v>10763.4</v>
+        <v>10989.5</v>
       </c>
       <c r="D49" t="n">
-        <v>10483.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E49" t="n">
-        <v>10736.2</v>
+        <v>10868.1</v>
       </c>
       <c r="F49" t="n">
-        <v>135.8</v>
+        <v>131.9</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0123</v>
       </c>
       <c r="H49" t="n">
-        <v>280.3</v>
+        <v>253.4</v>
       </c>
       <c r="I49" t="n">
-        <v>10222.3</v>
+        <v>10202.8</v>
       </c>
       <c r="J49" t="n">
-        <v>10438.23</v>
+        <v>10512.37</v>
       </c>
       <c r="K49" t="n">
-        <v>10500.05</v>
+        <v>10596.05</v>
       </c>
       <c r="L49" t="n">
-        <v>10561.88</v>
+        <v>10679.73</v>
       </c>
       <c r="M49" t="n">
-        <v>10700.75</v>
+        <v>10876.35</v>
       </c>
       <c r="N49" t="n">
-        <v>10839.63</v>
+        <v>11072.98</v>
       </c>
       <c r="O49" t="n">
-        <v>10824.4</v>
+        <v>11043.7</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4601,10 +4595,8 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
@@ -4622,7 +4614,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4632,50 +4624,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10736.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C50" t="n">
-        <v>10989.5</v>
+        <v>10959.9</v>
       </c>
       <c r="D50" t="n">
-        <v>10736.1</v>
+        <v>10832.5</v>
       </c>
       <c r="E50" t="n">
-        <v>10868.1</v>
+        <v>10901.1</v>
       </c>
       <c r="F50" t="n">
-        <v>131.9</v>
+        <v>33</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0123</v>
+        <v>0.003</v>
       </c>
       <c r="H50" t="n">
-        <v>253.4</v>
+        <v>127.4</v>
       </c>
       <c r="I50" t="n">
-        <v>10202.8</v>
+        <v>10482.7</v>
       </c>
       <c r="J50" t="n">
-        <v>10512.37</v>
+        <v>10617.35</v>
       </c>
       <c r="K50" t="n">
-        <v>10596.05</v>
+        <v>10741.4</v>
       </c>
       <c r="L50" t="n">
-        <v>10679.73</v>
+        <v>10865.45</v>
       </c>
       <c r="M50" t="n">
-        <v>10876.35</v>
+        <v>10994.8</v>
       </c>
       <c r="N50" t="n">
-        <v>11072.98</v>
+        <v>11124.15</v>
       </c>
       <c r="O50" t="n">
-        <v>11043.7</v>
+        <v>11242.9</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4688,13 +4680,11 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4702,73 +4692,81 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10868.1</v>
+        <v>10901.1</v>
       </c>
       <c r="C51" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D51" t="n">
-        <v>10832.5</v>
+        <v>10723.7</v>
       </c>
       <c r="E51" t="n">
-        <v>10901.1</v>
+        <v>10750.1</v>
       </c>
       <c r="F51" t="n">
-        <v>33</v>
+        <v>-151</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0139</v>
       </c>
       <c r="H51" t="n">
-        <v>127.4</v>
+        <v>187.2</v>
       </c>
       <c r="I51" t="n">
-        <v>10482.7</v>
+        <v>10705.1</v>
       </c>
       <c r="J51" t="n">
-        <v>10617.35</v>
+        <v>10776.15</v>
       </c>
       <c r="K51" t="n">
-        <v>10741.4</v>
+        <v>10837.4</v>
       </c>
       <c r="L51" t="n">
-        <v>10865.45</v>
+        <v>10898.65</v>
       </c>
       <c r="M51" t="n">
-        <v>10994.8</v>
+        <v>10964.8</v>
       </c>
       <c r="N51" t="n">
-        <v>11124.15</v>
+        <v>11030.95</v>
       </c>
       <c r="O51" t="n">
-        <v>11242.9</v>
+        <v>11087.3</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4782,144 +4780,142 @@
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10901.1</v>
+        <v>10750</v>
       </c>
       <c r="C52" t="n">
-        <v>10910.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D52" t="n">
-        <v>10723.7</v>
+        <v>10684.4</v>
       </c>
       <c r="E52" t="n">
-        <v>10750.1</v>
+        <v>10816.6</v>
       </c>
       <c r="F52" t="n">
-        <v>-151</v>
+        <v>66.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0139</v>
+        <v>0.0062</v>
       </c>
       <c r="H52" t="n">
-        <v>187.2</v>
+        <v>147.2</v>
       </c>
       <c r="I52" t="n">
-        <v>10705.1</v>
+        <v>10536.5</v>
       </c>
       <c r="J52" t="n">
-        <v>10776.15</v>
+        <v>10529.3</v>
       </c>
       <c r="K52" t="n">
-        <v>10837.4</v>
+        <v>10656.5</v>
       </c>
       <c r="L52" t="n">
-        <v>10898.65</v>
+        <v>10783.7</v>
       </c>
       <c r="M52" t="n">
-        <v>10964.8</v>
+        <v>10843.7</v>
       </c>
       <c r="N52" t="n">
-        <v>11030.95</v>
+        <v>10903.7</v>
       </c>
       <c r="O52" t="n">
-        <v>11087.3</v>
+        <v>11098.1</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10750</v>
+        <v>10816.3</v>
       </c>
       <c r="C53" t="n">
-        <v>10831.6</v>
+        <v>10920.5</v>
       </c>
       <c r="D53" t="n">
-        <v>10684.4</v>
+        <v>10772.6</v>
       </c>
       <c r="E53" t="n">
-        <v>10816.6</v>
+        <v>10824.3</v>
       </c>
       <c r="F53" t="n">
-        <v>66.5</v>
+        <v>7.7</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0007</v>
       </c>
       <c r="H53" t="n">
-        <v>147.2</v>
+        <v>147.9</v>
       </c>
       <c r="I53" t="n">
-        <v>10536.5</v>
+        <v>10537.2</v>
       </c>
       <c r="J53" t="n">
-        <v>10529.3</v>
+        <v>10698.7</v>
       </c>
       <c r="K53" t="n">
-        <v>10656.5</v>
+        <v>10743</v>
       </c>
       <c r="L53" t="n">
-        <v>10783.7</v>
+        <v>10787.3</v>
       </c>
       <c r="M53" t="n">
-        <v>10843.7</v>
+        <v>10890.2</v>
       </c>
       <c r="N53" t="n">
-        <v>10903.7</v>
+        <v>10993.1</v>
       </c>
       <c r="O53" t="n">
-        <v>11098.1</v>
+        <v>10978.8</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4932,12 +4928,12 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U53" s="8" t="n">
@@ -4946,64 +4942,64 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10816.3</v>
+        <v>10824.6</v>
       </c>
       <c r="C54" t="n">
-        <v>10920.5</v>
+        <v>10866.8</v>
       </c>
       <c r="D54" t="n">
-        <v>10772.6</v>
+        <v>10689.6</v>
       </c>
       <c r="E54" t="n">
-        <v>10824.3</v>
+        <v>10831.1</v>
       </c>
       <c r="F54" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>147.9</v>
+        <v>177.2</v>
       </c>
       <c r="I54" t="n">
-        <v>10537.2</v>
+        <v>10624.7</v>
       </c>
       <c r="J54" t="n">
-        <v>10698.7</v>
+        <v>10665.27</v>
       </c>
       <c r="K54" t="n">
-        <v>10743</v>
+        <v>10750.35</v>
       </c>
       <c r="L54" t="n">
-        <v>10787.3</v>
+        <v>10835.42</v>
       </c>
       <c r="M54" t="n">
-        <v>10890.2</v>
+        <v>10898.25</v>
       </c>
       <c r="N54" t="n">
-        <v>10993.1</v>
+        <v>10961.08</v>
       </c>
       <c r="O54" t="n">
-        <v>10978.8</v>
+        <v>11068.4</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5011,89 +5007,91 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10824.6</v>
+        <v>10831</v>
       </c>
       <c r="C55" t="n">
-        <v>10866.8</v>
+        <v>10868.3</v>
       </c>
       <c r="D55" t="n">
-        <v>10689.6</v>
+        <v>10594.3</v>
       </c>
       <c r="E55" t="n">
-        <v>10831.1</v>
+        <v>10650.4</v>
       </c>
       <c r="F55" t="n">
-        <v>6.8</v>
+        <v>-180.7</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0167</v>
       </c>
       <c r="H55" t="n">
-        <v>177.2</v>
+        <v>274</v>
       </c>
       <c r="I55" t="n">
-        <v>10624.7</v>
+        <v>10512.4</v>
       </c>
       <c r="J55" t="n">
-        <v>10665.27</v>
+        <v>10680.35</v>
       </c>
       <c r="K55" t="n">
-        <v>10750.35</v>
+        <v>10742.5</v>
       </c>
       <c r="L55" t="n">
-        <v>10835.42</v>
+        <v>10804.65</v>
       </c>
       <c r="M55" t="n">
-        <v>10898.25</v>
+        <v>10919.7</v>
       </c>
       <c r="N55" t="n">
-        <v>10961.08</v>
+        <v>11034.75</v>
       </c>
       <c r="O55" t="n">
-        <v>11068.4</v>
+        <v>11044</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
@@ -5102,7 +5100,7 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5114,7 +5112,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5128,79 +5126,77 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10831</v>
+        <v>10650.9</v>
       </c>
       <c r="C56" t="n">
-        <v>10868.3</v>
+        <v>10823</v>
       </c>
       <c r="D56" t="n">
-        <v>10594.3</v>
+        <v>10586.4</v>
       </c>
       <c r="E56" t="n">
-        <v>10650.4</v>
+        <v>10659.1</v>
       </c>
       <c r="F56" t="n">
-        <v>-180.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0167</v>
+        <v>0.0008</v>
       </c>
       <c r="H56" t="n">
-        <v>274</v>
+        <v>236.6</v>
       </c>
       <c r="I56" t="n">
-        <v>10512.4</v>
+        <v>10320.3</v>
       </c>
       <c r="J56" t="n">
-        <v>10680.35</v>
+        <v>10335.95</v>
       </c>
       <c r="K56" t="n">
-        <v>10742.5</v>
+        <v>10513.4</v>
       </c>
       <c r="L56" t="n">
-        <v>10804.65</v>
+        <v>10690.85</v>
       </c>
       <c r="M56" t="n">
-        <v>10919.7</v>
+        <v>10787.4</v>
       </c>
       <c r="N56" t="n">
-        <v>11034.75</v>
+        <v>10883.95</v>
       </c>
       <c r="O56" t="n">
-        <v>11044</v>
+        <v>11142.3</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5214,50 +5210,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10650.9</v>
+        <v>10659.1</v>
       </c>
       <c r="C57" t="n">
-        <v>10823</v>
+        <v>10774.7</v>
       </c>
       <c r="D57" t="n">
-        <v>10586.4</v>
+        <v>10656.7</v>
       </c>
       <c r="E57" t="n">
-        <v>10659.1</v>
+        <v>10695.25</v>
       </c>
       <c r="F57" t="n">
-        <v>8.699999999999999</v>
+        <v>36.15</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0034</v>
       </c>
       <c r="H57" t="n">
-        <v>236.6</v>
+        <v>118</v>
       </c>
       <c r="I57" t="n">
-        <v>10320.3</v>
+        <v>10349.8</v>
       </c>
       <c r="J57" t="n">
-        <v>10335.95</v>
+        <v>10399.7</v>
       </c>
       <c r="K57" t="n">
-        <v>10513.4</v>
+        <v>10540.8</v>
       </c>
       <c r="L57" t="n">
-        <v>10690.85</v>
+        <v>10681.9</v>
       </c>
       <c r="M57" t="n">
-        <v>10787.4</v>
+        <v>10777.4</v>
       </c>
       <c r="N57" t="n">
-        <v>10883.95</v>
+        <v>10872.9</v>
       </c>
       <c r="O57" t="n">
-        <v>11142.3</v>
+        <v>11059.6</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5268,15 +5264,13 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5284,94 +5278,12 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>10659.1</v>
-      </c>
-      <c r="C58" t="n">
-        <v>10774.7</v>
-      </c>
-      <c r="D58" t="n">
-        <v>10656.7</v>
-      </c>
-      <c r="E58" t="n">
-        <v>10679.99</v>
-      </c>
-      <c r="F58" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H58" t="n">
-        <v>118</v>
-      </c>
-      <c r="I58" t="n">
-        <v>10349.8</v>
-      </c>
-      <c r="J58" t="n">
-        <v>10399.7</v>
-      </c>
-      <c r="K58" t="n">
-        <v>10540.8</v>
-      </c>
-      <c r="L58" t="n">
-        <v>10681.9</v>
-      </c>
-      <c r="M58" t="n">
-        <v>10777.4</v>
-      </c>
-      <c r="N58" t="n">
-        <v>10872.9</v>
-      </c>
-      <c r="O58" t="n">
-        <v>11059.6</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5223,10 +5226,10 @@
         <v>10656.7</v>
       </c>
       <c r="E57" t="n">
-        <v>10695.25</v>
+        <v>10695.3</v>
       </c>
       <c r="F57" t="n">
-        <v>36.15</v>
+        <v>36.2</v>
       </c>
       <c r="G57" s="5" t="n">
         <v>0.0034</v>
@@ -5286,6 +5289,92 @@
       <c r="X57" t="inlineStr">
         <is>
           <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10695.19</v>
+      </c>
+      <c r="C58" t="n">
+        <v>10758.74</v>
+      </c>
+      <c r="D58" t="n">
+        <v>10684.88</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>73.86</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10538.7</v>
+      </c>
+      <c r="J58" t="n">
+        <v>10567.1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>10636.3</v>
+      </c>
+      <c r="L58" t="n">
+        <v>10705.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>10754.3</v>
+      </c>
+      <c r="N58" t="n">
+        <v>10803.1</v>
+      </c>
+      <c r="O58" t="n">
+        <v>10892.7</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5299,25 +5296,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10695.19</v>
+        <v>10695.2</v>
       </c>
       <c r="C58" t="n">
-        <v>10758.74</v>
+        <v>10758.7</v>
       </c>
       <c r="D58" t="n">
-        <v>10684.88</v>
+        <v>10622</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>10636.71</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-58.59</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0055</v>
       </c>
       <c r="H58" t="n">
-        <v>73.86</v>
+        <v>136.7</v>
       </c>
       <c r="I58" t="n">
         <v>10538.7</v>
@@ -5340,20 +5337,20 @@
       <c r="O58" t="n">
         <v>10892.7</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5372,11 +5369,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>146.1</v>
       </c>
       <c r="I2" t="n">
-        <v>9032.5</v>
+        <v>9056.5</v>
       </c>
       <c r="J2" t="n">
-        <v>9007.969999999999</v>
+        <v>9037.969999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>9113.950000000001</v>
+        <v>9125.950000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>9219.93</v>
+        <v>9213.93</v>
       </c>
       <c r="M2" t="n">
-        <v>9260.65</v>
+        <v>9248.65</v>
       </c>
       <c r="N2" t="n">
-        <v>9301.370000000001</v>
+        <v>9283.370000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>9472.6</v>
+        <v>9424.6</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,8 +695,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -5302,19 +5304,19 @@
         <v>10758.7</v>
       </c>
       <c r="D58" t="n">
-        <v>10622</v>
+        <v>10599.21</v>
       </c>
       <c r="E58" t="n">
-        <v>10636.71</v>
+        <v>10606</v>
       </c>
       <c r="F58" t="n">
-        <v>-58.59</v>
+        <v>-89.3</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0083</v>
       </c>
       <c r="H58" t="n">
-        <v>136.7</v>
+        <v>159.49</v>
       </c>
       <c r="I58" t="n">
         <v>10538.7</v>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -659,25 +659,25 @@
         <v>146.1</v>
       </c>
       <c r="I2" t="n">
-        <v>9056.5</v>
+        <v>9088.4</v>
       </c>
       <c r="J2" t="n">
-        <v>9037.969999999999</v>
+        <v>9077.85</v>
       </c>
       <c r="K2" t="n">
-        <v>9125.950000000001</v>
+        <v>9141.9</v>
       </c>
       <c r="L2" t="n">
-        <v>9213.93</v>
+        <v>9205.950000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>9248.65</v>
+        <v>9232.700000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>9283.370000000001</v>
+        <v>9259.450000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>9424.6</v>
+        <v>9360.799999999999</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,7 +692,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -774,7 +774,7 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -856,7 +856,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -938,7 +938,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1022,7 +1022,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1106,7 +1106,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1190,7 +1190,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1272,7 +1272,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1356,7 +1356,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1438,7 +1438,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1520,7 +1520,7 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1604,7 +1604,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1686,7 +1686,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1766,7 +1766,7 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1850,7 +1850,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1936,7 +1936,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2020,7 +2020,7 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2102,7 +2102,7 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2186,7 +2186,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2268,7 +2268,7 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2352,7 +2352,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2434,7 +2434,7 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2516,7 +2516,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2600,7 +2600,7 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2680,7 +2680,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2762,7 +2762,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2848,7 +2848,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2926,7 +2926,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3008,7 +3008,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3092,7 +3092,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3174,7 +3174,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3260,7 +3260,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3344,7 +3344,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3434,7 +3434,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3518,7 +3518,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3600,7 +3600,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3684,7 +3684,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3762,7 +3762,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3848,7 +3848,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3932,7 +3932,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4018,7 +4018,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4102,7 +4102,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4184,7 +4184,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4270,7 +4270,7 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4354,7 +4354,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4436,7 +4436,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4520,7 +4520,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4600,7 +4600,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4680,7 +4680,7 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4766,7 +4766,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4844,7 +4844,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4928,7 +4928,7 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -5014,7 +5014,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5100,7 +5100,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5182,7 +5182,7 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5266,7 +5266,7 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -5304,19 +5304,19 @@
         <v>10758.7</v>
       </c>
       <c r="D58" t="n">
-        <v>10599.21</v>
+        <v>10390.73</v>
       </c>
       <c r="E58" t="n">
-        <v>10606</v>
+        <v>10428.27</v>
       </c>
       <c r="F58" t="n">
-        <v>-89.3</v>
+        <v>-267.03</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.025</v>
       </c>
       <c r="H58" t="n">
-        <v>159.49</v>
+        <v>367.97</v>
       </c>
       <c r="I58" t="n">
         <v>10538.7</v>
@@ -5339,18 +5339,22 @@
       <c r="O58" t="n">
         <v>10892.7</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9187.299999999999</v>
+        <v>9208.200000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>9253.5</v>
+        <v>9340.700000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>9107.4</v>
+        <v>9190.6</v>
       </c>
       <c r="E2" t="n">
-        <v>9208.200000000001</v>
+        <v>9283.299999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>20.9</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>146.1</v>
+        <v>150.1</v>
       </c>
       <c r="I2" t="n">
-        <v>9088.4</v>
+        <v>8961.299999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>9077.85</v>
+        <v>9075.98</v>
       </c>
       <c r="K2" t="n">
-        <v>9141.9</v>
+        <v>9135.15</v>
       </c>
       <c r="L2" t="n">
-        <v>9205.950000000001</v>
+        <v>9194.33</v>
       </c>
       <c r="M2" t="n">
-        <v>9232.700000000001</v>
+        <v>9281.25</v>
       </c>
       <c r="N2" t="n">
-        <v>9259.450000000001</v>
+        <v>9368.17</v>
       </c>
       <c r="O2" t="n">
-        <v>9360.799999999999</v>
+        <v>9399.6</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,19 +685,17 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U2" s="8" t="n">
@@ -711,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9208.200000000001</v>
+        <v>9283.299999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>9340.700000000001</v>
+        <v>9314.4</v>
       </c>
       <c r="D3" t="n">
-        <v>9190.6</v>
+        <v>9195.700000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>9283.299999999999</v>
+        <v>9216.700000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>75.09999999999999</v>
+        <v>-66.59999999999999</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0072</v>
       </c>
       <c r="H3" t="n">
-        <v>150.1</v>
+        <v>118.7</v>
       </c>
       <c r="I3" t="n">
-        <v>8961.299999999999</v>
+        <v>9040.5</v>
       </c>
       <c r="J3" t="n">
-        <v>9075.98</v>
+        <v>9142.02</v>
       </c>
       <c r="K3" t="n">
-        <v>9135.15</v>
+        <v>9208.25</v>
       </c>
       <c r="L3" t="n">
-        <v>9194.33</v>
+        <v>9274.469999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>9281.25</v>
+        <v>9358.35</v>
       </c>
       <c r="N3" t="n">
-        <v>9368.17</v>
+        <v>9442.23</v>
       </c>
       <c r="O3" t="n">
-        <v>9399.6</v>
+        <v>9490.799999999999</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -771,19 +765,19 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -795,55 +789,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9283.299999999999</v>
+        <v>9216.700000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>9314.4</v>
+        <v>9292.1</v>
       </c>
       <c r="D4" t="n">
-        <v>9195.700000000001</v>
+        <v>9177.1</v>
       </c>
       <c r="E4" t="n">
-        <v>9216.700000000001</v>
+        <v>9284.799999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-66.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.0074</v>
       </c>
       <c r="H4" t="n">
-        <v>118.7</v>
+        <v>115</v>
       </c>
       <c r="I4" t="n">
-        <v>9040.5</v>
+        <v>9077</v>
       </c>
       <c r="J4" t="n">
-        <v>9142.02</v>
+        <v>9078.82</v>
       </c>
       <c r="K4" t="n">
-        <v>9208.25</v>
+        <v>9157.35</v>
       </c>
       <c r="L4" t="n">
-        <v>9274.469999999999</v>
+        <v>9235.879999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>9358.35</v>
+        <v>9276.049999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>9442.23</v>
+        <v>9316.23</v>
       </c>
       <c r="O4" t="n">
-        <v>9490.799999999999</v>
+        <v>9433.1</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,18 +849,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -884,50 +882,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9216.700000000001</v>
+        <v>9284.799999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>9292.1</v>
+        <v>9494.6</v>
       </c>
       <c r="D5" t="n">
-        <v>9177.1</v>
+        <v>9266.299999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>9284.799999999999</v>
+        <v>9491.299999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>68.09999999999999</v>
+        <v>206.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0222</v>
       </c>
       <c r="H5" t="n">
-        <v>115</v>
+        <v>228.3</v>
       </c>
       <c r="I5" t="n">
-        <v>9077</v>
+        <v>9062.1</v>
       </c>
       <c r="J5" t="n">
-        <v>9078.82</v>
+        <v>9194.9</v>
       </c>
       <c r="K5" t="n">
-        <v>9157.35</v>
+        <v>9227.299999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>9235.879999999999</v>
+        <v>9259.700000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>9276.049999999999</v>
+        <v>9342.299999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>9316.23</v>
+        <v>9424.9</v>
       </c>
       <c r="O5" t="n">
-        <v>9433.1</v>
+        <v>9407.1</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -945,73 +943,73 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9284.799999999999</v>
+        <v>9491.200000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>9494.6</v>
+        <v>9577.1</v>
       </c>
       <c r="D6" t="n">
-        <v>9266.299999999999</v>
+        <v>9414.6</v>
       </c>
       <c r="E6" t="n">
-        <v>9491.299999999999</v>
+        <v>9427.5</v>
       </c>
       <c r="F6" t="n">
-        <v>206.5</v>
+        <v>-63.8</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0067</v>
       </c>
       <c r="H6" t="n">
-        <v>228.3</v>
+        <v>162.5</v>
       </c>
       <c r="I6" t="n">
-        <v>9062.1</v>
+        <v>9038</v>
       </c>
       <c r="J6" t="n">
-        <v>9194.9</v>
+        <v>9318.43</v>
       </c>
       <c r="K6" t="n">
-        <v>9227.299999999999</v>
+        <v>9377.15</v>
       </c>
       <c r="L6" t="n">
-        <v>9259.700000000001</v>
+        <v>9435.870000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>9342.299999999999</v>
+        <v>9605.450000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>9424.9</v>
+        <v>9775.02</v>
       </c>
       <c r="O6" t="n">
-        <v>9407.1</v>
+        <v>9722.9</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1022,80 +1020,78 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9491.200000000001</v>
+        <v>9427.5</v>
       </c>
       <c r="C7" t="n">
-        <v>9577.1</v>
+        <v>9474.299999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>9414.6</v>
+        <v>9276.9</v>
       </c>
       <c r="E7" t="n">
-        <v>9427.5</v>
+        <v>9354.6</v>
       </c>
       <c r="F7" t="n">
-        <v>-63.8</v>
+        <v>-72.90000000000001</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0067</v>
+        <v>-0.0077</v>
       </c>
       <c r="H7" t="n">
-        <v>162.5</v>
+        <v>197.4</v>
       </c>
       <c r="I7" t="n">
-        <v>9038</v>
+        <v>9252.1</v>
       </c>
       <c r="J7" t="n">
-        <v>9318.43</v>
+        <v>9230.83</v>
       </c>
       <c r="K7" t="n">
-        <v>9377.15</v>
+        <v>9346.25</v>
       </c>
       <c r="L7" t="n">
-        <v>9435.870000000001</v>
+        <v>9461.67</v>
       </c>
       <c r="M7" t="n">
-        <v>9605.450000000001</v>
+        <v>9508.75</v>
       </c>
       <c r="N7" t="n">
-        <v>9775.02</v>
+        <v>9555.83</v>
       </c>
       <c r="O7" t="n">
-        <v>9722.9</v>
+        <v>9739.6</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1103,12 +1099,14 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1127,57 +1125,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9427.5</v>
+        <v>9354.5</v>
       </c>
       <c r="C8" t="n">
-        <v>9474.299999999999</v>
+        <v>9645.6</v>
       </c>
       <c r="D8" t="n">
-        <v>9276.9</v>
+        <v>9354.5</v>
       </c>
       <c r="E8" t="n">
-        <v>9354.6</v>
+        <v>9645.6</v>
       </c>
       <c r="F8" t="n">
-        <v>-72.90000000000001</v>
+        <v>291</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0311</v>
       </c>
       <c r="H8" t="n">
-        <v>197.4</v>
+        <v>291.1</v>
       </c>
       <c r="I8" t="n">
-        <v>9252.1</v>
+        <v>9079.5</v>
       </c>
       <c r="J8" t="n">
-        <v>9230.83</v>
+        <v>9146.700000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>9346.25</v>
+        <v>9255.9</v>
       </c>
       <c r="L8" t="n">
-        <v>9461.67</v>
+        <v>9365.1</v>
       </c>
       <c r="M8" t="n">
-        <v>9508.75</v>
+        <v>9453.299999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>9555.83</v>
+        <v>9541.5</v>
       </c>
       <c r="O8" t="n">
-        <v>9739.6</v>
+        <v>9671.700000000001</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1185,83 +1183,83 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
-      </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9354.5</v>
+        <v>9645.6</v>
       </c>
       <c r="C9" t="n">
-        <v>9645.6</v>
+        <v>9787.6</v>
       </c>
       <c r="D9" t="n">
-        <v>9354.5</v>
+        <v>9632.799999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>9645.6</v>
+        <v>9717.299999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>291</v>
+        <v>71.7</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0311</v>
+        <v>0.0074</v>
       </c>
       <c r="H9" t="n">
-        <v>291.1</v>
+        <v>154.8</v>
       </c>
       <c r="I9" t="n">
-        <v>9079.5</v>
+        <v>9063.4</v>
       </c>
       <c r="J9" t="n">
-        <v>9146.700000000001</v>
+        <v>9427.27</v>
       </c>
       <c r="K9" t="n">
-        <v>9255.9</v>
+        <v>9500.049999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>9365.1</v>
+        <v>9572.82</v>
       </c>
       <c r="M9" t="n">
-        <v>9453.299999999999</v>
+        <v>9791.15</v>
       </c>
       <c r="N9" t="n">
-        <v>9541.5</v>
+        <v>10009.47</v>
       </c>
       <c r="O9" t="n">
-        <v>9671.700000000001</v>
+        <v>9936.700000000001</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1279,18 +1277,14 @@
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
@@ -1302,50 +1296,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9645.6</v>
+        <v>9717.299999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>9787.6</v>
+        <v>9786.799999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>9632.799999999999</v>
+        <v>9574.200000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>9717.299999999999</v>
+        <v>9682.6</v>
       </c>
       <c r="F10" t="n">
-        <v>71.7</v>
+        <v>-34.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0036</v>
       </c>
       <c r="H10" t="n">
-        <v>154.8</v>
+        <v>212.6</v>
       </c>
       <c r="I10" t="n">
-        <v>9063.4</v>
+        <v>9478</v>
       </c>
       <c r="J10" t="n">
-        <v>9427.27</v>
+        <v>9566.049999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>9500.049999999999</v>
+        <v>9639.9</v>
       </c>
       <c r="L10" t="n">
-        <v>9572.82</v>
+        <v>9713.75</v>
       </c>
       <c r="M10" t="n">
-        <v>9791.15</v>
+        <v>9794.700000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>10009.47</v>
+        <v>9875.65</v>
       </c>
       <c r="O10" t="n">
-        <v>9936.700000000001</v>
+        <v>9942.4</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1353,18 +1347,18 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1377,55 +1371,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9717.299999999999</v>
+        <v>9682.6</v>
       </c>
       <c r="C11" t="n">
-        <v>9786.799999999999</v>
+        <v>9930.1</v>
       </c>
       <c r="D11" t="n">
-        <v>9574.200000000001</v>
+        <v>9610.5</v>
       </c>
       <c r="E11" t="n">
-        <v>9682.6</v>
+        <v>9698.4</v>
       </c>
       <c r="F11" t="n">
-        <v>-34.7</v>
+        <v>15.8</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0016</v>
       </c>
       <c r="H11" t="n">
-        <v>212.6</v>
+        <v>319.6</v>
       </c>
       <c r="I11" t="n">
-        <v>9478</v>
+        <v>9361.6</v>
       </c>
       <c r="J11" t="n">
-        <v>9566.049999999999</v>
+        <v>9471.049999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>9639.9</v>
+        <v>9576.299999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>9713.75</v>
+        <v>9681.549999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>9794.700000000001</v>
+        <v>9788.9</v>
       </c>
       <c r="N11" t="n">
-        <v>9875.65</v>
+        <v>9896.25</v>
       </c>
       <c r="O11" t="n">
-        <v>9942.4</v>
+        <v>9999.4</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1433,21 +1431,23 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1457,59 +1457,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9682.6</v>
+        <v>9698.4</v>
       </c>
       <c r="C12" t="n">
-        <v>9930.1</v>
+        <v>9707.700000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>9610.5</v>
+        <v>9423.9</v>
       </c>
       <c r="E12" t="n">
-        <v>9698.4</v>
+        <v>9539.700000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>15.8</v>
+        <v>-158.7</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0164</v>
       </c>
       <c r="H12" t="n">
-        <v>319.6</v>
+        <v>283.8</v>
       </c>
       <c r="I12" t="n">
-        <v>9361.6</v>
+        <v>9290.9</v>
       </c>
       <c r="J12" t="n">
-        <v>9471.049999999999</v>
+        <v>9342.85</v>
       </c>
       <c r="K12" t="n">
-        <v>9576.299999999999</v>
+        <v>9538.6</v>
       </c>
       <c r="L12" t="n">
-        <v>9681.549999999999</v>
+        <v>9734.35</v>
       </c>
       <c r="M12" t="n">
-        <v>9788.9</v>
+        <v>9858.200000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>9896.25</v>
+        <v>9982.049999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>9999.4</v>
+        <v>10249.7</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1517,23 +1513,21 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1543,55 +1537,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9698.4</v>
+        <v>9539.700000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>9707.700000000001</v>
+        <v>9740.200000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>9423.9</v>
+        <v>9521.5</v>
       </c>
       <c r="E13" t="n">
-        <v>9539.700000000001</v>
+        <v>9720.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-158.7</v>
+        <v>180.8</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.019</v>
       </c>
       <c r="H13" t="n">
-        <v>283.8</v>
+        <v>218.7</v>
       </c>
       <c r="I13" t="n">
-        <v>9290.9</v>
+        <v>9140.1</v>
       </c>
       <c r="J13" t="n">
-        <v>9342.85</v>
+        <v>9242.85</v>
       </c>
       <c r="K13" t="n">
-        <v>9538.6</v>
+        <v>9397.799999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>9734.35</v>
+        <v>9552.75</v>
       </c>
       <c r="M13" t="n">
-        <v>9858.200000000001</v>
+        <v>9681.6</v>
       </c>
       <c r="N13" t="n">
-        <v>9982.049999999999</v>
+        <v>9810.450000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>10249.7</v>
+        <v>9991.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1599,19 +1597,19 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1623,59 +1621,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9539.700000000001</v>
+        <v>9720.6</v>
       </c>
       <c r="C14" t="n">
-        <v>9740.200000000001</v>
+        <v>9744.799999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>9521.5</v>
+        <v>9667</v>
       </c>
       <c r="E14" t="n">
-        <v>9720.5</v>
+        <v>9667</v>
       </c>
       <c r="F14" t="n">
-        <v>180.8</v>
+        <v>-53.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.019</v>
+        <v>-0.0055</v>
       </c>
       <c r="H14" t="n">
-        <v>218.7</v>
+        <v>77.8</v>
       </c>
       <c r="I14" t="n">
-        <v>9140.1</v>
+        <v>9302.799999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>9242.85</v>
+        <v>9546.620000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>9397.799999999999</v>
+        <v>9611.15</v>
       </c>
       <c r="L14" t="n">
-        <v>9552.75</v>
+        <v>9675.68</v>
       </c>
       <c r="M14" t="n">
-        <v>9681.6</v>
+        <v>9829.85</v>
       </c>
       <c r="N14" t="n">
-        <v>9810.450000000001</v>
+        <v>9984.030000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>9991.5</v>
+        <v>9958.9</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1686,15 +1680,13 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1707,55 +1699,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9720.6</v>
+        <v>9667.1</v>
       </c>
       <c r="C15" t="n">
-        <v>9744.799999999999</v>
+        <v>9761.5</v>
       </c>
       <c r="D15" t="n">
-        <v>9667</v>
+        <v>9622.700000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>9667</v>
+        <v>9649</v>
       </c>
       <c r="F15" t="n">
-        <v>-53.5</v>
+        <v>-18</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0019</v>
       </c>
       <c r="H15" t="n">
-        <v>77.8</v>
+        <v>138.8</v>
       </c>
       <c r="I15" t="n">
-        <v>9302.799999999999</v>
+        <v>9589.200000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>9546.620000000001</v>
+        <v>9569.75</v>
       </c>
       <c r="K15" t="n">
-        <v>9611.15</v>
+        <v>9628.1</v>
       </c>
       <c r="L15" t="n">
-        <v>9675.68</v>
+        <v>9686.450000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>9829.85</v>
+        <v>9705.9</v>
       </c>
       <c r="N15" t="n">
-        <v>9984.030000000001</v>
+        <v>9725.35</v>
       </c>
       <c r="O15" t="n">
-        <v>9958.9</v>
+        <v>9822.6</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1763,19 +1759,25 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1787,57 +1789,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9667.1</v>
+        <v>9649</v>
       </c>
       <c r="C16" t="n">
-        <v>9761.5</v>
+        <v>9903.1</v>
       </c>
       <c r="D16" t="n">
-        <v>9622.700000000001</v>
+        <v>9649</v>
       </c>
       <c r="E16" t="n">
-        <v>9649</v>
+        <v>9897.4</v>
       </c>
       <c r="F16" t="n">
-        <v>-18</v>
+        <v>248.4</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0257</v>
       </c>
       <c r="H16" t="n">
-        <v>138.8</v>
+        <v>254.1</v>
       </c>
       <c r="I16" t="n">
-        <v>9589.200000000001</v>
+        <v>9483.9</v>
       </c>
       <c r="J16" t="n">
-        <v>9569.75</v>
+        <v>9488.65</v>
       </c>
       <c r="K16" t="n">
-        <v>9628.1</v>
+        <v>9579.6</v>
       </c>
       <c r="L16" t="n">
-        <v>9686.450000000001</v>
+        <v>9670.549999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>9705.9</v>
+        <v>9718.4</v>
       </c>
       <c r="N16" t="n">
-        <v>9725.35</v>
+        <v>9766.25</v>
       </c>
       <c r="O16" t="n">
-        <v>9822.6</v>
+        <v>9900.299999999999</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1845,87 +1847,83 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
-      </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9649</v>
+        <v>9897.4</v>
       </c>
       <c r="C17" t="n">
-        <v>9903.1</v>
+        <v>9901.5</v>
       </c>
       <c r="D17" t="n">
-        <v>9649</v>
+        <v>9829.4</v>
       </c>
       <c r="E17" t="n">
-        <v>9897.4</v>
+        <v>9870.700000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>248.4</v>
+        <v>-26.7</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0257</v>
+        <v>-0.0027</v>
       </c>
       <c r="H17" t="n">
-        <v>254.1</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>9483.9</v>
+        <v>9394.9</v>
       </c>
       <c r="J17" t="n">
-        <v>9488.65</v>
+        <v>9703.98</v>
       </c>
       <c r="K17" t="n">
-        <v>9579.6</v>
+        <v>9770.35</v>
       </c>
       <c r="L17" t="n">
-        <v>9670.549999999999</v>
+        <v>9836.73</v>
       </c>
       <c r="M17" t="n">
-        <v>9718.4</v>
+        <v>10024.45</v>
       </c>
       <c r="N17" t="n">
-        <v>9766.25</v>
+        <v>10212.18</v>
       </c>
       <c r="O17" t="n">
-        <v>9900.299999999999</v>
+        <v>10157.2</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1938,78 +1936,76 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9897.4</v>
+        <v>9870.700000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>9901.5</v>
+        <v>10046.3</v>
       </c>
       <c r="D18" t="n">
-        <v>9829.4</v>
+        <v>9858.5</v>
       </c>
       <c r="E18" t="n">
-        <v>9870.700000000001</v>
+        <v>9951.1</v>
       </c>
       <c r="F18" t="n">
-        <v>-26.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0081</v>
       </c>
       <c r="H18" t="n">
-        <v>72.09999999999999</v>
+        <v>187.8</v>
       </c>
       <c r="I18" t="n">
-        <v>9394.9</v>
+        <v>9757.299999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>9703.98</v>
+        <v>9801.23</v>
       </c>
       <c r="K18" t="n">
-        <v>9770.35</v>
+        <v>9834.65</v>
       </c>
       <c r="L18" t="n">
-        <v>9836.73</v>
+        <v>9868.08</v>
       </c>
       <c r="M18" t="n">
-        <v>10024.45</v>
+        <v>9906.75</v>
       </c>
       <c r="N18" t="n">
-        <v>10212.18</v>
+        <v>9945.42</v>
       </c>
       <c r="O18" t="n">
-        <v>10157.2</v>
+        <v>9973.6</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2022,76 +2018,78 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9870.700000000001</v>
+        <v>9951.5</v>
       </c>
       <c r="C19" t="n">
-        <v>10046.3</v>
+        <v>10158.4</v>
       </c>
       <c r="D19" t="n">
-        <v>9858.5</v>
+        <v>9951.5</v>
       </c>
       <c r="E19" t="n">
-        <v>9951.1</v>
+        <v>10124.6</v>
       </c>
       <c r="F19" t="n">
-        <v>80.40000000000001</v>
+        <v>173.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0081</v>
+        <v>0.0174</v>
       </c>
       <c r="H19" t="n">
-        <v>187.8</v>
+        <v>206.9</v>
       </c>
       <c r="I19" t="n">
-        <v>9757.299999999999</v>
+        <v>9670.700000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>9801.23</v>
+        <v>9762.65</v>
       </c>
       <c r="K19" t="n">
-        <v>9834.65</v>
+        <v>9857.200000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>9868.08</v>
+        <v>9951.75</v>
       </c>
       <c r="M19" t="n">
-        <v>9906.75</v>
+        <v>10045</v>
       </c>
       <c r="N19" t="n">
-        <v>9945.42</v>
+        <v>10138.25</v>
       </c>
       <c r="O19" t="n">
-        <v>9973.6</v>
+        <v>10234.1</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2117,10 +2115,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2132,50 +2128,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9951.5</v>
+        <v>10124.5</v>
       </c>
       <c r="C20" t="n">
-        <v>10158.4</v>
+        <v>10257.8</v>
       </c>
       <c r="D20" t="n">
-        <v>9951.5</v>
+        <v>10089.9</v>
       </c>
       <c r="E20" t="n">
-        <v>10124.6</v>
+        <v>10235.3</v>
       </c>
       <c r="F20" t="n">
-        <v>173.5</v>
+        <v>110.7</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0174</v>
+        <v>0.0109</v>
       </c>
       <c r="H20" t="n">
-        <v>206.9</v>
+        <v>167.9</v>
       </c>
       <c r="I20" t="n">
-        <v>9670.700000000001</v>
+        <v>9744.6</v>
       </c>
       <c r="J20" t="n">
-        <v>9762.65</v>
+        <v>9952.52</v>
       </c>
       <c r="K20" t="n">
-        <v>9857.200000000001</v>
+        <v>10021.15</v>
       </c>
       <c r="L20" t="n">
-        <v>9951.75</v>
+        <v>10089.77</v>
       </c>
       <c r="M20" t="n">
-        <v>10045</v>
+        <v>10228.05</v>
       </c>
       <c r="N20" t="n">
-        <v>10138.25</v>
+        <v>10366.32</v>
       </c>
       <c r="O20" t="n">
-        <v>10234.1</v>
+        <v>10365.3</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2193,13 +2189,11 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2214,70 +2208,72 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10124.5</v>
+        <v>10235.3</v>
       </c>
       <c r="C21" t="n">
-        <v>10257.8</v>
+        <v>10235.3</v>
       </c>
       <c r="D21" t="n">
-        <v>10089.9</v>
+        <v>10050.2</v>
       </c>
       <c r="E21" t="n">
-        <v>10235.3</v>
+        <v>10143.4</v>
       </c>
       <c r="F21" t="n">
-        <v>110.7</v>
+        <v>-91.90000000000001</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>167.9</v>
+        <v>185.1</v>
       </c>
       <c r="I21" t="n">
-        <v>9744.6</v>
+        <v>9922</v>
       </c>
       <c r="J21" t="n">
-        <v>9952.52</v>
+        <v>10098.13</v>
       </c>
       <c r="K21" t="n">
-        <v>10021.15</v>
+        <v>10151.35</v>
       </c>
       <c r="L21" t="n">
-        <v>10089.77</v>
+        <v>10204.57</v>
       </c>
       <c r="M21" t="n">
-        <v>10228.05</v>
+        <v>10319.25</v>
       </c>
       <c r="N21" t="n">
-        <v>10366.32</v>
+        <v>10433.92</v>
       </c>
       <c r="O21" t="n">
-        <v>10365.3</v>
+        <v>10425.7</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2289,77 +2285,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10235.3</v>
+        <v>10143.1</v>
       </c>
       <c r="C22" t="n">
-        <v>10235.3</v>
+        <v>10277.7</v>
       </c>
       <c r="D22" t="n">
-        <v>10050.2</v>
+        <v>10125.3</v>
       </c>
       <c r="E22" t="n">
-        <v>10143.4</v>
+        <v>10223.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-91.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>185.1</v>
+        <v>152.4</v>
       </c>
       <c r="I22" t="n">
-        <v>9922</v>
+        <v>9865.1</v>
       </c>
       <c r="J22" t="n">
-        <v>10098.13</v>
+        <v>9958.629999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>10151.35</v>
+        <v>10050.85</v>
       </c>
       <c r="L22" t="n">
-        <v>10204.57</v>
+        <v>10143.08</v>
       </c>
       <c r="M22" t="n">
-        <v>10319.25</v>
+        <v>10235.95</v>
       </c>
       <c r="N22" t="n">
-        <v>10433.92</v>
+        <v>10328.83</v>
       </c>
       <c r="O22" t="n">
-        <v>10425.7</v>
+        <v>10420.4</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2371,59 +2369,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10143.1</v>
+        <v>10223.7</v>
       </c>
       <c r="C23" t="n">
-        <v>10277.7</v>
+        <v>10481.5</v>
       </c>
       <c r="D23" t="n">
-        <v>10125.3</v>
+        <v>10145.4</v>
       </c>
       <c r="E23" t="n">
-        <v>10223.5</v>
+        <v>10369.8</v>
       </c>
       <c r="F23" t="n">
-        <v>80.09999999999999</v>
+        <v>146.3</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0143</v>
       </c>
       <c r="H23" t="n">
-        <v>152.4</v>
+        <v>336.1</v>
       </c>
       <c r="I23" t="n">
-        <v>9865.1</v>
+        <v>9972.9</v>
       </c>
       <c r="J23" t="n">
-        <v>9958.629999999999</v>
+        <v>10082.1</v>
       </c>
       <c r="K23" t="n">
-        <v>10050.85</v>
+        <v>10147.3</v>
       </c>
       <c r="L23" t="n">
-        <v>10143.08</v>
+        <v>10212.5</v>
       </c>
       <c r="M23" t="n">
-        <v>10235.95</v>
+        <v>10299.7</v>
       </c>
       <c r="N23" t="n">
-        <v>10328.83</v>
+        <v>10386.9</v>
       </c>
       <c r="O23" t="n">
-        <v>10420.4</v>
+        <v>10430.1</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2431,8 +2425,10 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
@@ -2441,14 +2437,18 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
@@ -2460,50 +2460,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10223.7</v>
+        <v>10369.8</v>
       </c>
       <c r="C24" t="n">
-        <v>10481.5</v>
+        <v>10535.8</v>
       </c>
       <c r="D24" t="n">
-        <v>10145.4</v>
+        <v>10316</v>
       </c>
       <c r="E24" t="n">
-        <v>10369.8</v>
+        <v>10446.4</v>
       </c>
       <c r="F24" t="n">
-        <v>146.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0074</v>
       </c>
       <c r="H24" t="n">
-        <v>336.1</v>
+        <v>219.8</v>
       </c>
       <c r="I24" t="n">
-        <v>9972.9</v>
+        <v>9809.299999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>10082.1</v>
+        <v>10061.88</v>
       </c>
       <c r="K24" t="n">
-        <v>10147.3</v>
+        <v>10201.75</v>
       </c>
       <c r="L24" t="n">
-        <v>10212.5</v>
+        <v>10341.62</v>
       </c>
       <c r="M24" t="n">
-        <v>10299.7</v>
+        <v>10537.85</v>
       </c>
       <c r="N24" t="n">
-        <v>10386.9</v>
+        <v>10734.07</v>
       </c>
       <c r="O24" t="n">
-        <v>10430.1</v>
+        <v>10817.6</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2511,10 +2511,8 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
@@ -2523,18 +2521,14 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
@@ -2546,50 +2540,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10369.8</v>
+        <v>10446.3</v>
       </c>
       <c r="C25" t="n">
-        <v>10535.8</v>
+        <v>10745.8</v>
       </c>
       <c r="D25" t="n">
-        <v>10316</v>
+        <v>10446.3</v>
       </c>
       <c r="E25" t="n">
-        <v>10446.4</v>
+        <v>10686.9</v>
       </c>
       <c r="F25" t="n">
-        <v>76.59999999999999</v>
+        <v>240.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.023</v>
       </c>
       <c r="H25" t="n">
-        <v>219.8</v>
+        <v>299.5</v>
       </c>
       <c r="I25" t="n">
-        <v>9809.299999999999</v>
+        <v>10096.2</v>
       </c>
       <c r="J25" t="n">
-        <v>10061.88</v>
+        <v>10236.85</v>
       </c>
       <c r="K25" t="n">
-        <v>10201.75</v>
+        <v>10336.5</v>
       </c>
       <c r="L25" t="n">
-        <v>10341.62</v>
+        <v>10436.15</v>
       </c>
       <c r="M25" t="n">
-        <v>10537.85</v>
+        <v>10556.3</v>
       </c>
       <c r="N25" t="n">
-        <v>10734.07</v>
+        <v>10676.45</v>
       </c>
       <c r="O25" t="n">
-        <v>10817.6</v>
+        <v>10755.6</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2607,11 +2601,13 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2626,50 +2622,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10446.3</v>
+        <v>10686.8</v>
       </c>
       <c r="C26" t="n">
-        <v>10745.8</v>
+        <v>10934.9</v>
       </c>
       <c r="D26" t="n">
-        <v>10446.3</v>
+        <v>10645.8</v>
       </c>
       <c r="E26" t="n">
-        <v>10686.9</v>
+        <v>10910.6</v>
       </c>
       <c r="F26" t="n">
-        <v>240.5</v>
+        <v>223.7</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0209</v>
       </c>
       <c r="H26" t="n">
-        <v>299.5</v>
+        <v>289.1</v>
       </c>
       <c r="I26" t="n">
-        <v>10096.2</v>
+        <v>10146.8</v>
       </c>
       <c r="J26" t="n">
-        <v>10236.85</v>
+        <v>10432.83</v>
       </c>
       <c r="K26" t="n">
-        <v>10336.5</v>
+        <v>10537.15</v>
       </c>
       <c r="L26" t="n">
-        <v>10436.15</v>
+        <v>10641.48</v>
       </c>
       <c r="M26" t="n">
-        <v>10556.3</v>
+        <v>10836.65</v>
       </c>
       <c r="N26" t="n">
-        <v>10676.45</v>
+        <v>11031.83</v>
       </c>
       <c r="O26" t="n">
-        <v>10755.6</v>
+        <v>11045.3</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2687,13 +2683,11 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2708,79 +2702,83 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10686.8</v>
+        <v>10911</v>
       </c>
       <c r="C27" t="n">
-        <v>10934.9</v>
+        <v>10911</v>
       </c>
       <c r="D27" t="n">
-        <v>10645.8</v>
+        <v>10234.5</v>
       </c>
       <c r="E27" t="n">
-        <v>10910.6</v>
+        <v>10284.8</v>
       </c>
       <c r="F27" t="n">
-        <v>223.7</v>
+        <v>-625.8</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0574</v>
       </c>
       <c r="H27" t="n">
-        <v>289.1</v>
+        <v>676.5</v>
       </c>
       <c r="I27" t="n">
-        <v>10146.8</v>
+        <v>10356.7</v>
       </c>
       <c r="J27" t="n">
-        <v>10432.83</v>
+        <v>10681.62</v>
       </c>
       <c r="K27" t="n">
-        <v>10537.15</v>
+        <v>10766.05</v>
       </c>
       <c r="L27" t="n">
-        <v>10641.48</v>
+        <v>10850.47</v>
       </c>
       <c r="M27" t="n">
-        <v>10836.65</v>
+        <v>11055.15</v>
       </c>
       <c r="N27" t="n">
-        <v>11031.83</v>
+        <v>11259.82</v>
       </c>
       <c r="O27" t="n">
-        <v>11045.3</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+        <v>11224</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -2788,69 +2786,63 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10911</v>
+        <v>10285</v>
       </c>
       <c r="C28" t="n">
-        <v>10911</v>
+        <v>10447.5</v>
       </c>
       <c r="D28" t="n">
-        <v>10234.5</v>
+        <v>10082</v>
       </c>
       <c r="E28" t="n">
-        <v>10284.8</v>
+        <v>10261.2</v>
       </c>
       <c r="F28" t="n">
-        <v>-625.8</v>
+        <v>-23.6</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0574</v>
+        <v>-0.0023</v>
       </c>
       <c r="H28" t="n">
-        <v>676.5</v>
+        <v>365.5</v>
       </c>
       <c r="I28" t="n">
-        <v>10356.7</v>
+        <v>9558</v>
       </c>
       <c r="J28" t="n">
-        <v>10681.62</v>
+        <v>9464.32</v>
       </c>
       <c r="K28" t="n">
-        <v>10766.05</v>
+        <v>9946.549999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>10850.47</v>
+        <v>10428.77</v>
       </c>
       <c r="M28" t="n">
-        <v>11055.15</v>
+        <v>10623.05</v>
       </c>
       <c r="N28" t="n">
-        <v>11259.82</v>
+        <v>10817.32</v>
       </c>
       <c r="O28" t="n">
-        <v>11224</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>11587.5</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2872,67 +2864,73 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10285</v>
+        <v>10261.1</v>
       </c>
       <c r="C29" t="n">
-        <v>10447.5</v>
+        <v>10447.7</v>
       </c>
       <c r="D29" t="n">
-        <v>10082</v>
+        <v>9915.700000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>10261.2</v>
+        <v>9918.299999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>-23.6</v>
+        <v>-342.9</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0334</v>
       </c>
       <c r="H29" t="n">
-        <v>365.5</v>
+        <v>532</v>
       </c>
       <c r="I29" t="n">
-        <v>9558</v>
+        <v>9716.5</v>
       </c>
       <c r="J29" t="n">
-        <v>9464.32</v>
+        <v>9893.93</v>
       </c>
       <c r="K29" t="n">
-        <v>9946.549999999999</v>
+        <v>10078.45</v>
       </c>
       <c r="L29" t="n">
-        <v>10428.77</v>
+        <v>10262.98</v>
       </c>
       <c r="M29" t="n">
-        <v>10623.05</v>
+        <v>10443.95</v>
       </c>
       <c r="N29" t="n">
-        <v>10817.32</v>
+        <v>10624.93</v>
       </c>
       <c r="O29" t="n">
-        <v>11587.5</v>
+        <v>10813</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2945,78 +2943,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10261.1</v>
+        <v>9918.5</v>
       </c>
       <c r="C30" t="n">
-        <v>10447.7</v>
+        <v>10118.2</v>
       </c>
       <c r="D30" t="n">
-        <v>9915.700000000001</v>
+        <v>9670.5</v>
       </c>
       <c r="E30" t="n">
-        <v>9918.299999999999</v>
+        <v>9967.4</v>
       </c>
       <c r="F30" t="n">
-        <v>-342.9</v>
+        <v>49.1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0334</v>
+        <v>0.005</v>
       </c>
       <c r="H30" t="n">
-        <v>532</v>
+        <v>447.7</v>
       </c>
       <c r="I30" t="n">
-        <v>9716.5</v>
+        <v>9383.700000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>9893.93</v>
+        <v>9254.6</v>
       </c>
       <c r="K30" t="n">
-        <v>10078.45</v>
+        <v>9652.299999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>10262.98</v>
+        <v>10050</v>
       </c>
       <c r="M30" t="n">
-        <v>10443.95</v>
+        <v>10184.3</v>
       </c>
       <c r="N30" t="n">
-        <v>10624.93</v>
+        <v>10318.6</v>
       </c>
       <c r="O30" t="n">
-        <v>10813</v>
+        <v>10979.7</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3038,50 +3034,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9918.5</v>
+        <v>9967.5</v>
       </c>
       <c r="C31" t="n">
-        <v>10118.2</v>
+        <v>10465.2</v>
       </c>
       <c r="D31" t="n">
-        <v>9670.5</v>
+        <v>9958.1</v>
       </c>
       <c r="E31" t="n">
-        <v>9967.4</v>
+        <v>10436.3</v>
       </c>
       <c r="F31" t="n">
-        <v>49.1</v>
+        <v>468.9</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.005</v>
+        <v>0.047</v>
       </c>
       <c r="H31" t="n">
-        <v>447.7</v>
+        <v>507.1</v>
       </c>
       <c r="I31" t="n">
-        <v>9383.700000000001</v>
+        <v>9222.799999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>9254.6</v>
+        <v>9556.23</v>
       </c>
       <c r="K31" t="n">
-        <v>9652.299999999999</v>
+        <v>9743.549999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>10050</v>
+        <v>9930.879999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>10184.3</v>
+        <v>10191.25</v>
       </c>
       <c r="N31" t="n">
-        <v>10318.6</v>
+        <v>10451.63</v>
       </c>
       <c r="O31" t="n">
-        <v>10979.7</v>
+        <v>10565.9</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3092,16 +3088,20 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3113,57 +3113,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9967.5</v>
+        <v>10436.2</v>
       </c>
       <c r="C32" t="n">
-        <v>10465.2</v>
+        <v>10687.9</v>
       </c>
       <c r="D32" t="n">
-        <v>9958.1</v>
+        <v>10330.9</v>
       </c>
       <c r="E32" t="n">
-        <v>10436.3</v>
+        <v>10600.5</v>
       </c>
       <c r="F32" t="n">
-        <v>468.9</v>
+        <v>164.2</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.047</v>
+        <v>0.0157</v>
       </c>
       <c r="H32" t="n">
-        <v>507.1</v>
+        <v>357</v>
       </c>
       <c r="I32" t="n">
-        <v>9222.799999999999</v>
+        <v>9451</v>
       </c>
       <c r="J32" t="n">
-        <v>9556.23</v>
+        <v>10041.52</v>
       </c>
       <c r="K32" t="n">
-        <v>9743.549999999999</v>
+        <v>10182.75</v>
       </c>
       <c r="L32" t="n">
-        <v>9930.879999999999</v>
+        <v>10323.97</v>
       </c>
       <c r="M32" t="n">
-        <v>10191.25</v>
+        <v>10689.85</v>
       </c>
       <c r="N32" t="n">
-        <v>10451.63</v>
+        <v>11055.73</v>
       </c>
       <c r="O32" t="n">
-        <v>10565.9</v>
+        <v>10972.3</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3181,13 +3181,11 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3206,50 +3204,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10436.2</v>
+        <v>10601.5</v>
       </c>
       <c r="C33" t="n">
-        <v>10687.9</v>
+        <v>10667.6</v>
       </c>
       <c r="D33" t="n">
-        <v>10330.9</v>
+        <v>10528.6</v>
       </c>
       <c r="E33" t="n">
-        <v>10600.5</v>
+        <v>10667.6</v>
       </c>
       <c r="F33" t="n">
-        <v>164.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0063</v>
       </c>
       <c r="H33" t="n">
-        <v>357</v>
+        <v>139</v>
       </c>
       <c r="I33" t="n">
-        <v>9451</v>
+        <v>9973.9</v>
       </c>
       <c r="J33" t="n">
-        <v>10041.52</v>
+        <v>10289.05</v>
       </c>
       <c r="K33" t="n">
-        <v>10182.75</v>
+        <v>10422</v>
       </c>
       <c r="L33" t="n">
-        <v>10323.97</v>
+        <v>10554.95</v>
       </c>
       <c r="M33" t="n">
-        <v>10689.85</v>
+        <v>10779</v>
       </c>
       <c r="N33" t="n">
-        <v>11055.73</v>
+        <v>11003.05</v>
       </c>
       <c r="O33" t="n">
-        <v>10972.3</v>
+        <v>11044.9</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3283,77 +3281,81 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10601.5</v>
+        <v>10668.4</v>
       </c>
       <c r="C34" t="n">
-        <v>10667.6</v>
+        <v>10683.7</v>
       </c>
       <c r="D34" t="n">
-        <v>10528.6</v>
+        <v>10361.5</v>
       </c>
       <c r="E34" t="n">
-        <v>10667.6</v>
+        <v>10379.1</v>
       </c>
       <c r="F34" t="n">
-        <v>67.09999999999999</v>
+        <v>-288.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0063</v>
+        <v>-0.027</v>
       </c>
       <c r="H34" t="n">
-        <v>139</v>
+        <v>322.2</v>
       </c>
       <c r="I34" t="n">
-        <v>9973.9</v>
+        <v>10389.6</v>
       </c>
       <c r="J34" t="n">
-        <v>10289.05</v>
+        <v>10563.35</v>
       </c>
       <c r="K34" t="n">
-        <v>10422</v>
+        <v>10598.1</v>
       </c>
       <c r="L34" t="n">
-        <v>10554.95</v>
+        <v>10632.85</v>
       </c>
       <c r="M34" t="n">
-        <v>10779</v>
+        <v>10737.1</v>
       </c>
       <c r="N34" t="n">
-        <v>11003.05</v>
+        <v>10841.35</v>
       </c>
       <c r="O34" t="n">
-        <v>11044.9</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+        <v>10806.6</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3367,76 +3369,72 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10668.4</v>
+        <v>10378.5</v>
       </c>
       <c r="C35" t="n">
-        <v>10683.7</v>
+        <v>10410.8</v>
       </c>
       <c r="D35" t="n">
-        <v>10361.5</v>
+        <v>10188.7</v>
       </c>
       <c r="E35" t="n">
-        <v>10379.1</v>
+        <v>10363.9</v>
       </c>
       <c r="F35" t="n">
-        <v>-288.5</v>
+        <v>-15.2</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.0015</v>
       </c>
       <c r="H35" t="n">
-        <v>322.2</v>
+        <v>222.1</v>
       </c>
       <c r="I35" t="n">
-        <v>10389.6</v>
+        <v>10039.3</v>
       </c>
       <c r="J35" t="n">
-        <v>10563.35</v>
+        <v>9985.15</v>
       </c>
       <c r="K35" t="n">
-        <v>10598.1</v>
+        <v>10218</v>
       </c>
       <c r="L35" t="n">
-        <v>10632.85</v>
+        <v>10450.85</v>
       </c>
       <c r="M35" t="n">
-        <v>10737.1</v>
+        <v>10540.2</v>
       </c>
       <c r="N35" t="n">
-        <v>10841.35</v>
+        <v>10629.55</v>
       </c>
       <c r="O35" t="n">
-        <v>10806.6</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
+        <v>11005.9</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3453,79 +3451,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10378.5</v>
+        <v>10365.4</v>
       </c>
       <c r="C36" t="n">
-        <v>10410.8</v>
+        <v>10488.2</v>
       </c>
       <c r="D36" t="n">
-        <v>10188.7</v>
+        <v>10164.3</v>
       </c>
       <c r="E36" t="n">
-        <v>10363.9</v>
+        <v>10233.1</v>
       </c>
       <c r="F36" t="n">
-        <v>-15.2</v>
+        <v>-130.8</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0126</v>
       </c>
       <c r="H36" t="n">
-        <v>222.1</v>
+        <v>323.9</v>
       </c>
       <c r="I36" t="n">
-        <v>10039.3</v>
+        <v>9966.6</v>
       </c>
       <c r="J36" t="n">
-        <v>9985.15</v>
+        <v>10173.88</v>
       </c>
       <c r="K36" t="n">
-        <v>10218</v>
+        <v>10252.85</v>
       </c>
       <c r="L36" t="n">
-        <v>10450.85</v>
+        <v>10331.83</v>
       </c>
       <c r="M36" t="n">
-        <v>10540.2</v>
+        <v>10474.95</v>
       </c>
       <c r="N36" t="n">
-        <v>10629.55</v>
+        <v>10618.08</v>
       </c>
       <c r="O36" t="n">
-        <v>11005.9</v>
+        <v>10632.9</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3537,78 +3535,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10365.4</v>
+        <v>10233.6</v>
       </c>
       <c r="C37" t="n">
-        <v>10488.2</v>
+        <v>10375.7</v>
       </c>
       <c r="D37" t="n">
-        <v>10164.3</v>
+        <v>10152.1</v>
       </c>
       <c r="E37" t="n">
-        <v>10233.1</v>
+        <v>10195.4</v>
       </c>
       <c r="F37" t="n">
-        <v>-130.8</v>
+        <v>-37.7</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0037</v>
       </c>
       <c r="H37" t="n">
-        <v>323.9</v>
+        <v>223.6</v>
       </c>
       <c r="I37" t="n">
-        <v>9966.6</v>
+        <v>9840.4</v>
       </c>
       <c r="J37" t="n">
-        <v>10173.88</v>
+        <v>9862.620000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>10252.85</v>
+        <v>10071.15</v>
       </c>
       <c r="L37" t="n">
-        <v>10331.83</v>
+        <v>10279.67</v>
       </c>
       <c r="M37" t="n">
-        <v>10474.95</v>
+        <v>10395.05</v>
       </c>
       <c r="N37" t="n">
-        <v>10618.08</v>
+        <v>10510.42</v>
       </c>
       <c r="O37" t="n">
-        <v>10632.9</v>
+        <v>10812.1</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3621,59 +3617,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10233.6</v>
+        <v>10194.8</v>
       </c>
       <c r="C38" t="n">
-        <v>10375.7</v>
+        <v>10497.2</v>
       </c>
       <c r="D38" t="n">
-        <v>10152.1</v>
+        <v>10151.5</v>
       </c>
       <c r="E38" t="n">
-        <v>10195.4</v>
+        <v>10466.3</v>
       </c>
       <c r="F38" t="n">
-        <v>-37.7</v>
+        <v>270.9</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0266</v>
       </c>
       <c r="H38" t="n">
-        <v>223.6</v>
+        <v>345.7</v>
       </c>
       <c r="I38" t="n">
-        <v>9840.4</v>
+        <v>9928.5</v>
       </c>
       <c r="J38" t="n">
-        <v>9862.620000000001</v>
+        <v>9937.549999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>10071.15</v>
+        <v>10083.6</v>
       </c>
       <c r="L38" t="n">
-        <v>10279.67</v>
+        <v>10229.65</v>
       </c>
       <c r="M38" t="n">
-        <v>10395.05</v>
+        <v>10307.2</v>
       </c>
       <c r="N38" t="n">
-        <v>10510.42</v>
+        <v>10384.75</v>
       </c>
       <c r="O38" t="n">
-        <v>10812.1</v>
+        <v>10599.3</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3684,74 +3676,82 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="W38" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10194.8</v>
+        <v>10465.6</v>
       </c>
       <c r="C39" t="n">
-        <v>10497.2</v>
+        <v>10557.2</v>
       </c>
       <c r="D39" t="n">
-        <v>10151.5</v>
+        <v>10381.2</v>
       </c>
       <c r="E39" t="n">
-        <v>10466.3</v>
+        <v>10409.3</v>
       </c>
       <c r="F39" t="n">
-        <v>270.9</v>
+        <v>-57</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0266</v>
+        <v>-0.0054</v>
       </c>
       <c r="H39" t="n">
-        <v>345.7</v>
+        <v>176</v>
       </c>
       <c r="I39" t="n">
-        <v>9928.5</v>
+        <v>9805.799999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>9937.549999999999</v>
+        <v>10191.57</v>
       </c>
       <c r="K39" t="n">
-        <v>10083.6</v>
+        <v>10293.45</v>
       </c>
       <c r="L39" t="n">
-        <v>10229.65</v>
+        <v>10395.32</v>
       </c>
       <c r="M39" t="n">
-        <v>10307.2</v>
+        <v>10639.15</v>
       </c>
       <c r="N39" t="n">
-        <v>10384.75</v>
+        <v>10882.97</v>
       </c>
       <c r="O39" t="n">
-        <v>10599.3</v>
+        <v>10842.9</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3764,18 +3764,14 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3794,50 +3790,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10465.6</v>
+        <v>10409.3</v>
       </c>
       <c r="C40" t="n">
-        <v>10557.2</v>
+        <v>10415.7</v>
       </c>
       <c r="D40" t="n">
-        <v>10381.2</v>
+        <v>10238.6</v>
       </c>
       <c r="E40" t="n">
-        <v>10409.3</v>
+        <v>10368.1</v>
       </c>
       <c r="F40" t="n">
-        <v>-57</v>
+        <v>-41.2</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.004</v>
       </c>
       <c r="H40" t="n">
-        <v>176</v>
+        <v>177.1</v>
       </c>
       <c r="I40" t="n">
-        <v>9805.799999999999</v>
+        <v>10205.2</v>
       </c>
       <c r="J40" t="n">
-        <v>10191.57</v>
+        <v>10203.35</v>
       </c>
       <c r="K40" t="n">
-        <v>10293.45</v>
+        <v>10321.3</v>
       </c>
       <c r="L40" t="n">
-        <v>10395.32</v>
+        <v>10439.25</v>
       </c>
       <c r="M40" t="n">
-        <v>10639.15</v>
+        <v>10497.3</v>
       </c>
       <c r="N40" t="n">
-        <v>10882.97</v>
+        <v>10555.35</v>
       </c>
       <c r="O40" t="n">
-        <v>10842.9</v>
+        <v>10733.2</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3845,12 +3841,14 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3869,77 +3867,81 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10409.3</v>
+        <v>10369.1</v>
       </c>
       <c r="C41" t="n">
-        <v>10415.7</v>
+        <v>10471.7</v>
       </c>
       <c r="D41" t="n">
-        <v>10238.6</v>
+        <v>10127.6</v>
       </c>
       <c r="E41" t="n">
-        <v>10368.1</v>
+        <v>10471.7</v>
       </c>
       <c r="F41" t="n">
-        <v>-41.2</v>
+        <v>103.6</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.01</v>
       </c>
       <c r="H41" t="n">
-        <v>177.1</v>
+        <v>344.1</v>
       </c>
       <c r="I41" t="n">
-        <v>10205.2</v>
+        <v>10061.5</v>
       </c>
       <c r="J41" t="n">
-        <v>10203.35</v>
+        <v>10211.47</v>
       </c>
       <c r="K41" t="n">
-        <v>10321.3</v>
+        <v>10279.55</v>
       </c>
       <c r="L41" t="n">
-        <v>10439.25</v>
+        <v>10347.62</v>
       </c>
       <c r="M41" t="n">
-        <v>10497.3</v>
+        <v>10456.65</v>
       </c>
       <c r="N41" t="n">
-        <v>10555.35</v>
+        <v>10565.68</v>
       </c>
       <c r="O41" t="n">
-        <v>10733.2</v>
+        <v>10592.8</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3953,80 +3955,74 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10369.1</v>
+        <v>10471.4</v>
       </c>
       <c r="C42" t="n">
-        <v>10471.7</v>
+        <v>10570.1</v>
       </c>
       <c r="D42" t="n">
-        <v>10127.6</v>
+        <v>10352.9</v>
       </c>
       <c r="E42" t="n">
-        <v>10471.7</v>
+        <v>10363.3</v>
       </c>
       <c r="F42" t="n">
-        <v>103.6</v>
+        <v>-108.4</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0104</v>
       </c>
       <c r="H42" t="n">
-        <v>344.1</v>
+        <v>217.2</v>
       </c>
       <c r="I42" t="n">
-        <v>10061.5</v>
+        <v>9783.5</v>
       </c>
       <c r="J42" t="n">
-        <v>10211.47</v>
+        <v>10213.62</v>
       </c>
       <c r="K42" t="n">
-        <v>10279.55</v>
+        <v>10299.65</v>
       </c>
       <c r="L42" t="n">
-        <v>10347.62</v>
+        <v>10385.68</v>
       </c>
       <c r="M42" t="n">
-        <v>10456.65</v>
+        <v>10643.75</v>
       </c>
       <c r="N42" t="n">
-        <v>10565.68</v>
+        <v>10901.83</v>
       </c>
       <c r="O42" t="n">
-        <v>10592.8</v>
+        <v>10815.8</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4048,50 +4044,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10471.4</v>
+        <v>10363.6</v>
       </c>
       <c r="C43" t="n">
-        <v>10570.1</v>
+        <v>10575.3</v>
       </c>
       <c r="D43" t="n">
-        <v>10352.9</v>
+        <v>10332.4</v>
       </c>
       <c r="E43" t="n">
-        <v>10363.3</v>
+        <v>10508</v>
       </c>
       <c r="F43" t="n">
-        <v>-108.4</v>
+        <v>144.7</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.014</v>
       </c>
       <c r="H43" t="n">
-        <v>217.2</v>
+        <v>242.9</v>
       </c>
       <c r="I43" t="n">
-        <v>9783.5</v>
+        <v>10135.7</v>
       </c>
       <c r="J43" t="n">
-        <v>10213.62</v>
+        <v>10097</v>
       </c>
       <c r="K43" t="n">
-        <v>10299.65</v>
+        <v>10254.7</v>
       </c>
       <c r="L43" t="n">
-        <v>10385.68</v>
+        <v>10412.4</v>
       </c>
       <c r="M43" t="n">
-        <v>10643.75</v>
+        <v>10471.9</v>
       </c>
       <c r="N43" t="n">
-        <v>10901.83</v>
+        <v>10531.4</v>
       </c>
       <c r="O43" t="n">
-        <v>10815.8</v>
+        <v>10787.3</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4102,16 +4098,20 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4130,50 +4130,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10363.6</v>
+        <v>10507.8</v>
       </c>
       <c r="C44" t="n">
-        <v>10575.3</v>
+        <v>10701.3</v>
       </c>
       <c r="D44" t="n">
-        <v>10332.4</v>
+        <v>10429.2</v>
       </c>
       <c r="E44" t="n">
-        <v>10508</v>
+        <v>10679</v>
       </c>
       <c r="F44" t="n">
-        <v>144.7</v>
+        <v>171</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0163</v>
       </c>
       <c r="H44" t="n">
-        <v>242.9</v>
+        <v>272.1</v>
       </c>
       <c r="I44" t="n">
-        <v>10135.7</v>
+        <v>10089.5</v>
       </c>
       <c r="J44" t="n">
-        <v>10097</v>
+        <v>10292.18</v>
       </c>
       <c r="K44" t="n">
-        <v>10254.7</v>
+        <v>10386.55</v>
       </c>
       <c r="L44" t="n">
-        <v>10412.4</v>
+        <v>10480.93</v>
       </c>
       <c r="M44" t="n">
-        <v>10471.9</v>
+        <v>10629.45</v>
       </c>
       <c r="N44" t="n">
-        <v>10531.4</v>
+        <v>10777.97</v>
       </c>
       <c r="O44" t="n">
-        <v>10787.3</v>
+        <v>10818.2</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4191,14 +4191,12 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4207,79 +4205,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10507.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C45" t="n">
-        <v>10701.3</v>
+        <v>10747</v>
       </c>
       <c r="D45" t="n">
-        <v>10429.2</v>
+        <v>10397.5</v>
       </c>
       <c r="E45" t="n">
-        <v>10679</v>
+        <v>10497.3</v>
       </c>
       <c r="F45" t="n">
-        <v>171</v>
+        <v>-181.7</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.017</v>
       </c>
       <c r="H45" t="n">
-        <v>272.1</v>
+        <v>349.5</v>
       </c>
       <c r="I45" t="n">
-        <v>10089.5</v>
+        <v>10157.1</v>
       </c>
       <c r="J45" t="n">
-        <v>10292.18</v>
+        <v>10463.78</v>
       </c>
       <c r="K45" t="n">
-        <v>10386.55</v>
+        <v>10542.95</v>
       </c>
       <c r="L45" t="n">
-        <v>10480.93</v>
+        <v>10622.12</v>
       </c>
       <c r="M45" t="n">
-        <v>10629.45</v>
+        <v>10815.05</v>
       </c>
       <c r="N45" t="n">
-        <v>10777.97</v>
+        <v>11007.97</v>
       </c>
       <c r="O45" t="n">
-        <v>10818.2</v>
+        <v>10973.4</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
+      <c r="Q45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4291,72 +4287,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10679.4</v>
+        <v>10498.1</v>
       </c>
       <c r="C46" t="n">
-        <v>10747</v>
+        <v>10623.7</v>
       </c>
       <c r="D46" t="n">
-        <v>10397.5</v>
+        <v>10423</v>
       </c>
       <c r="E46" t="n">
-        <v>10497.3</v>
+        <v>10600.4</v>
       </c>
       <c r="F46" t="n">
-        <v>-181.7</v>
+        <v>103.1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.017</v>
+        <v>0.0098</v>
       </c>
       <c r="H46" t="n">
-        <v>349.5</v>
+        <v>200.7</v>
       </c>
       <c r="I46" t="n">
-        <v>10157.1</v>
+        <v>10048</v>
       </c>
       <c r="J46" t="n">
-        <v>10463.78</v>
+        <v>10110.32</v>
       </c>
       <c r="K46" t="n">
-        <v>10542.95</v>
+        <v>10322.55</v>
       </c>
       <c r="L46" t="n">
-        <v>10622.12</v>
+        <v>10534.77</v>
       </c>
       <c r="M46" t="n">
-        <v>10815.05</v>
+        <v>10672.05</v>
       </c>
       <c r="N46" t="n">
-        <v>11007.97</v>
+        <v>10809.32</v>
       </c>
       <c r="O46" t="n">
-        <v>10973.4</v>
+        <v>11096.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4375,57 +4371,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10498.1</v>
+        <v>10600.3</v>
       </c>
       <c r="C47" t="n">
-        <v>10623.7</v>
+        <v>10763.4</v>
       </c>
       <c r="D47" t="n">
-        <v>10423</v>
+        <v>10483.1</v>
       </c>
       <c r="E47" t="n">
-        <v>10600.4</v>
+        <v>10736.2</v>
       </c>
       <c r="F47" t="n">
-        <v>103.1</v>
+        <v>135.8</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0128</v>
       </c>
       <c r="H47" t="n">
-        <v>200.7</v>
+        <v>280.3</v>
       </c>
       <c r="I47" t="n">
-        <v>10048</v>
+        <v>10222.3</v>
       </c>
       <c r="J47" t="n">
-        <v>10110.32</v>
+        <v>10438.23</v>
       </c>
       <c r="K47" t="n">
-        <v>10322.55</v>
+        <v>10500.05</v>
       </c>
       <c r="L47" t="n">
-        <v>10534.77</v>
+        <v>10561.88</v>
       </c>
       <c r="M47" t="n">
-        <v>10672.05</v>
+        <v>10700.75</v>
       </c>
       <c r="N47" t="n">
-        <v>10809.32</v>
+        <v>10839.63</v>
       </c>
       <c r="O47" t="n">
-        <v>11096.5</v>
+        <v>10824.4</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4433,16 +4429,20 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4455,59 +4455,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10600.3</v>
+        <v>10736.1</v>
       </c>
       <c r="C48" t="n">
-        <v>10763.4</v>
+        <v>10989.5</v>
       </c>
       <c r="D48" t="n">
-        <v>10483.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E48" t="n">
-        <v>10736.2</v>
+        <v>10868.1</v>
       </c>
       <c r="F48" t="n">
-        <v>135.8</v>
+        <v>131.9</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0123</v>
       </c>
       <c r="H48" t="n">
-        <v>280.3</v>
+        <v>253.4</v>
       </c>
       <c r="I48" t="n">
-        <v>10222.3</v>
+        <v>10202.8</v>
       </c>
       <c r="J48" t="n">
-        <v>10438.23</v>
+        <v>10512.37</v>
       </c>
       <c r="K48" t="n">
-        <v>10500.05</v>
+        <v>10596.05</v>
       </c>
       <c r="L48" t="n">
-        <v>10561.88</v>
+        <v>10679.73</v>
       </c>
       <c r="M48" t="n">
-        <v>10700.75</v>
+        <v>10876.35</v>
       </c>
       <c r="N48" t="n">
-        <v>10839.63</v>
+        <v>11072.98</v>
       </c>
       <c r="O48" t="n">
-        <v>10824.4</v>
+        <v>11043.7</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4515,10 +4511,8 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
@@ -4546,50 +4540,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10736.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C49" t="n">
-        <v>10989.5</v>
+        <v>10959.9</v>
       </c>
       <c r="D49" t="n">
-        <v>10736.1</v>
+        <v>10832.5</v>
       </c>
       <c r="E49" t="n">
-        <v>10868.1</v>
+        <v>10901.1</v>
       </c>
       <c r="F49" t="n">
-        <v>131.9</v>
+        <v>33</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0123</v>
+        <v>0.003</v>
       </c>
       <c r="H49" t="n">
-        <v>253.4</v>
+        <v>127.4</v>
       </c>
       <c r="I49" t="n">
-        <v>10202.8</v>
+        <v>10482.7</v>
       </c>
       <c r="J49" t="n">
-        <v>10512.37</v>
+        <v>10617.35</v>
       </c>
       <c r="K49" t="n">
-        <v>10596.05</v>
+        <v>10741.4</v>
       </c>
       <c r="L49" t="n">
-        <v>10679.73</v>
+        <v>10865.45</v>
       </c>
       <c r="M49" t="n">
-        <v>10876.35</v>
+        <v>10994.8</v>
       </c>
       <c r="N49" t="n">
-        <v>11072.98</v>
+        <v>11124.15</v>
       </c>
       <c r="O49" t="n">
-        <v>11043.7</v>
+        <v>11242.9</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4602,13 +4596,11 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4621,68 +4613,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10868.1</v>
+        <v>10901.1</v>
       </c>
       <c r="C50" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D50" t="n">
-        <v>10832.5</v>
+        <v>10723.7</v>
       </c>
       <c r="E50" t="n">
-        <v>10901.1</v>
+        <v>10750.1</v>
       </c>
       <c r="F50" t="n">
-        <v>33</v>
+        <v>-151</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0139</v>
       </c>
       <c r="H50" t="n">
-        <v>127.4</v>
+        <v>187.2</v>
       </c>
       <c r="I50" t="n">
-        <v>10482.7</v>
+        <v>10705.1</v>
       </c>
       <c r="J50" t="n">
-        <v>10617.35</v>
+        <v>10776.15</v>
       </c>
       <c r="K50" t="n">
-        <v>10741.4</v>
+        <v>10837.4</v>
       </c>
       <c r="L50" t="n">
-        <v>10865.45</v>
+        <v>10898.65</v>
       </c>
       <c r="M50" t="n">
-        <v>10994.8</v>
+        <v>10964.8</v>
       </c>
       <c r="N50" t="n">
-        <v>11124.15</v>
+        <v>11030.95</v>
       </c>
       <c r="O50" t="n">
-        <v>11242.9</v>
+        <v>11087.3</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4694,86 +4694,80 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10901.1</v>
+        <v>10750</v>
       </c>
       <c r="C51" t="n">
-        <v>10910.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D51" t="n">
-        <v>10723.7</v>
+        <v>10684.4</v>
       </c>
       <c r="E51" t="n">
-        <v>10750.1</v>
+        <v>10816.6</v>
       </c>
       <c r="F51" t="n">
-        <v>-151</v>
+        <v>66.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0139</v>
+        <v>0.0062</v>
       </c>
       <c r="H51" t="n">
-        <v>187.2</v>
+        <v>147.2</v>
       </c>
       <c r="I51" t="n">
-        <v>10705.1</v>
+        <v>10536.5</v>
       </c>
       <c r="J51" t="n">
-        <v>10776.15</v>
+        <v>10529.3</v>
       </c>
       <c r="K51" t="n">
-        <v>10837.4</v>
+        <v>10656.5</v>
       </c>
       <c r="L51" t="n">
-        <v>10898.65</v>
+        <v>10783.7</v>
       </c>
       <c r="M51" t="n">
-        <v>10964.8</v>
+        <v>10843.7</v>
       </c>
       <c r="N51" t="n">
-        <v>11030.95</v>
+        <v>10903.7</v>
       </c>
       <c r="O51" t="n">
-        <v>11087.3</v>
+        <v>11098.1</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4785,55 +4779,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10750</v>
+        <v>10816.3</v>
       </c>
       <c r="C52" t="n">
-        <v>10831.6</v>
+        <v>10920.5</v>
       </c>
       <c r="D52" t="n">
-        <v>10684.4</v>
+        <v>10772.6</v>
       </c>
       <c r="E52" t="n">
-        <v>10816.6</v>
+        <v>10824.3</v>
       </c>
       <c r="F52" t="n">
-        <v>66.5</v>
+        <v>7.7</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0007</v>
       </c>
       <c r="H52" t="n">
-        <v>147.2</v>
+        <v>147.9</v>
       </c>
       <c r="I52" t="n">
-        <v>10536.5</v>
+        <v>10537.2</v>
       </c>
       <c r="J52" t="n">
-        <v>10529.3</v>
+        <v>10698.7</v>
       </c>
       <c r="K52" t="n">
-        <v>10656.5</v>
+        <v>10743</v>
       </c>
       <c r="L52" t="n">
-        <v>10783.7</v>
+        <v>10787.3</v>
       </c>
       <c r="M52" t="n">
-        <v>10843.7</v>
+        <v>10890.2</v>
       </c>
       <c r="N52" t="n">
-        <v>10903.7</v>
+        <v>10993.1</v>
       </c>
       <c r="O52" t="n">
-        <v>11098.1</v>
+        <v>10978.8</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4846,12 +4844,12 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U52" s="8" t="n">
@@ -4867,57 +4865,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10816.3</v>
+        <v>10824.6</v>
       </c>
       <c r="C53" t="n">
-        <v>10920.5</v>
+        <v>10866.8</v>
       </c>
       <c r="D53" t="n">
-        <v>10772.6</v>
+        <v>10689.6</v>
       </c>
       <c r="E53" t="n">
-        <v>10824.3</v>
+        <v>10831.1</v>
       </c>
       <c r="F53" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>147.9</v>
+        <v>177.2</v>
       </c>
       <c r="I53" t="n">
-        <v>10537.2</v>
+        <v>10624.7</v>
       </c>
       <c r="J53" t="n">
-        <v>10698.7</v>
+        <v>10665.27</v>
       </c>
       <c r="K53" t="n">
-        <v>10743</v>
+        <v>10750.35</v>
       </c>
       <c r="L53" t="n">
-        <v>10787.3</v>
+        <v>10835.42</v>
       </c>
       <c r="M53" t="n">
-        <v>10890.2</v>
+        <v>10898.25</v>
       </c>
       <c r="N53" t="n">
-        <v>10993.1</v>
+        <v>10961.08</v>
       </c>
       <c r="O53" t="n">
-        <v>10978.8</v>
+        <v>11068.4</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4925,19 +4923,19 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4951,63 +4949,65 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10824.6</v>
+        <v>10831</v>
       </c>
       <c r="C54" t="n">
-        <v>10866.8</v>
+        <v>10868.3</v>
       </c>
       <c r="D54" t="n">
-        <v>10689.6</v>
+        <v>10594.3</v>
       </c>
       <c r="E54" t="n">
-        <v>10831.1</v>
+        <v>10650.4</v>
       </c>
       <c r="F54" t="n">
-        <v>6.8</v>
+        <v>-180.7</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0167</v>
       </c>
       <c r="H54" t="n">
-        <v>177.2</v>
+        <v>274</v>
       </c>
       <c r="I54" t="n">
-        <v>10624.7</v>
+        <v>10512.4</v>
       </c>
       <c r="J54" t="n">
-        <v>10665.27</v>
+        <v>10680.35</v>
       </c>
       <c r="K54" t="n">
-        <v>10750.35</v>
+        <v>10742.5</v>
       </c>
       <c r="L54" t="n">
-        <v>10835.42</v>
+        <v>10804.65</v>
       </c>
       <c r="M54" t="n">
-        <v>10898.25</v>
+        <v>10919.7</v>
       </c>
       <c r="N54" t="n">
-        <v>10961.08</v>
+        <v>11034.75</v>
       </c>
       <c r="O54" t="n">
-        <v>11068.4</v>
+        <v>11044</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5042,71 +5042,69 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10831</v>
+        <v>10650.9</v>
       </c>
       <c r="C55" t="n">
-        <v>10868.3</v>
+        <v>10823</v>
       </c>
       <c r="D55" t="n">
-        <v>10594.3</v>
+        <v>10586.4</v>
       </c>
       <c r="E55" t="n">
-        <v>10650.4</v>
+        <v>10659.1</v>
       </c>
       <c r="F55" t="n">
-        <v>-180.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0167</v>
+        <v>0.0008</v>
       </c>
       <c r="H55" t="n">
-        <v>274</v>
+        <v>236.6</v>
       </c>
       <c r="I55" t="n">
-        <v>10512.4</v>
+        <v>10320.3</v>
       </c>
       <c r="J55" t="n">
-        <v>10680.35</v>
+        <v>10335.95</v>
       </c>
       <c r="K55" t="n">
-        <v>10742.5</v>
+        <v>10513.4</v>
       </c>
       <c r="L55" t="n">
-        <v>10804.65</v>
+        <v>10690.85</v>
       </c>
       <c r="M55" t="n">
-        <v>10919.7</v>
+        <v>10787.4</v>
       </c>
       <c r="N55" t="n">
-        <v>11034.75</v>
+        <v>10883.95</v>
       </c>
       <c r="O55" t="n">
-        <v>11044</v>
+        <v>11142.3</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5128,50 +5126,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10650.9</v>
+        <v>10659.1</v>
       </c>
       <c r="C56" t="n">
-        <v>10823</v>
+        <v>10774.7</v>
       </c>
       <c r="D56" t="n">
-        <v>10586.4</v>
+        <v>10656.7</v>
       </c>
       <c r="E56" t="n">
-        <v>10659.1</v>
+        <v>10695.3</v>
       </c>
       <c r="F56" t="n">
-        <v>8.699999999999999</v>
+        <v>36.2</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0034</v>
       </c>
       <c r="H56" t="n">
-        <v>236.6</v>
+        <v>118</v>
       </c>
       <c r="I56" t="n">
-        <v>10320.3</v>
+        <v>10349.8</v>
       </c>
       <c r="J56" t="n">
-        <v>10335.95</v>
+        <v>10399.7</v>
       </c>
       <c r="K56" t="n">
-        <v>10513.4</v>
+        <v>10540.8</v>
       </c>
       <c r="L56" t="n">
-        <v>10690.85</v>
+        <v>10681.9</v>
       </c>
       <c r="M56" t="n">
-        <v>10787.4</v>
+        <v>10777.4</v>
       </c>
       <c r="N56" t="n">
-        <v>10883.95</v>
+        <v>10872.9</v>
       </c>
       <c r="O56" t="n">
-        <v>11142.3</v>
+        <v>11059.6</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5182,15 +5180,13 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5205,74 +5201,82 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10659.1</v>
+        <v>10695.2</v>
       </c>
       <c r="C57" t="n">
-        <v>10774.7</v>
+        <v>10758.7</v>
       </c>
       <c r="D57" t="n">
-        <v>10656.7</v>
+        <v>10390.7</v>
       </c>
       <c r="E57" t="n">
-        <v>10695.3</v>
+        <v>10461.95</v>
       </c>
       <c r="F57" t="n">
-        <v>36.2</v>
+        <v>-233.35</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.0218</v>
       </c>
       <c r="H57" t="n">
-        <v>118</v>
+        <v>368</v>
       </c>
       <c r="I57" t="n">
-        <v>10349.8</v>
+        <v>10538.7</v>
       </c>
       <c r="J57" t="n">
-        <v>10399.7</v>
+        <v>10567.1</v>
       </c>
       <c r="K57" t="n">
-        <v>10540.8</v>
+        <v>10636.3</v>
       </c>
       <c r="L57" t="n">
-        <v>10681.9</v>
+        <v>10705.5</v>
       </c>
       <c r="M57" t="n">
-        <v>10777.4</v>
+        <v>10754.3</v>
       </c>
       <c r="N57" t="n">
-        <v>10872.9</v>
+        <v>10803.1</v>
       </c>
       <c r="O57" t="n">
-        <v>11059.6</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+        <v>10892.7</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5285,97 +5289,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>10695.2</v>
-      </c>
-      <c r="C58" t="n">
-        <v>10758.7</v>
-      </c>
-      <c r="D58" t="n">
-        <v>10390.73</v>
-      </c>
-      <c r="E58" t="n">
-        <v>10428.27</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-267.03</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="H58" t="n">
-        <v>367.97</v>
-      </c>
-      <c r="I58" t="n">
-        <v>10538.7</v>
-      </c>
-      <c r="J58" t="n">
-        <v>10567.1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>10636.3</v>
-      </c>
-      <c r="L58" t="n">
-        <v>10705.5</v>
-      </c>
-      <c r="M58" t="n">
-        <v>10754.3</v>
-      </c>
-      <c r="N58" t="n">
-        <v>10803.1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>10892.7</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5221,10 +5224,10 @@
         <v>10390.7</v>
       </c>
       <c r="E57" t="n">
-        <v>10461.95</v>
+        <v>10462</v>
       </c>
       <c r="F57" t="n">
-        <v>-233.35</v>
+        <v>-233.3</v>
       </c>
       <c r="G57" s="5" t="n">
         <v>-0.0218</v>
@@ -5290,6 +5293,90 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10462.38</v>
+      </c>
+      <c r="C58" t="n">
+        <v>10527.46</v>
+      </c>
+      <c r="D58" t="n">
+        <v>10451.73</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>75.73</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10022.7</v>
+      </c>
+      <c r="J58" t="n">
+        <v>10037.65</v>
+      </c>
+      <c r="K58" t="n">
+        <v>10278</v>
+      </c>
+      <c r="L58" t="n">
+        <v>10518.35</v>
+      </c>
+      <c r="M58" t="n">
+        <v>10646</v>
+      </c>
+      <c r="N58" t="n">
+        <v>10773.65</v>
+      </c>
+      <c r="O58" t="n">
+        <v>11126.7</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5301,25 +5298,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10462.38</v>
+        <v>10462.4</v>
       </c>
       <c r="C58" t="n">
-        <v>10527.46</v>
+        <v>10602.6</v>
       </c>
       <c r="D58" t="n">
-        <v>10451.73</v>
+        <v>10451.7</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>10541.69</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>79.69</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0076</v>
       </c>
       <c r="H58" t="n">
-        <v>75.73</v>
+        <v>150.9</v>
       </c>
       <c r="I58" t="n">
         <v>10022.7</v>
@@ -5342,10 +5339,8 @@
       <c r="O58" t="n">
         <v>11126.7</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5353,9 +5348,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5374,7 +5369,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>150.1</v>
       </c>
       <c r="I2" t="n">
-        <v>8961.299999999999</v>
+        <v>9057.5</v>
       </c>
       <c r="J2" t="n">
-        <v>9075.98</v>
+        <v>9112.049999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>9135.15</v>
+        <v>9159.200000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>9194.33</v>
+        <v>9206.35</v>
       </c>
       <c r="M2" t="n">
-        <v>9281.25</v>
+        <v>9257.200000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>9368.17</v>
+        <v>9308.049999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>9399.6</v>
+        <v>9351.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,11 +695,13 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5304,19 +5306,19 @@
         <v>10602.6</v>
       </c>
       <c r="D58" t="n">
-        <v>10451.7</v>
+        <v>10445.42</v>
       </c>
       <c r="E58" t="n">
-        <v>10541.69</v>
+        <v>10458.5</v>
       </c>
       <c r="F58" t="n">
-        <v>79.69</v>
+        <v>-3.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0003</v>
       </c>
       <c r="H58" t="n">
-        <v>150.9</v>
+        <v>157.18</v>
       </c>
       <c r="I58" t="n">
         <v>10022.7</v>
@@ -5348,9 +5350,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5369,7 +5371,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -5306,7 +5306,7 @@
         <v>10602.6</v>
       </c>
       <c r="D58" t="n">
-        <v>10445.42</v>
+        <v>10445.4</v>
       </c>
       <c r="E58" t="n">
         <v>10458.5</v>
@@ -5318,7 +5318,7 @@
         <v>-0.0003</v>
       </c>
       <c r="H58" t="n">
-        <v>157.18</v>
+        <v>157.2</v>
       </c>
       <c r="I58" t="n">
         <v>10022.7</v>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>150.1</v>
       </c>
       <c r="I2" t="n">
-        <v>9057.5</v>
+        <v>9141.700000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>9112.049999999999</v>
+        <v>9143.620000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>9159.200000000001</v>
+        <v>9180.25</v>
       </c>
       <c r="L2" t="n">
-        <v>9206.35</v>
+        <v>9216.879999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>9257.200000000001</v>
+        <v>9236.15</v>
       </c>
       <c r="N2" t="n">
-        <v>9308.049999999999</v>
+        <v>9255.43</v>
       </c>
       <c r="O2" t="n">
-        <v>9351.5</v>
+        <v>9309.4</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,18 +700,24 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5306,19 +5312,19 @@
         <v>10602.6</v>
       </c>
       <c r="D58" t="n">
-        <v>10445.4</v>
+        <v>10367.25</v>
       </c>
       <c r="E58" t="n">
-        <v>10458.5</v>
+        <v>10441.6</v>
       </c>
       <c r="F58" t="n">
-        <v>-3.5</v>
+        <v>-20.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0019</v>
       </c>
       <c r="H58" t="n">
-        <v>157.2</v>
+        <v>235.35</v>
       </c>
       <c r="I58" t="n">
         <v>10022.7</v>
@@ -5369,11 +5375,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9208.200000000001</v>
+        <v>9283.299999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>9340.700000000001</v>
+        <v>9314.4</v>
       </c>
       <c r="D2" t="n">
-        <v>9190.6</v>
+        <v>9195.700000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9283.299999999999</v>
+        <v>9216.700000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>75.09999999999999</v>
+        <v>-66.59999999999999</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0072</v>
       </c>
       <c r="H2" t="n">
-        <v>150.1</v>
+        <v>118.7</v>
       </c>
       <c r="I2" t="n">
-        <v>9141.700000000001</v>
+        <v>9040.5</v>
       </c>
       <c r="J2" t="n">
-        <v>9143.620000000001</v>
+        <v>9142.02</v>
       </c>
       <c r="K2" t="n">
-        <v>9180.25</v>
+        <v>9208.25</v>
       </c>
       <c r="L2" t="n">
-        <v>9216.879999999999</v>
+        <v>9274.469999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>9236.15</v>
+        <v>9358.35</v>
       </c>
       <c r="N2" t="n">
-        <v>9255.43</v>
+        <v>9442.23</v>
       </c>
       <c r="O2" t="n">
-        <v>9309.4</v>
+        <v>9490.799999999999</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,28 +685,24 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -715,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9283.299999999999</v>
+        <v>9216.700000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>9314.4</v>
+        <v>9292.1</v>
       </c>
       <c r="D3" t="n">
-        <v>9195.700000000001</v>
+        <v>9177.1</v>
       </c>
       <c r="E3" t="n">
-        <v>9216.700000000001</v>
+        <v>9284.799999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-66.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.0074</v>
       </c>
       <c r="H3" t="n">
-        <v>118.7</v>
+        <v>115</v>
       </c>
       <c r="I3" t="n">
-        <v>9040.5</v>
+        <v>9077</v>
       </c>
       <c r="J3" t="n">
-        <v>9142.02</v>
+        <v>9078.82</v>
       </c>
       <c r="K3" t="n">
-        <v>9208.25</v>
+        <v>9157.35</v>
       </c>
       <c r="L3" t="n">
-        <v>9274.469999999999</v>
+        <v>9235.879999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>9358.35</v>
+        <v>9276.049999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>9442.23</v>
+        <v>9316.23</v>
       </c>
       <c r="O3" t="n">
-        <v>9490.799999999999</v>
+        <v>9433.1</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,18 +769,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -806,50 +802,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9216.700000000001</v>
+        <v>9284.799999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>9292.1</v>
+        <v>9494.6</v>
       </c>
       <c r="D4" t="n">
-        <v>9177.1</v>
+        <v>9266.299999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>9284.799999999999</v>
+        <v>9491.299999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>68.09999999999999</v>
+        <v>206.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0222</v>
       </c>
       <c r="H4" t="n">
-        <v>115</v>
+        <v>228.3</v>
       </c>
       <c r="I4" t="n">
-        <v>9077</v>
+        <v>9062.1</v>
       </c>
       <c r="J4" t="n">
-        <v>9078.82</v>
+        <v>9194.9</v>
       </c>
       <c r="K4" t="n">
-        <v>9157.35</v>
+        <v>9227.299999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>9235.879999999999</v>
+        <v>9259.700000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>9276.049999999999</v>
+        <v>9342.299999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>9316.23</v>
+        <v>9424.9</v>
       </c>
       <c r="O4" t="n">
-        <v>9433.1</v>
+        <v>9407.1</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -860,80 +856,80 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9284.799999999999</v>
+        <v>9491.200000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>9494.6</v>
+        <v>9577.1</v>
       </c>
       <c r="D5" t="n">
-        <v>9266.299999999999</v>
+        <v>9414.6</v>
       </c>
       <c r="E5" t="n">
-        <v>9491.299999999999</v>
+        <v>9427.5</v>
       </c>
       <c r="F5" t="n">
-        <v>206.5</v>
+        <v>-63.8</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0067</v>
       </c>
       <c r="H5" t="n">
-        <v>228.3</v>
+        <v>162.5</v>
       </c>
       <c r="I5" t="n">
-        <v>9062.1</v>
+        <v>9038</v>
       </c>
       <c r="J5" t="n">
-        <v>9194.9</v>
+        <v>9318.43</v>
       </c>
       <c r="K5" t="n">
-        <v>9227.299999999999</v>
+        <v>9377.15</v>
       </c>
       <c r="L5" t="n">
-        <v>9259.700000000001</v>
+        <v>9435.870000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>9342.299999999999</v>
+        <v>9605.450000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>9424.9</v>
+        <v>9775.02</v>
       </c>
       <c r="O5" t="n">
-        <v>9407.1</v>
+        <v>9722.9</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -946,78 +942,76 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9491.200000000001</v>
+        <v>9427.5</v>
       </c>
       <c r="C6" t="n">
-        <v>9577.1</v>
+        <v>9474.299999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>9414.6</v>
+        <v>9276.9</v>
       </c>
       <c r="E6" t="n">
-        <v>9427.5</v>
+        <v>9354.6</v>
       </c>
       <c r="F6" t="n">
-        <v>-63.8</v>
+        <v>-72.90000000000001</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0067</v>
+        <v>-0.0077</v>
       </c>
       <c r="H6" t="n">
-        <v>162.5</v>
+        <v>197.4</v>
       </c>
       <c r="I6" t="n">
-        <v>9038</v>
+        <v>9252.1</v>
       </c>
       <c r="J6" t="n">
-        <v>9318.43</v>
+        <v>9230.83</v>
       </c>
       <c r="K6" t="n">
-        <v>9377.15</v>
+        <v>9346.25</v>
       </c>
       <c r="L6" t="n">
-        <v>9435.870000000001</v>
+        <v>9461.67</v>
       </c>
       <c r="M6" t="n">
-        <v>9605.450000000001</v>
+        <v>9508.75</v>
       </c>
       <c r="N6" t="n">
-        <v>9775.02</v>
+        <v>9555.83</v>
       </c>
       <c r="O6" t="n">
-        <v>9722.9</v>
+        <v>9739.6</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1025,12 +1019,14 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1049,57 +1045,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9427.5</v>
+        <v>9354.5</v>
       </c>
       <c r="C7" t="n">
-        <v>9474.299999999999</v>
+        <v>9645.6</v>
       </c>
       <c r="D7" t="n">
-        <v>9276.9</v>
+        <v>9354.5</v>
       </c>
       <c r="E7" t="n">
-        <v>9354.6</v>
+        <v>9645.6</v>
       </c>
       <c r="F7" t="n">
-        <v>-72.90000000000001</v>
+        <v>291</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0311</v>
       </c>
       <c r="H7" t="n">
-        <v>197.4</v>
+        <v>291.1</v>
       </c>
       <c r="I7" t="n">
-        <v>9252.1</v>
+        <v>9079.5</v>
       </c>
       <c r="J7" t="n">
-        <v>9230.83</v>
+        <v>9146.700000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>9346.25</v>
+        <v>9255.9</v>
       </c>
       <c r="L7" t="n">
-        <v>9461.67</v>
+        <v>9365.1</v>
       </c>
       <c r="M7" t="n">
-        <v>9508.75</v>
+        <v>9453.299999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>9555.83</v>
+        <v>9541.5</v>
       </c>
       <c r="O7" t="n">
-        <v>9739.6</v>
+        <v>9671.700000000001</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1107,83 +1103,83 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
-      </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9354.5</v>
+        <v>9645.6</v>
       </c>
       <c r="C8" t="n">
-        <v>9645.6</v>
+        <v>9787.6</v>
       </c>
       <c r="D8" t="n">
-        <v>9354.5</v>
+        <v>9632.799999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>9645.6</v>
+        <v>9717.299999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>291</v>
+        <v>71.7</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0311</v>
+        <v>0.0074</v>
       </c>
       <c r="H8" t="n">
-        <v>291.1</v>
+        <v>154.8</v>
       </c>
       <c r="I8" t="n">
-        <v>9079.5</v>
+        <v>9063.4</v>
       </c>
       <c r="J8" t="n">
-        <v>9146.700000000001</v>
+        <v>9427.27</v>
       </c>
       <c r="K8" t="n">
-        <v>9255.9</v>
+        <v>9500.049999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>9365.1</v>
+        <v>9572.82</v>
       </c>
       <c r="M8" t="n">
-        <v>9453.299999999999</v>
+        <v>9791.15</v>
       </c>
       <c r="N8" t="n">
-        <v>9541.5</v>
+        <v>10009.47</v>
       </c>
       <c r="O8" t="n">
-        <v>9671.700000000001</v>
+        <v>9936.700000000001</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1194,25 +1190,21 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
@@ -1224,50 +1216,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9645.6</v>
+        <v>9717.299999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>9787.6</v>
+        <v>9786.799999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>9632.799999999999</v>
+        <v>9574.200000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>9717.299999999999</v>
+        <v>9682.6</v>
       </c>
       <c r="F9" t="n">
-        <v>71.7</v>
+        <v>-34.7</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0036</v>
       </c>
       <c r="H9" t="n">
-        <v>154.8</v>
+        <v>212.6</v>
       </c>
       <c r="I9" t="n">
-        <v>9063.4</v>
+        <v>9478</v>
       </c>
       <c r="J9" t="n">
-        <v>9427.27</v>
+        <v>9566.049999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>9500.049999999999</v>
+        <v>9639.9</v>
       </c>
       <c r="L9" t="n">
-        <v>9572.82</v>
+        <v>9713.75</v>
       </c>
       <c r="M9" t="n">
-        <v>9791.15</v>
+        <v>9794.700000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>10009.47</v>
+        <v>9875.65</v>
       </c>
       <c r="O9" t="n">
-        <v>9936.700000000001</v>
+        <v>9942.4</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1275,18 +1267,18 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1299,55 +1291,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9717.299999999999</v>
+        <v>9682.6</v>
       </c>
       <c r="C10" t="n">
-        <v>9786.799999999999</v>
+        <v>9930.1</v>
       </c>
       <c r="D10" t="n">
-        <v>9574.200000000001</v>
+        <v>9610.5</v>
       </c>
       <c r="E10" t="n">
-        <v>9682.6</v>
+        <v>9698.4</v>
       </c>
       <c r="F10" t="n">
-        <v>-34.7</v>
+        <v>15.8</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0016</v>
       </c>
       <c r="H10" t="n">
-        <v>212.6</v>
+        <v>319.6</v>
       </c>
       <c r="I10" t="n">
-        <v>9478</v>
+        <v>9361.6</v>
       </c>
       <c r="J10" t="n">
-        <v>9566.049999999999</v>
+        <v>9471.049999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>9639.9</v>
+        <v>9576.299999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>9713.75</v>
+        <v>9681.549999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>9794.700000000001</v>
+        <v>9788.9</v>
       </c>
       <c r="N10" t="n">
-        <v>9875.65</v>
+        <v>9896.25</v>
       </c>
       <c r="O10" t="n">
-        <v>9942.4</v>
+        <v>9999.4</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1355,21 +1351,23 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1379,59 +1377,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9682.6</v>
+        <v>9698.4</v>
       </c>
       <c r="C11" t="n">
-        <v>9930.1</v>
+        <v>9707.700000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>9610.5</v>
+        <v>9423.9</v>
       </c>
       <c r="E11" t="n">
-        <v>9698.4</v>
+        <v>9539.700000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>15.8</v>
+        <v>-158.7</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0164</v>
       </c>
       <c r="H11" t="n">
-        <v>319.6</v>
+        <v>283.8</v>
       </c>
       <c r="I11" t="n">
-        <v>9361.6</v>
+        <v>9290.9</v>
       </c>
       <c r="J11" t="n">
-        <v>9471.049999999999</v>
+        <v>9342.85</v>
       </c>
       <c r="K11" t="n">
-        <v>9576.299999999999</v>
+        <v>9538.6</v>
       </c>
       <c r="L11" t="n">
-        <v>9681.549999999999</v>
+        <v>9734.35</v>
       </c>
       <c r="M11" t="n">
-        <v>9788.9</v>
+        <v>9858.200000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>9896.25</v>
+        <v>9982.049999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>9999.4</v>
+        <v>10249.7</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1439,23 +1433,21 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1465,55 +1457,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9698.4</v>
+        <v>9539.700000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>9707.700000000001</v>
+        <v>9740.200000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>9423.9</v>
+        <v>9521.5</v>
       </c>
       <c r="E12" t="n">
-        <v>9539.700000000001</v>
+        <v>9720.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-158.7</v>
+        <v>180.8</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.019</v>
       </c>
       <c r="H12" t="n">
-        <v>283.8</v>
+        <v>218.7</v>
       </c>
       <c r="I12" t="n">
-        <v>9290.9</v>
+        <v>9140.1</v>
       </c>
       <c r="J12" t="n">
-        <v>9342.85</v>
+        <v>9242.85</v>
       </c>
       <c r="K12" t="n">
-        <v>9538.6</v>
+        <v>9397.799999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>9734.35</v>
+        <v>9552.75</v>
       </c>
       <c r="M12" t="n">
-        <v>9858.200000000001</v>
+        <v>9681.6</v>
       </c>
       <c r="N12" t="n">
-        <v>9982.049999999999</v>
+        <v>9810.450000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>10249.7</v>
+        <v>9991.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1521,19 +1517,19 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1545,59 +1541,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9539.700000000001</v>
+        <v>9720.6</v>
       </c>
       <c r="C13" t="n">
-        <v>9740.200000000001</v>
+        <v>9744.799999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>9521.5</v>
+        <v>9667</v>
       </c>
       <c r="E13" t="n">
-        <v>9720.5</v>
+        <v>9667</v>
       </c>
       <c r="F13" t="n">
-        <v>180.8</v>
+        <v>-53.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.019</v>
+        <v>-0.0055</v>
       </c>
       <c r="H13" t="n">
-        <v>218.7</v>
+        <v>77.8</v>
       </c>
       <c r="I13" t="n">
-        <v>9140.1</v>
+        <v>9302.799999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>9242.85</v>
+        <v>9546.620000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>9397.799999999999</v>
+        <v>9611.15</v>
       </c>
       <c r="L13" t="n">
-        <v>9552.75</v>
+        <v>9675.68</v>
       </c>
       <c r="M13" t="n">
-        <v>9681.6</v>
+        <v>9829.85</v>
       </c>
       <c r="N13" t="n">
-        <v>9810.450000000001</v>
+        <v>9984.030000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>9991.5</v>
+        <v>9958.9</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1610,13 +1602,11 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1629,55 +1619,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9720.6</v>
+        <v>9667.1</v>
       </c>
       <c r="C14" t="n">
-        <v>9744.799999999999</v>
+        <v>9761.5</v>
       </c>
       <c r="D14" t="n">
-        <v>9667</v>
+        <v>9622.700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>9667</v>
+        <v>9649</v>
       </c>
       <c r="F14" t="n">
-        <v>-53.5</v>
+        <v>-18</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0019</v>
       </c>
       <c r="H14" t="n">
-        <v>77.8</v>
+        <v>138.8</v>
       </c>
       <c r="I14" t="n">
-        <v>9302.799999999999</v>
+        <v>9589.200000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>9546.620000000001</v>
+        <v>9569.75</v>
       </c>
       <c r="K14" t="n">
-        <v>9611.15</v>
+        <v>9628.1</v>
       </c>
       <c r="L14" t="n">
-        <v>9675.68</v>
+        <v>9686.450000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>9829.85</v>
+        <v>9705.9</v>
       </c>
       <c r="N14" t="n">
-        <v>9984.030000000001</v>
+        <v>9725.35</v>
       </c>
       <c r="O14" t="n">
-        <v>9958.9</v>
+        <v>9822.6</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1685,19 +1679,25 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1709,57 +1709,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9667.1</v>
+        <v>9649</v>
       </c>
       <c r="C15" t="n">
-        <v>9761.5</v>
+        <v>9903.1</v>
       </c>
       <c r="D15" t="n">
-        <v>9622.700000000001</v>
+        <v>9649</v>
       </c>
       <c r="E15" t="n">
-        <v>9649</v>
+        <v>9897.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-18</v>
+        <v>248.4</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0257</v>
       </c>
       <c r="H15" t="n">
-        <v>138.8</v>
+        <v>254.1</v>
       </c>
       <c r="I15" t="n">
-        <v>9589.200000000001</v>
+        <v>9483.9</v>
       </c>
       <c r="J15" t="n">
-        <v>9569.75</v>
+        <v>9488.65</v>
       </c>
       <c r="K15" t="n">
-        <v>9628.1</v>
+        <v>9579.6</v>
       </c>
       <c r="L15" t="n">
-        <v>9686.450000000001</v>
+        <v>9670.549999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>9705.9</v>
+        <v>9718.4</v>
       </c>
       <c r="N15" t="n">
-        <v>9725.35</v>
+        <v>9766.25</v>
       </c>
       <c r="O15" t="n">
-        <v>9822.6</v>
+        <v>9900.299999999999</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1767,87 +1767,83 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
-      </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9649</v>
+        <v>9897.4</v>
       </c>
       <c r="C16" t="n">
-        <v>9903.1</v>
+        <v>9901.5</v>
       </c>
       <c r="D16" t="n">
-        <v>9649</v>
+        <v>9829.4</v>
       </c>
       <c r="E16" t="n">
-        <v>9897.4</v>
+        <v>9870.700000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>248.4</v>
+        <v>-26.7</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0257</v>
+        <v>-0.0027</v>
       </c>
       <c r="H16" t="n">
-        <v>254.1</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>9483.9</v>
+        <v>9394.9</v>
       </c>
       <c r="J16" t="n">
-        <v>9488.65</v>
+        <v>9703.98</v>
       </c>
       <c r="K16" t="n">
-        <v>9579.6</v>
+        <v>9770.35</v>
       </c>
       <c r="L16" t="n">
-        <v>9670.549999999999</v>
+        <v>9836.73</v>
       </c>
       <c r="M16" t="n">
-        <v>9718.4</v>
+        <v>10024.45</v>
       </c>
       <c r="N16" t="n">
-        <v>9766.25</v>
+        <v>10212.18</v>
       </c>
       <c r="O16" t="n">
-        <v>9900.299999999999</v>
+        <v>10157.2</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1858,80 +1854,78 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9897.4</v>
+        <v>9870.700000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>9901.5</v>
+        <v>10046.3</v>
       </c>
       <c r="D17" t="n">
-        <v>9829.4</v>
+        <v>9858.5</v>
       </c>
       <c r="E17" t="n">
-        <v>9870.700000000001</v>
+        <v>9951.1</v>
       </c>
       <c r="F17" t="n">
-        <v>-26.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0081</v>
       </c>
       <c r="H17" t="n">
-        <v>72.09999999999999</v>
+        <v>187.8</v>
       </c>
       <c r="I17" t="n">
-        <v>9394.9</v>
+        <v>9757.299999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>9703.98</v>
+        <v>9801.23</v>
       </c>
       <c r="K17" t="n">
-        <v>9770.35</v>
+        <v>9834.65</v>
       </c>
       <c r="L17" t="n">
-        <v>9836.73</v>
+        <v>9868.08</v>
       </c>
       <c r="M17" t="n">
-        <v>10024.45</v>
+        <v>9906.75</v>
       </c>
       <c r="N17" t="n">
-        <v>10212.18</v>
+        <v>9945.42</v>
       </c>
       <c r="O17" t="n">
-        <v>10157.2</v>
+        <v>9973.6</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1942,78 +1936,80 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9870.700000000001</v>
+        <v>9951.5</v>
       </c>
       <c r="C18" t="n">
-        <v>10046.3</v>
+        <v>10158.4</v>
       </c>
       <c r="D18" t="n">
-        <v>9858.5</v>
+        <v>9951.5</v>
       </c>
       <c r="E18" t="n">
-        <v>9951.1</v>
+        <v>10124.6</v>
       </c>
       <c r="F18" t="n">
-        <v>80.40000000000001</v>
+        <v>173.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0081</v>
+        <v>0.0174</v>
       </c>
       <c r="H18" t="n">
-        <v>187.8</v>
+        <v>206.9</v>
       </c>
       <c r="I18" t="n">
-        <v>9757.299999999999</v>
+        <v>9670.700000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>9801.23</v>
+        <v>9762.65</v>
       </c>
       <c r="K18" t="n">
-        <v>9834.65</v>
+        <v>9857.200000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>9868.08</v>
+        <v>9951.75</v>
       </c>
       <c r="M18" t="n">
-        <v>9906.75</v>
+        <v>10045</v>
       </c>
       <c r="N18" t="n">
-        <v>9945.42</v>
+        <v>10138.25</v>
       </c>
       <c r="O18" t="n">
-        <v>9973.6</v>
+        <v>10234.1</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2024,7 +2020,7 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2039,10 +2035,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2054,50 +2048,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9951.5</v>
+        <v>10124.5</v>
       </c>
       <c r="C19" t="n">
-        <v>10158.4</v>
+        <v>10257.8</v>
       </c>
       <c r="D19" t="n">
-        <v>9951.5</v>
+        <v>10089.9</v>
       </c>
       <c r="E19" t="n">
-        <v>10124.6</v>
+        <v>10235.3</v>
       </c>
       <c r="F19" t="n">
-        <v>173.5</v>
+        <v>110.7</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0174</v>
+        <v>0.0109</v>
       </c>
       <c r="H19" t="n">
-        <v>206.9</v>
+        <v>167.9</v>
       </c>
       <c r="I19" t="n">
-        <v>9670.700000000001</v>
+        <v>9744.6</v>
       </c>
       <c r="J19" t="n">
-        <v>9762.65</v>
+        <v>9952.52</v>
       </c>
       <c r="K19" t="n">
-        <v>9857.200000000001</v>
+        <v>10021.15</v>
       </c>
       <c r="L19" t="n">
-        <v>9951.75</v>
+        <v>10089.77</v>
       </c>
       <c r="M19" t="n">
-        <v>10045</v>
+        <v>10228.05</v>
       </c>
       <c r="N19" t="n">
-        <v>10138.25</v>
+        <v>10366.32</v>
       </c>
       <c r="O19" t="n">
-        <v>10234.1</v>
+        <v>10365.3</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2108,20 +2102,18 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2136,69 +2128,71 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10124.5</v>
+        <v>10235.3</v>
       </c>
       <c r="C20" t="n">
-        <v>10257.8</v>
+        <v>10235.3</v>
       </c>
       <c r="D20" t="n">
-        <v>10089.9</v>
+        <v>10050.2</v>
       </c>
       <c r="E20" t="n">
-        <v>10235.3</v>
+        <v>10143.4</v>
       </c>
       <c r="F20" t="n">
-        <v>110.7</v>
+        <v>-91.90000000000001</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>167.9</v>
+        <v>185.1</v>
       </c>
       <c r="I20" t="n">
-        <v>9744.6</v>
+        <v>9922</v>
       </c>
       <c r="J20" t="n">
-        <v>9952.52</v>
+        <v>10098.13</v>
       </c>
       <c r="K20" t="n">
-        <v>10021.15</v>
+        <v>10151.35</v>
       </c>
       <c r="L20" t="n">
-        <v>10089.77</v>
+        <v>10204.57</v>
       </c>
       <c r="M20" t="n">
-        <v>10228.05</v>
+        <v>10319.25</v>
       </c>
       <c r="N20" t="n">
-        <v>10366.32</v>
+        <v>10433.92</v>
       </c>
       <c r="O20" t="n">
-        <v>10365.3</v>
+        <v>10425.7</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2211,77 +2205,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10235.3</v>
+        <v>10143.1</v>
       </c>
       <c r="C21" t="n">
-        <v>10235.3</v>
+        <v>10277.7</v>
       </c>
       <c r="D21" t="n">
-        <v>10050.2</v>
+        <v>10125.3</v>
       </c>
       <c r="E21" t="n">
-        <v>10143.4</v>
+        <v>10223.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-91.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>185.1</v>
+        <v>152.4</v>
       </c>
       <c r="I21" t="n">
-        <v>9922</v>
+        <v>9865.1</v>
       </c>
       <c r="J21" t="n">
-        <v>10098.13</v>
+        <v>9958.629999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>10151.35</v>
+        <v>10050.85</v>
       </c>
       <c r="L21" t="n">
-        <v>10204.57</v>
+        <v>10143.08</v>
       </c>
       <c r="M21" t="n">
-        <v>10319.25</v>
+        <v>10235.95</v>
       </c>
       <c r="N21" t="n">
-        <v>10433.92</v>
+        <v>10328.83</v>
       </c>
       <c r="O21" t="n">
-        <v>10425.7</v>
+        <v>10420.4</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2293,59 +2289,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10143.1</v>
+        <v>10223.7</v>
       </c>
       <c r="C22" t="n">
-        <v>10277.7</v>
+        <v>10481.5</v>
       </c>
       <c r="D22" t="n">
-        <v>10125.3</v>
+        <v>10145.4</v>
       </c>
       <c r="E22" t="n">
-        <v>10223.5</v>
+        <v>10369.8</v>
       </c>
       <c r="F22" t="n">
-        <v>80.09999999999999</v>
+        <v>146.3</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0143</v>
       </c>
       <c r="H22" t="n">
-        <v>152.4</v>
+        <v>336.1</v>
       </c>
       <c r="I22" t="n">
-        <v>9865.1</v>
+        <v>9972.9</v>
       </c>
       <c r="J22" t="n">
-        <v>9958.629999999999</v>
+        <v>10082.1</v>
       </c>
       <c r="K22" t="n">
-        <v>10050.85</v>
+        <v>10147.3</v>
       </c>
       <c r="L22" t="n">
-        <v>10143.08</v>
+        <v>10212.5</v>
       </c>
       <c r="M22" t="n">
-        <v>10235.95</v>
+        <v>10299.7</v>
       </c>
       <c r="N22" t="n">
-        <v>10328.83</v>
+        <v>10386.9</v>
       </c>
       <c r="O22" t="n">
-        <v>10420.4</v>
+        <v>10430.1</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2353,24 +2345,30 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2382,50 +2380,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10223.7</v>
+        <v>10369.8</v>
       </c>
       <c r="C23" t="n">
-        <v>10481.5</v>
+        <v>10535.8</v>
       </c>
       <c r="D23" t="n">
-        <v>10145.4</v>
+        <v>10316</v>
       </c>
       <c r="E23" t="n">
-        <v>10369.8</v>
+        <v>10446.4</v>
       </c>
       <c r="F23" t="n">
-        <v>146.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0074</v>
       </c>
       <c r="H23" t="n">
-        <v>336.1</v>
+        <v>219.8</v>
       </c>
       <c r="I23" t="n">
-        <v>9972.9</v>
+        <v>9809.299999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>10082.1</v>
+        <v>10061.88</v>
       </c>
       <c r="K23" t="n">
-        <v>10147.3</v>
+        <v>10201.75</v>
       </c>
       <c r="L23" t="n">
-        <v>10212.5</v>
+        <v>10341.62</v>
       </c>
       <c r="M23" t="n">
-        <v>10299.7</v>
+        <v>10537.85</v>
       </c>
       <c r="N23" t="n">
-        <v>10386.9</v>
+        <v>10734.07</v>
       </c>
       <c r="O23" t="n">
-        <v>10430.1</v>
+        <v>10817.6</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2433,30 +2431,24 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
@@ -2468,50 +2460,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10369.8</v>
+        <v>10446.3</v>
       </c>
       <c r="C24" t="n">
-        <v>10535.8</v>
+        <v>10745.8</v>
       </c>
       <c r="D24" t="n">
-        <v>10316</v>
+        <v>10446.3</v>
       </c>
       <c r="E24" t="n">
-        <v>10446.4</v>
+        <v>10686.9</v>
       </c>
       <c r="F24" t="n">
-        <v>76.59999999999999</v>
+        <v>240.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.023</v>
       </c>
       <c r="H24" t="n">
-        <v>219.8</v>
+        <v>299.5</v>
       </c>
       <c r="I24" t="n">
-        <v>9809.299999999999</v>
+        <v>10096.2</v>
       </c>
       <c r="J24" t="n">
-        <v>10061.88</v>
+        <v>10236.85</v>
       </c>
       <c r="K24" t="n">
-        <v>10201.75</v>
+        <v>10336.5</v>
       </c>
       <c r="L24" t="n">
-        <v>10341.62</v>
+        <v>10436.15</v>
       </c>
       <c r="M24" t="n">
-        <v>10537.85</v>
+        <v>10556.3</v>
       </c>
       <c r="N24" t="n">
-        <v>10734.07</v>
+        <v>10676.45</v>
       </c>
       <c r="O24" t="n">
-        <v>10817.6</v>
+        <v>10755.6</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2522,18 +2514,20 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2548,50 +2542,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10446.3</v>
+        <v>10686.8</v>
       </c>
       <c r="C25" t="n">
-        <v>10745.8</v>
+        <v>10934.9</v>
       </c>
       <c r="D25" t="n">
-        <v>10446.3</v>
+        <v>10645.8</v>
       </c>
       <c r="E25" t="n">
-        <v>10686.9</v>
+        <v>10910.6</v>
       </c>
       <c r="F25" t="n">
-        <v>240.5</v>
+        <v>223.7</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0209</v>
       </c>
       <c r="H25" t="n">
-        <v>299.5</v>
+        <v>289.1</v>
       </c>
       <c r="I25" t="n">
-        <v>10096.2</v>
+        <v>10146.8</v>
       </c>
       <c r="J25" t="n">
-        <v>10236.85</v>
+        <v>10432.83</v>
       </c>
       <c r="K25" t="n">
-        <v>10336.5</v>
+        <v>10537.15</v>
       </c>
       <c r="L25" t="n">
-        <v>10436.15</v>
+        <v>10641.48</v>
       </c>
       <c r="M25" t="n">
-        <v>10556.3</v>
+        <v>10836.65</v>
       </c>
       <c r="N25" t="n">
-        <v>10676.45</v>
+        <v>11031.83</v>
       </c>
       <c r="O25" t="n">
-        <v>10755.6</v>
+        <v>11045.3</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2602,20 +2596,18 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2630,69 +2622,73 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10686.8</v>
+        <v>10911</v>
       </c>
       <c r="C26" t="n">
-        <v>10934.9</v>
+        <v>10911</v>
       </c>
       <c r="D26" t="n">
-        <v>10645.8</v>
+        <v>10234.5</v>
       </c>
       <c r="E26" t="n">
-        <v>10910.6</v>
+        <v>10284.8</v>
       </c>
       <c r="F26" t="n">
-        <v>223.7</v>
+        <v>-625.8</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0574</v>
       </c>
       <c r="H26" t="n">
-        <v>289.1</v>
+        <v>676.5</v>
       </c>
       <c r="I26" t="n">
-        <v>10146.8</v>
+        <v>10356.7</v>
       </c>
       <c r="J26" t="n">
-        <v>10432.83</v>
+        <v>10681.62</v>
       </c>
       <c r="K26" t="n">
-        <v>10537.15</v>
+        <v>10766.05</v>
       </c>
       <c r="L26" t="n">
-        <v>10641.48</v>
+        <v>10850.47</v>
       </c>
       <c r="M26" t="n">
-        <v>10836.65</v>
+        <v>11055.15</v>
       </c>
       <c r="N26" t="n">
-        <v>11031.83</v>
+        <v>11259.82</v>
       </c>
       <c r="O26" t="n">
-        <v>11045.3</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+        <v>11224</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2700,9 +2696,9 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
@@ -2710,69 +2706,63 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10911</v>
+        <v>10285</v>
       </c>
       <c r="C27" t="n">
-        <v>10911</v>
+        <v>10447.5</v>
       </c>
       <c r="D27" t="n">
-        <v>10234.5</v>
+        <v>10082</v>
       </c>
       <c r="E27" t="n">
-        <v>10284.8</v>
+        <v>10261.2</v>
       </c>
       <c r="F27" t="n">
-        <v>-625.8</v>
+        <v>-23.6</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0574</v>
+        <v>-0.0023</v>
       </c>
       <c r="H27" t="n">
-        <v>676.5</v>
+        <v>365.5</v>
       </c>
       <c r="I27" t="n">
-        <v>10356.7</v>
+        <v>9558</v>
       </c>
       <c r="J27" t="n">
-        <v>10681.62</v>
+        <v>9464.32</v>
       </c>
       <c r="K27" t="n">
-        <v>10766.05</v>
+        <v>9946.549999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>10850.47</v>
+        <v>10428.77</v>
       </c>
       <c r="M27" t="n">
-        <v>11055.15</v>
+        <v>10623.05</v>
       </c>
       <c r="N27" t="n">
-        <v>11259.82</v>
+        <v>10817.32</v>
       </c>
       <c r="O27" t="n">
-        <v>11224</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>11587.5</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2794,67 +2784,73 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10285</v>
+        <v>10261.1</v>
       </c>
       <c r="C28" t="n">
-        <v>10447.5</v>
+        <v>10447.7</v>
       </c>
       <c r="D28" t="n">
-        <v>10082</v>
+        <v>9915.700000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>10261.2</v>
+        <v>9918.299999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-23.6</v>
+        <v>-342.9</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0334</v>
       </c>
       <c r="H28" t="n">
-        <v>365.5</v>
+        <v>532</v>
       </c>
       <c r="I28" t="n">
-        <v>9558</v>
+        <v>9716.5</v>
       </c>
       <c r="J28" t="n">
-        <v>9464.32</v>
+        <v>9893.93</v>
       </c>
       <c r="K28" t="n">
-        <v>9946.549999999999</v>
+        <v>10078.45</v>
       </c>
       <c r="L28" t="n">
-        <v>10428.77</v>
+        <v>10262.98</v>
       </c>
       <c r="M28" t="n">
-        <v>10623.05</v>
+        <v>10443.95</v>
       </c>
       <c r="N28" t="n">
-        <v>10817.32</v>
+        <v>10624.93</v>
       </c>
       <c r="O28" t="n">
-        <v>11587.5</v>
+        <v>10813</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2867,78 +2863,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10261.1</v>
+        <v>9918.5</v>
       </c>
       <c r="C29" t="n">
-        <v>10447.7</v>
+        <v>10118.2</v>
       </c>
       <c r="D29" t="n">
-        <v>9915.700000000001</v>
+        <v>9670.5</v>
       </c>
       <c r="E29" t="n">
-        <v>9918.299999999999</v>
+        <v>9967.4</v>
       </c>
       <c r="F29" t="n">
-        <v>-342.9</v>
+        <v>49.1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0334</v>
+        <v>0.005</v>
       </c>
       <c r="H29" t="n">
-        <v>532</v>
+        <v>447.7</v>
       </c>
       <c r="I29" t="n">
-        <v>9716.5</v>
+        <v>9383.700000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>9893.93</v>
+        <v>9254.6</v>
       </c>
       <c r="K29" t="n">
-        <v>10078.45</v>
+        <v>9652.299999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>10262.98</v>
+        <v>10050</v>
       </c>
       <c r="M29" t="n">
-        <v>10443.95</v>
+        <v>10184.3</v>
       </c>
       <c r="N29" t="n">
-        <v>10624.93</v>
+        <v>10318.6</v>
       </c>
       <c r="O29" t="n">
-        <v>10813</v>
+        <v>10979.7</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2960,50 +2954,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9918.5</v>
+        <v>9967.5</v>
       </c>
       <c r="C30" t="n">
-        <v>10118.2</v>
+        <v>10465.2</v>
       </c>
       <c r="D30" t="n">
-        <v>9670.5</v>
+        <v>9958.1</v>
       </c>
       <c r="E30" t="n">
-        <v>9967.4</v>
+        <v>10436.3</v>
       </c>
       <c r="F30" t="n">
-        <v>49.1</v>
+        <v>468.9</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.005</v>
+        <v>0.047</v>
       </c>
       <c r="H30" t="n">
-        <v>447.7</v>
+        <v>507.1</v>
       </c>
       <c r="I30" t="n">
-        <v>9383.700000000001</v>
+        <v>9222.799999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>9254.6</v>
+        <v>9556.23</v>
       </c>
       <c r="K30" t="n">
-        <v>9652.299999999999</v>
+        <v>9743.549999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>10050</v>
+        <v>9930.879999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>10184.3</v>
+        <v>10191.25</v>
       </c>
       <c r="N30" t="n">
-        <v>10318.6</v>
+        <v>10451.63</v>
       </c>
       <c r="O30" t="n">
-        <v>10979.7</v>
+        <v>10565.9</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3016,14 +3010,18 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3035,57 +3033,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9967.5</v>
+        <v>10436.2</v>
       </c>
       <c r="C31" t="n">
-        <v>10465.2</v>
+        <v>10687.9</v>
       </c>
       <c r="D31" t="n">
-        <v>9958.1</v>
+        <v>10330.9</v>
       </c>
       <c r="E31" t="n">
-        <v>10436.3</v>
+        <v>10600.5</v>
       </c>
       <c r="F31" t="n">
-        <v>468.9</v>
+        <v>164.2</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.047</v>
+        <v>0.0157</v>
       </c>
       <c r="H31" t="n">
-        <v>507.1</v>
+        <v>357</v>
       </c>
       <c r="I31" t="n">
-        <v>9222.799999999999</v>
+        <v>9451</v>
       </c>
       <c r="J31" t="n">
-        <v>9556.23</v>
+        <v>10041.52</v>
       </c>
       <c r="K31" t="n">
-        <v>9743.549999999999</v>
+        <v>10182.75</v>
       </c>
       <c r="L31" t="n">
-        <v>9930.879999999999</v>
+        <v>10323.97</v>
       </c>
       <c r="M31" t="n">
-        <v>10191.25</v>
+        <v>10689.85</v>
       </c>
       <c r="N31" t="n">
-        <v>10451.63</v>
+        <v>11055.73</v>
       </c>
       <c r="O31" t="n">
-        <v>10565.9</v>
+        <v>10972.3</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3096,20 +3094,18 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3128,50 +3124,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10436.2</v>
+        <v>10601.5</v>
       </c>
       <c r="C32" t="n">
-        <v>10687.9</v>
+        <v>10667.6</v>
       </c>
       <c r="D32" t="n">
-        <v>10330.9</v>
+        <v>10528.6</v>
       </c>
       <c r="E32" t="n">
-        <v>10600.5</v>
+        <v>10667.6</v>
       </c>
       <c r="F32" t="n">
-        <v>164.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0063</v>
       </c>
       <c r="H32" t="n">
-        <v>357</v>
+        <v>139</v>
       </c>
       <c r="I32" t="n">
-        <v>9451</v>
+        <v>9973.9</v>
       </c>
       <c r="J32" t="n">
-        <v>10041.52</v>
+        <v>10289.05</v>
       </c>
       <c r="K32" t="n">
-        <v>10182.75</v>
+        <v>10422</v>
       </c>
       <c r="L32" t="n">
-        <v>10323.97</v>
+        <v>10554.95</v>
       </c>
       <c r="M32" t="n">
-        <v>10689.85</v>
+        <v>10779</v>
       </c>
       <c r="N32" t="n">
-        <v>11055.73</v>
+        <v>11003.05</v>
       </c>
       <c r="O32" t="n">
-        <v>10972.3</v>
+        <v>11044.9</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3182,7 +3178,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3205,76 +3201,80 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10601.5</v>
+        <v>10668.4</v>
       </c>
       <c r="C33" t="n">
-        <v>10667.6</v>
+        <v>10683.7</v>
       </c>
       <c r="D33" t="n">
-        <v>10528.6</v>
+        <v>10361.5</v>
       </c>
       <c r="E33" t="n">
-        <v>10667.6</v>
+        <v>10379.1</v>
       </c>
       <c r="F33" t="n">
-        <v>67.09999999999999</v>
+        <v>-288.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0063</v>
+        <v>-0.027</v>
       </c>
       <c r="H33" t="n">
-        <v>139</v>
+        <v>322.2</v>
       </c>
       <c r="I33" t="n">
-        <v>9973.9</v>
+        <v>10389.6</v>
       </c>
       <c r="J33" t="n">
-        <v>10289.05</v>
+        <v>10563.35</v>
       </c>
       <c r="K33" t="n">
-        <v>10422</v>
+        <v>10598.1</v>
       </c>
       <c r="L33" t="n">
-        <v>10554.95</v>
+        <v>10632.85</v>
       </c>
       <c r="M33" t="n">
-        <v>10779</v>
+        <v>10737.1</v>
       </c>
       <c r="N33" t="n">
-        <v>11003.05</v>
+        <v>10841.35</v>
       </c>
       <c r="O33" t="n">
-        <v>11044.9</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+        <v>10806.6</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3289,76 +3289,72 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10668.4</v>
+        <v>10378.5</v>
       </c>
       <c r="C34" t="n">
-        <v>10683.7</v>
+        <v>10410.8</v>
       </c>
       <c r="D34" t="n">
-        <v>10361.5</v>
+        <v>10188.7</v>
       </c>
       <c r="E34" t="n">
-        <v>10379.1</v>
+        <v>10363.9</v>
       </c>
       <c r="F34" t="n">
-        <v>-288.5</v>
+        <v>-15.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.0015</v>
       </c>
       <c r="H34" t="n">
-        <v>322.2</v>
+        <v>222.1</v>
       </c>
       <c r="I34" t="n">
-        <v>10389.6</v>
+        <v>10039.3</v>
       </c>
       <c r="J34" t="n">
-        <v>10563.35</v>
+        <v>9985.15</v>
       </c>
       <c r="K34" t="n">
-        <v>10598.1</v>
+        <v>10218</v>
       </c>
       <c r="L34" t="n">
-        <v>10632.85</v>
+        <v>10450.85</v>
       </c>
       <c r="M34" t="n">
-        <v>10737.1</v>
+        <v>10540.2</v>
       </c>
       <c r="N34" t="n">
-        <v>10841.35</v>
+        <v>10629.55</v>
       </c>
       <c r="O34" t="n">
-        <v>10806.6</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
+        <v>11005.9</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3375,79 +3371,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10378.5</v>
+        <v>10365.4</v>
       </c>
       <c r="C35" t="n">
-        <v>10410.8</v>
+        <v>10488.2</v>
       </c>
       <c r="D35" t="n">
-        <v>10188.7</v>
+        <v>10164.3</v>
       </c>
       <c r="E35" t="n">
-        <v>10363.9</v>
+        <v>10233.1</v>
       </c>
       <c r="F35" t="n">
-        <v>-15.2</v>
+        <v>-130.8</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0126</v>
       </c>
       <c r="H35" t="n">
-        <v>222.1</v>
+        <v>323.9</v>
       </c>
       <c r="I35" t="n">
-        <v>10039.3</v>
+        <v>9966.6</v>
       </c>
       <c r="J35" t="n">
-        <v>9985.15</v>
+        <v>10173.88</v>
       </c>
       <c r="K35" t="n">
-        <v>10218</v>
+        <v>10252.85</v>
       </c>
       <c r="L35" t="n">
-        <v>10450.85</v>
+        <v>10331.83</v>
       </c>
       <c r="M35" t="n">
-        <v>10540.2</v>
+        <v>10474.95</v>
       </c>
       <c r="N35" t="n">
-        <v>10629.55</v>
+        <v>10618.08</v>
       </c>
       <c r="O35" t="n">
-        <v>11005.9</v>
+        <v>10632.9</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3459,78 +3455,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10365.4</v>
+        <v>10233.6</v>
       </c>
       <c r="C36" t="n">
-        <v>10488.2</v>
+        <v>10375.7</v>
       </c>
       <c r="D36" t="n">
-        <v>10164.3</v>
+        <v>10152.1</v>
       </c>
       <c r="E36" t="n">
-        <v>10233.1</v>
+        <v>10195.4</v>
       </c>
       <c r="F36" t="n">
-        <v>-130.8</v>
+        <v>-37.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0037</v>
       </c>
       <c r="H36" t="n">
-        <v>323.9</v>
+        <v>223.6</v>
       </c>
       <c r="I36" t="n">
-        <v>9966.6</v>
+        <v>9840.4</v>
       </c>
       <c r="J36" t="n">
-        <v>10173.88</v>
+        <v>9862.620000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>10252.85</v>
+        <v>10071.15</v>
       </c>
       <c r="L36" t="n">
-        <v>10331.83</v>
+        <v>10279.67</v>
       </c>
       <c r="M36" t="n">
-        <v>10474.95</v>
+        <v>10395.05</v>
       </c>
       <c r="N36" t="n">
-        <v>10618.08</v>
+        <v>10510.42</v>
       </c>
       <c r="O36" t="n">
-        <v>10632.9</v>
+        <v>10812.1</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3543,59 +3537,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10233.6</v>
+        <v>10194.8</v>
       </c>
       <c r="C37" t="n">
-        <v>10375.7</v>
+        <v>10497.2</v>
       </c>
       <c r="D37" t="n">
-        <v>10152.1</v>
+        <v>10151.5</v>
       </c>
       <c r="E37" t="n">
-        <v>10195.4</v>
+        <v>10466.3</v>
       </c>
       <c r="F37" t="n">
-        <v>-37.7</v>
+        <v>270.9</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0266</v>
       </c>
       <c r="H37" t="n">
-        <v>223.6</v>
+        <v>345.7</v>
       </c>
       <c r="I37" t="n">
-        <v>9840.4</v>
+        <v>9928.5</v>
       </c>
       <c r="J37" t="n">
-        <v>9862.620000000001</v>
+        <v>9937.549999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>10071.15</v>
+        <v>10083.6</v>
       </c>
       <c r="L37" t="n">
-        <v>10279.67</v>
+        <v>10229.65</v>
       </c>
       <c r="M37" t="n">
-        <v>10395.05</v>
+        <v>10307.2</v>
       </c>
       <c r="N37" t="n">
-        <v>10510.42</v>
+        <v>10384.75</v>
       </c>
       <c r="O37" t="n">
-        <v>10812.1</v>
+        <v>10599.3</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3608,72 +3598,80 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="W37" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10194.8</v>
+        <v>10465.6</v>
       </c>
       <c r="C38" t="n">
-        <v>10497.2</v>
+        <v>10557.2</v>
       </c>
       <c r="D38" t="n">
-        <v>10151.5</v>
+        <v>10381.2</v>
       </c>
       <c r="E38" t="n">
-        <v>10466.3</v>
+        <v>10409.3</v>
       </c>
       <c r="F38" t="n">
-        <v>270.9</v>
+        <v>-57</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0266</v>
+        <v>-0.0054</v>
       </c>
       <c r="H38" t="n">
-        <v>345.7</v>
+        <v>176</v>
       </c>
       <c r="I38" t="n">
-        <v>9928.5</v>
+        <v>9805.799999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>9937.549999999999</v>
+        <v>10191.57</v>
       </c>
       <c r="K38" t="n">
-        <v>10083.6</v>
+        <v>10293.45</v>
       </c>
       <c r="L38" t="n">
-        <v>10229.65</v>
+        <v>10395.32</v>
       </c>
       <c r="M38" t="n">
-        <v>10307.2</v>
+        <v>10639.15</v>
       </c>
       <c r="N38" t="n">
-        <v>10384.75</v>
+        <v>10882.97</v>
       </c>
       <c r="O38" t="n">
-        <v>10599.3</v>
+        <v>10842.9</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3684,20 +3682,16 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3716,50 +3710,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10465.6</v>
+        <v>10409.3</v>
       </c>
       <c r="C39" t="n">
-        <v>10557.2</v>
+        <v>10415.7</v>
       </c>
       <c r="D39" t="n">
-        <v>10381.2</v>
+        <v>10238.6</v>
       </c>
       <c r="E39" t="n">
-        <v>10409.3</v>
+        <v>10368.1</v>
       </c>
       <c r="F39" t="n">
-        <v>-57</v>
+        <v>-41.2</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.004</v>
       </c>
       <c r="H39" t="n">
-        <v>176</v>
+        <v>177.1</v>
       </c>
       <c r="I39" t="n">
-        <v>9805.799999999999</v>
+        <v>10205.2</v>
       </c>
       <c r="J39" t="n">
-        <v>10191.57</v>
+        <v>10203.35</v>
       </c>
       <c r="K39" t="n">
-        <v>10293.45</v>
+        <v>10321.3</v>
       </c>
       <c r="L39" t="n">
-        <v>10395.32</v>
+        <v>10439.25</v>
       </c>
       <c r="M39" t="n">
-        <v>10639.15</v>
+        <v>10497.3</v>
       </c>
       <c r="N39" t="n">
-        <v>10882.97</v>
+        <v>10555.35</v>
       </c>
       <c r="O39" t="n">
-        <v>10842.9</v>
+        <v>10733.2</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3767,12 +3761,14 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3791,77 +3787,81 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10409.3</v>
+        <v>10369.1</v>
       </c>
       <c r="C40" t="n">
-        <v>10415.7</v>
+        <v>10471.7</v>
       </c>
       <c r="D40" t="n">
-        <v>10238.6</v>
+        <v>10127.6</v>
       </c>
       <c r="E40" t="n">
-        <v>10368.1</v>
+        <v>10471.7</v>
       </c>
       <c r="F40" t="n">
-        <v>-41.2</v>
+        <v>103.6</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.01</v>
       </c>
       <c r="H40" t="n">
-        <v>177.1</v>
+        <v>344.1</v>
       </c>
       <c r="I40" t="n">
-        <v>10205.2</v>
+        <v>10061.5</v>
       </c>
       <c r="J40" t="n">
-        <v>10203.35</v>
+        <v>10211.47</v>
       </c>
       <c r="K40" t="n">
-        <v>10321.3</v>
+        <v>10279.55</v>
       </c>
       <c r="L40" t="n">
-        <v>10439.25</v>
+        <v>10347.62</v>
       </c>
       <c r="M40" t="n">
-        <v>10497.3</v>
+        <v>10456.65</v>
       </c>
       <c r="N40" t="n">
-        <v>10555.35</v>
+        <v>10565.68</v>
       </c>
       <c r="O40" t="n">
-        <v>10733.2</v>
+        <v>10592.8</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3875,80 +3875,74 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10369.1</v>
+        <v>10471.4</v>
       </c>
       <c r="C41" t="n">
-        <v>10471.7</v>
+        <v>10570.1</v>
       </c>
       <c r="D41" t="n">
-        <v>10127.6</v>
+        <v>10352.9</v>
       </c>
       <c r="E41" t="n">
-        <v>10471.7</v>
+        <v>10363.3</v>
       </c>
       <c r="F41" t="n">
-        <v>103.6</v>
+        <v>-108.4</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0104</v>
       </c>
       <c r="H41" t="n">
-        <v>344.1</v>
+        <v>217.2</v>
       </c>
       <c r="I41" t="n">
-        <v>10061.5</v>
+        <v>9783.5</v>
       </c>
       <c r="J41" t="n">
-        <v>10211.47</v>
+        <v>10213.62</v>
       </c>
       <c r="K41" t="n">
-        <v>10279.55</v>
+        <v>10299.65</v>
       </c>
       <c r="L41" t="n">
-        <v>10347.62</v>
+        <v>10385.68</v>
       </c>
       <c r="M41" t="n">
-        <v>10456.65</v>
+        <v>10643.75</v>
       </c>
       <c r="N41" t="n">
-        <v>10565.68</v>
+        <v>10901.83</v>
       </c>
       <c r="O41" t="n">
-        <v>10592.8</v>
+        <v>10815.8</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3970,50 +3964,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10471.4</v>
+        <v>10363.6</v>
       </c>
       <c r="C42" t="n">
-        <v>10570.1</v>
+        <v>10575.3</v>
       </c>
       <c r="D42" t="n">
-        <v>10352.9</v>
+        <v>10332.4</v>
       </c>
       <c r="E42" t="n">
-        <v>10363.3</v>
+        <v>10508</v>
       </c>
       <c r="F42" t="n">
-        <v>-108.4</v>
+        <v>144.7</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.014</v>
       </c>
       <c r="H42" t="n">
-        <v>217.2</v>
+        <v>242.9</v>
       </c>
       <c r="I42" t="n">
-        <v>9783.5</v>
+        <v>10135.7</v>
       </c>
       <c r="J42" t="n">
-        <v>10213.62</v>
+        <v>10097</v>
       </c>
       <c r="K42" t="n">
-        <v>10299.65</v>
+        <v>10254.7</v>
       </c>
       <c r="L42" t="n">
-        <v>10385.68</v>
+        <v>10412.4</v>
       </c>
       <c r="M42" t="n">
-        <v>10643.75</v>
+        <v>10471.9</v>
       </c>
       <c r="N42" t="n">
-        <v>10901.83</v>
+        <v>10531.4</v>
       </c>
       <c r="O42" t="n">
-        <v>10815.8</v>
+        <v>10787.3</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4026,14 +4020,18 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4052,50 +4050,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10363.6</v>
+        <v>10507.8</v>
       </c>
       <c r="C43" t="n">
-        <v>10575.3</v>
+        <v>10701.3</v>
       </c>
       <c r="D43" t="n">
-        <v>10332.4</v>
+        <v>10429.2</v>
       </c>
       <c r="E43" t="n">
-        <v>10508</v>
+        <v>10679</v>
       </c>
       <c r="F43" t="n">
-        <v>144.7</v>
+        <v>171</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0163</v>
       </c>
       <c r="H43" t="n">
-        <v>242.9</v>
+        <v>272.1</v>
       </c>
       <c r="I43" t="n">
-        <v>10135.7</v>
+        <v>10089.5</v>
       </c>
       <c r="J43" t="n">
-        <v>10097</v>
+        <v>10292.18</v>
       </c>
       <c r="K43" t="n">
-        <v>10254.7</v>
+        <v>10386.55</v>
       </c>
       <c r="L43" t="n">
-        <v>10412.4</v>
+        <v>10480.93</v>
       </c>
       <c r="M43" t="n">
-        <v>10471.9</v>
+        <v>10629.45</v>
       </c>
       <c r="N43" t="n">
-        <v>10531.4</v>
+        <v>10777.97</v>
       </c>
       <c r="O43" t="n">
-        <v>10787.3</v>
+        <v>10818.2</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4106,21 +4104,19 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
@@ -4129,78 +4125,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10507.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C44" t="n">
-        <v>10701.3</v>
+        <v>10747</v>
       </c>
       <c r="D44" t="n">
-        <v>10429.2</v>
+        <v>10397.5</v>
       </c>
       <c r="E44" t="n">
-        <v>10679</v>
+        <v>10497.3</v>
       </c>
       <c r="F44" t="n">
-        <v>171</v>
+        <v>-181.7</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.017</v>
       </c>
       <c r="H44" t="n">
-        <v>272.1</v>
+        <v>349.5</v>
       </c>
       <c r="I44" t="n">
-        <v>10089.5</v>
+        <v>10157.1</v>
       </c>
       <c r="J44" t="n">
-        <v>10292.18</v>
+        <v>10463.78</v>
       </c>
       <c r="K44" t="n">
-        <v>10386.55</v>
+        <v>10542.95</v>
       </c>
       <c r="L44" t="n">
-        <v>10480.93</v>
+        <v>10622.12</v>
       </c>
       <c r="M44" t="n">
-        <v>10629.45</v>
+        <v>10815.05</v>
       </c>
       <c r="N44" t="n">
-        <v>10777.97</v>
+        <v>11007.97</v>
       </c>
       <c r="O44" t="n">
-        <v>10818.2</v>
+        <v>10973.4</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4213,72 +4207,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10679.4</v>
+        <v>10498.1</v>
       </c>
       <c r="C45" t="n">
-        <v>10747</v>
+        <v>10623.7</v>
       </c>
       <c r="D45" t="n">
-        <v>10397.5</v>
+        <v>10423</v>
       </c>
       <c r="E45" t="n">
-        <v>10497.3</v>
+        <v>10600.4</v>
       </c>
       <c r="F45" t="n">
-        <v>-181.7</v>
+        <v>103.1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.017</v>
+        <v>0.0098</v>
       </c>
       <c r="H45" t="n">
-        <v>349.5</v>
+        <v>200.7</v>
       </c>
       <c r="I45" t="n">
-        <v>10157.1</v>
+        <v>10048</v>
       </c>
       <c r="J45" t="n">
-        <v>10463.78</v>
+        <v>10110.32</v>
       </c>
       <c r="K45" t="n">
-        <v>10542.95</v>
+        <v>10322.55</v>
       </c>
       <c r="L45" t="n">
-        <v>10622.12</v>
+        <v>10534.77</v>
       </c>
       <c r="M45" t="n">
-        <v>10815.05</v>
+        <v>10672.05</v>
       </c>
       <c r="N45" t="n">
-        <v>11007.97</v>
+        <v>10809.32</v>
       </c>
       <c r="O45" t="n">
-        <v>10973.4</v>
+        <v>11096.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4297,57 +4291,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10498.1</v>
+        <v>10600.3</v>
       </c>
       <c r="C46" t="n">
-        <v>10623.7</v>
+        <v>10763.4</v>
       </c>
       <c r="D46" t="n">
-        <v>10423</v>
+        <v>10483.1</v>
       </c>
       <c r="E46" t="n">
-        <v>10600.4</v>
+        <v>10736.2</v>
       </c>
       <c r="F46" t="n">
-        <v>103.1</v>
+        <v>135.8</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0128</v>
       </c>
       <c r="H46" t="n">
-        <v>200.7</v>
+        <v>280.3</v>
       </c>
       <c r="I46" t="n">
-        <v>10048</v>
+        <v>10222.3</v>
       </c>
       <c r="J46" t="n">
-        <v>10110.32</v>
+        <v>10438.23</v>
       </c>
       <c r="K46" t="n">
-        <v>10322.55</v>
+        <v>10500.05</v>
       </c>
       <c r="L46" t="n">
-        <v>10534.77</v>
+        <v>10561.88</v>
       </c>
       <c r="M46" t="n">
-        <v>10672.05</v>
+        <v>10700.75</v>
       </c>
       <c r="N46" t="n">
-        <v>10809.32</v>
+        <v>10839.63</v>
       </c>
       <c r="O46" t="n">
-        <v>11096.5</v>
+        <v>10824.4</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4355,16 +4349,20 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4377,59 +4375,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10600.3</v>
+        <v>10736.1</v>
       </c>
       <c r="C47" t="n">
-        <v>10763.4</v>
+        <v>10989.5</v>
       </c>
       <c r="D47" t="n">
-        <v>10483.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E47" t="n">
-        <v>10736.2</v>
+        <v>10868.1</v>
       </c>
       <c r="F47" t="n">
-        <v>135.8</v>
+        <v>131.9</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0123</v>
       </c>
       <c r="H47" t="n">
-        <v>280.3</v>
+        <v>253.4</v>
       </c>
       <c r="I47" t="n">
-        <v>10222.3</v>
+        <v>10202.8</v>
       </c>
       <c r="J47" t="n">
-        <v>10438.23</v>
+        <v>10512.37</v>
       </c>
       <c r="K47" t="n">
-        <v>10500.05</v>
+        <v>10596.05</v>
       </c>
       <c r="L47" t="n">
-        <v>10561.88</v>
+        <v>10679.73</v>
       </c>
       <c r="M47" t="n">
-        <v>10700.75</v>
+        <v>10876.35</v>
       </c>
       <c r="N47" t="n">
-        <v>10839.63</v>
+        <v>11072.98</v>
       </c>
       <c r="O47" t="n">
-        <v>10824.4</v>
+        <v>11043.7</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4437,12 +4431,10 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4468,50 +4460,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10736.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C48" t="n">
-        <v>10989.5</v>
+        <v>10959.9</v>
       </c>
       <c r="D48" t="n">
-        <v>10736.1</v>
+        <v>10832.5</v>
       </c>
       <c r="E48" t="n">
-        <v>10868.1</v>
+        <v>10901.1</v>
       </c>
       <c r="F48" t="n">
-        <v>131.9</v>
+        <v>33</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0123</v>
+        <v>0.003</v>
       </c>
       <c r="H48" t="n">
-        <v>253.4</v>
+        <v>127.4</v>
       </c>
       <c r="I48" t="n">
-        <v>10202.8</v>
+        <v>10482.7</v>
       </c>
       <c r="J48" t="n">
-        <v>10512.37</v>
+        <v>10617.35</v>
       </c>
       <c r="K48" t="n">
-        <v>10596.05</v>
+        <v>10741.4</v>
       </c>
       <c r="L48" t="n">
-        <v>10679.73</v>
+        <v>10865.45</v>
       </c>
       <c r="M48" t="n">
-        <v>10876.35</v>
+        <v>10994.8</v>
       </c>
       <c r="N48" t="n">
-        <v>11072.98</v>
+        <v>11124.15</v>
       </c>
       <c r="O48" t="n">
-        <v>11043.7</v>
+        <v>11242.9</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4522,15 +4514,13 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4543,68 +4533,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10868.1</v>
+        <v>10901.1</v>
       </c>
       <c r="C49" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D49" t="n">
-        <v>10832.5</v>
+        <v>10723.7</v>
       </c>
       <c r="E49" t="n">
-        <v>10901.1</v>
+        <v>10750.1</v>
       </c>
       <c r="F49" t="n">
-        <v>33</v>
+        <v>-151</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0139</v>
       </c>
       <c r="H49" t="n">
-        <v>127.4</v>
+        <v>187.2</v>
       </c>
       <c r="I49" t="n">
-        <v>10482.7</v>
+        <v>10705.1</v>
       </c>
       <c r="J49" t="n">
-        <v>10617.35</v>
+        <v>10776.15</v>
       </c>
       <c r="K49" t="n">
-        <v>10741.4</v>
+        <v>10837.4</v>
       </c>
       <c r="L49" t="n">
-        <v>10865.45</v>
+        <v>10898.65</v>
       </c>
       <c r="M49" t="n">
-        <v>10994.8</v>
+        <v>10964.8</v>
       </c>
       <c r="N49" t="n">
-        <v>11124.15</v>
+        <v>11030.95</v>
       </c>
       <c r="O49" t="n">
-        <v>11242.9</v>
+        <v>11087.3</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4616,86 +4614,80 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10901.1</v>
+        <v>10750</v>
       </c>
       <c r="C50" t="n">
-        <v>10910.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D50" t="n">
-        <v>10723.7</v>
+        <v>10684.4</v>
       </c>
       <c r="E50" t="n">
-        <v>10750.1</v>
+        <v>10816.6</v>
       </c>
       <c r="F50" t="n">
-        <v>-151</v>
+        <v>66.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0139</v>
+        <v>0.0062</v>
       </c>
       <c r="H50" t="n">
-        <v>187.2</v>
+        <v>147.2</v>
       </c>
       <c r="I50" t="n">
-        <v>10705.1</v>
+        <v>10536.5</v>
       </c>
       <c r="J50" t="n">
-        <v>10776.15</v>
+        <v>10529.3</v>
       </c>
       <c r="K50" t="n">
-        <v>10837.4</v>
+        <v>10656.5</v>
       </c>
       <c r="L50" t="n">
-        <v>10898.65</v>
+        <v>10783.7</v>
       </c>
       <c r="M50" t="n">
-        <v>10964.8</v>
+        <v>10843.7</v>
       </c>
       <c r="N50" t="n">
-        <v>11030.95</v>
+        <v>10903.7</v>
       </c>
       <c r="O50" t="n">
-        <v>11087.3</v>
+        <v>11098.1</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
@@ -4707,55 +4699,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10750</v>
+        <v>10816.3</v>
       </c>
       <c r="C51" t="n">
-        <v>10831.6</v>
+        <v>10920.5</v>
       </c>
       <c r="D51" t="n">
-        <v>10684.4</v>
+        <v>10772.6</v>
       </c>
       <c r="E51" t="n">
-        <v>10816.6</v>
+        <v>10824.3</v>
       </c>
       <c r="F51" t="n">
-        <v>66.5</v>
+        <v>7.7</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0007</v>
       </c>
       <c r="H51" t="n">
-        <v>147.2</v>
+        <v>147.9</v>
       </c>
       <c r="I51" t="n">
-        <v>10536.5</v>
+        <v>10537.2</v>
       </c>
       <c r="J51" t="n">
-        <v>10529.3</v>
+        <v>10698.7</v>
       </c>
       <c r="K51" t="n">
-        <v>10656.5</v>
+        <v>10743</v>
       </c>
       <c r="L51" t="n">
-        <v>10783.7</v>
+        <v>10787.3</v>
       </c>
       <c r="M51" t="n">
-        <v>10843.7</v>
+        <v>10890.2</v>
       </c>
       <c r="N51" t="n">
-        <v>10903.7</v>
+        <v>10993.1</v>
       </c>
       <c r="O51" t="n">
-        <v>11098.1</v>
+        <v>10978.8</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4766,14 +4762,14 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U51" s="8" t="n">
@@ -4789,57 +4785,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10816.3</v>
+        <v>10824.6</v>
       </c>
       <c r="C52" t="n">
-        <v>10920.5</v>
+        <v>10866.8</v>
       </c>
       <c r="D52" t="n">
-        <v>10772.6</v>
+        <v>10689.6</v>
       </c>
       <c r="E52" t="n">
-        <v>10824.3</v>
+        <v>10831.1</v>
       </c>
       <c r="F52" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>147.9</v>
+        <v>177.2</v>
       </c>
       <c r="I52" t="n">
-        <v>10537.2</v>
+        <v>10624.7</v>
       </c>
       <c r="J52" t="n">
-        <v>10698.7</v>
+        <v>10665.27</v>
       </c>
       <c r="K52" t="n">
-        <v>10743</v>
+        <v>10750.35</v>
       </c>
       <c r="L52" t="n">
-        <v>10787.3</v>
+        <v>10835.42</v>
       </c>
       <c r="M52" t="n">
-        <v>10890.2</v>
+        <v>10898.25</v>
       </c>
       <c r="N52" t="n">
-        <v>10993.1</v>
+        <v>10961.08</v>
       </c>
       <c r="O52" t="n">
-        <v>10978.8</v>
+        <v>11068.4</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4847,18 +4843,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4873,72 +4869,74 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10824.6</v>
+        <v>10831</v>
       </c>
       <c r="C53" t="n">
-        <v>10866.8</v>
+        <v>10868.3</v>
       </c>
       <c r="D53" t="n">
-        <v>10689.6</v>
+        <v>10594.3</v>
       </c>
       <c r="E53" t="n">
-        <v>10831.1</v>
+        <v>10650.4</v>
       </c>
       <c r="F53" t="n">
-        <v>6.8</v>
+        <v>-180.7</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0167</v>
       </c>
       <c r="H53" t="n">
-        <v>177.2</v>
+        <v>274</v>
       </c>
       <c r="I53" t="n">
-        <v>10624.7</v>
+        <v>10512.4</v>
       </c>
       <c r="J53" t="n">
-        <v>10665.27</v>
+        <v>10680.35</v>
       </c>
       <c r="K53" t="n">
-        <v>10750.35</v>
+        <v>10742.5</v>
       </c>
       <c r="L53" t="n">
-        <v>10835.42</v>
+        <v>10804.65</v>
       </c>
       <c r="M53" t="n">
-        <v>10898.25</v>
+        <v>10919.7</v>
       </c>
       <c r="N53" t="n">
-        <v>10961.08</v>
+        <v>11034.75</v>
       </c>
       <c r="O53" t="n">
-        <v>11068.4</v>
+        <v>11044</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4964,71 +4962,69 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10831</v>
+        <v>10650.9</v>
       </c>
       <c r="C54" t="n">
-        <v>10868.3</v>
+        <v>10823</v>
       </c>
       <c r="D54" t="n">
-        <v>10594.3</v>
+        <v>10586.4</v>
       </c>
       <c r="E54" t="n">
-        <v>10650.4</v>
+        <v>10659.1</v>
       </c>
       <c r="F54" t="n">
-        <v>-180.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0167</v>
+        <v>0.0008</v>
       </c>
       <c r="H54" t="n">
-        <v>274</v>
+        <v>236.6</v>
       </c>
       <c r="I54" t="n">
-        <v>10512.4</v>
+        <v>10320.3</v>
       </c>
       <c r="J54" t="n">
-        <v>10680.35</v>
+        <v>10335.95</v>
       </c>
       <c r="K54" t="n">
-        <v>10742.5</v>
+        <v>10513.4</v>
       </c>
       <c r="L54" t="n">
-        <v>10804.65</v>
+        <v>10690.85</v>
       </c>
       <c r="M54" t="n">
-        <v>10919.7</v>
+        <v>10787.4</v>
       </c>
       <c r="N54" t="n">
-        <v>11034.75</v>
+        <v>10883.95</v>
       </c>
       <c r="O54" t="n">
-        <v>11044</v>
+        <v>11142.3</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5050,50 +5046,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10650.9</v>
+        <v>10659.1</v>
       </c>
       <c r="C55" t="n">
-        <v>10823</v>
+        <v>10774.7</v>
       </c>
       <c r="D55" t="n">
-        <v>10586.4</v>
+        <v>10656.7</v>
       </c>
       <c r="E55" t="n">
-        <v>10659.1</v>
+        <v>10695.3</v>
       </c>
       <c r="F55" t="n">
-        <v>8.699999999999999</v>
+        <v>36.2</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0034</v>
       </c>
       <c r="H55" t="n">
-        <v>236.6</v>
+        <v>118</v>
       </c>
       <c r="I55" t="n">
-        <v>10320.3</v>
+        <v>10349.8</v>
       </c>
       <c r="J55" t="n">
-        <v>10335.95</v>
+        <v>10399.7</v>
       </c>
       <c r="K55" t="n">
-        <v>10513.4</v>
+        <v>10540.8</v>
       </c>
       <c r="L55" t="n">
-        <v>10690.85</v>
+        <v>10681.9</v>
       </c>
       <c r="M55" t="n">
-        <v>10787.4</v>
+        <v>10777.4</v>
       </c>
       <c r="N55" t="n">
-        <v>10883.95</v>
+        <v>10872.9</v>
       </c>
       <c r="O55" t="n">
-        <v>11142.3</v>
+        <v>11059.6</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5106,13 +5102,11 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5127,74 +5121,82 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10659.1</v>
+        <v>10695.2</v>
       </c>
       <c r="C56" t="n">
-        <v>10774.7</v>
+        <v>10758.7</v>
       </c>
       <c r="D56" t="n">
-        <v>10656.7</v>
+        <v>10390.7</v>
       </c>
       <c r="E56" t="n">
-        <v>10695.3</v>
+        <v>10462</v>
       </c>
       <c r="F56" t="n">
-        <v>36.2</v>
+        <v>-233.3</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.0218</v>
       </c>
       <c r="H56" t="n">
-        <v>118</v>
+        <v>368</v>
       </c>
       <c r="I56" t="n">
-        <v>10349.8</v>
+        <v>10538.7</v>
       </c>
       <c r="J56" t="n">
-        <v>10399.7</v>
+        <v>10567.1</v>
       </c>
       <c r="K56" t="n">
-        <v>10540.8</v>
+        <v>10636.3</v>
       </c>
       <c r="L56" t="n">
-        <v>10681.9</v>
+        <v>10705.5</v>
       </c>
       <c r="M56" t="n">
-        <v>10777.4</v>
+        <v>10754.3</v>
       </c>
       <c r="N56" t="n">
-        <v>10872.9</v>
+        <v>10803.1</v>
       </c>
       <c r="O56" t="n">
-        <v>11059.6</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+        <v>10892.7</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5207,84 +5209,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10695.2</v>
+        <v>10462.4</v>
       </c>
       <c r="C57" t="n">
-        <v>10758.7</v>
+        <v>10602.6</v>
       </c>
       <c r="D57" t="n">
-        <v>10390.7</v>
+        <v>10367.3</v>
       </c>
       <c r="E57" t="n">
-        <v>10462</v>
+        <v>10552.05</v>
       </c>
       <c r="F57" t="n">
-        <v>-233.3</v>
+        <v>90.05</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0218</v>
+        <v>0.0086</v>
       </c>
       <c r="H57" t="n">
-        <v>368</v>
+        <v>235.3</v>
       </c>
       <c r="I57" t="n">
-        <v>10538.7</v>
+        <v>10022.7</v>
       </c>
       <c r="J57" t="n">
-        <v>10567.1</v>
+        <v>10037.65</v>
       </c>
       <c r="K57" t="n">
-        <v>10636.3</v>
+        <v>10278</v>
       </c>
       <c r="L57" t="n">
-        <v>10705.5</v>
+        <v>10518.35</v>
       </c>
       <c r="M57" t="n">
-        <v>10754.3</v>
+        <v>10646</v>
       </c>
       <c r="N57" t="n">
-        <v>10803.1</v>
+        <v>10773.65</v>
       </c>
       <c r="O57" t="n">
-        <v>10892.7</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>11126.7</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5297,85 +5287,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>10462.4</v>
-      </c>
-      <c r="C58" t="n">
-        <v>10602.6</v>
-      </c>
-      <c r="D58" t="n">
-        <v>10367.25</v>
-      </c>
-      <c r="E58" t="n">
-        <v>10441.6</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-20.4</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0019</v>
-      </c>
-      <c r="H58" t="n">
-        <v>235.35</v>
-      </c>
-      <c r="I58" t="n">
-        <v>10022.7</v>
-      </c>
-      <c r="J58" t="n">
-        <v>10037.65</v>
-      </c>
-      <c r="K58" t="n">
-        <v>10278</v>
-      </c>
-      <c r="L58" t="n">
-        <v>10518.35</v>
-      </c>
-      <c r="M58" t="n">
-        <v>10646</v>
-      </c>
-      <c r="N58" t="n">
-        <v>10773.65</v>
-      </c>
-      <c r="O58" t="n">
-        <v>11126.7</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -5227,10 +5227,10 @@
         <v>10367.3</v>
       </c>
       <c r="E57" t="n">
-        <v>10552.05</v>
+        <v>10552.1</v>
       </c>
       <c r="F57" t="n">
-        <v>90.05</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G57" s="5" t="n">
         <v>0.0086</v>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +659,25 @@
         <v>118.7</v>
       </c>
       <c r="I2" t="n">
-        <v>9040.5</v>
+        <v>9102.1</v>
       </c>
       <c r="J2" t="n">
-        <v>9142.02</v>
+        <v>9165.120000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>9208.25</v>
+        <v>9223.65</v>
       </c>
       <c r="L2" t="n">
-        <v>9274.469999999999</v>
+        <v>9282.18</v>
       </c>
       <c r="M2" t="n">
-        <v>9358.35</v>
+        <v>9342.950000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>9442.23</v>
+        <v>9403.719999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>9490.799999999999</v>
+        <v>9460</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -711,7 +711,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
@@ -5290,6 +5290,90 @@
       <c r="X57" t="inlineStr">
         <is>
           <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10551.6</v>
+      </c>
+      <c r="C58" t="n">
+        <v>10656.3</v>
+      </c>
+      <c r="D58" t="n">
+        <v>10549.6</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10656.3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10132</v>
+      </c>
+      <c r="J58" t="n">
+        <v>10350.37</v>
+      </c>
+      <c r="K58" t="n">
+        <v>10434.45</v>
+      </c>
+      <c r="L58" t="n">
+        <v>10518.52</v>
+      </c>
+      <c r="M58" t="n">
+        <v>10669.75</v>
+      </c>
+      <c r="N58" t="n">
+        <v>10820.97</v>
+      </c>
+      <c r="O58" t="n">
+        <v>10837.9</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>118.7</v>
       </c>
       <c r="I2" t="n">
-        <v>9102.1</v>
+        <v>9104.1</v>
       </c>
       <c r="J2" t="n">
-        <v>9165.120000000001</v>
+        <v>9165.870000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>9223.65</v>
+        <v>9224.15</v>
       </c>
       <c r="L2" t="n">
-        <v>9282.18</v>
+        <v>9282.43</v>
       </c>
       <c r="M2" t="n">
-        <v>9342.950000000001</v>
+        <v>9342.450000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>9403.719999999999</v>
+        <v>9402.469999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>9460</v>
+        <v>9459</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5303,22 +5303,22 @@
         <v>10551.6</v>
       </c>
       <c r="C58" t="n">
-        <v>10656.3</v>
+        <v>10762.01</v>
       </c>
       <c r="D58" t="n">
         <v>10549.6</v>
       </c>
       <c r="E58" t="n">
-        <v>10656.3</v>
+        <v>10650.33</v>
       </c>
       <c r="F58" t="n">
-        <v>104.2</v>
+        <v>98.23</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>106.7</v>
+        <v>212.41</v>
       </c>
       <c r="I58" t="n">
         <v>10132</v>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>118.7</v>
       </c>
       <c r="I2" t="n">
-        <v>9104.1</v>
+        <v>9110.1</v>
       </c>
       <c r="J2" t="n">
-        <v>9165.870000000001</v>
+        <v>9168.120000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>9224.15</v>
+        <v>9225.65</v>
       </c>
       <c r="L2" t="n">
-        <v>9282.43</v>
+        <v>9283.18</v>
       </c>
       <c r="M2" t="n">
-        <v>9342.450000000001</v>
+        <v>9340.950000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>9402.469999999999</v>
+        <v>9398.719999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>9459</v>
+        <v>9456</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5303,22 +5303,22 @@
         <v>10551.6</v>
       </c>
       <c r="C58" t="n">
-        <v>10762.01</v>
+        <v>10762</v>
       </c>
       <c r="D58" t="n">
         <v>10549.6</v>
       </c>
       <c r="E58" t="n">
-        <v>10650.33</v>
+        <v>10724.86</v>
       </c>
       <c r="F58" t="n">
-        <v>98.23</v>
+        <v>172.76</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0164</v>
       </c>
       <c r="H58" t="n">
-        <v>212.41</v>
+        <v>212.4</v>
       </c>
       <c r="I58" t="n">
         <v>10132</v>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -659,35 +659,39 @@
         <v>118.7</v>
       </c>
       <c r="I2" t="n">
-        <v>9110.1</v>
+        <v>9225.9</v>
       </c>
       <c r="J2" t="n">
-        <v>9168.120000000001</v>
+        <v>9211.549999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>9225.65</v>
+        <v>9254.6</v>
       </c>
       <c r="L2" t="n">
-        <v>9283.18</v>
+        <v>9297.65</v>
       </c>
       <c r="M2" t="n">
-        <v>9340.950000000001</v>
+        <v>9312</v>
       </c>
       <c r="N2" t="n">
-        <v>9398.719999999999</v>
+        <v>9326.35</v>
       </c>
       <c r="O2" t="n">
-        <v>9456</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>9398.1</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -695,8 +699,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -5303,22 +5309,22 @@
         <v>10551.6</v>
       </c>
       <c r="C58" t="n">
-        <v>10762</v>
+        <v>10868.53</v>
       </c>
       <c r="D58" t="n">
         <v>10549.6</v>
       </c>
       <c r="E58" t="n">
-        <v>10724.86</v>
+        <v>10840.35</v>
       </c>
       <c r="F58" t="n">
-        <v>172.76</v>
+        <v>288.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0164</v>
+        <v>0.0273</v>
       </c>
       <c r="H58" t="n">
-        <v>212.4</v>
+        <v>318.93</v>
       </c>
       <c r="I58" t="n">
         <v>10132</v>
@@ -5357,25 +5363,25 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,76 +634,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9283.299999999999</v>
+        <v>9216.700000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>9314.4</v>
+        <v>9292.1</v>
       </c>
       <c r="D2" t="n">
-        <v>9195.700000000001</v>
+        <v>9177.1</v>
       </c>
       <c r="E2" t="n">
-        <v>9216.700000000001</v>
+        <v>9284.799999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-66.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.0074</v>
       </c>
       <c r="H2" t="n">
-        <v>118.7</v>
+        <v>115</v>
       </c>
       <c r="I2" t="n">
-        <v>9225.9</v>
+        <v>9077</v>
       </c>
       <c r="J2" t="n">
-        <v>9211.549999999999</v>
+        <v>9078.82</v>
       </c>
       <c r="K2" t="n">
-        <v>9254.6</v>
+        <v>9157.35</v>
       </c>
       <c r="L2" t="n">
-        <v>9297.65</v>
+        <v>9235.879999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>9312</v>
+        <v>9276.049999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>9326.35</v>
+        <v>9316.23</v>
       </c>
       <c r="O2" t="n">
-        <v>9398.1</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
+        <v>9433.1</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -717,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9216.700000000001</v>
+        <v>9284.799999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>9292.1</v>
+        <v>9494.6</v>
       </c>
       <c r="D3" t="n">
-        <v>9177.1</v>
+        <v>9266.299999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>9284.799999999999</v>
+        <v>9491.299999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>68.09999999999999</v>
+        <v>206.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0222</v>
       </c>
       <c r="H3" t="n">
-        <v>115</v>
+        <v>228.3</v>
       </c>
       <c r="I3" t="n">
-        <v>9077</v>
+        <v>9062.1</v>
       </c>
       <c r="J3" t="n">
-        <v>9078.82</v>
+        <v>9194.9</v>
       </c>
       <c r="K3" t="n">
-        <v>9157.35</v>
+        <v>9227.299999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>9235.879999999999</v>
+        <v>9259.700000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>9276.049999999999</v>
+        <v>9342.299999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>9316.23</v>
+        <v>9424.9</v>
       </c>
       <c r="O3" t="n">
-        <v>9433.1</v>
+        <v>9407.1</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -778,80 +772,80 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9284.799999999999</v>
+        <v>9491.200000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>9494.6</v>
+        <v>9577.1</v>
       </c>
       <c r="D4" t="n">
-        <v>9266.299999999999</v>
+        <v>9414.6</v>
       </c>
       <c r="E4" t="n">
-        <v>9491.299999999999</v>
+        <v>9427.5</v>
       </c>
       <c r="F4" t="n">
-        <v>206.5</v>
+        <v>-63.8</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0067</v>
       </c>
       <c r="H4" t="n">
-        <v>228.3</v>
+        <v>162.5</v>
       </c>
       <c r="I4" t="n">
-        <v>9062.1</v>
+        <v>9038</v>
       </c>
       <c r="J4" t="n">
-        <v>9194.9</v>
+        <v>9318.43</v>
       </c>
       <c r="K4" t="n">
-        <v>9227.299999999999</v>
+        <v>9377.15</v>
       </c>
       <c r="L4" t="n">
-        <v>9259.700000000001</v>
+        <v>9435.870000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>9342.299999999999</v>
+        <v>9605.450000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>9424.9</v>
+        <v>9775.02</v>
       </c>
       <c r="O4" t="n">
-        <v>9407.1</v>
+        <v>9722.9</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -864,78 +858,76 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9491.200000000001</v>
+        <v>9427.5</v>
       </c>
       <c r="C5" t="n">
-        <v>9577.1</v>
+        <v>9474.299999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>9414.6</v>
+        <v>9276.9</v>
       </c>
       <c r="E5" t="n">
-        <v>9427.5</v>
+        <v>9354.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-63.8</v>
+        <v>-72.90000000000001</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0067</v>
+        <v>-0.0077</v>
       </c>
       <c r="H5" t="n">
-        <v>162.5</v>
+        <v>197.4</v>
       </c>
       <c r="I5" t="n">
-        <v>9038</v>
+        <v>9252.1</v>
       </c>
       <c r="J5" t="n">
-        <v>9318.43</v>
+        <v>9230.83</v>
       </c>
       <c r="K5" t="n">
-        <v>9377.15</v>
+        <v>9346.25</v>
       </c>
       <c r="L5" t="n">
-        <v>9435.870000000001</v>
+        <v>9461.67</v>
       </c>
       <c r="M5" t="n">
-        <v>9605.450000000001</v>
+        <v>9508.75</v>
       </c>
       <c r="N5" t="n">
-        <v>9775.02</v>
+        <v>9555.83</v>
       </c>
       <c r="O5" t="n">
-        <v>9722.9</v>
+        <v>9739.6</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -943,12 +935,14 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -967,57 +961,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9427.5</v>
+        <v>9354.5</v>
       </c>
       <c r="C6" t="n">
-        <v>9474.299999999999</v>
+        <v>9645.6</v>
       </c>
       <c r="D6" t="n">
-        <v>9276.9</v>
+        <v>9354.5</v>
       </c>
       <c r="E6" t="n">
-        <v>9354.6</v>
+        <v>9645.6</v>
       </c>
       <c r="F6" t="n">
-        <v>-72.90000000000001</v>
+        <v>291</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0311</v>
       </c>
       <c r="H6" t="n">
-        <v>197.4</v>
+        <v>291.1</v>
       </c>
       <c r="I6" t="n">
-        <v>9252.1</v>
+        <v>9079.5</v>
       </c>
       <c r="J6" t="n">
-        <v>9230.83</v>
+        <v>9146.700000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>9346.25</v>
+        <v>9255.9</v>
       </c>
       <c r="L6" t="n">
-        <v>9461.67</v>
+        <v>9365.1</v>
       </c>
       <c r="M6" t="n">
-        <v>9508.75</v>
+        <v>9453.299999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>9555.83</v>
+        <v>9541.5</v>
       </c>
       <c r="O6" t="n">
-        <v>9739.6</v>
+        <v>9671.700000000001</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1025,83 +1019,83 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
-      </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9354.5</v>
+        <v>9645.6</v>
       </c>
       <c r="C7" t="n">
-        <v>9645.6</v>
+        <v>9787.6</v>
       </c>
       <c r="D7" t="n">
-        <v>9354.5</v>
+        <v>9632.799999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>9645.6</v>
+        <v>9717.299999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>291</v>
+        <v>71.7</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0311</v>
+        <v>0.0074</v>
       </c>
       <c r="H7" t="n">
-        <v>291.1</v>
+        <v>154.8</v>
       </c>
       <c r="I7" t="n">
-        <v>9079.5</v>
+        <v>9063.4</v>
       </c>
       <c r="J7" t="n">
-        <v>9146.700000000001</v>
+        <v>9427.27</v>
       </c>
       <c r="K7" t="n">
-        <v>9255.9</v>
+        <v>9500.049999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>9365.1</v>
+        <v>9572.82</v>
       </c>
       <c r="M7" t="n">
-        <v>9453.299999999999</v>
+        <v>9791.15</v>
       </c>
       <c r="N7" t="n">
-        <v>9541.5</v>
+        <v>10009.47</v>
       </c>
       <c r="O7" t="n">
-        <v>9671.700000000001</v>
+        <v>9936.700000000001</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1112,25 +1106,21 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
@@ -1142,50 +1132,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9645.6</v>
+        <v>9717.299999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>9787.6</v>
+        <v>9786.799999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>9632.799999999999</v>
+        <v>9574.200000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>9717.299999999999</v>
+        <v>9682.6</v>
       </c>
       <c r="F8" t="n">
-        <v>71.7</v>
+        <v>-34.7</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0036</v>
       </c>
       <c r="H8" t="n">
-        <v>154.8</v>
+        <v>212.6</v>
       </c>
       <c r="I8" t="n">
-        <v>9063.4</v>
+        <v>9478</v>
       </c>
       <c r="J8" t="n">
-        <v>9427.27</v>
+        <v>9566.049999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>9500.049999999999</v>
+        <v>9639.9</v>
       </c>
       <c r="L8" t="n">
-        <v>9572.82</v>
+        <v>9713.75</v>
       </c>
       <c r="M8" t="n">
-        <v>9791.15</v>
+        <v>9794.700000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>10009.47</v>
+        <v>9875.65</v>
       </c>
       <c r="O8" t="n">
-        <v>9936.700000000001</v>
+        <v>9942.4</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1193,18 +1183,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1217,55 +1207,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9717.299999999999</v>
+        <v>9682.6</v>
       </c>
       <c r="C9" t="n">
-        <v>9786.799999999999</v>
+        <v>9930.1</v>
       </c>
       <c r="D9" t="n">
-        <v>9574.200000000001</v>
+        <v>9610.5</v>
       </c>
       <c r="E9" t="n">
-        <v>9682.6</v>
+        <v>9698.4</v>
       </c>
       <c r="F9" t="n">
-        <v>-34.7</v>
+        <v>15.8</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0016</v>
       </c>
       <c r="H9" t="n">
-        <v>212.6</v>
+        <v>319.6</v>
       </c>
       <c r="I9" t="n">
-        <v>9478</v>
+        <v>9361.6</v>
       </c>
       <c r="J9" t="n">
-        <v>9566.049999999999</v>
+        <v>9471.049999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>9639.9</v>
+        <v>9576.299999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>9713.75</v>
+        <v>9681.549999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>9794.700000000001</v>
+        <v>9788.9</v>
       </c>
       <c r="N9" t="n">
-        <v>9875.65</v>
+        <v>9896.25</v>
       </c>
       <c r="O9" t="n">
-        <v>9942.4</v>
+        <v>9999.4</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,21 +1267,23 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1297,59 +1293,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9682.6</v>
+        <v>9698.4</v>
       </c>
       <c r="C10" t="n">
-        <v>9930.1</v>
+        <v>9707.700000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>9610.5</v>
+        <v>9423.9</v>
       </c>
       <c r="E10" t="n">
-        <v>9698.4</v>
+        <v>9539.700000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>15.8</v>
+        <v>-158.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0164</v>
       </c>
       <c r="H10" t="n">
-        <v>319.6</v>
+        <v>283.8</v>
       </c>
       <c r="I10" t="n">
-        <v>9361.6</v>
+        <v>9290.9</v>
       </c>
       <c r="J10" t="n">
-        <v>9471.049999999999</v>
+        <v>9342.85</v>
       </c>
       <c r="K10" t="n">
-        <v>9576.299999999999</v>
+        <v>9538.6</v>
       </c>
       <c r="L10" t="n">
-        <v>9681.549999999999</v>
+        <v>9734.35</v>
       </c>
       <c r="M10" t="n">
-        <v>9788.9</v>
+        <v>9858.200000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>9896.25</v>
+        <v>9982.049999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>9999.4</v>
+        <v>10249.7</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1357,23 +1349,21 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1383,55 +1373,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9698.4</v>
+        <v>9539.700000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>9707.700000000001</v>
+        <v>9740.200000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>9423.9</v>
+        <v>9521.5</v>
       </c>
       <c r="E11" t="n">
-        <v>9539.700000000001</v>
+        <v>9720.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-158.7</v>
+        <v>180.8</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.019</v>
       </c>
       <c r="H11" t="n">
-        <v>283.8</v>
+        <v>218.7</v>
       </c>
       <c r="I11" t="n">
-        <v>9290.9</v>
+        <v>9140.1</v>
       </c>
       <c r="J11" t="n">
-        <v>9342.85</v>
+        <v>9242.85</v>
       </c>
       <c r="K11" t="n">
-        <v>9538.6</v>
+        <v>9397.799999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>9734.35</v>
+        <v>9552.75</v>
       </c>
       <c r="M11" t="n">
-        <v>9858.200000000001</v>
+        <v>9681.6</v>
       </c>
       <c r="N11" t="n">
-        <v>9982.049999999999</v>
+        <v>9810.450000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>10249.7</v>
+        <v>9991.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1439,19 +1433,19 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1463,59 +1457,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9539.700000000001</v>
+        <v>9720.6</v>
       </c>
       <c r="C12" t="n">
-        <v>9740.200000000001</v>
+        <v>9744.799999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>9521.5</v>
+        <v>9667</v>
       </c>
       <c r="E12" t="n">
-        <v>9720.5</v>
+        <v>9667</v>
       </c>
       <c r="F12" t="n">
-        <v>180.8</v>
+        <v>-53.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.019</v>
+        <v>-0.0055</v>
       </c>
       <c r="H12" t="n">
-        <v>218.7</v>
+        <v>77.8</v>
       </c>
       <c r="I12" t="n">
-        <v>9140.1</v>
+        <v>9302.799999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>9242.85</v>
+        <v>9546.620000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>9397.799999999999</v>
+        <v>9611.15</v>
       </c>
       <c r="L12" t="n">
-        <v>9552.75</v>
+        <v>9675.68</v>
       </c>
       <c r="M12" t="n">
-        <v>9681.6</v>
+        <v>9829.85</v>
       </c>
       <c r="N12" t="n">
-        <v>9810.450000000001</v>
+        <v>9984.030000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>9991.5</v>
+        <v>9958.9</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1528,13 +1518,11 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1547,55 +1535,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9720.6</v>
+        <v>9667.1</v>
       </c>
       <c r="C13" t="n">
-        <v>9744.799999999999</v>
+        <v>9761.5</v>
       </c>
       <c r="D13" t="n">
-        <v>9667</v>
+        <v>9622.700000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>9667</v>
+        <v>9649</v>
       </c>
       <c r="F13" t="n">
-        <v>-53.5</v>
+        <v>-18</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0019</v>
       </c>
       <c r="H13" t="n">
-        <v>77.8</v>
+        <v>138.8</v>
       </c>
       <c r="I13" t="n">
-        <v>9302.799999999999</v>
+        <v>9589.200000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>9546.620000000001</v>
+        <v>9569.75</v>
       </c>
       <c r="K13" t="n">
-        <v>9611.15</v>
+        <v>9628.1</v>
       </c>
       <c r="L13" t="n">
-        <v>9675.68</v>
+        <v>9686.450000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>9829.85</v>
+        <v>9705.9</v>
       </c>
       <c r="N13" t="n">
-        <v>9984.030000000001</v>
+        <v>9725.35</v>
       </c>
       <c r="O13" t="n">
-        <v>9958.9</v>
+        <v>9822.6</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1603,19 +1595,25 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1627,57 +1625,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9667.1</v>
+        <v>9649</v>
       </c>
       <c r="C14" t="n">
-        <v>9761.5</v>
+        <v>9903.1</v>
       </c>
       <c r="D14" t="n">
-        <v>9622.700000000001</v>
+        <v>9649</v>
       </c>
       <c r="E14" t="n">
-        <v>9649</v>
+        <v>9897.4</v>
       </c>
       <c r="F14" t="n">
-        <v>-18</v>
+        <v>248.4</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0257</v>
       </c>
       <c r="H14" t="n">
-        <v>138.8</v>
+        <v>254.1</v>
       </c>
       <c r="I14" t="n">
-        <v>9589.200000000001</v>
+        <v>9483.9</v>
       </c>
       <c r="J14" t="n">
-        <v>9569.75</v>
+        <v>9488.65</v>
       </c>
       <c r="K14" t="n">
-        <v>9628.1</v>
+        <v>9579.6</v>
       </c>
       <c r="L14" t="n">
-        <v>9686.450000000001</v>
+        <v>9670.549999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>9705.9</v>
+        <v>9718.4</v>
       </c>
       <c r="N14" t="n">
-        <v>9725.35</v>
+        <v>9766.25</v>
       </c>
       <c r="O14" t="n">
-        <v>9822.6</v>
+        <v>9900.299999999999</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1685,87 +1683,83 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
-      </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9649</v>
+        <v>9897.4</v>
       </c>
       <c r="C15" t="n">
-        <v>9903.1</v>
+        <v>9901.5</v>
       </c>
       <c r="D15" t="n">
-        <v>9649</v>
+        <v>9829.4</v>
       </c>
       <c r="E15" t="n">
-        <v>9897.4</v>
+        <v>9870.700000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>248.4</v>
+        <v>-26.7</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0257</v>
+        <v>-0.0027</v>
       </c>
       <c r="H15" t="n">
-        <v>254.1</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>9483.9</v>
+        <v>9394.9</v>
       </c>
       <c r="J15" t="n">
-        <v>9488.65</v>
+        <v>9703.98</v>
       </c>
       <c r="K15" t="n">
-        <v>9579.6</v>
+        <v>9770.35</v>
       </c>
       <c r="L15" t="n">
-        <v>9670.549999999999</v>
+        <v>9836.73</v>
       </c>
       <c r="M15" t="n">
-        <v>9718.4</v>
+        <v>10024.45</v>
       </c>
       <c r="N15" t="n">
-        <v>9766.25</v>
+        <v>10212.18</v>
       </c>
       <c r="O15" t="n">
-        <v>9900.299999999999</v>
+        <v>10157.2</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1776,80 +1770,78 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9897.4</v>
+        <v>9870.700000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>9901.5</v>
+        <v>10046.3</v>
       </c>
       <c r="D16" t="n">
-        <v>9829.4</v>
+        <v>9858.5</v>
       </c>
       <c r="E16" t="n">
-        <v>9870.700000000001</v>
+        <v>9951.1</v>
       </c>
       <c r="F16" t="n">
-        <v>-26.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0081</v>
       </c>
       <c r="H16" t="n">
-        <v>72.09999999999999</v>
+        <v>187.8</v>
       </c>
       <c r="I16" t="n">
-        <v>9394.9</v>
+        <v>9757.299999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>9703.98</v>
+        <v>9801.23</v>
       </c>
       <c r="K16" t="n">
-        <v>9770.35</v>
+        <v>9834.65</v>
       </c>
       <c r="L16" t="n">
-        <v>9836.73</v>
+        <v>9868.08</v>
       </c>
       <c r="M16" t="n">
-        <v>10024.45</v>
+        <v>9906.75</v>
       </c>
       <c r="N16" t="n">
-        <v>10212.18</v>
+        <v>9945.42</v>
       </c>
       <c r="O16" t="n">
-        <v>10157.2</v>
+        <v>9973.6</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1860,78 +1852,80 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9870.700000000001</v>
+        <v>9951.5</v>
       </c>
       <c r="C17" t="n">
-        <v>10046.3</v>
+        <v>10158.4</v>
       </c>
       <c r="D17" t="n">
-        <v>9858.5</v>
+        <v>9951.5</v>
       </c>
       <c r="E17" t="n">
-        <v>9951.1</v>
+        <v>10124.6</v>
       </c>
       <c r="F17" t="n">
-        <v>80.40000000000001</v>
+        <v>173.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0081</v>
+        <v>0.0174</v>
       </c>
       <c r="H17" t="n">
-        <v>187.8</v>
+        <v>206.9</v>
       </c>
       <c r="I17" t="n">
-        <v>9757.299999999999</v>
+        <v>9670.700000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>9801.23</v>
+        <v>9762.65</v>
       </c>
       <c r="K17" t="n">
-        <v>9834.65</v>
+        <v>9857.200000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>9868.08</v>
+        <v>9951.75</v>
       </c>
       <c r="M17" t="n">
-        <v>9906.75</v>
+        <v>10045</v>
       </c>
       <c r="N17" t="n">
-        <v>9945.42</v>
+        <v>10138.25</v>
       </c>
       <c r="O17" t="n">
-        <v>9973.6</v>
+        <v>10234.1</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1942,7 +1936,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1957,10 +1951,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1972,50 +1964,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9951.5</v>
+        <v>10124.5</v>
       </c>
       <c r="C18" t="n">
-        <v>10158.4</v>
+        <v>10257.8</v>
       </c>
       <c r="D18" t="n">
-        <v>9951.5</v>
+        <v>10089.9</v>
       </c>
       <c r="E18" t="n">
-        <v>10124.6</v>
+        <v>10235.3</v>
       </c>
       <c r="F18" t="n">
-        <v>173.5</v>
+        <v>110.7</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0174</v>
+        <v>0.0109</v>
       </c>
       <c r="H18" t="n">
-        <v>206.9</v>
+        <v>167.9</v>
       </c>
       <c r="I18" t="n">
-        <v>9670.700000000001</v>
+        <v>9744.6</v>
       </c>
       <c r="J18" t="n">
-        <v>9762.65</v>
+        <v>9952.52</v>
       </c>
       <c r="K18" t="n">
-        <v>9857.200000000001</v>
+        <v>10021.15</v>
       </c>
       <c r="L18" t="n">
-        <v>9951.75</v>
+        <v>10089.77</v>
       </c>
       <c r="M18" t="n">
-        <v>10045</v>
+        <v>10228.05</v>
       </c>
       <c r="N18" t="n">
-        <v>10138.25</v>
+        <v>10366.32</v>
       </c>
       <c r="O18" t="n">
-        <v>10234.1</v>
+        <v>10365.3</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2026,20 +2018,18 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2054,69 +2044,71 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10124.5</v>
+        <v>10235.3</v>
       </c>
       <c r="C19" t="n">
-        <v>10257.8</v>
+        <v>10235.3</v>
       </c>
       <c r="D19" t="n">
-        <v>10089.9</v>
+        <v>10050.2</v>
       </c>
       <c r="E19" t="n">
-        <v>10235.3</v>
+        <v>10143.4</v>
       </c>
       <c r="F19" t="n">
-        <v>110.7</v>
+        <v>-91.90000000000001</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>167.9</v>
+        <v>185.1</v>
       </c>
       <c r="I19" t="n">
-        <v>9744.6</v>
+        <v>9922</v>
       </c>
       <c r="J19" t="n">
-        <v>9952.52</v>
+        <v>10098.13</v>
       </c>
       <c r="K19" t="n">
-        <v>10021.15</v>
+        <v>10151.35</v>
       </c>
       <c r="L19" t="n">
-        <v>10089.77</v>
+        <v>10204.57</v>
       </c>
       <c r="M19" t="n">
-        <v>10228.05</v>
+        <v>10319.25</v>
       </c>
       <c r="N19" t="n">
-        <v>10366.32</v>
+        <v>10433.92</v>
       </c>
       <c r="O19" t="n">
-        <v>10365.3</v>
+        <v>10425.7</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2129,77 +2121,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10235.3</v>
+        <v>10143.1</v>
       </c>
       <c r="C20" t="n">
-        <v>10235.3</v>
+        <v>10277.7</v>
       </c>
       <c r="D20" t="n">
-        <v>10050.2</v>
+        <v>10125.3</v>
       </c>
       <c r="E20" t="n">
-        <v>10143.4</v>
+        <v>10223.5</v>
       </c>
       <c r="F20" t="n">
-        <v>-91.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>185.1</v>
+        <v>152.4</v>
       </c>
       <c r="I20" t="n">
-        <v>9922</v>
+        <v>9865.1</v>
       </c>
       <c r="J20" t="n">
-        <v>10098.13</v>
+        <v>9958.629999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>10151.35</v>
+        <v>10050.85</v>
       </c>
       <c r="L20" t="n">
-        <v>10204.57</v>
+        <v>10143.08</v>
       </c>
       <c r="M20" t="n">
-        <v>10319.25</v>
+        <v>10235.95</v>
       </c>
       <c r="N20" t="n">
-        <v>10433.92</v>
+        <v>10328.83</v>
       </c>
       <c r="O20" t="n">
-        <v>10425.7</v>
+        <v>10420.4</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2211,59 +2205,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10143.1</v>
+        <v>10223.7</v>
       </c>
       <c r="C21" t="n">
-        <v>10277.7</v>
+        <v>10481.5</v>
       </c>
       <c r="D21" t="n">
-        <v>10125.3</v>
+        <v>10145.4</v>
       </c>
       <c r="E21" t="n">
-        <v>10223.5</v>
+        <v>10369.8</v>
       </c>
       <c r="F21" t="n">
-        <v>80.09999999999999</v>
+        <v>146.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0143</v>
       </c>
       <c r="H21" t="n">
-        <v>152.4</v>
+        <v>336.1</v>
       </c>
       <c r="I21" t="n">
-        <v>9865.1</v>
+        <v>9972.9</v>
       </c>
       <c r="J21" t="n">
-        <v>9958.629999999999</v>
+        <v>10082.1</v>
       </c>
       <c r="K21" t="n">
-        <v>10050.85</v>
+        <v>10147.3</v>
       </c>
       <c r="L21" t="n">
-        <v>10143.08</v>
+        <v>10212.5</v>
       </c>
       <c r="M21" t="n">
-        <v>10235.95</v>
+        <v>10299.7</v>
       </c>
       <c r="N21" t="n">
-        <v>10328.83</v>
+        <v>10386.9</v>
       </c>
       <c r="O21" t="n">
-        <v>10420.4</v>
+        <v>10430.1</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2271,24 +2261,30 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2300,50 +2296,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10223.7</v>
+        <v>10369.8</v>
       </c>
       <c r="C22" t="n">
-        <v>10481.5</v>
+        <v>10535.8</v>
       </c>
       <c r="D22" t="n">
-        <v>10145.4</v>
+        <v>10316</v>
       </c>
       <c r="E22" t="n">
-        <v>10369.8</v>
+        <v>10446.4</v>
       </c>
       <c r="F22" t="n">
-        <v>146.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0074</v>
       </c>
       <c r="H22" t="n">
-        <v>336.1</v>
+        <v>219.8</v>
       </c>
       <c r="I22" t="n">
-        <v>9972.9</v>
+        <v>9809.299999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>10082.1</v>
+        <v>10061.88</v>
       </c>
       <c r="K22" t="n">
-        <v>10147.3</v>
+        <v>10201.75</v>
       </c>
       <c r="L22" t="n">
-        <v>10212.5</v>
+        <v>10341.62</v>
       </c>
       <c r="M22" t="n">
-        <v>10299.7</v>
+        <v>10537.85</v>
       </c>
       <c r="N22" t="n">
-        <v>10386.9</v>
+        <v>10734.07</v>
       </c>
       <c r="O22" t="n">
-        <v>10430.1</v>
+        <v>10817.6</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2351,30 +2347,24 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2386,50 +2376,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10369.8</v>
+        <v>10446.3</v>
       </c>
       <c r="C23" t="n">
-        <v>10535.8</v>
+        <v>10745.8</v>
       </c>
       <c r="D23" t="n">
-        <v>10316</v>
+        <v>10446.3</v>
       </c>
       <c r="E23" t="n">
-        <v>10446.4</v>
+        <v>10686.9</v>
       </c>
       <c r="F23" t="n">
-        <v>76.59999999999999</v>
+        <v>240.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.023</v>
       </c>
       <c r="H23" t="n">
-        <v>219.8</v>
+        <v>299.5</v>
       </c>
       <c r="I23" t="n">
-        <v>9809.299999999999</v>
+        <v>10096.2</v>
       </c>
       <c r="J23" t="n">
-        <v>10061.88</v>
+        <v>10236.85</v>
       </c>
       <c r="K23" t="n">
-        <v>10201.75</v>
+        <v>10336.5</v>
       </c>
       <c r="L23" t="n">
-        <v>10341.62</v>
+        <v>10436.15</v>
       </c>
       <c r="M23" t="n">
-        <v>10537.85</v>
+        <v>10556.3</v>
       </c>
       <c r="N23" t="n">
-        <v>10734.07</v>
+        <v>10676.45</v>
       </c>
       <c r="O23" t="n">
-        <v>10817.6</v>
+        <v>10755.6</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2440,18 +2430,20 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2466,50 +2458,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10446.3</v>
+        <v>10686.8</v>
       </c>
       <c r="C24" t="n">
-        <v>10745.8</v>
+        <v>10934.9</v>
       </c>
       <c r="D24" t="n">
-        <v>10446.3</v>
+        <v>10645.8</v>
       </c>
       <c r="E24" t="n">
-        <v>10686.9</v>
+        <v>10910.6</v>
       </c>
       <c r="F24" t="n">
-        <v>240.5</v>
+        <v>223.7</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0209</v>
       </c>
       <c r="H24" t="n">
-        <v>299.5</v>
+        <v>289.1</v>
       </c>
       <c r="I24" t="n">
-        <v>10096.2</v>
+        <v>10146.8</v>
       </c>
       <c r="J24" t="n">
-        <v>10236.85</v>
+        <v>10432.83</v>
       </c>
       <c r="K24" t="n">
-        <v>10336.5</v>
+        <v>10537.15</v>
       </c>
       <c r="L24" t="n">
-        <v>10436.15</v>
+        <v>10641.48</v>
       </c>
       <c r="M24" t="n">
-        <v>10556.3</v>
+        <v>10836.65</v>
       </c>
       <c r="N24" t="n">
-        <v>10676.45</v>
+        <v>11031.83</v>
       </c>
       <c r="O24" t="n">
-        <v>10755.6</v>
+        <v>11045.3</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2520,20 +2512,18 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2548,69 +2538,73 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10686.8</v>
+        <v>10911</v>
       </c>
       <c r="C25" t="n">
-        <v>10934.9</v>
+        <v>10911</v>
       </c>
       <c r="D25" t="n">
-        <v>10645.8</v>
+        <v>10234.5</v>
       </c>
       <c r="E25" t="n">
-        <v>10910.6</v>
+        <v>10284.8</v>
       </c>
       <c r="F25" t="n">
-        <v>223.7</v>
+        <v>-625.8</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0574</v>
       </c>
       <c r="H25" t="n">
-        <v>289.1</v>
+        <v>676.5</v>
       </c>
       <c r="I25" t="n">
-        <v>10146.8</v>
+        <v>10356.7</v>
       </c>
       <c r="J25" t="n">
-        <v>10432.83</v>
+        <v>10681.62</v>
       </c>
       <c r="K25" t="n">
-        <v>10537.15</v>
+        <v>10766.05</v>
       </c>
       <c r="L25" t="n">
-        <v>10641.48</v>
+        <v>10850.47</v>
       </c>
       <c r="M25" t="n">
-        <v>10836.65</v>
+        <v>11055.15</v>
       </c>
       <c r="N25" t="n">
-        <v>11031.83</v>
+        <v>11259.82</v>
       </c>
       <c r="O25" t="n">
-        <v>11045.3</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+        <v>11224</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2618,9 +2612,9 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -2628,69 +2622,63 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10911</v>
+        <v>10285</v>
       </c>
       <c r="C26" t="n">
-        <v>10911</v>
+        <v>10447.5</v>
       </c>
       <c r="D26" t="n">
-        <v>10234.5</v>
+        <v>10082</v>
       </c>
       <c r="E26" t="n">
-        <v>10284.8</v>
+        <v>10261.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-625.8</v>
+        <v>-23.6</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0574</v>
+        <v>-0.0023</v>
       </c>
       <c r="H26" t="n">
-        <v>676.5</v>
+        <v>365.5</v>
       </c>
       <c r="I26" t="n">
-        <v>10356.7</v>
+        <v>9558</v>
       </c>
       <c r="J26" t="n">
-        <v>10681.62</v>
+        <v>9464.32</v>
       </c>
       <c r="K26" t="n">
-        <v>10766.05</v>
+        <v>9946.549999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>10850.47</v>
+        <v>10428.77</v>
       </c>
       <c r="M26" t="n">
-        <v>11055.15</v>
+        <v>10623.05</v>
       </c>
       <c r="N26" t="n">
-        <v>11259.82</v>
+        <v>10817.32</v>
       </c>
       <c r="O26" t="n">
-        <v>11224</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>11587.5</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2712,67 +2700,73 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10285</v>
+        <v>10261.1</v>
       </c>
       <c r="C27" t="n">
-        <v>10447.5</v>
+        <v>10447.7</v>
       </c>
       <c r="D27" t="n">
-        <v>10082</v>
+        <v>9915.700000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>10261.2</v>
+        <v>9918.299999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-23.6</v>
+        <v>-342.9</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0334</v>
       </c>
       <c r="H27" t="n">
-        <v>365.5</v>
+        <v>532</v>
       </c>
       <c r="I27" t="n">
-        <v>9558</v>
+        <v>9716.5</v>
       </c>
       <c r="J27" t="n">
-        <v>9464.32</v>
+        <v>9893.93</v>
       </c>
       <c r="K27" t="n">
-        <v>9946.549999999999</v>
+        <v>10078.45</v>
       </c>
       <c r="L27" t="n">
-        <v>10428.77</v>
+        <v>10262.98</v>
       </c>
       <c r="M27" t="n">
-        <v>10623.05</v>
+        <v>10443.95</v>
       </c>
       <c r="N27" t="n">
-        <v>10817.32</v>
+        <v>10624.93</v>
       </c>
       <c r="O27" t="n">
-        <v>11587.5</v>
+        <v>10813</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2785,78 +2779,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10261.1</v>
+        <v>9918.5</v>
       </c>
       <c r="C28" t="n">
-        <v>10447.7</v>
+        <v>10118.2</v>
       </c>
       <c r="D28" t="n">
-        <v>9915.700000000001</v>
+        <v>9670.5</v>
       </c>
       <c r="E28" t="n">
-        <v>9918.299999999999</v>
+        <v>9967.4</v>
       </c>
       <c r="F28" t="n">
-        <v>-342.9</v>
+        <v>49.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0334</v>
+        <v>0.005</v>
       </c>
       <c r="H28" t="n">
-        <v>532</v>
+        <v>447.7</v>
       </c>
       <c r="I28" t="n">
-        <v>9716.5</v>
+        <v>9383.700000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>9893.93</v>
+        <v>9254.6</v>
       </c>
       <c r="K28" t="n">
-        <v>10078.45</v>
+        <v>9652.299999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>10262.98</v>
+        <v>10050</v>
       </c>
       <c r="M28" t="n">
-        <v>10443.95</v>
+        <v>10184.3</v>
       </c>
       <c r="N28" t="n">
-        <v>10624.93</v>
+        <v>10318.6</v>
       </c>
       <c r="O28" t="n">
-        <v>10813</v>
+        <v>10979.7</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2878,50 +2870,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9918.5</v>
+        <v>9967.5</v>
       </c>
       <c r="C29" t="n">
-        <v>10118.2</v>
+        <v>10465.2</v>
       </c>
       <c r="D29" t="n">
-        <v>9670.5</v>
+        <v>9958.1</v>
       </c>
       <c r="E29" t="n">
-        <v>9967.4</v>
+        <v>10436.3</v>
       </c>
       <c r="F29" t="n">
-        <v>49.1</v>
+        <v>468.9</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.005</v>
+        <v>0.047</v>
       </c>
       <c r="H29" t="n">
-        <v>447.7</v>
+        <v>507.1</v>
       </c>
       <c r="I29" t="n">
-        <v>9383.700000000001</v>
+        <v>9222.799999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>9254.6</v>
+        <v>9556.23</v>
       </c>
       <c r="K29" t="n">
-        <v>9652.299999999999</v>
+        <v>9743.549999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>10050</v>
+        <v>9930.879999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>10184.3</v>
+        <v>10191.25</v>
       </c>
       <c r="N29" t="n">
-        <v>10318.6</v>
+        <v>10451.63</v>
       </c>
       <c r="O29" t="n">
-        <v>10979.7</v>
+        <v>10565.9</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2934,14 +2926,18 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2953,57 +2949,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9967.5</v>
+        <v>10436.2</v>
       </c>
       <c r="C30" t="n">
-        <v>10465.2</v>
+        <v>10687.9</v>
       </c>
       <c r="D30" t="n">
-        <v>9958.1</v>
+        <v>10330.9</v>
       </c>
       <c r="E30" t="n">
-        <v>10436.3</v>
+        <v>10600.5</v>
       </c>
       <c r="F30" t="n">
-        <v>468.9</v>
+        <v>164.2</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.047</v>
+        <v>0.0157</v>
       </c>
       <c r="H30" t="n">
-        <v>507.1</v>
+        <v>357</v>
       </c>
       <c r="I30" t="n">
-        <v>9222.799999999999</v>
+        <v>9451</v>
       </c>
       <c r="J30" t="n">
-        <v>9556.23</v>
+        <v>10041.52</v>
       </c>
       <c r="K30" t="n">
-        <v>9743.549999999999</v>
+        <v>10182.75</v>
       </c>
       <c r="L30" t="n">
-        <v>9930.879999999999</v>
+        <v>10323.97</v>
       </c>
       <c r="M30" t="n">
-        <v>10191.25</v>
+        <v>10689.85</v>
       </c>
       <c r="N30" t="n">
-        <v>10451.63</v>
+        <v>11055.73</v>
       </c>
       <c r="O30" t="n">
-        <v>10565.9</v>
+        <v>10972.3</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3014,20 +3010,18 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3046,50 +3040,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10436.2</v>
+        <v>10601.5</v>
       </c>
       <c r="C31" t="n">
-        <v>10687.9</v>
+        <v>10667.6</v>
       </c>
       <c r="D31" t="n">
-        <v>10330.9</v>
+        <v>10528.6</v>
       </c>
       <c r="E31" t="n">
-        <v>10600.5</v>
+        <v>10667.6</v>
       </c>
       <c r="F31" t="n">
-        <v>164.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0063</v>
       </c>
       <c r="H31" t="n">
-        <v>357</v>
+        <v>139</v>
       </c>
       <c r="I31" t="n">
-        <v>9451</v>
+        <v>9973.9</v>
       </c>
       <c r="J31" t="n">
-        <v>10041.52</v>
+        <v>10289.05</v>
       </c>
       <c r="K31" t="n">
-        <v>10182.75</v>
+        <v>10422</v>
       </c>
       <c r="L31" t="n">
-        <v>10323.97</v>
+        <v>10554.95</v>
       </c>
       <c r="M31" t="n">
-        <v>10689.85</v>
+        <v>10779</v>
       </c>
       <c r="N31" t="n">
-        <v>11055.73</v>
+        <v>11003.05</v>
       </c>
       <c r="O31" t="n">
-        <v>10972.3</v>
+        <v>11044.9</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3100,7 +3094,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3123,76 +3117,80 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10601.5</v>
+        <v>10668.4</v>
       </c>
       <c r="C32" t="n">
-        <v>10667.6</v>
+        <v>10683.7</v>
       </c>
       <c r="D32" t="n">
-        <v>10528.6</v>
+        <v>10361.5</v>
       </c>
       <c r="E32" t="n">
-        <v>10667.6</v>
+        <v>10379.1</v>
       </c>
       <c r="F32" t="n">
-        <v>67.09999999999999</v>
+        <v>-288.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0063</v>
+        <v>-0.027</v>
       </c>
       <c r="H32" t="n">
-        <v>139</v>
+        <v>322.2</v>
       </c>
       <c r="I32" t="n">
-        <v>9973.9</v>
+        <v>10389.6</v>
       </c>
       <c r="J32" t="n">
-        <v>10289.05</v>
+        <v>10563.35</v>
       </c>
       <c r="K32" t="n">
-        <v>10422</v>
+        <v>10598.1</v>
       </c>
       <c r="L32" t="n">
-        <v>10554.95</v>
+        <v>10632.85</v>
       </c>
       <c r="M32" t="n">
-        <v>10779</v>
+        <v>10737.1</v>
       </c>
       <c r="N32" t="n">
-        <v>11003.05</v>
+        <v>10841.35</v>
       </c>
       <c r="O32" t="n">
-        <v>11044.9</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+        <v>10806.6</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3207,76 +3205,72 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10668.4</v>
+        <v>10378.5</v>
       </c>
       <c r="C33" t="n">
-        <v>10683.7</v>
+        <v>10410.8</v>
       </c>
       <c r="D33" t="n">
-        <v>10361.5</v>
+        <v>10188.7</v>
       </c>
       <c r="E33" t="n">
-        <v>10379.1</v>
+        <v>10363.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-288.5</v>
+        <v>-15.2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.0015</v>
       </c>
       <c r="H33" t="n">
-        <v>322.2</v>
+        <v>222.1</v>
       </c>
       <c r="I33" t="n">
-        <v>10389.6</v>
+        <v>10039.3</v>
       </c>
       <c r="J33" t="n">
-        <v>10563.35</v>
+        <v>9985.15</v>
       </c>
       <c r="K33" t="n">
-        <v>10598.1</v>
+        <v>10218</v>
       </c>
       <c r="L33" t="n">
-        <v>10632.85</v>
+        <v>10450.85</v>
       </c>
       <c r="M33" t="n">
-        <v>10737.1</v>
+        <v>10540.2</v>
       </c>
       <c r="N33" t="n">
-        <v>10841.35</v>
+        <v>10629.55</v>
       </c>
       <c r="O33" t="n">
-        <v>10806.6</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
+        <v>11005.9</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3293,79 +3287,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10378.5</v>
+        <v>10365.4</v>
       </c>
       <c r="C34" t="n">
-        <v>10410.8</v>
+        <v>10488.2</v>
       </c>
       <c r="D34" t="n">
-        <v>10188.7</v>
+        <v>10164.3</v>
       </c>
       <c r="E34" t="n">
-        <v>10363.9</v>
+        <v>10233.1</v>
       </c>
       <c r="F34" t="n">
-        <v>-15.2</v>
+        <v>-130.8</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0126</v>
       </c>
       <c r="H34" t="n">
-        <v>222.1</v>
+        <v>323.9</v>
       </c>
       <c r="I34" t="n">
-        <v>10039.3</v>
+        <v>9966.6</v>
       </c>
       <c r="J34" t="n">
-        <v>9985.15</v>
+        <v>10173.88</v>
       </c>
       <c r="K34" t="n">
-        <v>10218</v>
+        <v>10252.85</v>
       </c>
       <c r="L34" t="n">
-        <v>10450.85</v>
+        <v>10331.83</v>
       </c>
       <c r="M34" t="n">
-        <v>10540.2</v>
+        <v>10474.95</v>
       </c>
       <c r="N34" t="n">
-        <v>10629.55</v>
+        <v>10618.08</v>
       </c>
       <c r="O34" t="n">
-        <v>11005.9</v>
+        <v>10632.9</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3377,78 +3371,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10365.4</v>
+        <v>10233.6</v>
       </c>
       <c r="C35" t="n">
-        <v>10488.2</v>
+        <v>10375.7</v>
       </c>
       <c r="D35" t="n">
-        <v>10164.3</v>
+        <v>10152.1</v>
       </c>
       <c r="E35" t="n">
-        <v>10233.1</v>
+        <v>10195.4</v>
       </c>
       <c r="F35" t="n">
-        <v>-130.8</v>
+        <v>-37.7</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0037</v>
       </c>
       <c r="H35" t="n">
-        <v>323.9</v>
+        <v>223.6</v>
       </c>
       <c r="I35" t="n">
-        <v>9966.6</v>
+        <v>9840.4</v>
       </c>
       <c r="J35" t="n">
-        <v>10173.88</v>
+        <v>9862.620000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>10252.85</v>
+        <v>10071.15</v>
       </c>
       <c r="L35" t="n">
-        <v>10331.83</v>
+        <v>10279.67</v>
       </c>
       <c r="M35" t="n">
-        <v>10474.95</v>
+        <v>10395.05</v>
       </c>
       <c r="N35" t="n">
-        <v>10618.08</v>
+        <v>10510.42</v>
       </c>
       <c r="O35" t="n">
-        <v>10632.9</v>
+        <v>10812.1</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3461,59 +3453,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10233.6</v>
+        <v>10194.8</v>
       </c>
       <c r="C36" t="n">
-        <v>10375.7</v>
+        <v>10497.2</v>
       </c>
       <c r="D36" t="n">
-        <v>10152.1</v>
+        <v>10151.5</v>
       </c>
       <c r="E36" t="n">
-        <v>10195.4</v>
+        <v>10466.3</v>
       </c>
       <c r="F36" t="n">
-        <v>-37.7</v>
+        <v>270.9</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0266</v>
       </c>
       <c r="H36" t="n">
-        <v>223.6</v>
+        <v>345.7</v>
       </c>
       <c r="I36" t="n">
-        <v>9840.4</v>
+        <v>9928.5</v>
       </c>
       <c r="J36" t="n">
-        <v>9862.620000000001</v>
+        <v>9937.549999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>10071.15</v>
+        <v>10083.6</v>
       </c>
       <c r="L36" t="n">
-        <v>10279.67</v>
+        <v>10229.65</v>
       </c>
       <c r="M36" t="n">
-        <v>10395.05</v>
+        <v>10307.2</v>
       </c>
       <c r="N36" t="n">
-        <v>10510.42</v>
+        <v>10384.75</v>
       </c>
       <c r="O36" t="n">
-        <v>10812.1</v>
+        <v>10599.3</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3526,72 +3514,80 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10194.8</v>
+        <v>10465.6</v>
       </c>
       <c r="C37" t="n">
-        <v>10497.2</v>
+        <v>10557.2</v>
       </c>
       <c r="D37" t="n">
-        <v>10151.5</v>
+        <v>10381.2</v>
       </c>
       <c r="E37" t="n">
-        <v>10466.3</v>
+        <v>10409.3</v>
       </c>
       <c r="F37" t="n">
-        <v>270.9</v>
+        <v>-57</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0266</v>
+        <v>-0.0054</v>
       </c>
       <c r="H37" t="n">
-        <v>345.7</v>
+        <v>176</v>
       </c>
       <c r="I37" t="n">
-        <v>9928.5</v>
+        <v>9805.799999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>9937.549999999999</v>
+        <v>10191.57</v>
       </c>
       <c r="K37" t="n">
-        <v>10083.6</v>
+        <v>10293.45</v>
       </c>
       <c r="L37" t="n">
-        <v>10229.65</v>
+        <v>10395.32</v>
       </c>
       <c r="M37" t="n">
-        <v>10307.2</v>
+        <v>10639.15</v>
       </c>
       <c r="N37" t="n">
-        <v>10384.75</v>
+        <v>10882.97</v>
       </c>
       <c r="O37" t="n">
-        <v>10599.3</v>
+        <v>10842.9</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3602,20 +3598,16 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3634,50 +3626,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10465.6</v>
+        <v>10409.3</v>
       </c>
       <c r="C38" t="n">
-        <v>10557.2</v>
+        <v>10415.7</v>
       </c>
       <c r="D38" t="n">
-        <v>10381.2</v>
+        <v>10238.6</v>
       </c>
       <c r="E38" t="n">
-        <v>10409.3</v>
+        <v>10368.1</v>
       </c>
       <c r="F38" t="n">
-        <v>-57</v>
+        <v>-41.2</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.004</v>
       </c>
       <c r="H38" t="n">
-        <v>176</v>
+        <v>177.1</v>
       </c>
       <c r="I38" t="n">
-        <v>9805.799999999999</v>
+        <v>10205.2</v>
       </c>
       <c r="J38" t="n">
-        <v>10191.57</v>
+        <v>10203.35</v>
       </c>
       <c r="K38" t="n">
-        <v>10293.45</v>
+        <v>10321.3</v>
       </c>
       <c r="L38" t="n">
-        <v>10395.32</v>
+        <v>10439.25</v>
       </c>
       <c r="M38" t="n">
-        <v>10639.15</v>
+        <v>10497.3</v>
       </c>
       <c r="N38" t="n">
-        <v>10882.97</v>
+        <v>10555.35</v>
       </c>
       <c r="O38" t="n">
-        <v>10842.9</v>
+        <v>10733.2</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3685,12 +3677,14 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3709,77 +3703,81 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10409.3</v>
+        <v>10369.1</v>
       </c>
       <c r="C39" t="n">
-        <v>10415.7</v>
+        <v>10471.7</v>
       </c>
       <c r="D39" t="n">
-        <v>10238.6</v>
+        <v>10127.6</v>
       </c>
       <c r="E39" t="n">
-        <v>10368.1</v>
+        <v>10471.7</v>
       </c>
       <c r="F39" t="n">
-        <v>-41.2</v>
+        <v>103.6</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.01</v>
       </c>
       <c r="H39" t="n">
-        <v>177.1</v>
+        <v>344.1</v>
       </c>
       <c r="I39" t="n">
-        <v>10205.2</v>
+        <v>10061.5</v>
       </c>
       <c r="J39" t="n">
-        <v>10203.35</v>
+        <v>10211.47</v>
       </c>
       <c r="K39" t="n">
-        <v>10321.3</v>
+        <v>10279.55</v>
       </c>
       <c r="L39" t="n">
-        <v>10439.25</v>
+        <v>10347.62</v>
       </c>
       <c r="M39" t="n">
-        <v>10497.3</v>
+        <v>10456.65</v>
       </c>
       <c r="N39" t="n">
-        <v>10555.35</v>
+        <v>10565.68</v>
       </c>
       <c r="O39" t="n">
-        <v>10733.2</v>
+        <v>10592.8</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3793,80 +3791,74 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10369.1</v>
+        <v>10471.4</v>
       </c>
       <c r="C40" t="n">
-        <v>10471.7</v>
+        <v>10570.1</v>
       </c>
       <c r="D40" t="n">
-        <v>10127.6</v>
+        <v>10352.9</v>
       </c>
       <c r="E40" t="n">
-        <v>10471.7</v>
+        <v>10363.3</v>
       </c>
       <c r="F40" t="n">
-        <v>103.6</v>
+        <v>-108.4</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0104</v>
       </c>
       <c r="H40" t="n">
-        <v>344.1</v>
+        <v>217.2</v>
       </c>
       <c r="I40" t="n">
-        <v>10061.5</v>
+        <v>9783.5</v>
       </c>
       <c r="J40" t="n">
-        <v>10211.47</v>
+        <v>10213.62</v>
       </c>
       <c r="K40" t="n">
-        <v>10279.55</v>
+        <v>10299.65</v>
       </c>
       <c r="L40" t="n">
-        <v>10347.62</v>
+        <v>10385.68</v>
       </c>
       <c r="M40" t="n">
-        <v>10456.65</v>
+        <v>10643.75</v>
       </c>
       <c r="N40" t="n">
-        <v>10565.68</v>
+        <v>10901.83</v>
       </c>
       <c r="O40" t="n">
-        <v>10592.8</v>
+        <v>10815.8</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3888,50 +3880,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10471.4</v>
+        <v>10363.6</v>
       </c>
       <c r="C41" t="n">
-        <v>10570.1</v>
+        <v>10575.3</v>
       </c>
       <c r="D41" t="n">
-        <v>10352.9</v>
+        <v>10332.4</v>
       </c>
       <c r="E41" t="n">
-        <v>10363.3</v>
+        <v>10508</v>
       </c>
       <c r="F41" t="n">
-        <v>-108.4</v>
+        <v>144.7</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.014</v>
       </c>
       <c r="H41" t="n">
-        <v>217.2</v>
+        <v>242.9</v>
       </c>
       <c r="I41" t="n">
-        <v>9783.5</v>
+        <v>10135.7</v>
       </c>
       <c r="J41" t="n">
-        <v>10213.62</v>
+        <v>10097</v>
       </c>
       <c r="K41" t="n">
-        <v>10299.65</v>
+        <v>10254.7</v>
       </c>
       <c r="L41" t="n">
-        <v>10385.68</v>
+        <v>10412.4</v>
       </c>
       <c r="M41" t="n">
-        <v>10643.75</v>
+        <v>10471.9</v>
       </c>
       <c r="N41" t="n">
-        <v>10901.83</v>
+        <v>10531.4</v>
       </c>
       <c r="O41" t="n">
-        <v>10815.8</v>
+        <v>10787.3</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3944,14 +3936,18 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3970,50 +3966,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10363.6</v>
+        <v>10507.8</v>
       </c>
       <c r="C42" t="n">
-        <v>10575.3</v>
+        <v>10701.3</v>
       </c>
       <c r="D42" t="n">
-        <v>10332.4</v>
+        <v>10429.2</v>
       </c>
       <c r="E42" t="n">
-        <v>10508</v>
+        <v>10679</v>
       </c>
       <c r="F42" t="n">
-        <v>144.7</v>
+        <v>171</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0163</v>
       </c>
       <c r="H42" t="n">
-        <v>242.9</v>
+        <v>272.1</v>
       </c>
       <c r="I42" t="n">
-        <v>10135.7</v>
+        <v>10089.5</v>
       </c>
       <c r="J42" t="n">
-        <v>10097</v>
+        <v>10292.18</v>
       </c>
       <c r="K42" t="n">
-        <v>10254.7</v>
+        <v>10386.55</v>
       </c>
       <c r="L42" t="n">
-        <v>10412.4</v>
+        <v>10480.93</v>
       </c>
       <c r="M42" t="n">
-        <v>10471.9</v>
+        <v>10629.45</v>
       </c>
       <c r="N42" t="n">
-        <v>10531.4</v>
+        <v>10777.97</v>
       </c>
       <c r="O42" t="n">
-        <v>10787.3</v>
+        <v>10818.2</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4024,21 +4020,19 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4047,78 +4041,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10507.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C43" t="n">
-        <v>10701.3</v>
+        <v>10747</v>
       </c>
       <c r="D43" t="n">
-        <v>10429.2</v>
+        <v>10397.5</v>
       </c>
       <c r="E43" t="n">
-        <v>10679</v>
+        <v>10497.3</v>
       </c>
       <c r="F43" t="n">
-        <v>171</v>
+        <v>-181.7</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.017</v>
       </c>
       <c r="H43" t="n">
-        <v>272.1</v>
+        <v>349.5</v>
       </c>
       <c r="I43" t="n">
-        <v>10089.5</v>
+        <v>10157.1</v>
       </c>
       <c r="J43" t="n">
-        <v>10292.18</v>
+        <v>10463.78</v>
       </c>
       <c r="K43" t="n">
-        <v>10386.55</v>
+        <v>10542.95</v>
       </c>
       <c r="L43" t="n">
-        <v>10480.93</v>
+        <v>10622.12</v>
       </c>
       <c r="M43" t="n">
-        <v>10629.45</v>
+        <v>10815.05</v>
       </c>
       <c r="N43" t="n">
-        <v>10777.97</v>
+        <v>11007.97</v>
       </c>
       <c r="O43" t="n">
-        <v>10818.2</v>
+        <v>10973.4</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4131,72 +4123,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10679.4</v>
+        <v>10498.1</v>
       </c>
       <c r="C44" t="n">
-        <v>10747</v>
+        <v>10623.7</v>
       </c>
       <c r="D44" t="n">
-        <v>10397.5</v>
+        <v>10423</v>
       </c>
       <c r="E44" t="n">
-        <v>10497.3</v>
+        <v>10600.4</v>
       </c>
       <c r="F44" t="n">
-        <v>-181.7</v>
+        <v>103.1</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.017</v>
+        <v>0.0098</v>
       </c>
       <c r="H44" t="n">
-        <v>349.5</v>
+        <v>200.7</v>
       </c>
       <c r="I44" t="n">
-        <v>10157.1</v>
+        <v>10048</v>
       </c>
       <c r="J44" t="n">
-        <v>10463.78</v>
+        <v>10110.32</v>
       </c>
       <c r="K44" t="n">
-        <v>10542.95</v>
+        <v>10322.55</v>
       </c>
       <c r="L44" t="n">
-        <v>10622.12</v>
+        <v>10534.77</v>
       </c>
       <c r="M44" t="n">
-        <v>10815.05</v>
+        <v>10672.05</v>
       </c>
       <c r="N44" t="n">
-        <v>11007.97</v>
+        <v>10809.32</v>
       </c>
       <c r="O44" t="n">
-        <v>10973.4</v>
+        <v>11096.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4215,57 +4207,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10498.1</v>
+        <v>10600.3</v>
       </c>
       <c r="C45" t="n">
-        <v>10623.7</v>
+        <v>10763.4</v>
       </c>
       <c r="D45" t="n">
-        <v>10423</v>
+        <v>10483.1</v>
       </c>
       <c r="E45" t="n">
-        <v>10600.4</v>
+        <v>10736.2</v>
       </c>
       <c r="F45" t="n">
-        <v>103.1</v>
+        <v>135.8</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0128</v>
       </c>
       <c r="H45" t="n">
-        <v>200.7</v>
+        <v>280.3</v>
       </c>
       <c r="I45" t="n">
-        <v>10048</v>
+        <v>10222.3</v>
       </c>
       <c r="J45" t="n">
-        <v>10110.32</v>
+        <v>10438.23</v>
       </c>
       <c r="K45" t="n">
-        <v>10322.55</v>
+        <v>10500.05</v>
       </c>
       <c r="L45" t="n">
-        <v>10534.77</v>
+        <v>10561.88</v>
       </c>
       <c r="M45" t="n">
-        <v>10672.05</v>
+        <v>10700.75</v>
       </c>
       <c r="N45" t="n">
-        <v>10809.32</v>
+        <v>10839.63</v>
       </c>
       <c r="O45" t="n">
-        <v>11096.5</v>
+        <v>10824.4</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4273,16 +4265,20 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4295,59 +4291,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10600.3</v>
+        <v>10736.1</v>
       </c>
       <c r="C46" t="n">
-        <v>10763.4</v>
+        <v>10989.5</v>
       </c>
       <c r="D46" t="n">
-        <v>10483.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E46" t="n">
-        <v>10736.2</v>
+        <v>10868.1</v>
       </c>
       <c r="F46" t="n">
-        <v>135.8</v>
+        <v>131.9</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0123</v>
       </c>
       <c r="H46" t="n">
-        <v>280.3</v>
+        <v>253.4</v>
       </c>
       <c r="I46" t="n">
-        <v>10222.3</v>
+        <v>10202.8</v>
       </c>
       <c r="J46" t="n">
-        <v>10438.23</v>
+        <v>10512.37</v>
       </c>
       <c r="K46" t="n">
-        <v>10500.05</v>
+        <v>10596.05</v>
       </c>
       <c r="L46" t="n">
-        <v>10561.88</v>
+        <v>10679.73</v>
       </c>
       <c r="M46" t="n">
-        <v>10700.75</v>
+        <v>10876.35</v>
       </c>
       <c r="N46" t="n">
-        <v>10839.63</v>
+        <v>11072.98</v>
       </c>
       <c r="O46" t="n">
-        <v>10824.4</v>
+        <v>11043.7</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4355,12 +4347,10 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4386,50 +4376,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10736.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C47" t="n">
-        <v>10989.5</v>
+        <v>10959.9</v>
       </c>
       <c r="D47" t="n">
-        <v>10736.1</v>
+        <v>10832.5</v>
       </c>
       <c r="E47" t="n">
-        <v>10868.1</v>
+        <v>10901.1</v>
       </c>
       <c r="F47" t="n">
-        <v>131.9</v>
+        <v>33</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0123</v>
+        <v>0.003</v>
       </c>
       <c r="H47" t="n">
-        <v>253.4</v>
+        <v>127.4</v>
       </c>
       <c r="I47" t="n">
-        <v>10202.8</v>
+        <v>10482.7</v>
       </c>
       <c r="J47" t="n">
-        <v>10512.37</v>
+        <v>10617.35</v>
       </c>
       <c r="K47" t="n">
-        <v>10596.05</v>
+        <v>10741.4</v>
       </c>
       <c r="L47" t="n">
-        <v>10679.73</v>
+        <v>10865.45</v>
       </c>
       <c r="M47" t="n">
-        <v>10876.35</v>
+        <v>10994.8</v>
       </c>
       <c r="N47" t="n">
-        <v>11072.98</v>
+        <v>11124.15</v>
       </c>
       <c r="O47" t="n">
-        <v>11043.7</v>
+        <v>11242.9</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4440,15 +4430,13 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4461,68 +4449,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10868.1</v>
+        <v>10901.1</v>
       </c>
       <c r="C48" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D48" t="n">
-        <v>10832.5</v>
+        <v>10723.7</v>
       </c>
       <c r="E48" t="n">
-        <v>10901.1</v>
+        <v>10750.1</v>
       </c>
       <c r="F48" t="n">
-        <v>33</v>
+        <v>-151</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0139</v>
       </c>
       <c r="H48" t="n">
-        <v>127.4</v>
+        <v>187.2</v>
       </c>
       <c r="I48" t="n">
-        <v>10482.7</v>
+        <v>10705.1</v>
       </c>
       <c r="J48" t="n">
-        <v>10617.35</v>
+        <v>10776.15</v>
       </c>
       <c r="K48" t="n">
-        <v>10741.4</v>
+        <v>10837.4</v>
       </c>
       <c r="L48" t="n">
-        <v>10865.45</v>
+        <v>10898.65</v>
       </c>
       <c r="M48" t="n">
-        <v>10994.8</v>
+        <v>10964.8</v>
       </c>
       <c r="N48" t="n">
-        <v>11124.15</v>
+        <v>11030.95</v>
       </c>
       <c r="O48" t="n">
-        <v>11242.9</v>
+        <v>11087.3</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4534,86 +4530,80 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10901.1</v>
+        <v>10750</v>
       </c>
       <c r="C49" t="n">
-        <v>10910.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D49" t="n">
-        <v>10723.7</v>
+        <v>10684.4</v>
       </c>
       <c r="E49" t="n">
-        <v>10750.1</v>
+        <v>10816.6</v>
       </c>
       <c r="F49" t="n">
-        <v>-151</v>
+        <v>66.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0139</v>
+        <v>0.0062</v>
       </c>
       <c r="H49" t="n">
-        <v>187.2</v>
+        <v>147.2</v>
       </c>
       <c r="I49" t="n">
-        <v>10705.1</v>
+        <v>10536.5</v>
       </c>
       <c r="J49" t="n">
-        <v>10776.15</v>
+        <v>10529.3</v>
       </c>
       <c r="K49" t="n">
-        <v>10837.4</v>
+        <v>10656.5</v>
       </c>
       <c r="L49" t="n">
-        <v>10898.65</v>
+        <v>10783.7</v>
       </c>
       <c r="M49" t="n">
-        <v>10964.8</v>
+        <v>10843.7</v>
       </c>
       <c r="N49" t="n">
-        <v>11030.95</v>
+        <v>10903.7</v>
       </c>
       <c r="O49" t="n">
-        <v>11087.3</v>
+        <v>11098.1</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
@@ -4625,55 +4615,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10750</v>
+        <v>10816.3</v>
       </c>
       <c r="C50" t="n">
-        <v>10831.6</v>
+        <v>10920.5</v>
       </c>
       <c r="D50" t="n">
-        <v>10684.4</v>
+        <v>10772.6</v>
       </c>
       <c r="E50" t="n">
-        <v>10816.6</v>
+        <v>10824.3</v>
       </c>
       <c r="F50" t="n">
-        <v>66.5</v>
+        <v>7.7</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0007</v>
       </c>
       <c r="H50" t="n">
-        <v>147.2</v>
+        <v>147.9</v>
       </c>
       <c r="I50" t="n">
-        <v>10536.5</v>
+        <v>10537.2</v>
       </c>
       <c r="J50" t="n">
-        <v>10529.3</v>
+        <v>10698.7</v>
       </c>
       <c r="K50" t="n">
-        <v>10656.5</v>
+        <v>10743</v>
       </c>
       <c r="L50" t="n">
-        <v>10783.7</v>
+        <v>10787.3</v>
       </c>
       <c r="M50" t="n">
-        <v>10843.7</v>
+        <v>10890.2</v>
       </c>
       <c r="N50" t="n">
-        <v>10903.7</v>
+        <v>10993.1</v>
       </c>
       <c r="O50" t="n">
-        <v>11098.1</v>
+        <v>10978.8</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4684,14 +4678,14 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U50" s="8" t="n">
@@ -4707,57 +4701,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10816.3</v>
+        <v>10824.6</v>
       </c>
       <c r="C51" t="n">
-        <v>10920.5</v>
+        <v>10866.8</v>
       </c>
       <c r="D51" t="n">
-        <v>10772.6</v>
+        <v>10689.6</v>
       </c>
       <c r="E51" t="n">
-        <v>10824.3</v>
+        <v>10831.1</v>
       </c>
       <c r="F51" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>147.9</v>
+        <v>177.2</v>
       </c>
       <c r="I51" t="n">
-        <v>10537.2</v>
+        <v>10624.7</v>
       </c>
       <c r="J51" t="n">
-        <v>10698.7</v>
+        <v>10665.27</v>
       </c>
       <c r="K51" t="n">
-        <v>10743</v>
+        <v>10750.35</v>
       </c>
       <c r="L51" t="n">
-        <v>10787.3</v>
+        <v>10835.42</v>
       </c>
       <c r="M51" t="n">
-        <v>10890.2</v>
+        <v>10898.25</v>
       </c>
       <c r="N51" t="n">
-        <v>10993.1</v>
+        <v>10961.08</v>
       </c>
       <c r="O51" t="n">
-        <v>10978.8</v>
+        <v>11068.4</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4765,18 +4759,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4791,72 +4785,74 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10824.6</v>
+        <v>10831</v>
       </c>
       <c r="C52" t="n">
-        <v>10866.8</v>
+        <v>10868.3</v>
       </c>
       <c r="D52" t="n">
-        <v>10689.6</v>
+        <v>10594.3</v>
       </c>
       <c r="E52" t="n">
-        <v>10831.1</v>
+        <v>10650.4</v>
       </c>
       <c r="F52" t="n">
-        <v>6.8</v>
+        <v>-180.7</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0167</v>
       </c>
       <c r="H52" t="n">
-        <v>177.2</v>
+        <v>274</v>
       </c>
       <c r="I52" t="n">
-        <v>10624.7</v>
+        <v>10512.4</v>
       </c>
       <c r="J52" t="n">
-        <v>10665.27</v>
+        <v>10680.35</v>
       </c>
       <c r="K52" t="n">
-        <v>10750.35</v>
+        <v>10742.5</v>
       </c>
       <c r="L52" t="n">
-        <v>10835.42</v>
+        <v>10804.65</v>
       </c>
       <c r="M52" t="n">
-        <v>10898.25</v>
+        <v>10919.7</v>
       </c>
       <c r="N52" t="n">
-        <v>10961.08</v>
+        <v>11034.75</v>
       </c>
       <c r="O52" t="n">
-        <v>11068.4</v>
+        <v>11044</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4882,71 +4878,69 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10831</v>
+        <v>10650.9</v>
       </c>
       <c r="C53" t="n">
-        <v>10868.3</v>
+        <v>10823</v>
       </c>
       <c r="D53" t="n">
-        <v>10594.3</v>
+        <v>10586.4</v>
       </c>
       <c r="E53" t="n">
-        <v>10650.4</v>
+        <v>10659.1</v>
       </c>
       <c r="F53" t="n">
-        <v>-180.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0167</v>
+        <v>0.0008</v>
       </c>
       <c r="H53" t="n">
-        <v>274</v>
+        <v>236.6</v>
       </c>
       <c r="I53" t="n">
-        <v>10512.4</v>
+        <v>10320.3</v>
       </c>
       <c r="J53" t="n">
-        <v>10680.35</v>
+        <v>10335.95</v>
       </c>
       <c r="K53" t="n">
-        <v>10742.5</v>
+        <v>10513.4</v>
       </c>
       <c r="L53" t="n">
-        <v>10804.65</v>
+        <v>10690.85</v>
       </c>
       <c r="M53" t="n">
-        <v>10919.7</v>
+        <v>10787.4</v>
       </c>
       <c r="N53" t="n">
-        <v>11034.75</v>
+        <v>10883.95</v>
       </c>
       <c r="O53" t="n">
-        <v>11044</v>
+        <v>11142.3</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4968,50 +4962,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10650.9</v>
+        <v>10659.1</v>
       </c>
       <c r="C54" t="n">
-        <v>10823</v>
+        <v>10774.7</v>
       </c>
       <c r="D54" t="n">
-        <v>10586.4</v>
+        <v>10656.7</v>
       </c>
       <c r="E54" t="n">
-        <v>10659.1</v>
+        <v>10695.3</v>
       </c>
       <c r="F54" t="n">
-        <v>8.699999999999999</v>
+        <v>36.2</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0034</v>
       </c>
       <c r="H54" t="n">
-        <v>236.6</v>
+        <v>118</v>
       </c>
       <c r="I54" t="n">
-        <v>10320.3</v>
+        <v>10349.8</v>
       </c>
       <c r="J54" t="n">
-        <v>10335.95</v>
+        <v>10399.7</v>
       </c>
       <c r="K54" t="n">
-        <v>10513.4</v>
+        <v>10540.8</v>
       </c>
       <c r="L54" t="n">
-        <v>10690.85</v>
+        <v>10681.9</v>
       </c>
       <c r="M54" t="n">
-        <v>10787.4</v>
+        <v>10777.4</v>
       </c>
       <c r="N54" t="n">
-        <v>10883.95</v>
+        <v>10872.9</v>
       </c>
       <c r="O54" t="n">
-        <v>11142.3</v>
+        <v>11059.6</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5024,13 +5018,11 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5045,74 +5037,82 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10659.1</v>
+        <v>10695.2</v>
       </c>
       <c r="C55" t="n">
-        <v>10774.7</v>
+        <v>10758.7</v>
       </c>
       <c r="D55" t="n">
-        <v>10656.7</v>
+        <v>10390.7</v>
       </c>
       <c r="E55" t="n">
-        <v>10695.3</v>
+        <v>10462</v>
       </c>
       <c r="F55" t="n">
-        <v>36.2</v>
+        <v>-233.3</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.0218</v>
       </c>
       <c r="H55" t="n">
-        <v>118</v>
+        <v>368</v>
       </c>
       <c r="I55" t="n">
-        <v>10349.8</v>
+        <v>10538.7</v>
       </c>
       <c r="J55" t="n">
-        <v>10399.7</v>
+        <v>10567.1</v>
       </c>
       <c r="K55" t="n">
-        <v>10540.8</v>
+        <v>10636.3</v>
       </c>
       <c r="L55" t="n">
-        <v>10681.9</v>
+        <v>10705.5</v>
       </c>
       <c r="M55" t="n">
-        <v>10777.4</v>
+        <v>10754.3</v>
       </c>
       <c r="N55" t="n">
-        <v>10872.9</v>
+        <v>10803.1</v>
       </c>
       <c r="O55" t="n">
-        <v>11059.6</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+        <v>10892.7</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5125,84 +5125,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10695.2</v>
+        <v>10462.4</v>
       </c>
       <c r="C56" t="n">
-        <v>10758.7</v>
+        <v>10602.6</v>
       </c>
       <c r="D56" t="n">
-        <v>10390.7</v>
+        <v>10367.3</v>
       </c>
       <c r="E56" t="n">
-        <v>10462</v>
+        <v>10552.1</v>
       </c>
       <c r="F56" t="n">
-        <v>-233.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0218</v>
+        <v>0.0086</v>
       </c>
       <c r="H56" t="n">
-        <v>368</v>
+        <v>235.3</v>
       </c>
       <c r="I56" t="n">
-        <v>10538.7</v>
+        <v>10022.7</v>
       </c>
       <c r="J56" t="n">
-        <v>10567.1</v>
+        <v>10037.65</v>
       </c>
       <c r="K56" t="n">
-        <v>10636.3</v>
+        <v>10278</v>
       </c>
       <c r="L56" t="n">
-        <v>10705.5</v>
+        <v>10518.35</v>
       </c>
       <c r="M56" t="n">
-        <v>10754.3</v>
+        <v>10646</v>
       </c>
       <c r="N56" t="n">
-        <v>10803.1</v>
+        <v>10773.65</v>
       </c>
       <c r="O56" t="n">
-        <v>10892.7</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>11126.7</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5215,55 +5203,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10462.4</v>
+        <v>10551.6</v>
       </c>
       <c r="C57" t="n">
-        <v>10602.6</v>
+        <v>10892.38</v>
       </c>
       <c r="D57" t="n">
-        <v>10367.3</v>
+        <v>10549.6</v>
       </c>
       <c r="E57" t="n">
-        <v>10552.1</v>
+        <v>10881.9</v>
       </c>
       <c r="F57" t="n">
-        <v>90.09999999999999</v>
+        <v>329.8</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0313</v>
       </c>
       <c r="H57" t="n">
-        <v>235.3</v>
+        <v>342.78</v>
       </c>
       <c r="I57" t="n">
-        <v>10022.7</v>
+        <v>10132</v>
       </c>
       <c r="J57" t="n">
-        <v>10037.65</v>
+        <v>10350.37</v>
       </c>
       <c r="K57" t="n">
-        <v>10278</v>
+        <v>10434.45</v>
       </c>
       <c r="L57" t="n">
-        <v>10518.35</v>
+        <v>10518.52</v>
       </c>
       <c r="M57" t="n">
-        <v>10646</v>
+        <v>10669.75</v>
       </c>
       <c r="N57" t="n">
-        <v>10773.65</v>
+        <v>10820.97</v>
       </c>
       <c r="O57" t="n">
-        <v>11126.7</v>
+        <v>10837.9</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5274,114 +5266,32 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>10551.6</v>
-      </c>
-      <c r="C58" t="n">
-        <v>10868.53</v>
-      </c>
-      <c r="D58" t="n">
-        <v>10549.6</v>
-      </c>
-      <c r="E58" t="n">
-        <v>10840.35</v>
-      </c>
-      <c r="F58" t="n">
-        <v>288.25</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0273</v>
-      </c>
-      <c r="H58" t="n">
-        <v>318.93</v>
-      </c>
-      <c r="I58" t="n">
-        <v>10132</v>
-      </c>
-      <c r="J58" t="n">
-        <v>10350.37</v>
-      </c>
-      <c r="K58" t="n">
-        <v>10434.45</v>
-      </c>
-      <c r="L58" t="n">
-        <v>10518.52</v>
-      </c>
-      <c r="M58" t="n">
-        <v>10669.75</v>
-      </c>
-      <c r="N58" t="n">
-        <v>10820.97</v>
-      </c>
-      <c r="O58" t="n">
-        <v>10837.9</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T58" s="8" t="inlineStr">
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U58" s="8" t="inlineStr">
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V58" s="8" t="inlineStr">
+      <c r="V57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -5219,7 +5219,7 @@
         <v>10551.6</v>
       </c>
       <c r="C57" t="n">
-        <v>10892.38</v>
+        <v>10892.4</v>
       </c>
       <c r="D57" t="n">
         <v>10549.6</v>
@@ -5234,7 +5234,7 @@
         <v>0.0313</v>
       </c>
       <c r="H57" t="n">
-        <v>342.78</v>
+        <v>342.8</v>
       </c>
       <c r="I57" t="n">
         <v>10132</v>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +662,25 @@
         <v>115</v>
       </c>
       <c r="I2" t="n">
-        <v>9077</v>
+        <v>9109.299999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>9078.82</v>
+        <v>9119.200000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>9157.35</v>
+        <v>9173.5</v>
       </c>
       <c r="L2" t="n">
-        <v>9235.879999999999</v>
+        <v>9227.799999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>9276.049999999999</v>
+        <v>9259.9</v>
       </c>
       <c r="N2" t="n">
-        <v>9316.23</v>
+        <v>9292</v>
       </c>
       <c r="O2" t="n">
-        <v>9433.1</v>
+        <v>9368.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,12 +698,14 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
@@ -711,7 +716,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -5292,6 +5297,90 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10882.26</v>
+      </c>
+      <c r="C58" t="n">
+        <v>10889.9</v>
+      </c>
+      <c r="D58" t="n">
+        <v>10730.23</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>159.67</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10206.8</v>
+      </c>
+      <c r="J58" t="n">
+        <v>10619.55</v>
+      </c>
+      <c r="K58" t="n">
+        <v>10710.5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>10801.45</v>
+      </c>
+      <c r="M58" t="n">
+        <v>11053.3</v>
+      </c>
+      <c r="N58" t="n">
+        <v>11305.15</v>
+      </c>
+      <c r="O58" t="n">
+        <v>11235.2</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5305,25 +5302,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10882.26</v>
+        <v>10882.3</v>
       </c>
       <c r="C58" t="n">
         <v>10889.9</v>
       </c>
       <c r="D58" t="n">
-        <v>10730.23</v>
+        <v>10730.2</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>10764.7</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-117.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0108</v>
       </c>
       <c r="H58" t="n">
-        <v>159.67</v>
+        <v>159.7</v>
       </c>
       <c r="I58" t="n">
         <v>10206.8</v>
@@ -5346,10 +5343,8 @@
       <c r="O58" t="n">
         <v>11235.2</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5357,9 +5352,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5378,7 +5373,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>115</v>
       </c>
       <c r="I2" t="n">
-        <v>9109.299999999999</v>
+        <v>9140.4</v>
       </c>
       <c r="J2" t="n">
-        <v>9119.200000000001</v>
+        <v>9158.08</v>
       </c>
       <c r="K2" t="n">
-        <v>9173.5</v>
+        <v>9189.049999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>9227.799999999999</v>
+        <v>9220.030000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>9259.9</v>
+        <v>9244.35</v>
       </c>
       <c r="N2" t="n">
-        <v>9292</v>
+        <v>9268.68</v>
       </c>
       <c r="O2" t="n">
-        <v>9368.5</v>
+        <v>9306.299999999999</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -5308,19 +5310,19 @@
         <v>10889.9</v>
       </c>
       <c r="D58" t="n">
-        <v>10730.2</v>
+        <v>10673</v>
       </c>
       <c r="E58" t="n">
-        <v>10764.7</v>
+        <v>10733</v>
       </c>
       <c r="F58" t="n">
-        <v>-117.2</v>
+        <v>-148.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0137</v>
       </c>
       <c r="H58" t="n">
-        <v>159.7</v>
+        <v>216.9</v>
       </c>
       <c r="I58" t="n">
         <v>10206.8</v>
@@ -5349,12 +5351,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>115</v>
       </c>
       <c r="I2" t="n">
-        <v>9140.4</v>
+        <v>9164.4</v>
       </c>
       <c r="J2" t="n">
-        <v>9158.08</v>
+        <v>9167.08</v>
       </c>
       <c r="K2" t="n">
-        <v>9189.049999999999</v>
+        <v>9195.049999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>9220.030000000001</v>
+        <v>9223.030000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>9244.35</v>
+        <v>9238.35</v>
       </c>
       <c r="N2" t="n">
-        <v>9268.68</v>
+        <v>9253.68</v>
       </c>
       <c r="O2" t="n">
-        <v>9306.299999999999</v>
+        <v>9294.299999999999</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -702,11 +702,13 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5313,13 +5315,13 @@
         <v>10673</v>
       </c>
       <c r="E58" t="n">
-        <v>10733</v>
+        <v>10752.88</v>
       </c>
       <c r="F58" t="n">
-        <v>-148.9</v>
+        <v>-129.02</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0119</v>
       </c>
       <c r="H58" t="n">
         <v>216.9</v>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -5312,19 +5312,19 @@
         <v>10889.9</v>
       </c>
       <c r="D58" t="n">
-        <v>10673</v>
+        <v>10669.39</v>
       </c>
       <c r="E58" t="n">
-        <v>10752.88</v>
+        <v>10725.03</v>
       </c>
       <c r="F58" t="n">
-        <v>-129.02</v>
+        <v>-156.87</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0119</v>
+        <v>-0.0144</v>
       </c>
       <c r="H58" t="n">
-        <v>216.9</v>
+        <v>220.51</v>
       </c>
       <c r="I58" t="n">
         <v>10206.8</v>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9216.700000000001</v>
+        <v>9284.799999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>9292.1</v>
+        <v>9494.6</v>
       </c>
       <c r="D2" t="n">
-        <v>9177.1</v>
+        <v>9266.299999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>9284.799999999999</v>
+        <v>9491.299999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>68.09999999999999</v>
+        <v>206.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0222</v>
       </c>
       <c r="H2" t="n">
-        <v>115</v>
+        <v>228.3</v>
       </c>
       <c r="I2" t="n">
-        <v>9164.4</v>
+        <v>9062.1</v>
       </c>
       <c r="J2" t="n">
-        <v>9167.08</v>
+        <v>9194.9</v>
       </c>
       <c r="K2" t="n">
-        <v>9195.049999999999</v>
+        <v>9227.299999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>9223.030000000001</v>
+        <v>9259.700000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>9238.35</v>
+        <v>9342.299999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>9253.68</v>
+        <v>9424.9</v>
       </c>
       <c r="O2" t="n">
-        <v>9294.299999999999</v>
+        <v>9407.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,89 +685,83 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9284.799999999999</v>
+        <v>9491.200000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>9494.6</v>
+        <v>9577.1</v>
       </c>
       <c r="D3" t="n">
-        <v>9266.299999999999</v>
+        <v>9414.6</v>
       </c>
       <c r="E3" t="n">
-        <v>9491.299999999999</v>
+        <v>9427.5</v>
       </c>
       <c r="F3" t="n">
-        <v>206.5</v>
+        <v>-63.8</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0067</v>
       </c>
       <c r="H3" t="n">
-        <v>228.3</v>
+        <v>162.5</v>
       </c>
       <c r="I3" t="n">
-        <v>9062.1</v>
+        <v>9038</v>
       </c>
       <c r="J3" t="n">
-        <v>9194.9</v>
+        <v>9318.43</v>
       </c>
       <c r="K3" t="n">
-        <v>9227.299999999999</v>
+        <v>9377.15</v>
       </c>
       <c r="L3" t="n">
-        <v>9259.700000000001</v>
+        <v>9435.870000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>9342.299999999999</v>
+        <v>9605.450000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>9424.9</v>
+        <v>9775.02</v>
       </c>
       <c r="O3" t="n">
-        <v>9407.1</v>
+        <v>9722.9</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -778,80 +772,78 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9491.200000000001</v>
+        <v>9427.5</v>
       </c>
       <c r="C4" t="n">
-        <v>9577.1</v>
+        <v>9474.299999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>9414.6</v>
+        <v>9276.9</v>
       </c>
       <c r="E4" t="n">
-        <v>9427.5</v>
+        <v>9354.6</v>
       </c>
       <c r="F4" t="n">
-        <v>-63.8</v>
+        <v>-72.90000000000001</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0067</v>
+        <v>-0.0077</v>
       </c>
       <c r="H4" t="n">
-        <v>162.5</v>
+        <v>197.4</v>
       </c>
       <c r="I4" t="n">
-        <v>9038</v>
+        <v>9252.1</v>
       </c>
       <c r="J4" t="n">
-        <v>9318.43</v>
+        <v>9230.83</v>
       </c>
       <c r="K4" t="n">
-        <v>9377.15</v>
+        <v>9346.25</v>
       </c>
       <c r="L4" t="n">
-        <v>9435.870000000001</v>
+        <v>9461.67</v>
       </c>
       <c r="M4" t="n">
-        <v>9605.450000000001</v>
+        <v>9508.75</v>
       </c>
       <c r="N4" t="n">
-        <v>9775.02</v>
+        <v>9555.83</v>
       </c>
       <c r="O4" t="n">
-        <v>9722.9</v>
+        <v>9739.6</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -859,12 +851,14 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -883,57 +877,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9427.5</v>
+        <v>9354.5</v>
       </c>
       <c r="C5" t="n">
-        <v>9474.299999999999</v>
+        <v>9645.6</v>
       </c>
       <c r="D5" t="n">
-        <v>9276.9</v>
+        <v>9354.5</v>
       </c>
       <c r="E5" t="n">
-        <v>9354.6</v>
+        <v>9645.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-72.90000000000001</v>
+        <v>291</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0311</v>
       </c>
       <c r="H5" t="n">
-        <v>197.4</v>
+        <v>291.1</v>
       </c>
       <c r="I5" t="n">
-        <v>9252.1</v>
+        <v>9079.5</v>
       </c>
       <c r="J5" t="n">
-        <v>9230.83</v>
+        <v>9146.700000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>9346.25</v>
+        <v>9255.9</v>
       </c>
       <c r="L5" t="n">
-        <v>9461.67</v>
+        <v>9365.1</v>
       </c>
       <c r="M5" t="n">
-        <v>9508.75</v>
+        <v>9453.299999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>9555.83</v>
+        <v>9541.5</v>
       </c>
       <c r="O5" t="n">
-        <v>9739.6</v>
+        <v>9671.700000000001</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -941,83 +935,83 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
-      </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9354.5</v>
+        <v>9645.6</v>
       </c>
       <c r="C6" t="n">
-        <v>9645.6</v>
+        <v>9787.6</v>
       </c>
       <c r="D6" t="n">
-        <v>9354.5</v>
+        <v>9632.799999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>9645.6</v>
+        <v>9717.299999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>291</v>
+        <v>71.7</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0311</v>
+        <v>0.0074</v>
       </c>
       <c r="H6" t="n">
-        <v>291.1</v>
+        <v>154.8</v>
       </c>
       <c r="I6" t="n">
-        <v>9079.5</v>
+        <v>9063.4</v>
       </c>
       <c r="J6" t="n">
-        <v>9146.700000000001</v>
+        <v>9427.27</v>
       </c>
       <c r="K6" t="n">
-        <v>9255.9</v>
+        <v>9500.049999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>9365.1</v>
+        <v>9572.82</v>
       </c>
       <c r="M6" t="n">
-        <v>9453.299999999999</v>
+        <v>9791.15</v>
       </c>
       <c r="N6" t="n">
-        <v>9541.5</v>
+        <v>10009.47</v>
       </c>
       <c r="O6" t="n">
-        <v>9671.700000000001</v>
+        <v>9936.700000000001</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1035,18 +1029,14 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -1058,50 +1048,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9645.6</v>
+        <v>9717.299999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>9787.6</v>
+        <v>9786.799999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>9632.799999999999</v>
+        <v>9574.200000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>9717.299999999999</v>
+        <v>9682.6</v>
       </c>
       <c r="F7" t="n">
-        <v>71.7</v>
+        <v>-34.7</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0036</v>
       </c>
       <c r="H7" t="n">
-        <v>154.8</v>
+        <v>212.6</v>
       </c>
       <c r="I7" t="n">
-        <v>9063.4</v>
+        <v>9478</v>
       </c>
       <c r="J7" t="n">
-        <v>9427.27</v>
+        <v>9566.049999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>9500.049999999999</v>
+        <v>9639.9</v>
       </c>
       <c r="L7" t="n">
-        <v>9572.82</v>
+        <v>9713.75</v>
       </c>
       <c r="M7" t="n">
-        <v>9791.15</v>
+        <v>9794.700000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>10009.47</v>
+        <v>9875.65</v>
       </c>
       <c r="O7" t="n">
-        <v>9936.700000000001</v>
+        <v>9942.4</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1109,18 +1099,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1133,55 +1123,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9717.299999999999</v>
+        <v>9682.6</v>
       </c>
       <c r="C8" t="n">
-        <v>9786.799999999999</v>
+        <v>9930.1</v>
       </c>
       <c r="D8" t="n">
-        <v>9574.200000000001</v>
+        <v>9610.5</v>
       </c>
       <c r="E8" t="n">
-        <v>9682.6</v>
+        <v>9698.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-34.7</v>
+        <v>15.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0016</v>
       </c>
       <c r="H8" t="n">
-        <v>212.6</v>
+        <v>319.6</v>
       </c>
       <c r="I8" t="n">
-        <v>9478</v>
+        <v>9361.6</v>
       </c>
       <c r="J8" t="n">
-        <v>9566.049999999999</v>
+        <v>9471.049999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>9639.9</v>
+        <v>9576.299999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>9713.75</v>
+        <v>9681.549999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>9794.700000000001</v>
+        <v>9788.9</v>
       </c>
       <c r="N8" t="n">
-        <v>9875.65</v>
+        <v>9896.25</v>
       </c>
       <c r="O8" t="n">
-        <v>9942.4</v>
+        <v>9999.4</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1189,21 +1183,23 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1213,59 +1209,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9682.6</v>
+        <v>9698.4</v>
       </c>
       <c r="C9" t="n">
-        <v>9930.1</v>
+        <v>9707.700000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>9610.5</v>
+        <v>9423.9</v>
       </c>
       <c r="E9" t="n">
-        <v>9698.4</v>
+        <v>9539.700000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>15.8</v>
+        <v>-158.7</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0164</v>
       </c>
       <c r="H9" t="n">
-        <v>319.6</v>
+        <v>283.8</v>
       </c>
       <c r="I9" t="n">
-        <v>9361.6</v>
+        <v>9290.9</v>
       </c>
       <c r="J9" t="n">
-        <v>9471.049999999999</v>
+        <v>9342.85</v>
       </c>
       <c r="K9" t="n">
-        <v>9576.299999999999</v>
+        <v>9538.6</v>
       </c>
       <c r="L9" t="n">
-        <v>9681.549999999999</v>
+        <v>9734.35</v>
       </c>
       <c r="M9" t="n">
-        <v>9788.9</v>
+        <v>9858.200000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>9896.25</v>
+        <v>9982.049999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>9999.4</v>
+        <v>10249.7</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,23 +1265,21 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1299,55 +1289,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9698.4</v>
+        <v>9539.700000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>9707.700000000001</v>
+        <v>9740.200000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>9423.9</v>
+        <v>9521.5</v>
       </c>
       <c r="E10" t="n">
-        <v>9539.700000000001</v>
+        <v>9720.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-158.7</v>
+        <v>180.8</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.019</v>
       </c>
       <c r="H10" t="n">
-        <v>283.8</v>
+        <v>218.7</v>
       </c>
       <c r="I10" t="n">
-        <v>9290.9</v>
+        <v>9140.1</v>
       </c>
       <c r="J10" t="n">
-        <v>9342.85</v>
+        <v>9242.85</v>
       </c>
       <c r="K10" t="n">
-        <v>9538.6</v>
+        <v>9397.799999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>9734.35</v>
+        <v>9552.75</v>
       </c>
       <c r="M10" t="n">
-        <v>9858.200000000001</v>
+        <v>9681.6</v>
       </c>
       <c r="N10" t="n">
-        <v>9982.049999999999</v>
+        <v>9810.450000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>10249.7</v>
+        <v>9991.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1355,19 +1349,19 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1379,59 +1373,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9539.700000000001</v>
+        <v>9720.6</v>
       </c>
       <c r="C11" t="n">
-        <v>9740.200000000001</v>
+        <v>9744.799999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>9521.5</v>
+        <v>9667</v>
       </c>
       <c r="E11" t="n">
-        <v>9720.5</v>
+        <v>9667</v>
       </c>
       <c r="F11" t="n">
-        <v>180.8</v>
+        <v>-53.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.019</v>
+        <v>-0.0055</v>
       </c>
       <c r="H11" t="n">
-        <v>218.7</v>
+        <v>77.8</v>
       </c>
       <c r="I11" t="n">
-        <v>9140.1</v>
+        <v>9302.799999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>9242.85</v>
+        <v>9546.620000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>9397.799999999999</v>
+        <v>9611.15</v>
       </c>
       <c r="L11" t="n">
-        <v>9552.75</v>
+        <v>9675.68</v>
       </c>
       <c r="M11" t="n">
-        <v>9681.6</v>
+        <v>9829.85</v>
       </c>
       <c r="N11" t="n">
-        <v>9810.450000000001</v>
+        <v>9984.030000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>9991.5</v>
+        <v>9958.9</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1442,15 +1432,13 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1463,55 +1451,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9720.6</v>
+        <v>9667.1</v>
       </c>
       <c r="C12" t="n">
-        <v>9744.799999999999</v>
+        <v>9761.5</v>
       </c>
       <c r="D12" t="n">
-        <v>9667</v>
+        <v>9622.700000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>9667</v>
+        <v>9649</v>
       </c>
       <c r="F12" t="n">
-        <v>-53.5</v>
+        <v>-18</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0019</v>
       </c>
       <c r="H12" t="n">
-        <v>77.8</v>
+        <v>138.8</v>
       </c>
       <c r="I12" t="n">
-        <v>9302.799999999999</v>
+        <v>9589.200000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>9546.620000000001</v>
+        <v>9569.75</v>
       </c>
       <c r="K12" t="n">
-        <v>9611.15</v>
+        <v>9628.1</v>
       </c>
       <c r="L12" t="n">
-        <v>9675.68</v>
+        <v>9686.450000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>9829.85</v>
+        <v>9705.9</v>
       </c>
       <c r="N12" t="n">
-        <v>9984.030000000001</v>
+        <v>9725.35</v>
       </c>
       <c r="O12" t="n">
-        <v>9958.9</v>
+        <v>9822.6</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1519,19 +1511,25 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1543,57 +1541,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9667.1</v>
+        <v>9649</v>
       </c>
       <c r="C13" t="n">
-        <v>9761.5</v>
+        <v>9903.1</v>
       </c>
       <c r="D13" t="n">
-        <v>9622.700000000001</v>
+        <v>9649</v>
       </c>
       <c r="E13" t="n">
-        <v>9649</v>
+        <v>9897.4</v>
       </c>
       <c r="F13" t="n">
-        <v>-18</v>
+        <v>248.4</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0257</v>
       </c>
       <c r="H13" t="n">
-        <v>138.8</v>
+        <v>254.1</v>
       </c>
       <c r="I13" t="n">
-        <v>9589.200000000001</v>
+        <v>9483.9</v>
       </c>
       <c r="J13" t="n">
-        <v>9569.75</v>
+        <v>9488.65</v>
       </c>
       <c r="K13" t="n">
-        <v>9628.1</v>
+        <v>9579.6</v>
       </c>
       <c r="L13" t="n">
-        <v>9686.450000000001</v>
+        <v>9670.549999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>9705.9</v>
+        <v>9718.4</v>
       </c>
       <c r="N13" t="n">
-        <v>9725.35</v>
+        <v>9766.25</v>
       </c>
       <c r="O13" t="n">
-        <v>9822.6</v>
+        <v>9900.299999999999</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1601,87 +1599,83 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
-      </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9649</v>
+        <v>9897.4</v>
       </c>
       <c r="C14" t="n">
-        <v>9903.1</v>
+        <v>9901.5</v>
       </c>
       <c r="D14" t="n">
-        <v>9649</v>
+        <v>9829.4</v>
       </c>
       <c r="E14" t="n">
-        <v>9897.4</v>
+        <v>9870.700000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>248.4</v>
+        <v>-26.7</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0257</v>
+        <v>-0.0027</v>
       </c>
       <c r="H14" t="n">
-        <v>254.1</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>9483.9</v>
+        <v>9394.9</v>
       </c>
       <c r="J14" t="n">
-        <v>9488.65</v>
+        <v>9703.98</v>
       </c>
       <c r="K14" t="n">
-        <v>9579.6</v>
+        <v>9770.35</v>
       </c>
       <c r="L14" t="n">
-        <v>9670.549999999999</v>
+        <v>9836.73</v>
       </c>
       <c r="M14" t="n">
-        <v>9718.4</v>
+        <v>10024.45</v>
       </c>
       <c r="N14" t="n">
-        <v>9766.25</v>
+        <v>10212.18</v>
       </c>
       <c r="O14" t="n">
-        <v>9900.299999999999</v>
+        <v>10157.2</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1694,78 +1688,76 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9897.4</v>
+        <v>9870.700000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>9901.5</v>
+        <v>10046.3</v>
       </c>
       <c r="D15" t="n">
-        <v>9829.4</v>
+        <v>9858.5</v>
       </c>
       <c r="E15" t="n">
-        <v>9870.700000000001</v>
+        <v>9951.1</v>
       </c>
       <c r="F15" t="n">
-        <v>-26.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0081</v>
       </c>
       <c r="H15" t="n">
-        <v>72.09999999999999</v>
+        <v>187.8</v>
       </c>
       <c r="I15" t="n">
-        <v>9394.9</v>
+        <v>9757.299999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>9703.98</v>
+        <v>9801.23</v>
       </c>
       <c r="K15" t="n">
-        <v>9770.35</v>
+        <v>9834.65</v>
       </c>
       <c r="L15" t="n">
-        <v>9836.73</v>
+        <v>9868.08</v>
       </c>
       <c r="M15" t="n">
-        <v>10024.45</v>
+        <v>9906.75</v>
       </c>
       <c r="N15" t="n">
-        <v>10212.18</v>
+        <v>9945.42</v>
       </c>
       <c r="O15" t="n">
-        <v>10157.2</v>
+        <v>9973.6</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1778,76 +1770,78 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9870.700000000001</v>
+        <v>9951.5</v>
       </c>
       <c r="C16" t="n">
-        <v>10046.3</v>
+        <v>10158.4</v>
       </c>
       <c r="D16" t="n">
-        <v>9858.5</v>
+        <v>9951.5</v>
       </c>
       <c r="E16" t="n">
-        <v>9951.1</v>
+        <v>10124.6</v>
       </c>
       <c r="F16" t="n">
-        <v>80.40000000000001</v>
+        <v>173.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0081</v>
+        <v>0.0174</v>
       </c>
       <c r="H16" t="n">
-        <v>187.8</v>
+        <v>206.9</v>
       </c>
       <c r="I16" t="n">
-        <v>9757.299999999999</v>
+        <v>9670.700000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>9801.23</v>
+        <v>9762.65</v>
       </c>
       <c r="K16" t="n">
-        <v>9834.65</v>
+        <v>9857.200000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>9868.08</v>
+        <v>9951.75</v>
       </c>
       <c r="M16" t="n">
-        <v>9906.75</v>
+        <v>10045</v>
       </c>
       <c r="N16" t="n">
-        <v>9945.42</v>
+        <v>10138.25</v>
       </c>
       <c r="O16" t="n">
-        <v>9973.6</v>
+        <v>10234.1</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1873,10 +1867,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1888,50 +1880,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9951.5</v>
+        <v>10124.5</v>
       </c>
       <c r="C17" t="n">
-        <v>10158.4</v>
+        <v>10257.8</v>
       </c>
       <c r="D17" t="n">
-        <v>9951.5</v>
+        <v>10089.9</v>
       </c>
       <c r="E17" t="n">
-        <v>10124.6</v>
+        <v>10235.3</v>
       </c>
       <c r="F17" t="n">
-        <v>173.5</v>
+        <v>110.7</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0174</v>
+        <v>0.0109</v>
       </c>
       <c r="H17" t="n">
-        <v>206.9</v>
+        <v>167.9</v>
       </c>
       <c r="I17" t="n">
-        <v>9670.700000000001</v>
+        <v>9744.6</v>
       </c>
       <c r="J17" t="n">
-        <v>9762.65</v>
+        <v>9952.52</v>
       </c>
       <c r="K17" t="n">
-        <v>9857.200000000001</v>
+        <v>10021.15</v>
       </c>
       <c r="L17" t="n">
-        <v>9951.75</v>
+        <v>10089.77</v>
       </c>
       <c r="M17" t="n">
-        <v>10045</v>
+        <v>10228.05</v>
       </c>
       <c r="N17" t="n">
-        <v>10138.25</v>
+        <v>10366.32</v>
       </c>
       <c r="O17" t="n">
-        <v>10234.1</v>
+        <v>10365.3</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1949,13 +1941,11 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1970,70 +1960,72 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10124.5</v>
+        <v>10235.3</v>
       </c>
       <c r="C18" t="n">
-        <v>10257.8</v>
+        <v>10235.3</v>
       </c>
       <c r="D18" t="n">
-        <v>10089.9</v>
+        <v>10050.2</v>
       </c>
       <c r="E18" t="n">
-        <v>10235.3</v>
+        <v>10143.4</v>
       </c>
       <c r="F18" t="n">
-        <v>110.7</v>
+        <v>-91.90000000000001</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>167.9</v>
+        <v>185.1</v>
       </c>
       <c r="I18" t="n">
-        <v>9744.6</v>
+        <v>9922</v>
       </c>
       <c r="J18" t="n">
-        <v>9952.52</v>
+        <v>10098.13</v>
       </c>
       <c r="K18" t="n">
-        <v>10021.15</v>
+        <v>10151.35</v>
       </c>
       <c r="L18" t="n">
-        <v>10089.77</v>
+        <v>10204.57</v>
       </c>
       <c r="M18" t="n">
-        <v>10228.05</v>
+        <v>10319.25</v>
       </c>
       <c r="N18" t="n">
-        <v>10366.32</v>
+        <v>10433.92</v>
       </c>
       <c r="O18" t="n">
-        <v>10365.3</v>
+        <v>10425.7</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2045,77 +2037,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10235.3</v>
+        <v>10143.1</v>
       </c>
       <c r="C19" t="n">
-        <v>10235.3</v>
+        <v>10277.7</v>
       </c>
       <c r="D19" t="n">
-        <v>10050.2</v>
+        <v>10125.3</v>
       </c>
       <c r="E19" t="n">
-        <v>10143.4</v>
+        <v>10223.5</v>
       </c>
       <c r="F19" t="n">
-        <v>-91.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>185.1</v>
+        <v>152.4</v>
       </c>
       <c r="I19" t="n">
-        <v>9922</v>
+        <v>9865.1</v>
       </c>
       <c r="J19" t="n">
-        <v>10098.13</v>
+        <v>9958.629999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>10151.35</v>
+        <v>10050.85</v>
       </c>
       <c r="L19" t="n">
-        <v>10204.57</v>
+        <v>10143.08</v>
       </c>
       <c r="M19" t="n">
-        <v>10319.25</v>
+        <v>10235.95</v>
       </c>
       <c r="N19" t="n">
-        <v>10433.92</v>
+        <v>10328.83</v>
       </c>
       <c r="O19" t="n">
-        <v>10425.7</v>
+        <v>10420.4</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2127,59 +2121,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10143.1</v>
+        <v>10223.7</v>
       </c>
       <c r="C20" t="n">
-        <v>10277.7</v>
+        <v>10481.5</v>
       </c>
       <c r="D20" t="n">
-        <v>10125.3</v>
+        <v>10145.4</v>
       </c>
       <c r="E20" t="n">
-        <v>10223.5</v>
+        <v>10369.8</v>
       </c>
       <c r="F20" t="n">
-        <v>80.09999999999999</v>
+        <v>146.3</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0143</v>
       </c>
       <c r="H20" t="n">
-        <v>152.4</v>
+        <v>336.1</v>
       </c>
       <c r="I20" t="n">
-        <v>9865.1</v>
+        <v>9972.9</v>
       </c>
       <c r="J20" t="n">
-        <v>9958.629999999999</v>
+        <v>10082.1</v>
       </c>
       <c r="K20" t="n">
-        <v>10050.85</v>
+        <v>10147.3</v>
       </c>
       <c r="L20" t="n">
-        <v>10143.08</v>
+        <v>10212.5</v>
       </c>
       <c r="M20" t="n">
-        <v>10235.95</v>
+        <v>10299.7</v>
       </c>
       <c r="N20" t="n">
-        <v>10328.83</v>
+        <v>10386.9</v>
       </c>
       <c r="O20" t="n">
-        <v>10420.4</v>
+        <v>10430.1</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2187,8 +2177,10 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
@@ -2197,14 +2189,18 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2216,50 +2212,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10223.7</v>
+        <v>10369.8</v>
       </c>
       <c r="C21" t="n">
-        <v>10481.5</v>
+        <v>10535.8</v>
       </c>
       <c r="D21" t="n">
-        <v>10145.4</v>
+        <v>10316</v>
       </c>
       <c r="E21" t="n">
-        <v>10369.8</v>
+        <v>10446.4</v>
       </c>
       <c r="F21" t="n">
-        <v>146.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0074</v>
       </c>
       <c r="H21" t="n">
-        <v>336.1</v>
+        <v>219.8</v>
       </c>
       <c r="I21" t="n">
-        <v>9972.9</v>
+        <v>9809.299999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>10082.1</v>
+        <v>10061.88</v>
       </c>
       <c r="K21" t="n">
-        <v>10147.3</v>
+        <v>10201.75</v>
       </c>
       <c r="L21" t="n">
-        <v>10212.5</v>
+        <v>10341.62</v>
       </c>
       <c r="M21" t="n">
-        <v>10299.7</v>
+        <v>10537.85</v>
       </c>
       <c r="N21" t="n">
-        <v>10386.9</v>
+        <v>10734.07</v>
       </c>
       <c r="O21" t="n">
-        <v>10430.1</v>
+        <v>10817.6</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2267,10 +2263,8 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
@@ -2279,18 +2273,14 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2302,50 +2292,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10369.8</v>
+        <v>10446.3</v>
       </c>
       <c r="C22" t="n">
-        <v>10535.8</v>
+        <v>10745.8</v>
       </c>
       <c r="D22" t="n">
-        <v>10316</v>
+        <v>10446.3</v>
       </c>
       <c r="E22" t="n">
-        <v>10446.4</v>
+        <v>10686.9</v>
       </c>
       <c r="F22" t="n">
-        <v>76.59999999999999</v>
+        <v>240.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.023</v>
       </c>
       <c r="H22" t="n">
-        <v>219.8</v>
+        <v>299.5</v>
       </c>
       <c r="I22" t="n">
-        <v>9809.299999999999</v>
+        <v>10096.2</v>
       </c>
       <c r="J22" t="n">
-        <v>10061.88</v>
+        <v>10236.85</v>
       </c>
       <c r="K22" t="n">
-        <v>10201.75</v>
+        <v>10336.5</v>
       </c>
       <c r="L22" t="n">
-        <v>10341.62</v>
+        <v>10436.15</v>
       </c>
       <c r="M22" t="n">
-        <v>10537.85</v>
+        <v>10556.3</v>
       </c>
       <c r="N22" t="n">
-        <v>10734.07</v>
+        <v>10676.45</v>
       </c>
       <c r="O22" t="n">
-        <v>10817.6</v>
+        <v>10755.6</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2363,11 +2353,13 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2382,50 +2374,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10446.3</v>
+        <v>10686.8</v>
       </c>
       <c r="C23" t="n">
-        <v>10745.8</v>
+        <v>10934.9</v>
       </c>
       <c r="D23" t="n">
-        <v>10446.3</v>
+        <v>10645.8</v>
       </c>
       <c r="E23" t="n">
-        <v>10686.9</v>
+        <v>10910.6</v>
       </c>
       <c r="F23" t="n">
-        <v>240.5</v>
+        <v>223.7</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0209</v>
       </c>
       <c r="H23" t="n">
-        <v>299.5</v>
+        <v>289.1</v>
       </c>
       <c r="I23" t="n">
-        <v>10096.2</v>
+        <v>10146.8</v>
       </c>
       <c r="J23" t="n">
-        <v>10236.85</v>
+        <v>10432.83</v>
       </c>
       <c r="K23" t="n">
-        <v>10336.5</v>
+        <v>10537.15</v>
       </c>
       <c r="L23" t="n">
-        <v>10436.15</v>
+        <v>10641.48</v>
       </c>
       <c r="M23" t="n">
-        <v>10556.3</v>
+        <v>10836.65</v>
       </c>
       <c r="N23" t="n">
-        <v>10676.45</v>
+        <v>11031.83</v>
       </c>
       <c r="O23" t="n">
-        <v>10755.6</v>
+        <v>11045.3</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2443,13 +2435,11 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2464,79 +2454,83 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10686.8</v>
+        <v>10911</v>
       </c>
       <c r="C24" t="n">
-        <v>10934.9</v>
+        <v>10911</v>
       </c>
       <c r="D24" t="n">
-        <v>10645.8</v>
+        <v>10234.5</v>
       </c>
       <c r="E24" t="n">
-        <v>10910.6</v>
+        <v>10284.8</v>
       </c>
       <c r="F24" t="n">
-        <v>223.7</v>
+        <v>-625.8</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0574</v>
       </c>
       <c r="H24" t="n">
-        <v>289.1</v>
+        <v>676.5</v>
       </c>
       <c r="I24" t="n">
-        <v>10146.8</v>
+        <v>10356.7</v>
       </c>
       <c r="J24" t="n">
-        <v>10432.83</v>
+        <v>10681.62</v>
       </c>
       <c r="K24" t="n">
-        <v>10537.15</v>
+        <v>10766.05</v>
       </c>
       <c r="L24" t="n">
-        <v>10641.48</v>
+        <v>10850.47</v>
       </c>
       <c r="M24" t="n">
-        <v>10836.65</v>
+        <v>11055.15</v>
       </c>
       <c r="N24" t="n">
-        <v>11031.83</v>
+        <v>11259.82</v>
       </c>
       <c r="O24" t="n">
-        <v>11045.3</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
+        <v>11224</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2544,69 +2538,63 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10911</v>
+        <v>10285</v>
       </c>
       <c r="C25" t="n">
-        <v>10911</v>
+        <v>10447.5</v>
       </c>
       <c r="D25" t="n">
-        <v>10234.5</v>
+        <v>10082</v>
       </c>
       <c r="E25" t="n">
-        <v>10284.8</v>
+        <v>10261.2</v>
       </c>
       <c r="F25" t="n">
-        <v>-625.8</v>
+        <v>-23.6</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0574</v>
+        <v>-0.0023</v>
       </c>
       <c r="H25" t="n">
-        <v>676.5</v>
+        <v>365.5</v>
       </c>
       <c r="I25" t="n">
-        <v>10356.7</v>
+        <v>9558</v>
       </c>
       <c r="J25" t="n">
-        <v>10681.62</v>
+        <v>9464.32</v>
       </c>
       <c r="K25" t="n">
-        <v>10766.05</v>
+        <v>9946.549999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>10850.47</v>
+        <v>10428.77</v>
       </c>
       <c r="M25" t="n">
-        <v>11055.15</v>
+        <v>10623.05</v>
       </c>
       <c r="N25" t="n">
-        <v>11259.82</v>
+        <v>10817.32</v>
       </c>
       <c r="O25" t="n">
-        <v>11224</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>11587.5</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2628,67 +2616,73 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10285</v>
+        <v>10261.1</v>
       </c>
       <c r="C26" t="n">
-        <v>10447.5</v>
+        <v>10447.7</v>
       </c>
       <c r="D26" t="n">
-        <v>10082</v>
+        <v>9915.700000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>10261.2</v>
+        <v>9918.299999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-23.6</v>
+        <v>-342.9</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0334</v>
       </c>
       <c r="H26" t="n">
-        <v>365.5</v>
+        <v>532</v>
       </c>
       <c r="I26" t="n">
-        <v>9558</v>
+        <v>9716.5</v>
       </c>
       <c r="J26" t="n">
-        <v>9464.32</v>
+        <v>9893.93</v>
       </c>
       <c r="K26" t="n">
-        <v>9946.549999999999</v>
+        <v>10078.45</v>
       </c>
       <c r="L26" t="n">
-        <v>10428.77</v>
+        <v>10262.98</v>
       </c>
       <c r="M26" t="n">
-        <v>10623.05</v>
+        <v>10443.95</v>
       </c>
       <c r="N26" t="n">
-        <v>10817.32</v>
+        <v>10624.93</v>
       </c>
       <c r="O26" t="n">
-        <v>11587.5</v>
+        <v>10813</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2701,78 +2695,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10261.1</v>
+        <v>9918.5</v>
       </c>
       <c r="C27" t="n">
-        <v>10447.7</v>
+        <v>10118.2</v>
       </c>
       <c r="D27" t="n">
-        <v>9915.700000000001</v>
+        <v>9670.5</v>
       </c>
       <c r="E27" t="n">
-        <v>9918.299999999999</v>
+        <v>9967.4</v>
       </c>
       <c r="F27" t="n">
-        <v>-342.9</v>
+        <v>49.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0334</v>
+        <v>0.005</v>
       </c>
       <c r="H27" t="n">
-        <v>532</v>
+        <v>447.7</v>
       </c>
       <c r="I27" t="n">
-        <v>9716.5</v>
+        <v>9383.700000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>9893.93</v>
+        <v>9254.6</v>
       </c>
       <c r="K27" t="n">
-        <v>10078.45</v>
+        <v>9652.299999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>10262.98</v>
+        <v>10050</v>
       </c>
       <c r="M27" t="n">
-        <v>10443.95</v>
+        <v>10184.3</v>
       </c>
       <c r="N27" t="n">
-        <v>10624.93</v>
+        <v>10318.6</v>
       </c>
       <c r="O27" t="n">
-        <v>10813</v>
+        <v>10979.7</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2794,50 +2786,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9918.5</v>
+        <v>9967.5</v>
       </c>
       <c r="C28" t="n">
-        <v>10118.2</v>
+        <v>10465.2</v>
       </c>
       <c r="D28" t="n">
-        <v>9670.5</v>
+        <v>9958.1</v>
       </c>
       <c r="E28" t="n">
-        <v>9967.4</v>
+        <v>10436.3</v>
       </c>
       <c r="F28" t="n">
-        <v>49.1</v>
+        <v>468.9</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.005</v>
+        <v>0.047</v>
       </c>
       <c r="H28" t="n">
-        <v>447.7</v>
+        <v>507.1</v>
       </c>
       <c r="I28" t="n">
-        <v>9383.700000000001</v>
+        <v>9222.799999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>9254.6</v>
+        <v>9556.23</v>
       </c>
       <c r="K28" t="n">
-        <v>9652.299999999999</v>
+        <v>9743.549999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>10050</v>
+        <v>9930.879999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>10184.3</v>
+        <v>10191.25</v>
       </c>
       <c r="N28" t="n">
-        <v>10318.6</v>
+        <v>10451.63</v>
       </c>
       <c r="O28" t="n">
-        <v>10979.7</v>
+        <v>10565.9</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2848,16 +2840,20 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2869,57 +2865,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9967.5</v>
+        <v>10436.2</v>
       </c>
       <c r="C29" t="n">
-        <v>10465.2</v>
+        <v>10687.9</v>
       </c>
       <c r="D29" t="n">
-        <v>9958.1</v>
+        <v>10330.9</v>
       </c>
       <c r="E29" t="n">
-        <v>10436.3</v>
+        <v>10600.5</v>
       </c>
       <c r="F29" t="n">
-        <v>468.9</v>
+        <v>164.2</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.047</v>
+        <v>0.0157</v>
       </c>
       <c r="H29" t="n">
-        <v>507.1</v>
+        <v>357</v>
       </c>
       <c r="I29" t="n">
-        <v>9222.799999999999</v>
+        <v>9451</v>
       </c>
       <c r="J29" t="n">
-        <v>9556.23</v>
+        <v>10041.52</v>
       </c>
       <c r="K29" t="n">
-        <v>9743.549999999999</v>
+        <v>10182.75</v>
       </c>
       <c r="L29" t="n">
-        <v>9930.879999999999</v>
+        <v>10323.97</v>
       </c>
       <c r="M29" t="n">
-        <v>10191.25</v>
+        <v>10689.85</v>
       </c>
       <c r="N29" t="n">
-        <v>10451.63</v>
+        <v>11055.73</v>
       </c>
       <c r="O29" t="n">
-        <v>10565.9</v>
+        <v>10972.3</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2937,13 +2933,11 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2962,50 +2956,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10436.2</v>
+        <v>10601.5</v>
       </c>
       <c r="C30" t="n">
-        <v>10687.9</v>
+        <v>10667.6</v>
       </c>
       <c r="D30" t="n">
-        <v>10330.9</v>
+        <v>10528.6</v>
       </c>
       <c r="E30" t="n">
-        <v>10600.5</v>
+        <v>10667.6</v>
       </c>
       <c r="F30" t="n">
-        <v>164.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0063</v>
       </c>
       <c r="H30" t="n">
-        <v>357</v>
+        <v>139</v>
       </c>
       <c r="I30" t="n">
-        <v>9451</v>
+        <v>9973.9</v>
       </c>
       <c r="J30" t="n">
-        <v>10041.52</v>
+        <v>10289.05</v>
       </c>
       <c r="K30" t="n">
-        <v>10182.75</v>
+        <v>10422</v>
       </c>
       <c r="L30" t="n">
-        <v>10323.97</v>
+        <v>10554.95</v>
       </c>
       <c r="M30" t="n">
-        <v>10689.85</v>
+        <v>10779</v>
       </c>
       <c r="N30" t="n">
-        <v>11055.73</v>
+        <v>11003.05</v>
       </c>
       <c r="O30" t="n">
-        <v>10972.3</v>
+        <v>11044.9</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3039,77 +3033,81 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10601.5</v>
+        <v>10668.4</v>
       </c>
       <c r="C31" t="n">
-        <v>10667.6</v>
+        <v>10683.7</v>
       </c>
       <c r="D31" t="n">
-        <v>10528.6</v>
+        <v>10361.5</v>
       </c>
       <c r="E31" t="n">
-        <v>10667.6</v>
+        <v>10379.1</v>
       </c>
       <c r="F31" t="n">
-        <v>67.09999999999999</v>
+        <v>-288.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0063</v>
+        <v>-0.027</v>
       </c>
       <c r="H31" t="n">
-        <v>139</v>
+        <v>322.2</v>
       </c>
       <c r="I31" t="n">
-        <v>9973.9</v>
+        <v>10389.6</v>
       </c>
       <c r="J31" t="n">
-        <v>10289.05</v>
+        <v>10563.35</v>
       </c>
       <c r="K31" t="n">
-        <v>10422</v>
+        <v>10598.1</v>
       </c>
       <c r="L31" t="n">
-        <v>10554.95</v>
+        <v>10632.85</v>
       </c>
       <c r="M31" t="n">
-        <v>10779</v>
+        <v>10737.1</v>
       </c>
       <c r="N31" t="n">
-        <v>11003.05</v>
+        <v>10841.35</v>
       </c>
       <c r="O31" t="n">
-        <v>11044.9</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
+        <v>10806.6</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3123,76 +3121,72 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10668.4</v>
+        <v>10378.5</v>
       </c>
       <c r="C32" t="n">
-        <v>10683.7</v>
+        <v>10410.8</v>
       </c>
       <c r="D32" t="n">
-        <v>10361.5</v>
+        <v>10188.7</v>
       </c>
       <c r="E32" t="n">
-        <v>10379.1</v>
+        <v>10363.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-288.5</v>
+        <v>-15.2</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.0015</v>
       </c>
       <c r="H32" t="n">
-        <v>322.2</v>
+        <v>222.1</v>
       </c>
       <c r="I32" t="n">
-        <v>10389.6</v>
+        <v>10039.3</v>
       </c>
       <c r="J32" t="n">
-        <v>10563.35</v>
+        <v>9985.15</v>
       </c>
       <c r="K32" t="n">
-        <v>10598.1</v>
+        <v>10218</v>
       </c>
       <c r="L32" t="n">
-        <v>10632.85</v>
+        <v>10450.85</v>
       </c>
       <c r="M32" t="n">
-        <v>10737.1</v>
+        <v>10540.2</v>
       </c>
       <c r="N32" t="n">
-        <v>10841.35</v>
+        <v>10629.55</v>
       </c>
       <c r="O32" t="n">
-        <v>10806.6</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
+        <v>11005.9</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3209,79 +3203,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10378.5</v>
+        <v>10365.4</v>
       </c>
       <c r="C33" t="n">
-        <v>10410.8</v>
+        <v>10488.2</v>
       </c>
       <c r="D33" t="n">
-        <v>10188.7</v>
+        <v>10164.3</v>
       </c>
       <c r="E33" t="n">
-        <v>10363.9</v>
+        <v>10233.1</v>
       </c>
       <c r="F33" t="n">
-        <v>-15.2</v>
+        <v>-130.8</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0126</v>
       </c>
       <c r="H33" t="n">
-        <v>222.1</v>
+        <v>323.9</v>
       </c>
       <c r="I33" t="n">
-        <v>10039.3</v>
+        <v>9966.6</v>
       </c>
       <c r="J33" t="n">
-        <v>9985.15</v>
+        <v>10173.88</v>
       </c>
       <c r="K33" t="n">
-        <v>10218</v>
+        <v>10252.85</v>
       </c>
       <c r="L33" t="n">
-        <v>10450.85</v>
+        <v>10331.83</v>
       </c>
       <c r="M33" t="n">
-        <v>10540.2</v>
+        <v>10474.95</v>
       </c>
       <c r="N33" t="n">
-        <v>10629.55</v>
+        <v>10618.08</v>
       </c>
       <c r="O33" t="n">
-        <v>11005.9</v>
+        <v>10632.9</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3293,78 +3287,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10365.4</v>
+        <v>10233.6</v>
       </c>
       <c r="C34" t="n">
-        <v>10488.2</v>
+        <v>10375.7</v>
       </c>
       <c r="D34" t="n">
-        <v>10164.3</v>
+        <v>10152.1</v>
       </c>
       <c r="E34" t="n">
-        <v>10233.1</v>
+        <v>10195.4</v>
       </c>
       <c r="F34" t="n">
-        <v>-130.8</v>
+        <v>-37.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0037</v>
       </c>
       <c r="H34" t="n">
-        <v>323.9</v>
+        <v>223.6</v>
       </c>
       <c r="I34" t="n">
-        <v>9966.6</v>
+        <v>9840.4</v>
       </c>
       <c r="J34" t="n">
-        <v>10173.88</v>
+        <v>9862.620000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>10252.85</v>
+        <v>10071.15</v>
       </c>
       <c r="L34" t="n">
-        <v>10331.83</v>
+        <v>10279.67</v>
       </c>
       <c r="M34" t="n">
-        <v>10474.95</v>
+        <v>10395.05</v>
       </c>
       <c r="N34" t="n">
-        <v>10618.08</v>
+        <v>10510.42</v>
       </c>
       <c r="O34" t="n">
-        <v>10632.9</v>
+        <v>10812.1</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3377,59 +3369,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10233.6</v>
+        <v>10194.8</v>
       </c>
       <c r="C35" t="n">
-        <v>10375.7</v>
+        <v>10497.2</v>
       </c>
       <c r="D35" t="n">
-        <v>10152.1</v>
+        <v>10151.5</v>
       </c>
       <c r="E35" t="n">
-        <v>10195.4</v>
+        <v>10466.3</v>
       </c>
       <c r="F35" t="n">
-        <v>-37.7</v>
+        <v>270.9</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0266</v>
       </c>
       <c r="H35" t="n">
-        <v>223.6</v>
+        <v>345.7</v>
       </c>
       <c r="I35" t="n">
-        <v>9840.4</v>
+        <v>9928.5</v>
       </c>
       <c r="J35" t="n">
-        <v>9862.620000000001</v>
+        <v>9937.549999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>10071.15</v>
+        <v>10083.6</v>
       </c>
       <c r="L35" t="n">
-        <v>10279.67</v>
+        <v>10229.65</v>
       </c>
       <c r="M35" t="n">
-        <v>10395.05</v>
+        <v>10307.2</v>
       </c>
       <c r="N35" t="n">
-        <v>10510.42</v>
+        <v>10384.75</v>
       </c>
       <c r="O35" t="n">
-        <v>10812.1</v>
+        <v>10599.3</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3440,74 +3428,82 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10194.8</v>
+        <v>10465.6</v>
       </c>
       <c r="C36" t="n">
-        <v>10497.2</v>
+        <v>10557.2</v>
       </c>
       <c r="D36" t="n">
-        <v>10151.5</v>
+        <v>10381.2</v>
       </c>
       <c r="E36" t="n">
-        <v>10466.3</v>
+        <v>10409.3</v>
       </c>
       <c r="F36" t="n">
-        <v>270.9</v>
+        <v>-57</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0266</v>
+        <v>-0.0054</v>
       </c>
       <c r="H36" t="n">
-        <v>345.7</v>
+        <v>176</v>
       </c>
       <c r="I36" t="n">
-        <v>9928.5</v>
+        <v>9805.799999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>9937.549999999999</v>
+        <v>10191.57</v>
       </c>
       <c r="K36" t="n">
-        <v>10083.6</v>
+        <v>10293.45</v>
       </c>
       <c r="L36" t="n">
-        <v>10229.65</v>
+        <v>10395.32</v>
       </c>
       <c r="M36" t="n">
-        <v>10307.2</v>
+        <v>10639.15</v>
       </c>
       <c r="N36" t="n">
-        <v>10384.75</v>
+        <v>10882.97</v>
       </c>
       <c r="O36" t="n">
-        <v>10599.3</v>
+        <v>10842.9</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3520,18 +3516,14 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3550,50 +3542,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10465.6</v>
+        <v>10409.3</v>
       </c>
       <c r="C37" t="n">
-        <v>10557.2</v>
+        <v>10415.7</v>
       </c>
       <c r="D37" t="n">
-        <v>10381.2</v>
+        <v>10238.6</v>
       </c>
       <c r="E37" t="n">
-        <v>10409.3</v>
+        <v>10368.1</v>
       </c>
       <c r="F37" t="n">
-        <v>-57</v>
+        <v>-41.2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.004</v>
       </c>
       <c r="H37" t="n">
-        <v>176</v>
+        <v>177.1</v>
       </c>
       <c r="I37" t="n">
-        <v>9805.799999999999</v>
+        <v>10205.2</v>
       </c>
       <c r="J37" t="n">
-        <v>10191.57</v>
+        <v>10203.35</v>
       </c>
       <c r="K37" t="n">
-        <v>10293.45</v>
+        <v>10321.3</v>
       </c>
       <c r="L37" t="n">
-        <v>10395.32</v>
+        <v>10439.25</v>
       </c>
       <c r="M37" t="n">
-        <v>10639.15</v>
+        <v>10497.3</v>
       </c>
       <c r="N37" t="n">
-        <v>10882.97</v>
+        <v>10555.35</v>
       </c>
       <c r="O37" t="n">
-        <v>10842.9</v>
+        <v>10733.2</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3601,12 +3593,14 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3625,77 +3619,81 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10409.3</v>
+        <v>10369.1</v>
       </c>
       <c r="C38" t="n">
-        <v>10415.7</v>
+        <v>10471.7</v>
       </c>
       <c r="D38" t="n">
-        <v>10238.6</v>
+        <v>10127.6</v>
       </c>
       <c r="E38" t="n">
-        <v>10368.1</v>
+        <v>10471.7</v>
       </c>
       <c r="F38" t="n">
-        <v>-41.2</v>
+        <v>103.6</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.01</v>
       </c>
       <c r="H38" t="n">
-        <v>177.1</v>
+        <v>344.1</v>
       </c>
       <c r="I38" t="n">
-        <v>10205.2</v>
+        <v>10061.5</v>
       </c>
       <c r="J38" t="n">
-        <v>10203.35</v>
+        <v>10211.47</v>
       </c>
       <c r="K38" t="n">
-        <v>10321.3</v>
+        <v>10279.55</v>
       </c>
       <c r="L38" t="n">
-        <v>10439.25</v>
+        <v>10347.62</v>
       </c>
       <c r="M38" t="n">
-        <v>10497.3</v>
+        <v>10456.65</v>
       </c>
       <c r="N38" t="n">
-        <v>10555.35</v>
+        <v>10565.68</v>
       </c>
       <c r="O38" t="n">
-        <v>10733.2</v>
+        <v>10592.8</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3709,80 +3707,74 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10369.1</v>
+        <v>10471.4</v>
       </c>
       <c r="C39" t="n">
-        <v>10471.7</v>
+        <v>10570.1</v>
       </c>
       <c r="D39" t="n">
-        <v>10127.6</v>
+        <v>10352.9</v>
       </c>
       <c r="E39" t="n">
-        <v>10471.7</v>
+        <v>10363.3</v>
       </c>
       <c r="F39" t="n">
-        <v>103.6</v>
+        <v>-108.4</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0104</v>
       </c>
       <c r="H39" t="n">
-        <v>344.1</v>
+        <v>217.2</v>
       </c>
       <c r="I39" t="n">
-        <v>10061.5</v>
+        <v>9783.5</v>
       </c>
       <c r="J39" t="n">
-        <v>10211.47</v>
+        <v>10213.62</v>
       </c>
       <c r="K39" t="n">
-        <v>10279.55</v>
+        <v>10299.65</v>
       </c>
       <c r="L39" t="n">
-        <v>10347.62</v>
+        <v>10385.68</v>
       </c>
       <c r="M39" t="n">
-        <v>10456.65</v>
+        <v>10643.75</v>
       </c>
       <c r="N39" t="n">
-        <v>10565.68</v>
+        <v>10901.83</v>
       </c>
       <c r="O39" t="n">
-        <v>10592.8</v>
+        <v>10815.8</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3804,50 +3796,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10471.4</v>
+        <v>10363.6</v>
       </c>
       <c r="C40" t="n">
-        <v>10570.1</v>
+        <v>10575.3</v>
       </c>
       <c r="D40" t="n">
-        <v>10352.9</v>
+        <v>10332.4</v>
       </c>
       <c r="E40" t="n">
-        <v>10363.3</v>
+        <v>10508</v>
       </c>
       <c r="F40" t="n">
-        <v>-108.4</v>
+        <v>144.7</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.014</v>
       </c>
       <c r="H40" t="n">
-        <v>217.2</v>
+        <v>242.9</v>
       </c>
       <c r="I40" t="n">
-        <v>9783.5</v>
+        <v>10135.7</v>
       </c>
       <c r="J40" t="n">
-        <v>10213.62</v>
+        <v>10097</v>
       </c>
       <c r="K40" t="n">
-        <v>10299.65</v>
+        <v>10254.7</v>
       </c>
       <c r="L40" t="n">
-        <v>10385.68</v>
+        <v>10412.4</v>
       </c>
       <c r="M40" t="n">
-        <v>10643.75</v>
+        <v>10471.9</v>
       </c>
       <c r="N40" t="n">
-        <v>10901.83</v>
+        <v>10531.4</v>
       </c>
       <c r="O40" t="n">
-        <v>10815.8</v>
+        <v>10787.3</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3858,16 +3850,20 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3886,50 +3882,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10363.6</v>
+        <v>10507.8</v>
       </c>
       <c r="C41" t="n">
-        <v>10575.3</v>
+        <v>10701.3</v>
       </c>
       <c r="D41" t="n">
-        <v>10332.4</v>
+        <v>10429.2</v>
       </c>
       <c r="E41" t="n">
-        <v>10508</v>
+        <v>10679</v>
       </c>
       <c r="F41" t="n">
-        <v>144.7</v>
+        <v>171</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0163</v>
       </c>
       <c r="H41" t="n">
-        <v>242.9</v>
+        <v>272.1</v>
       </c>
       <c r="I41" t="n">
-        <v>10135.7</v>
+        <v>10089.5</v>
       </c>
       <c r="J41" t="n">
-        <v>10097</v>
+        <v>10292.18</v>
       </c>
       <c r="K41" t="n">
-        <v>10254.7</v>
+        <v>10386.55</v>
       </c>
       <c r="L41" t="n">
-        <v>10412.4</v>
+        <v>10480.93</v>
       </c>
       <c r="M41" t="n">
-        <v>10471.9</v>
+        <v>10629.45</v>
       </c>
       <c r="N41" t="n">
-        <v>10531.4</v>
+        <v>10777.97</v>
       </c>
       <c r="O41" t="n">
-        <v>10787.3</v>
+        <v>10818.2</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3947,14 +3943,12 @@
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
@@ -3963,79 +3957,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10507.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C42" t="n">
-        <v>10701.3</v>
+        <v>10747</v>
       </c>
       <c r="D42" t="n">
-        <v>10429.2</v>
+        <v>10397.5</v>
       </c>
       <c r="E42" t="n">
-        <v>10679</v>
+        <v>10497.3</v>
       </c>
       <c r="F42" t="n">
-        <v>171</v>
+        <v>-181.7</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.017</v>
       </c>
       <c r="H42" t="n">
-        <v>272.1</v>
+        <v>349.5</v>
       </c>
       <c r="I42" t="n">
-        <v>10089.5</v>
+        <v>10157.1</v>
       </c>
       <c r="J42" t="n">
-        <v>10292.18</v>
+        <v>10463.78</v>
       </c>
       <c r="K42" t="n">
-        <v>10386.55</v>
+        <v>10542.95</v>
       </c>
       <c r="L42" t="n">
-        <v>10480.93</v>
+        <v>10622.12</v>
       </c>
       <c r="M42" t="n">
-        <v>10629.45</v>
+        <v>10815.05</v>
       </c>
       <c r="N42" t="n">
-        <v>10777.97</v>
+        <v>11007.97</v>
       </c>
       <c r="O42" t="n">
-        <v>10818.2</v>
+        <v>10973.4</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+      <c r="Q42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4047,72 +4039,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10679.4</v>
+        <v>10498.1</v>
       </c>
       <c r="C43" t="n">
-        <v>10747</v>
+        <v>10623.7</v>
       </c>
       <c r="D43" t="n">
-        <v>10397.5</v>
+        <v>10423</v>
       </c>
       <c r="E43" t="n">
-        <v>10497.3</v>
+        <v>10600.4</v>
       </c>
       <c r="F43" t="n">
-        <v>-181.7</v>
+        <v>103.1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.017</v>
+        <v>0.0098</v>
       </c>
       <c r="H43" t="n">
-        <v>349.5</v>
+        <v>200.7</v>
       </c>
       <c r="I43" t="n">
-        <v>10157.1</v>
+        <v>10048</v>
       </c>
       <c r="J43" t="n">
-        <v>10463.78</v>
+        <v>10110.32</v>
       </c>
       <c r="K43" t="n">
-        <v>10542.95</v>
+        <v>10322.55</v>
       </c>
       <c r="L43" t="n">
-        <v>10622.12</v>
+        <v>10534.77</v>
       </c>
       <c r="M43" t="n">
-        <v>10815.05</v>
+        <v>10672.05</v>
       </c>
       <c r="N43" t="n">
-        <v>11007.97</v>
+        <v>10809.32</v>
       </c>
       <c r="O43" t="n">
-        <v>10973.4</v>
+        <v>11096.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4131,57 +4123,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10498.1</v>
+        <v>10600.3</v>
       </c>
       <c r="C44" t="n">
-        <v>10623.7</v>
+        <v>10763.4</v>
       </c>
       <c r="D44" t="n">
-        <v>10423</v>
+        <v>10483.1</v>
       </c>
       <c r="E44" t="n">
-        <v>10600.4</v>
+        <v>10736.2</v>
       </c>
       <c r="F44" t="n">
-        <v>103.1</v>
+        <v>135.8</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0128</v>
       </c>
       <c r="H44" t="n">
-        <v>200.7</v>
+        <v>280.3</v>
       </c>
       <c r="I44" t="n">
-        <v>10048</v>
+        <v>10222.3</v>
       </c>
       <c r="J44" t="n">
-        <v>10110.32</v>
+        <v>10438.23</v>
       </c>
       <c r="K44" t="n">
-        <v>10322.55</v>
+        <v>10500.05</v>
       </c>
       <c r="L44" t="n">
-        <v>10534.77</v>
+        <v>10561.88</v>
       </c>
       <c r="M44" t="n">
-        <v>10672.05</v>
+        <v>10700.75</v>
       </c>
       <c r="N44" t="n">
-        <v>10809.32</v>
+        <v>10839.63</v>
       </c>
       <c r="O44" t="n">
-        <v>11096.5</v>
+        <v>10824.4</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4189,16 +4181,20 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4211,59 +4207,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10600.3</v>
+        <v>10736.1</v>
       </c>
       <c r="C45" t="n">
-        <v>10763.4</v>
+        <v>10989.5</v>
       </c>
       <c r="D45" t="n">
-        <v>10483.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E45" t="n">
-        <v>10736.2</v>
+        <v>10868.1</v>
       </c>
       <c r="F45" t="n">
-        <v>135.8</v>
+        <v>131.9</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0123</v>
       </c>
       <c r="H45" t="n">
-        <v>280.3</v>
+        <v>253.4</v>
       </c>
       <c r="I45" t="n">
-        <v>10222.3</v>
+        <v>10202.8</v>
       </c>
       <c r="J45" t="n">
-        <v>10438.23</v>
+        <v>10512.37</v>
       </c>
       <c r="K45" t="n">
-        <v>10500.05</v>
+        <v>10596.05</v>
       </c>
       <c r="L45" t="n">
-        <v>10561.88</v>
+        <v>10679.73</v>
       </c>
       <c r="M45" t="n">
-        <v>10700.75</v>
+        <v>10876.35</v>
       </c>
       <c r="N45" t="n">
-        <v>10839.63</v>
+        <v>11072.98</v>
       </c>
       <c r="O45" t="n">
-        <v>10824.4</v>
+        <v>11043.7</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4271,10 +4263,8 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
@@ -4302,50 +4292,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10736.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C46" t="n">
-        <v>10989.5</v>
+        <v>10959.9</v>
       </c>
       <c r="D46" t="n">
-        <v>10736.1</v>
+        <v>10832.5</v>
       </c>
       <c r="E46" t="n">
-        <v>10868.1</v>
+        <v>10901.1</v>
       </c>
       <c r="F46" t="n">
-        <v>131.9</v>
+        <v>33</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0123</v>
+        <v>0.003</v>
       </c>
       <c r="H46" t="n">
-        <v>253.4</v>
+        <v>127.4</v>
       </c>
       <c r="I46" t="n">
-        <v>10202.8</v>
+        <v>10482.7</v>
       </c>
       <c r="J46" t="n">
-        <v>10512.37</v>
+        <v>10617.35</v>
       </c>
       <c r="K46" t="n">
-        <v>10596.05</v>
+        <v>10741.4</v>
       </c>
       <c r="L46" t="n">
-        <v>10679.73</v>
+        <v>10865.45</v>
       </c>
       <c r="M46" t="n">
-        <v>10876.35</v>
+        <v>10994.8</v>
       </c>
       <c r="N46" t="n">
-        <v>11072.98</v>
+        <v>11124.15</v>
       </c>
       <c r="O46" t="n">
-        <v>11043.7</v>
+        <v>11242.9</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4358,13 +4348,11 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4377,68 +4365,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10868.1</v>
+        <v>10901.1</v>
       </c>
       <c r="C47" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D47" t="n">
-        <v>10832.5</v>
+        <v>10723.7</v>
       </c>
       <c r="E47" t="n">
-        <v>10901.1</v>
+        <v>10750.1</v>
       </c>
       <c r="F47" t="n">
-        <v>33</v>
+        <v>-151</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0139</v>
       </c>
       <c r="H47" t="n">
-        <v>127.4</v>
+        <v>187.2</v>
       </c>
       <c r="I47" t="n">
-        <v>10482.7</v>
+        <v>10705.1</v>
       </c>
       <c r="J47" t="n">
-        <v>10617.35</v>
+        <v>10776.15</v>
       </c>
       <c r="K47" t="n">
-        <v>10741.4</v>
+        <v>10837.4</v>
       </c>
       <c r="L47" t="n">
-        <v>10865.45</v>
+        <v>10898.65</v>
       </c>
       <c r="M47" t="n">
-        <v>10994.8</v>
+        <v>10964.8</v>
       </c>
       <c r="N47" t="n">
-        <v>11124.15</v>
+        <v>11030.95</v>
       </c>
       <c r="O47" t="n">
-        <v>11242.9</v>
+        <v>11087.3</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4450,86 +4446,80 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W47" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10901.1</v>
+        <v>10750</v>
       </c>
       <c r="C48" t="n">
-        <v>10910.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D48" t="n">
-        <v>10723.7</v>
+        <v>10684.4</v>
       </c>
       <c r="E48" t="n">
-        <v>10750.1</v>
+        <v>10816.6</v>
       </c>
       <c r="F48" t="n">
-        <v>-151</v>
+        <v>66.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0139</v>
+        <v>0.0062</v>
       </c>
       <c r="H48" t="n">
-        <v>187.2</v>
+        <v>147.2</v>
       </c>
       <c r="I48" t="n">
-        <v>10705.1</v>
+        <v>10536.5</v>
       </c>
       <c r="J48" t="n">
-        <v>10776.15</v>
+        <v>10529.3</v>
       </c>
       <c r="K48" t="n">
-        <v>10837.4</v>
+        <v>10656.5</v>
       </c>
       <c r="L48" t="n">
-        <v>10898.65</v>
+        <v>10783.7</v>
       </c>
       <c r="M48" t="n">
-        <v>10964.8</v>
+        <v>10843.7</v>
       </c>
       <c r="N48" t="n">
-        <v>11030.95</v>
+        <v>10903.7</v>
       </c>
       <c r="O48" t="n">
-        <v>11087.3</v>
+        <v>11098.1</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4541,55 +4531,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10750</v>
+        <v>10816.3</v>
       </c>
       <c r="C49" t="n">
-        <v>10831.6</v>
+        <v>10920.5</v>
       </c>
       <c r="D49" t="n">
-        <v>10684.4</v>
+        <v>10772.6</v>
       </c>
       <c r="E49" t="n">
-        <v>10816.6</v>
+        <v>10824.3</v>
       </c>
       <c r="F49" t="n">
-        <v>66.5</v>
+        <v>7.7</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0007</v>
       </c>
       <c r="H49" t="n">
-        <v>147.2</v>
+        <v>147.9</v>
       </c>
       <c r="I49" t="n">
-        <v>10536.5</v>
+        <v>10537.2</v>
       </c>
       <c r="J49" t="n">
-        <v>10529.3</v>
+        <v>10698.7</v>
       </c>
       <c r="K49" t="n">
-        <v>10656.5</v>
+        <v>10743</v>
       </c>
       <c r="L49" t="n">
-        <v>10783.7</v>
+        <v>10787.3</v>
       </c>
       <c r="M49" t="n">
-        <v>10843.7</v>
+        <v>10890.2</v>
       </c>
       <c r="N49" t="n">
-        <v>10903.7</v>
+        <v>10993.1</v>
       </c>
       <c r="O49" t="n">
-        <v>11098.1</v>
+        <v>10978.8</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4602,12 +4596,12 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U49" s="8" t="n">
@@ -4623,57 +4617,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10816.3</v>
+        <v>10824.6</v>
       </c>
       <c r="C50" t="n">
-        <v>10920.5</v>
+        <v>10866.8</v>
       </c>
       <c r="D50" t="n">
-        <v>10772.6</v>
+        <v>10689.6</v>
       </c>
       <c r="E50" t="n">
-        <v>10824.3</v>
+        <v>10831.1</v>
       </c>
       <c r="F50" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>147.9</v>
+        <v>177.2</v>
       </c>
       <c r="I50" t="n">
-        <v>10537.2</v>
+        <v>10624.7</v>
       </c>
       <c r="J50" t="n">
-        <v>10698.7</v>
+        <v>10665.27</v>
       </c>
       <c r="K50" t="n">
-        <v>10743</v>
+        <v>10750.35</v>
       </c>
       <c r="L50" t="n">
-        <v>10787.3</v>
+        <v>10835.42</v>
       </c>
       <c r="M50" t="n">
-        <v>10890.2</v>
+        <v>10898.25</v>
       </c>
       <c r="N50" t="n">
-        <v>10993.1</v>
+        <v>10961.08</v>
       </c>
       <c r="O50" t="n">
-        <v>10978.8</v>
+        <v>11068.4</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4681,19 +4675,19 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
@@ -4707,63 +4701,65 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10824.6</v>
+        <v>10831</v>
       </c>
       <c r="C51" t="n">
-        <v>10866.8</v>
+        <v>10868.3</v>
       </c>
       <c r="D51" t="n">
-        <v>10689.6</v>
+        <v>10594.3</v>
       </c>
       <c r="E51" t="n">
-        <v>10831.1</v>
+        <v>10650.4</v>
       </c>
       <c r="F51" t="n">
-        <v>6.8</v>
+        <v>-180.7</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0167</v>
       </c>
       <c r="H51" t="n">
-        <v>177.2</v>
+        <v>274</v>
       </c>
       <c r="I51" t="n">
-        <v>10624.7</v>
+        <v>10512.4</v>
       </c>
       <c r="J51" t="n">
-        <v>10665.27</v>
+        <v>10680.35</v>
       </c>
       <c r="K51" t="n">
-        <v>10750.35</v>
+        <v>10742.5</v>
       </c>
       <c r="L51" t="n">
-        <v>10835.42</v>
+        <v>10804.65</v>
       </c>
       <c r="M51" t="n">
-        <v>10898.25</v>
+        <v>10919.7</v>
       </c>
       <c r="N51" t="n">
-        <v>10961.08</v>
+        <v>11034.75</v>
       </c>
       <c r="O51" t="n">
-        <v>11068.4</v>
+        <v>11044</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
@@ -4772,7 +4768,7 @@
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4798,71 +4794,69 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10831</v>
+        <v>10650.9</v>
       </c>
       <c r="C52" t="n">
-        <v>10868.3</v>
+        <v>10823</v>
       </c>
       <c r="D52" t="n">
-        <v>10594.3</v>
+        <v>10586.4</v>
       </c>
       <c r="E52" t="n">
-        <v>10650.4</v>
+        <v>10659.1</v>
       </c>
       <c r="F52" t="n">
-        <v>-180.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0167</v>
+        <v>0.0008</v>
       </c>
       <c r="H52" t="n">
-        <v>274</v>
+        <v>236.6</v>
       </c>
       <c r="I52" t="n">
-        <v>10512.4</v>
+        <v>10320.3</v>
       </c>
       <c r="J52" t="n">
-        <v>10680.35</v>
+        <v>10335.95</v>
       </c>
       <c r="K52" t="n">
-        <v>10742.5</v>
+        <v>10513.4</v>
       </c>
       <c r="L52" t="n">
-        <v>10804.65</v>
+        <v>10690.85</v>
       </c>
       <c r="M52" t="n">
-        <v>10919.7</v>
+        <v>10787.4</v>
       </c>
       <c r="N52" t="n">
-        <v>11034.75</v>
+        <v>10883.95</v>
       </c>
       <c r="O52" t="n">
-        <v>11044</v>
+        <v>11142.3</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4884,50 +4878,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10650.9</v>
+        <v>10659.1</v>
       </c>
       <c r="C53" t="n">
-        <v>10823</v>
+        <v>10774.7</v>
       </c>
       <c r="D53" t="n">
-        <v>10586.4</v>
+        <v>10656.7</v>
       </c>
       <c r="E53" t="n">
-        <v>10659.1</v>
+        <v>10695.3</v>
       </c>
       <c r="F53" t="n">
-        <v>8.699999999999999</v>
+        <v>36.2</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0034</v>
       </c>
       <c r="H53" t="n">
-        <v>236.6</v>
+        <v>118</v>
       </c>
       <c r="I53" t="n">
-        <v>10320.3</v>
+        <v>10349.8</v>
       </c>
       <c r="J53" t="n">
-        <v>10335.95</v>
+        <v>10399.7</v>
       </c>
       <c r="K53" t="n">
-        <v>10513.4</v>
+        <v>10540.8</v>
       </c>
       <c r="L53" t="n">
-        <v>10690.85</v>
+        <v>10681.9</v>
       </c>
       <c r="M53" t="n">
-        <v>10787.4</v>
+        <v>10777.4</v>
       </c>
       <c r="N53" t="n">
-        <v>10883.95</v>
+        <v>10872.9</v>
       </c>
       <c r="O53" t="n">
-        <v>11142.3</v>
+        <v>11059.6</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4938,15 +4932,13 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4961,74 +4953,82 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10659.1</v>
+        <v>10695.2</v>
       </c>
       <c r="C54" t="n">
-        <v>10774.7</v>
+        <v>10758.7</v>
       </c>
       <c r="D54" t="n">
-        <v>10656.7</v>
+        <v>10390.7</v>
       </c>
       <c r="E54" t="n">
-        <v>10695.3</v>
+        <v>10462</v>
       </c>
       <c r="F54" t="n">
-        <v>36.2</v>
+        <v>-233.3</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.0218</v>
       </c>
       <c r="H54" t="n">
-        <v>118</v>
+        <v>368</v>
       </c>
       <c r="I54" t="n">
-        <v>10349.8</v>
+        <v>10538.7</v>
       </c>
       <c r="J54" t="n">
-        <v>10399.7</v>
+        <v>10567.1</v>
       </c>
       <c r="K54" t="n">
-        <v>10540.8</v>
+        <v>10636.3</v>
       </c>
       <c r="L54" t="n">
-        <v>10681.9</v>
+        <v>10705.5</v>
       </c>
       <c r="M54" t="n">
-        <v>10777.4</v>
+        <v>10754.3</v>
       </c>
       <c r="N54" t="n">
-        <v>10872.9</v>
+        <v>10803.1</v>
       </c>
       <c r="O54" t="n">
-        <v>11059.6</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+        <v>10892.7</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5041,84 +5041,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10695.2</v>
+        <v>10462.4</v>
       </c>
       <c r="C55" t="n">
-        <v>10758.7</v>
+        <v>10602.6</v>
       </c>
       <c r="D55" t="n">
-        <v>10390.7</v>
+        <v>10367.3</v>
       </c>
       <c r="E55" t="n">
-        <v>10462</v>
+        <v>10552.1</v>
       </c>
       <c r="F55" t="n">
-        <v>-233.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0218</v>
+        <v>0.0086</v>
       </c>
       <c r="H55" t="n">
-        <v>368</v>
+        <v>235.3</v>
       </c>
       <c r="I55" t="n">
-        <v>10538.7</v>
+        <v>10022.7</v>
       </c>
       <c r="J55" t="n">
-        <v>10567.1</v>
+        <v>10037.65</v>
       </c>
       <c r="K55" t="n">
-        <v>10636.3</v>
+        <v>10278</v>
       </c>
       <c r="L55" t="n">
-        <v>10705.5</v>
+        <v>10518.35</v>
       </c>
       <c r="M55" t="n">
-        <v>10754.3</v>
+        <v>10646</v>
       </c>
       <c r="N55" t="n">
-        <v>10803.1</v>
+        <v>10773.65</v>
       </c>
       <c r="O55" t="n">
-        <v>10892.7</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>11126.7</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5131,55 +5119,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10462.4</v>
+        <v>10551.6</v>
       </c>
       <c r="C56" t="n">
-        <v>10602.6</v>
+        <v>10892.4</v>
       </c>
       <c r="D56" t="n">
-        <v>10367.3</v>
+        <v>10549.6</v>
       </c>
       <c r="E56" t="n">
-        <v>10552.1</v>
+        <v>10881.9</v>
       </c>
       <c r="F56" t="n">
-        <v>90.09999999999999</v>
+        <v>329.8</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0313</v>
       </c>
       <c r="H56" t="n">
-        <v>235.3</v>
+        <v>342.8</v>
       </c>
       <c r="I56" t="n">
-        <v>10022.7</v>
+        <v>10132</v>
       </c>
       <c r="J56" t="n">
-        <v>10037.65</v>
+        <v>10350.37</v>
       </c>
       <c r="K56" t="n">
-        <v>10278</v>
+        <v>10434.45</v>
       </c>
       <c r="L56" t="n">
-        <v>10518.35</v>
+        <v>10518.52</v>
       </c>
       <c r="M56" t="n">
-        <v>10646</v>
+        <v>10669.75</v>
       </c>
       <c r="N56" t="n">
-        <v>10773.65</v>
+        <v>10820.97</v>
       </c>
       <c r="O56" t="n">
-        <v>11126.7</v>
+        <v>10837.9</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5192,76 +5184,78 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10551.6</v>
+        <v>10882.3</v>
       </c>
       <c r="C57" t="n">
-        <v>10892.4</v>
+        <v>10889.9</v>
       </c>
       <c r="D57" t="n">
-        <v>10549.6</v>
+        <v>10630</v>
       </c>
       <c r="E57" t="n">
-        <v>10881.9</v>
+        <v>10690.36</v>
       </c>
       <c r="F57" t="n">
-        <v>329.8</v>
+        <v>-191.54</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0313</v>
+        <v>-0.0176</v>
       </c>
       <c r="H57" t="n">
-        <v>342.8</v>
+        <v>259.9</v>
       </c>
       <c r="I57" t="n">
-        <v>10132</v>
+        <v>10206.8</v>
       </c>
       <c r="J57" t="n">
-        <v>10350.37</v>
+        <v>10619.55</v>
       </c>
       <c r="K57" t="n">
-        <v>10434.45</v>
+        <v>10710.5</v>
       </c>
       <c r="L57" t="n">
-        <v>10518.52</v>
+        <v>10801.45</v>
       </c>
       <c r="M57" t="n">
-        <v>10669.75</v>
+        <v>11053.3</v>
       </c>
       <c r="N57" t="n">
-        <v>10820.97</v>
+        <v>11305.15</v>
       </c>
       <c r="O57" t="n">
-        <v>10837.9</v>
+        <v>11235.2</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5269,115 +5263,31 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>10882.3</v>
-      </c>
-      <c r="C58" t="n">
-        <v>10889.9</v>
-      </c>
-      <c r="D58" t="n">
-        <v>10669.39</v>
-      </c>
-      <c r="E58" t="n">
-        <v>10725.03</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-156.87</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0144</v>
-      </c>
-      <c r="H58" t="n">
-        <v>220.51</v>
-      </c>
-      <c r="I58" t="n">
-        <v>10206.8</v>
-      </c>
-      <c r="J58" t="n">
-        <v>10619.55</v>
-      </c>
-      <c r="K58" t="n">
-        <v>10710.5</v>
-      </c>
-      <c r="L58" t="n">
-        <v>10801.45</v>
-      </c>
-      <c r="M58" t="n">
-        <v>11053.3</v>
-      </c>
-      <c r="N58" t="n">
-        <v>11305.15</v>
-      </c>
-      <c r="O58" t="n">
-        <v>11235.2</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -5225,10 +5225,10 @@
         <v>10630</v>
       </c>
       <c r="E57" t="n">
-        <v>10690.36</v>
+        <v>10690.4</v>
       </c>
       <c r="F57" t="n">
-        <v>-191.54</v>
+        <v>-191.5</v>
       </c>
       <c r="G57" s="5" t="n">
         <v>-0.0176</v>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5293,6 +5293,88 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10690.9</v>
+      </c>
+      <c r="C58" t="n">
+        <v>10774.5</v>
+      </c>
+      <c r="D58" t="n">
+        <v>10689.9</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10767.3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="H58" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10370.1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>10395.73</v>
+      </c>
+      <c r="K58" t="n">
+        <v>10560.45</v>
+      </c>
+      <c r="L58" t="n">
+        <v>10725.18</v>
+      </c>
+      <c r="M58" t="n">
+        <v>10820.35</v>
+      </c>
+      <c r="N58" t="n">
+        <v>10915.53</v>
+      </c>
+      <c r="O58" t="n">
+        <v>11149.8</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -5306,19 +5306,19 @@
         <v>10774.5</v>
       </c>
       <c r="D58" t="n">
-        <v>10689.9</v>
+        <v>10649.65</v>
       </c>
       <c r="E58" t="n">
-        <v>10767.3</v>
+        <v>10686.54</v>
       </c>
       <c r="F58" t="n">
-        <v>76.90000000000001</v>
+        <v>-3.86</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0004</v>
       </c>
       <c r="H58" t="n">
-        <v>84.59999999999999</v>
+        <v>124.85</v>
       </c>
       <c r="I58" t="n">
         <v>10370.1</v>
@@ -5350,9 +5350,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>228.3</v>
       </c>
       <c r="I2" t="n">
-        <v>9062.1</v>
+        <v>9114.299999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>9194.9</v>
+        <v>9214.48</v>
       </c>
       <c r="K2" t="n">
-        <v>9227.299999999999</v>
+        <v>9240.35</v>
       </c>
       <c r="L2" t="n">
-        <v>9259.700000000001</v>
+        <v>9266.219999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>9342.299999999999</v>
+        <v>9329.25</v>
       </c>
       <c r="N2" t="n">
-        <v>9424.9</v>
+        <v>9392.27</v>
       </c>
       <c r="O2" t="n">
-        <v>9407.1</v>
+        <v>9381</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5306,19 +5306,19 @@
         <v>10774.5</v>
       </c>
       <c r="D58" t="n">
-        <v>10649.65</v>
+        <v>10643.25</v>
       </c>
       <c r="E58" t="n">
-        <v>10686.54</v>
+        <v>10694.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-3.86</v>
+        <v>4.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0004</v>
       </c>
       <c r="H58" t="n">
-        <v>124.85</v>
+        <v>131.25</v>
       </c>
       <c r="I58" t="n">
         <v>10370.1</v>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>228.3</v>
       </c>
       <c r="I2" t="n">
-        <v>9114.299999999999</v>
+        <v>9124.9</v>
       </c>
       <c r="J2" t="n">
-        <v>9214.48</v>
+        <v>9218.450000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>9240.35</v>
+        <v>9243</v>
       </c>
       <c r="L2" t="n">
-        <v>9266.219999999999</v>
+        <v>9267.549999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>9329.25</v>
+        <v>9326.6</v>
       </c>
       <c r="N2" t="n">
-        <v>9392.27</v>
+        <v>9385.65</v>
       </c>
       <c r="O2" t="n">
-        <v>9381</v>
+        <v>9375.700000000001</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5306,19 +5306,19 @@
         <v>10774.5</v>
       </c>
       <c r="D58" t="n">
-        <v>10643.25</v>
+        <v>10643.3</v>
       </c>
       <c r="E58" t="n">
-        <v>10694.5</v>
+        <v>10722.07</v>
       </c>
       <c r="F58" t="n">
-        <v>4.1</v>
+        <v>31.67</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.003</v>
       </c>
       <c r="H58" t="n">
-        <v>131.25</v>
+        <v>131.2</v>
       </c>
       <c r="I58" t="n">
         <v>10370.1</v>

--- a/three_gate/analysis/FTSE_weekly.xlsx
+++ b/three_gate/analysis/FTSE_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9284.799999999999</v>
+        <v>9491.200000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>9494.6</v>
+        <v>9577.1</v>
       </c>
       <c r="D2" t="n">
-        <v>9266.299999999999</v>
+        <v>9414.6</v>
       </c>
       <c r="E2" t="n">
-        <v>9491.299999999999</v>
+        <v>9427.5</v>
       </c>
       <c r="F2" t="n">
-        <v>206.5</v>
+        <v>-63.8</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0067</v>
       </c>
       <c r="H2" t="n">
-        <v>228.3</v>
+        <v>162.5</v>
       </c>
       <c r="I2" t="n">
-        <v>9124.9</v>
+        <v>9038</v>
       </c>
       <c r="J2" t="n">
-        <v>9218.450000000001</v>
+        <v>9318.43</v>
       </c>
       <c r="K2" t="n">
-        <v>9243</v>
+        <v>9377.15</v>
       </c>
       <c r="L2" t="n">
-        <v>9267.549999999999</v>
+        <v>9435.870000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>9326.6</v>
+        <v>9605.450000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>9385.65</v>
+        <v>9775.02</v>
       </c>
       <c r="O2" t="n">
-        <v>9375.700000000001</v>
+        <v>9722.9</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,78 +690,76 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9491.200000000001</v>
+        <v>9427.5</v>
       </c>
       <c r="C3" t="n">
-        <v>9577.1</v>
+        <v>9474.299999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>9414.6</v>
+        <v>9276.9</v>
       </c>
       <c r="E3" t="n">
-        <v>9427.5</v>
+        <v>9354.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-63.8</v>
+        <v>-72.90000000000001</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0067</v>
+        <v>-0.0077</v>
       </c>
       <c r="H3" t="n">
-        <v>162.5</v>
+        <v>197.4</v>
       </c>
       <c r="I3" t="n">
-        <v>9038</v>
+        <v>9252.1</v>
       </c>
       <c r="J3" t="n">
-        <v>9318.43</v>
+        <v>9230.83</v>
       </c>
       <c r="K3" t="n">
-        <v>9377.15</v>
+        <v>9346.25</v>
       </c>
       <c r="L3" t="n">
-        <v>9435.870000000001</v>
+        <v>9461.67</v>
       </c>
       <c r="M3" t="n">
-        <v>9605.450000000001</v>
+        <v>9508.75</v>
       </c>
       <c r="N3" t="n">
-        <v>9775.02</v>
+        <v>9555.83</v>
       </c>
       <c r="O3" t="n">
-        <v>9722.9</v>
+        <v>9739.6</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,12 +767,14 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -793,57 +793,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9427.5</v>
+        <v>9354.5</v>
       </c>
       <c r="C4" t="n">
-        <v>9474.299999999999</v>
+        <v>9645.6</v>
       </c>
       <c r="D4" t="n">
-        <v>9276.9</v>
+        <v>9354.5</v>
       </c>
       <c r="E4" t="n">
-        <v>9354.6</v>
+        <v>9645.6</v>
       </c>
       <c r="F4" t="n">
-        <v>-72.90000000000001</v>
+        <v>291</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0311</v>
       </c>
       <c r="H4" t="n">
-        <v>197.4</v>
+        <v>291.1</v>
       </c>
       <c r="I4" t="n">
-        <v>9252.1</v>
+        <v>9079.5</v>
       </c>
       <c r="J4" t="n">
-        <v>9230.83</v>
+        <v>9146.700000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>9346.25</v>
+        <v>9255.9</v>
       </c>
       <c r="L4" t="n">
-        <v>9461.67</v>
+        <v>9365.1</v>
       </c>
       <c r="M4" t="n">
-        <v>9508.75</v>
+        <v>9453.299999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>9555.83</v>
+        <v>9541.5</v>
       </c>
       <c r="O4" t="n">
-        <v>9739.6</v>
+        <v>9671.700000000001</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,83 +851,83 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
-      </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9354.5</v>
+        <v>9645.6</v>
       </c>
       <c r="C5" t="n">
-        <v>9645.6</v>
+        <v>9787.6</v>
       </c>
       <c r="D5" t="n">
-        <v>9354.5</v>
+        <v>9632.799999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>9645.6</v>
+        <v>9717.299999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>291</v>
+        <v>71.7</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0311</v>
+        <v>0.0074</v>
       </c>
       <c r="H5" t="n">
-        <v>291.1</v>
+        <v>154.8</v>
       </c>
       <c r="I5" t="n">
-        <v>9079.5</v>
+        <v>9063.4</v>
       </c>
       <c r="J5" t="n">
-        <v>9146.700000000001</v>
+        <v>9427.27</v>
       </c>
       <c r="K5" t="n">
-        <v>9255.9</v>
+        <v>9500.049999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>9365.1</v>
+        <v>9572.82</v>
       </c>
       <c r="M5" t="n">
-        <v>9453.299999999999</v>
+        <v>9791.15</v>
       </c>
       <c r="N5" t="n">
-        <v>9541.5</v>
+        <v>10009.47</v>
       </c>
       <c r="O5" t="n">
-        <v>9671.700000000001</v>
+        <v>9936.700000000001</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -938,25 +938,21 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -968,50 +964,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9645.6</v>
+        <v>9717.299999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>9787.6</v>
+        <v>9786.799999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>9632.799999999999</v>
+        <v>9574.200000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>9717.299999999999</v>
+        <v>9682.6</v>
       </c>
       <c r="F6" t="n">
-        <v>71.7</v>
+        <v>-34.7</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0036</v>
       </c>
       <c r="H6" t="n">
-        <v>154.8</v>
+        <v>212.6</v>
       </c>
       <c r="I6" t="n">
-        <v>9063.4</v>
+        <v>9478</v>
       </c>
       <c r="J6" t="n">
-        <v>9427.27</v>
+        <v>9566.049999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>9500.049999999999</v>
+        <v>9639.9</v>
       </c>
       <c r="L6" t="n">
-        <v>9572.82</v>
+        <v>9713.75</v>
       </c>
       <c r="M6" t="n">
-        <v>9791.15</v>
+        <v>9794.700000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>10009.47</v>
+        <v>9875.65</v>
       </c>
       <c r="O6" t="n">
-        <v>9936.700000000001</v>
+        <v>9942.4</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1019,18 +1015,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1043,55 +1039,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9717.299999999999</v>
+        <v>9682.6</v>
       </c>
       <c r="C7" t="n">
-        <v>9786.799999999999</v>
+        <v>9930.1</v>
       </c>
       <c r="D7" t="n">
-        <v>9574.200000000001</v>
+        <v>9610.5</v>
       </c>
       <c r="E7" t="n">
-        <v>9682.6</v>
+        <v>9698.4</v>
       </c>
       <c r="F7" t="n">
-        <v>-34.7</v>
+        <v>15.8</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0016</v>
       </c>
       <c r="H7" t="n">
-        <v>212.6</v>
+        <v>319.6</v>
       </c>
       <c r="I7" t="n">
-        <v>9478</v>
+        <v>9361.6</v>
       </c>
       <c r="J7" t="n">
-        <v>9566.049999999999</v>
+        <v>9471.049999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>9639.9</v>
+        <v>9576.299999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>9713.75</v>
+        <v>9681.549999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>9794.700000000001</v>
+        <v>9788.9</v>
       </c>
       <c r="N7" t="n">
-        <v>9875.65</v>
+        <v>9896.25</v>
       </c>
       <c r="O7" t="n">
-        <v>9942.4</v>
+        <v>9999.4</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1099,21 +1099,23 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1123,59 +1125,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9682.6</v>
+        <v>9698.4</v>
       </c>
       <c r="C8" t="n">
-        <v>9930.1</v>
+        <v>9707.700000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>9610.5</v>
+        <v>9423.9</v>
       </c>
       <c r="E8" t="n">
-        <v>9698.4</v>
+        <v>9539.700000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>15.8</v>
+        <v>-158.7</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0164</v>
       </c>
       <c r="H8" t="n">
-        <v>319.6</v>
+        <v>283.8</v>
       </c>
       <c r="I8" t="n">
-        <v>9361.6</v>
+        <v>9290.9</v>
       </c>
       <c r="J8" t="n">
-        <v>9471.049999999999</v>
+        <v>9342.85</v>
       </c>
       <c r="K8" t="n">
-        <v>9576.299999999999</v>
+        <v>9538.6</v>
       </c>
       <c r="L8" t="n">
-        <v>9681.549999999999</v>
+        <v>9734.35</v>
       </c>
       <c r="M8" t="n">
-        <v>9788.9</v>
+        <v>9858.200000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>9896.25</v>
+        <v>9982.049999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>9999.4</v>
+        <v>10249.7</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1183,23 +1181,21 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1209,55 +1205,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9698.4</v>
+        <v>9539.700000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>9707.700000000001</v>
+        <v>9740.200000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>9423.9</v>
+        <v>9521.5</v>
       </c>
       <c r="E9" t="n">
-        <v>9539.700000000001</v>
+        <v>9720.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-158.7</v>
+        <v>180.8</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0164</v>
+        <v>0.019</v>
       </c>
       <c r="H9" t="n">
-        <v>283.8</v>
+        <v>218.7</v>
       </c>
       <c r="I9" t="n">
-        <v>9290.9</v>
+        <v>9140.1</v>
       </c>
       <c r="J9" t="n">
-        <v>9342.85</v>
+        <v>9242.85</v>
       </c>
       <c r="K9" t="n">
-        <v>9538.6</v>
+        <v>9397.799999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>9734.35</v>
+        <v>9552.75</v>
       </c>
       <c r="M9" t="n">
-        <v>9858.200000000001</v>
+        <v>9681.6</v>
       </c>
       <c r="N9" t="n">
-        <v>9982.049999999999</v>
+        <v>9810.450000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>10249.7</v>
+        <v>9991.5</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1265,19 +1265,19 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1289,59 +1289,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9539.700000000001</v>
+        <v>9720.6</v>
       </c>
       <c r="C10" t="n">
-        <v>9740.200000000001</v>
+        <v>9744.799999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>9521.5</v>
+        <v>9667</v>
       </c>
       <c r="E10" t="n">
-        <v>9720.5</v>
+        <v>9667</v>
       </c>
       <c r="F10" t="n">
-        <v>180.8</v>
+        <v>-53.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.019</v>
+        <v>-0.0055</v>
       </c>
       <c r="H10" t="n">
-        <v>218.7</v>
+        <v>77.8</v>
       </c>
       <c r="I10" t="n">
-        <v>9140.1</v>
+        <v>9302.799999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>9242.85</v>
+        <v>9546.620000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>9397.799999999999</v>
+        <v>9611.15</v>
       </c>
       <c r="L10" t="n">
-        <v>9552.75</v>
+        <v>9675.68</v>
       </c>
       <c r="M10" t="n">
-        <v>9681.6</v>
+        <v>9829.85</v>
       </c>
       <c r="N10" t="n">
-        <v>9810.450000000001</v>
+        <v>9984.030000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>9991.5</v>
+        <v>9958.9</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1354,13 +1350,11 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1373,55 +1367,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9720.6</v>
+        <v>9667.1</v>
       </c>
       <c r="C11" t="n">
-        <v>9744.799999999999</v>
+        <v>9761.5</v>
       </c>
       <c r="D11" t="n">
-        <v>9667</v>
+        <v>9622.700000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>9667</v>
+        <v>9649</v>
       </c>
       <c r="F11" t="n">
-        <v>-53.5</v>
+        <v>-18</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0019</v>
       </c>
       <c r="H11" t="n">
-        <v>77.8</v>
+        <v>138.8</v>
       </c>
       <c r="I11" t="n">
-        <v>9302.799999999999</v>
+        <v>9589.200000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>9546.620000000001</v>
+        <v>9569.75</v>
       </c>
       <c r="K11" t="n">
-        <v>9611.15</v>
+        <v>9628.1</v>
       </c>
       <c r="L11" t="n">
-        <v>9675.68</v>
+        <v>9686.450000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>9829.85</v>
+        <v>9705.9</v>
       </c>
       <c r="N11" t="n">
-        <v>9984.030000000001</v>
+        <v>9725.35</v>
       </c>
       <c r="O11" t="n">
-        <v>9958.9</v>
+        <v>9822.6</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1429,19 +1427,25 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1453,57 +1457,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9667.1</v>
+        <v>9649</v>
       </c>
       <c r="C12" t="n">
-        <v>9761.5</v>
+        <v>9903.1</v>
       </c>
       <c r="D12" t="n">
-        <v>9622.700000000001</v>
+        <v>9649</v>
       </c>
       <c r="E12" t="n">
-        <v>9649</v>
+        <v>9897.4</v>
       </c>
       <c r="F12" t="n">
-        <v>-18</v>
+        <v>248.4</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0257</v>
       </c>
       <c r="H12" t="n">
-        <v>138.8</v>
+        <v>254.1</v>
       </c>
       <c r="I12" t="n">
-        <v>9589.200000000001</v>
+        <v>9483.9</v>
       </c>
       <c r="J12" t="n">
-        <v>9569.75</v>
+        <v>9488.65</v>
       </c>
       <c r="K12" t="n">
-        <v>9628.1</v>
+        <v>9579.6</v>
       </c>
       <c r="L12" t="n">
-        <v>9686.450000000001</v>
+        <v>9670.549999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>9705.9</v>
+        <v>9718.4</v>
       </c>
       <c r="N12" t="n">
-        <v>9725.35</v>
+        <v>9766.25</v>
       </c>
       <c r="O12" t="n">
-        <v>9822.6</v>
+        <v>9900.299999999999</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1511,87 +1515,83 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
-      </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9649</v>
+        <v>9897.4</v>
       </c>
       <c r="C13" t="n">
-        <v>9903.1</v>
+        <v>9901.5</v>
       </c>
       <c r="D13" t="n">
-        <v>9649</v>
+        <v>9829.4</v>
       </c>
       <c r="E13" t="n">
-        <v>9897.4</v>
+        <v>9870.700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>248.4</v>
+        <v>-26.7</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0257</v>
+        <v>-0.0027</v>
       </c>
       <c r="H13" t="n">
-        <v>254.1</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>9483.9</v>
+        <v>9394.9</v>
       </c>
       <c r="J13" t="n">
-        <v>9488.65</v>
+        <v>9703.98</v>
       </c>
       <c r="K13" t="n">
-        <v>9579.6</v>
+        <v>9770.35</v>
       </c>
       <c r="L13" t="n">
-        <v>9670.549999999999</v>
+        <v>9836.73</v>
       </c>
       <c r="M13" t="n">
-        <v>9718.4</v>
+        <v>10024.45</v>
       </c>
       <c r="N13" t="n">
-        <v>9766.25</v>
+        <v>10212.18</v>
       </c>
       <c r="O13" t="n">
-        <v>9900.299999999999</v>
+        <v>10157.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1602,80 +1602,78 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9897.4</v>
+        <v>9870.700000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>9901.5</v>
+        <v>10046.3</v>
       </c>
       <c r="D14" t="n">
-        <v>9829.4</v>
+        <v>9858.5</v>
       </c>
       <c r="E14" t="n">
-        <v>9870.700000000001</v>
+        <v>9951.1</v>
       </c>
       <c r="F14" t="n">
-        <v>-26.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0081</v>
       </c>
       <c r="H14" t="n">
-        <v>72.09999999999999</v>
+        <v>187.8</v>
       </c>
       <c r="I14" t="n">
-        <v>9394.9</v>
+        <v>9757.299999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>9703.98</v>
+        <v>9801.23</v>
       </c>
       <c r="K14" t="n">
-        <v>9770.35</v>
+        <v>9834.65</v>
       </c>
       <c r="L14" t="n">
-        <v>9836.73</v>
+        <v>9868.08</v>
       </c>
       <c r="M14" t="n">
-        <v>10024.45</v>
+        <v>9906.75</v>
       </c>
       <c r="N14" t="n">
-        <v>10212.18</v>
+        <v>9945.42</v>
       </c>
       <c r="O14" t="n">
-        <v>10157.2</v>
+        <v>9973.6</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1686,78 +1684,80 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9870.700000000001</v>
+        <v>9951.5</v>
       </c>
       <c r="C15" t="n">
-        <v>10046.3</v>
+        <v>10158.4</v>
       </c>
       <c r="D15" t="n">
-        <v>9858.5</v>
+        <v>9951.5</v>
       </c>
       <c r="E15" t="n">
-        <v>9951.1</v>
+        <v>10124.6</v>
       </c>
       <c r="F15" t="n">
-        <v>80.40000000000001</v>
+        <v>173.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0081</v>
+        <v>0.0174</v>
       </c>
       <c r="H15" t="n">
-        <v>187.8</v>
+        <v>206.9</v>
       </c>
       <c r="I15" t="n">
-        <v>9757.299999999999</v>
+        <v>9670.700000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>9801.23</v>
+        <v>9762.65</v>
       </c>
       <c r="K15" t="n">
-        <v>9834.65</v>
+        <v>9857.200000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>9868.08</v>
+        <v>9951.75</v>
       </c>
       <c r="M15" t="n">
-        <v>9906.75</v>
+        <v>10045</v>
       </c>
       <c r="N15" t="n">
-        <v>9945.42</v>
+        <v>10138.25</v>
       </c>
       <c r="O15" t="n">
-        <v>9973.6</v>
+        <v>10234.1</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1768,7 +1768,7 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1783,10 +1783,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1798,50 +1796,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9951.5</v>
+        <v>10124.5</v>
       </c>
       <c r="C16" t="n">
-        <v>10158.4</v>
+        <v>10257.8</v>
       </c>
       <c r="D16" t="n">
-        <v>9951.5</v>
+        <v>10089.9</v>
       </c>
       <c r="E16" t="n">
-        <v>10124.6</v>
+        <v>10235.3</v>
       </c>
       <c r="F16" t="n">
-        <v>173.5</v>
+        <v>110.7</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0174</v>
+        <v>0.0109</v>
       </c>
       <c r="H16" t="n">
-        <v>206.9</v>
+        <v>167.9</v>
       </c>
       <c r="I16" t="n">
-        <v>9670.700000000001</v>
+        <v>9744.6</v>
       </c>
       <c r="J16" t="n">
-        <v>9762.65</v>
+        <v>9952.52</v>
       </c>
       <c r="K16" t="n">
-        <v>9857.200000000001</v>
+        <v>10021.15</v>
       </c>
       <c r="L16" t="n">
-        <v>9951.75</v>
+        <v>10089.77</v>
       </c>
       <c r="M16" t="n">
-        <v>10045</v>
+        <v>10228.05</v>
       </c>
       <c r="N16" t="n">
-        <v>10138.25</v>
+        <v>10366.32</v>
       </c>
       <c r="O16" t="n">
-        <v>10234.1</v>
+        <v>10365.3</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1852,20 +1850,18 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1880,69 +1876,71 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10124.5</v>
+        <v>10235.3</v>
       </c>
       <c r="C17" t="n">
-        <v>10257.8</v>
+        <v>10235.3</v>
       </c>
       <c r="D17" t="n">
-        <v>10089.9</v>
+        <v>10050.2</v>
       </c>
       <c r="E17" t="n">
-        <v>10235.3</v>
+        <v>10143.4</v>
       </c>
       <c r="F17" t="n">
-        <v>110.7</v>
+        <v>-91.90000000000001</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>167.9</v>
+        <v>185.1</v>
       </c>
       <c r="I17" t="n">
-        <v>9744.6</v>
+        <v>9922</v>
       </c>
       <c r="J17" t="n">
-        <v>9952.52</v>
+        <v>10098.13</v>
       </c>
       <c r="K17" t="n">
-        <v>10021.15</v>
+        <v>10151.35</v>
       </c>
       <c r="L17" t="n">
-        <v>10089.77</v>
+        <v>10204.57</v>
       </c>
       <c r="M17" t="n">
-        <v>10228.05</v>
+        <v>10319.25</v>
       </c>
       <c r="N17" t="n">
-        <v>10366.32</v>
+        <v>10433.92</v>
       </c>
       <c r="O17" t="n">
-        <v>10365.3</v>
+        <v>10425.7</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1955,77 +1953,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10235.3</v>
+        <v>10143.1</v>
       </c>
       <c r="C18" t="n">
-        <v>10235.3</v>
+        <v>10277.7</v>
       </c>
       <c r="D18" t="n">
-        <v>10050.2</v>
+        <v>10125.3</v>
       </c>
       <c r="E18" t="n">
-        <v>10143.4</v>
+        <v>10223.5</v>
       </c>
       <c r="F18" t="n">
-        <v>-91.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>185.1</v>
+        <v>152.4</v>
       </c>
       <c r="I18" t="n">
-        <v>9922</v>
+        <v>9865.1</v>
       </c>
       <c r="J18" t="n">
-        <v>10098.13</v>
+        <v>9958.629999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>10151.35</v>
+        <v>10050.85</v>
       </c>
       <c r="L18" t="n">
-        <v>10204.57</v>
+        <v>10143.08</v>
       </c>
       <c r="M18" t="n">
-        <v>10319.25</v>
+        <v>10235.95</v>
       </c>
       <c r="N18" t="n">
-        <v>10433.92</v>
+        <v>10328.83</v>
       </c>
       <c r="O18" t="n">
-        <v>10425.7</v>
+        <v>10420.4</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2037,59 +2037,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10143.1</v>
+        <v>10223.7</v>
       </c>
       <c r="C19" t="n">
-        <v>10277.7</v>
+        <v>10481.5</v>
       </c>
       <c r="D19" t="n">
-        <v>10125.3</v>
+        <v>10145.4</v>
       </c>
       <c r="E19" t="n">
-        <v>10223.5</v>
+        <v>10369.8</v>
       </c>
       <c r="F19" t="n">
-        <v>80.09999999999999</v>
+        <v>146.3</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0143</v>
       </c>
       <c r="H19" t="n">
-        <v>152.4</v>
+        <v>336.1</v>
       </c>
       <c r="I19" t="n">
-        <v>9865.1</v>
+        <v>9972.9</v>
       </c>
       <c r="J19" t="n">
-        <v>9958.629999999999</v>
+        <v>10082.1</v>
       </c>
       <c r="K19" t="n">
-        <v>10050.85</v>
+        <v>10147.3</v>
       </c>
       <c r="L19" t="n">
-        <v>10143.08</v>
+        <v>10212.5</v>
       </c>
       <c r="M19" t="n">
-        <v>10235.95</v>
+        <v>10299.7</v>
       </c>
       <c r="N19" t="n">
-        <v>10328.83</v>
+        <v>10386.9</v>
       </c>
       <c r="O19" t="n">
-        <v>10420.4</v>
+        <v>10430.1</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2097,24 +2093,30 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2126,50 +2128,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10223.7</v>
+        <v>10369.8</v>
       </c>
       <c r="C20" t="n">
-        <v>10481.5</v>
+        <v>10535.8</v>
       </c>
       <c r="D20" t="n">
-        <v>10145.4</v>
+        <v>10316</v>
       </c>
       <c r="E20" t="n">
-        <v>10369.8</v>
+        <v>10446.4</v>
       </c>
       <c r="F20" t="n">
-        <v>146.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0074</v>
       </c>
       <c r="H20" t="n">
-        <v>336.1</v>
+        <v>219.8</v>
       </c>
       <c r="I20" t="n">
-        <v>9972.9</v>
+        <v>9809.299999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>10082.1</v>
+        <v>10061.88</v>
       </c>
       <c r="K20" t="n">
-        <v>10147.3</v>
+        <v>10201.75</v>
       </c>
       <c r="L20" t="n">
-        <v>10212.5</v>
+        <v>10341.62</v>
       </c>
       <c r="M20" t="n">
-        <v>10299.7</v>
+        <v>10537.85</v>
       </c>
       <c r="N20" t="n">
-        <v>10386.9</v>
+        <v>10734.07</v>
       </c>
       <c r="O20" t="n">
-        <v>10430.1</v>
+        <v>10817.6</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2177,30 +2179,24 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2212,50 +2208,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10369.8</v>
+        <v>10446.3</v>
       </c>
       <c r="C21" t="n">
-        <v>10535.8</v>
+        <v>10745.8</v>
       </c>
       <c r="D21" t="n">
-        <v>10316</v>
+        <v>10446.3</v>
       </c>
       <c r="E21" t="n">
-        <v>10446.4</v>
+        <v>10686.9</v>
       </c>
       <c r="F21" t="n">
-        <v>76.59999999999999</v>
+        <v>240.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.023</v>
       </c>
       <c r="H21" t="n">
-        <v>219.8</v>
+        <v>299.5</v>
       </c>
       <c r="I21" t="n">
-        <v>9809.299999999999</v>
+        <v>10096.2</v>
       </c>
       <c r="J21" t="n">
-        <v>10061.88</v>
+        <v>10236.85</v>
       </c>
       <c r="K21" t="n">
-        <v>10201.75</v>
+        <v>10336.5</v>
       </c>
       <c r="L21" t="n">
-        <v>10341.62</v>
+        <v>10436.15</v>
       </c>
       <c r="M21" t="n">
-        <v>10537.85</v>
+        <v>10556.3</v>
       </c>
       <c r="N21" t="n">
-        <v>10734.07</v>
+        <v>10676.45</v>
       </c>
       <c r="O21" t="n">
-        <v>10817.6</v>
+        <v>10755.6</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2266,18 +2262,20 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2292,50 +2290,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10446.3</v>
+        <v>10686.8</v>
       </c>
       <c r="C22" t="n">
-        <v>10745.8</v>
+        <v>10934.9</v>
       </c>
       <c r="D22" t="n">
-        <v>10446.3</v>
+        <v>10645.8</v>
       </c>
       <c r="E22" t="n">
-        <v>10686.9</v>
+        <v>10910.6</v>
       </c>
       <c r="F22" t="n">
-        <v>240.5</v>
+        <v>223.7</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0209</v>
       </c>
       <c r="H22" t="n">
-        <v>299.5</v>
+        <v>289.1</v>
       </c>
       <c r="I22" t="n">
-        <v>10096.2</v>
+        <v>10146.8</v>
       </c>
       <c r="J22" t="n">
-        <v>10236.85</v>
+        <v>10432.83</v>
       </c>
       <c r="K22" t="n">
-        <v>10336.5</v>
+        <v>10537.15</v>
       </c>
       <c r="L22" t="n">
-        <v>10436.15</v>
+        <v>10641.48</v>
       </c>
       <c r="M22" t="n">
-        <v>10556.3</v>
+        <v>10836.65</v>
       </c>
       <c r="N22" t="n">
-        <v>10676.45</v>
+        <v>11031.83</v>
       </c>
       <c r="O22" t="n">
-        <v>10755.6</v>
+        <v>11045.3</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2346,20 +2344,18 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2374,69 +2370,73 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10686.8</v>
+        <v>10911</v>
       </c>
       <c r="C23" t="n">
-        <v>10934.9</v>
+        <v>10911</v>
       </c>
       <c r="D23" t="n">
-        <v>10645.8</v>
+        <v>10234.5</v>
       </c>
       <c r="E23" t="n">
-        <v>10910.6</v>
+        <v>10284.8</v>
       </c>
       <c r="F23" t="n">
-        <v>223.7</v>
+        <v>-625.8</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0209</v>
+        <v>-0.0574</v>
       </c>
       <c r="H23" t="n">
-        <v>289.1</v>
+        <v>676.5</v>
       </c>
       <c r="I23" t="n">
-        <v>10146.8</v>
+        <v>10356.7</v>
       </c>
       <c r="J23" t="n">
-        <v>10432.83</v>
+        <v>10681.62</v>
       </c>
       <c r="K23" t="n">
-        <v>10537.15</v>
+        <v>10766.05</v>
       </c>
       <c r="L23" t="n">
-        <v>10641.48</v>
+        <v>10850.47</v>
       </c>
       <c r="M23" t="n">
-        <v>10836.65</v>
+        <v>11055.15</v>
       </c>
       <c r="N23" t="n">
-        <v>11031.83</v>
+        <v>11259.82</v>
       </c>
       <c r="O23" t="n">
-        <v>11045.3</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+        <v>11224</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2444,9 +2444,9 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2454,69 +2454,63 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10911</v>
+        <v>10285</v>
       </c>
       <c r="C24" t="n">
-        <v>10911</v>
+        <v>10447.5</v>
       </c>
       <c r="D24" t="n">
-        <v>10234.5</v>
+        <v>10082</v>
       </c>
       <c r="E24" t="n">
-        <v>10284.8</v>
+        <v>10261.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-625.8</v>
+        <v>-23.6</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0574</v>
+        <v>-0.0023</v>
       </c>
       <c r="H24" t="n">
-        <v>676.5</v>
+        <v>365.5</v>
       </c>
       <c r="I24" t="n">
-        <v>10356.7</v>
+        <v>9558</v>
       </c>
       <c r="J24" t="n">
-        <v>10681.62</v>
+        <v>9464.32</v>
       </c>
       <c r="K24" t="n">
-        <v>10766.05</v>
+        <v>9946.549999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>10850.47</v>
+        <v>10428.77</v>
       </c>
       <c r="M24" t="n">
-        <v>11055.15</v>
+        <v>10623.05</v>
       </c>
       <c r="N24" t="n">
-        <v>11259.82</v>
+        <v>10817.32</v>
       </c>
       <c r="O24" t="n">
-        <v>11224</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>11587.5</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2538,67 +2532,73 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10285</v>
+        <v>10261.1</v>
       </c>
       <c r="C25" t="n">
-        <v>10447.5</v>
+        <v>10447.7</v>
       </c>
       <c r="D25" t="n">
-        <v>10082</v>
+        <v>9915.700000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>10261.2</v>
+        <v>9918.299999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-23.6</v>
+        <v>-342.9</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0334</v>
       </c>
       <c r="H25" t="n">
-        <v>365.5</v>
+        <v>532</v>
       </c>
       <c r="I25" t="n">
-        <v>9558</v>
+        <v>9716.5</v>
       </c>
       <c r="J25" t="n">
-        <v>9464.32</v>
+        <v>9893.93</v>
       </c>
       <c r="K25" t="n">
-        <v>9946.549999999999</v>
+        <v>10078.45</v>
       </c>
       <c r="L25" t="n">
-        <v>10428.77</v>
+        <v>10262.98</v>
       </c>
       <c r="M25" t="n">
-        <v>10623.05</v>
+        <v>10443.95</v>
       </c>
       <c r="N25" t="n">
-        <v>10817.32</v>
+        <v>10624.93</v>
       </c>
       <c r="O25" t="n">
-        <v>11587.5</v>
+        <v>10813</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2611,78 +2611,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10261.1</v>
+        <v>9918.5</v>
       </c>
       <c r="C26" t="n">
-        <v>10447.7</v>
+        <v>10118.2</v>
       </c>
       <c r="D26" t="n">
-        <v>9915.700000000001</v>
+        <v>9670.5</v>
       </c>
       <c r="E26" t="n">
-        <v>9918.299999999999</v>
+        <v>9967.4</v>
       </c>
       <c r="F26" t="n">
-        <v>-342.9</v>
+        <v>49.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0334</v>
+        <v>0.005</v>
       </c>
       <c r="H26" t="n">
-        <v>532</v>
+        <v>447.7</v>
       </c>
       <c r="I26" t="n">
-        <v>9716.5</v>
+        <v>9383.700000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>9893.93</v>
+        <v>9254.6</v>
       </c>
       <c r="K26" t="n">
-        <v>10078.45</v>
+        <v>9652.299999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>10262.98</v>
+        <v>10050</v>
       </c>
       <c r="M26" t="n">
-        <v>10443.95</v>
+        <v>10184.3</v>
       </c>
       <c r="N26" t="n">
-        <v>10624.93</v>
+        <v>10318.6</v>
       </c>
       <c r="O26" t="n">
-        <v>10813</v>
+        <v>10979.7</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2704,50 +2702,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9918.5</v>
+        <v>9967.5</v>
       </c>
       <c r="C27" t="n">
-        <v>10118.2</v>
+        <v>10465.2</v>
       </c>
       <c r="D27" t="n">
-        <v>9670.5</v>
+        <v>9958.1</v>
       </c>
       <c r="E27" t="n">
-        <v>9967.4</v>
+        <v>10436.3</v>
       </c>
       <c r="F27" t="n">
-        <v>49.1</v>
+        <v>468.9</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.005</v>
+        <v>0.047</v>
       </c>
       <c r="H27" t="n">
-        <v>447.7</v>
+        <v>507.1</v>
       </c>
       <c r="I27" t="n">
-        <v>9383.700000000001</v>
+        <v>9222.799999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>9254.6</v>
+        <v>9556.23</v>
       </c>
       <c r="K27" t="n">
-        <v>9652.299999999999</v>
+        <v>9743.549999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>10050</v>
+        <v>9930.879999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>10184.3</v>
+        <v>10191.25</v>
       </c>
       <c r="N27" t="n">
-        <v>10318.6</v>
+        <v>10451.63</v>
       </c>
       <c r="O27" t="n">
-        <v>10979.7</v>
+        <v>10565.9</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2760,14 +2758,18 @@
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2779,57 +2781,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9967.5</v>
+        <v>10436.2</v>
       </c>
       <c r="C28" t="n">
-        <v>10465.2</v>
+        <v>10687.9</v>
       </c>
       <c r="D28" t="n">
-        <v>9958.1</v>
+        <v>10330.9</v>
       </c>
       <c r="E28" t="n">
-        <v>10436.3</v>
+        <v>10600.5</v>
       </c>
       <c r="F28" t="n">
-        <v>468.9</v>
+        <v>164.2</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.047</v>
+        <v>0.0157</v>
       </c>
       <c r="H28" t="n">
-        <v>507.1</v>
+        <v>357</v>
       </c>
       <c r="I28" t="n">
-        <v>9222.799999999999</v>
+        <v>9451</v>
       </c>
       <c r="J28" t="n">
-        <v>9556.23</v>
+        <v>10041.52</v>
       </c>
       <c r="K28" t="n">
-        <v>9743.549999999999</v>
+        <v>10182.75</v>
       </c>
       <c r="L28" t="n">
-        <v>9930.879999999999</v>
+        <v>10323.97</v>
       </c>
       <c r="M28" t="n">
-        <v>10191.25</v>
+        <v>10689.85</v>
       </c>
       <c r="N28" t="n">
-        <v>10451.63</v>
+        <v>11055.73</v>
       </c>
       <c r="O28" t="n">
-        <v>10565.9</v>
+        <v>10972.3</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2840,20 +2842,18 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2872,50 +2872,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10436.2</v>
+        <v>10601.5</v>
       </c>
       <c r="C29" t="n">
-        <v>10687.9</v>
+        <v>10667.6</v>
       </c>
       <c r="D29" t="n">
-        <v>10330.9</v>
+        <v>10528.6</v>
       </c>
       <c r="E29" t="n">
-        <v>10600.5</v>
+        <v>10667.6</v>
       </c>
       <c r="F29" t="n">
-        <v>164.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0063</v>
       </c>
       <c r="H29" t="n">
-        <v>357</v>
+        <v>139</v>
       </c>
       <c r="I29" t="n">
-        <v>9451</v>
+        <v>9973.9</v>
       </c>
       <c r="J29" t="n">
-        <v>10041.52</v>
+        <v>10289.05</v>
       </c>
       <c r="K29" t="n">
-        <v>10182.75</v>
+        <v>10422</v>
       </c>
       <c r="L29" t="n">
-        <v>10323.97</v>
+        <v>10554.95</v>
       </c>
       <c r="M29" t="n">
-        <v>10689.85</v>
+        <v>10779</v>
       </c>
       <c r="N29" t="n">
-        <v>11055.73</v>
+        <v>11003.05</v>
       </c>
       <c r="O29" t="n">
-        <v>10972.3</v>
+        <v>11044.9</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2926,7 +2926,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2949,76 +2949,80 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10601.5</v>
+        <v>10668.4</v>
       </c>
       <c r="C30" t="n">
-        <v>10667.6</v>
+        <v>10683.7</v>
       </c>
       <c r="D30" t="n">
-        <v>10528.6</v>
+        <v>10361.5</v>
       </c>
       <c r="E30" t="n">
-        <v>10667.6</v>
+        <v>10379.1</v>
       </c>
       <c r="F30" t="n">
-        <v>67.09999999999999</v>
+        <v>-288.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0063</v>
+        <v>-0.027</v>
       </c>
       <c r="H30" t="n">
-        <v>139</v>
+        <v>322.2</v>
       </c>
       <c r="I30" t="n">
-        <v>9973.9</v>
+        <v>10389.6</v>
       </c>
       <c r="J30" t="n">
-        <v>10289.05</v>
+        <v>10563.35</v>
       </c>
       <c r="K30" t="n">
-        <v>10422</v>
+        <v>10598.1</v>
       </c>
       <c r="L30" t="n">
-        <v>10554.95</v>
+        <v>10632.85</v>
       </c>
       <c r="M30" t="n">
-        <v>10779</v>
+        <v>10737.1</v>
       </c>
       <c r="N30" t="n">
-        <v>11003.05</v>
+        <v>10841.35</v>
       </c>
       <c r="O30" t="n">
-        <v>11044.9</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+        <v>10806.6</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3033,76 +3037,72 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10668.4</v>
+        <v>10378.5</v>
       </c>
       <c r="C31" t="n">
-        <v>10683.7</v>
+        <v>10410.8</v>
       </c>
       <c r="D31" t="n">
-        <v>10361.5</v>
+        <v>10188.7</v>
       </c>
       <c r="E31" t="n">
-        <v>10379.1</v>
+        <v>10363.9</v>
       </c>
       <c r="F31" t="n">
-        <v>-288.5</v>
+        <v>-15.2</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.0015</v>
       </c>
       <c r="H31" t="n">
-        <v>322.2</v>
+        <v>222.1</v>
       </c>
       <c r="I31" t="n">
-        <v>10389.6</v>
+        <v>10039.3</v>
       </c>
       <c r="J31" t="n">
-        <v>10563.35</v>
+        <v>9985.15</v>
       </c>
       <c r="K31" t="n">
-        <v>10598.1</v>
+        <v>10218</v>
       </c>
       <c r="L31" t="n">
-        <v>10632.85</v>
+        <v>10450.85</v>
       </c>
       <c r="M31" t="n">
-        <v>10737.1</v>
+        <v>10540.2</v>
       </c>
       <c r="N31" t="n">
-        <v>10841.35</v>
+        <v>10629.55</v>
       </c>
       <c r="O31" t="n">
-        <v>10806.6</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
+        <v>11005.9</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3119,79 +3119,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10378.5</v>
+        <v>10365.4</v>
       </c>
       <c r="C32" t="n">
-        <v>10410.8</v>
+        <v>10488.2</v>
       </c>
       <c r="D32" t="n">
-        <v>10188.7</v>
+        <v>10164.3</v>
       </c>
       <c r="E32" t="n">
-        <v>10363.9</v>
+        <v>10233.1</v>
       </c>
       <c r="F32" t="n">
-        <v>-15.2</v>
+        <v>-130.8</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0126</v>
       </c>
       <c r="H32" t="n">
-        <v>222.1</v>
+        <v>323.9</v>
       </c>
       <c r="I32" t="n">
-        <v>10039.3</v>
+        <v>9966.6</v>
       </c>
       <c r="J32" t="n">
-        <v>9985.15</v>
+        <v>10173.88</v>
       </c>
       <c r="K32" t="n">
-        <v>10218</v>
+        <v>10252.85</v>
       </c>
       <c r="L32" t="n">
-        <v>10450.85</v>
+        <v>10331.83</v>
       </c>
       <c r="M32" t="n">
-        <v>10540.2</v>
+        <v>10474.95</v>
       </c>
       <c r="N32" t="n">
-        <v>10629.55</v>
+        <v>10618.08</v>
       </c>
       <c r="O32" t="n">
-        <v>11005.9</v>
+        <v>10632.9</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3203,78 +3203,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10365.4</v>
+        <v>10233.6</v>
       </c>
       <c r="C33" t="n">
-        <v>10488.2</v>
+        <v>10375.7</v>
       </c>
       <c r="D33" t="n">
-        <v>10164.3</v>
+        <v>10152.1</v>
       </c>
       <c r="E33" t="n">
-        <v>10233.1</v>
+        <v>10195.4</v>
       </c>
       <c r="F33" t="n">
-        <v>-130.8</v>
+        <v>-37.7</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0037</v>
       </c>
       <c r="H33" t="n">
-        <v>323.9</v>
+        <v>223.6</v>
       </c>
       <c r="I33" t="n">
-        <v>9966.6</v>
+        <v>9840.4</v>
       </c>
       <c r="J33" t="n">
-        <v>10173.88</v>
+        <v>9862.620000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>10252.85</v>
+        <v>10071.15</v>
       </c>
       <c r="L33" t="n">
-        <v>10331.83</v>
+        <v>10279.67</v>
       </c>
       <c r="M33" t="n">
-        <v>10474.95</v>
+        <v>10395.05</v>
       </c>
       <c r="N33" t="n">
-        <v>10618.08</v>
+        <v>10510.42</v>
       </c>
       <c r="O33" t="n">
-        <v>10632.9</v>
+        <v>10812.1</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3287,59 +3285,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10233.6</v>
+        <v>10194.8</v>
       </c>
       <c r="C34" t="n">
-        <v>10375.7</v>
+        <v>10497.2</v>
       </c>
       <c r="D34" t="n">
-        <v>10152.1</v>
+        <v>10151.5</v>
       </c>
       <c r="E34" t="n">
-        <v>10195.4</v>
+        <v>10466.3</v>
       </c>
       <c r="F34" t="n">
-        <v>-37.7</v>
+        <v>270.9</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0266</v>
       </c>
       <c r="H34" t="n">
-        <v>223.6</v>
+        <v>345.7</v>
       </c>
       <c r="I34" t="n">
-        <v>9840.4</v>
+        <v>9928.5</v>
       </c>
       <c r="J34" t="n">
-        <v>9862.620000000001</v>
+        <v>9937.549999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>10071.15</v>
+        <v>10083.6</v>
       </c>
       <c r="L34" t="n">
-        <v>10279.67</v>
+        <v>10229.65</v>
       </c>
       <c r="M34" t="n">
-        <v>10395.05</v>
+        <v>10307.2</v>
       </c>
       <c r="N34" t="n">
-        <v>10510.42</v>
+        <v>10384.75</v>
       </c>
       <c r="O34" t="n">
-        <v>10812.1</v>
+        <v>10599.3</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3352,72 +3346,80 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10194.8</v>
+        <v>10465.6</v>
       </c>
       <c r="C35" t="n">
-        <v>10497.2</v>
+        <v>10557.2</v>
       </c>
       <c r="D35" t="n">
-        <v>10151.5</v>
+        <v>10381.2</v>
       </c>
       <c r="E35" t="n">
-        <v>10466.3</v>
+        <v>10409.3</v>
       </c>
       <c r="F35" t="n">
-        <v>270.9</v>
+        <v>-57</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0266</v>
+        <v>-0.0054</v>
       </c>
       <c r="H35" t="n">
-        <v>345.7</v>
+        <v>176</v>
       </c>
       <c r="I35" t="n">
-        <v>9928.5</v>
+        <v>9805.799999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>9937.549999999999</v>
+        <v>10191.57</v>
       </c>
       <c r="K35" t="n">
-        <v>10083.6</v>
+        <v>10293.45</v>
       </c>
       <c r="L35" t="n">
-        <v>10229.65</v>
+        <v>10395.32</v>
       </c>
       <c r="M35" t="n">
-        <v>10307.2</v>
+        <v>10639.15</v>
       </c>
       <c r="N35" t="n">
-        <v>10384.75</v>
+        <v>10882.97</v>
       </c>
       <c r="O35" t="n">
-        <v>10599.3</v>
+        <v>10842.9</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3428,20 +3430,16 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3460,50 +3458,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10465.6</v>
+        <v>10409.3</v>
       </c>
       <c r="C36" t="n">
-        <v>10557.2</v>
+        <v>10415.7</v>
       </c>
       <c r="D36" t="n">
-        <v>10381.2</v>
+        <v>10238.6</v>
       </c>
       <c r="E36" t="n">
-        <v>10409.3</v>
+        <v>10368.1</v>
       </c>
       <c r="F36" t="n">
-        <v>-57</v>
+        <v>-41.2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.004</v>
       </c>
       <c r="H36" t="n">
-        <v>176</v>
+        <v>177.1</v>
       </c>
       <c r="I36" t="n">
-        <v>9805.799999999999</v>
+        <v>10205.2</v>
       </c>
       <c r="J36" t="n">
-        <v>10191.57</v>
+        <v>10203.35</v>
       </c>
       <c r="K36" t="n">
-        <v>10293.45</v>
+        <v>10321.3</v>
       </c>
       <c r="L36" t="n">
-        <v>10395.32</v>
+        <v>10439.25</v>
       </c>
       <c r="M36" t="n">
-        <v>10639.15</v>
+        <v>10497.3</v>
       </c>
       <c r="N36" t="n">
-        <v>10882.97</v>
+        <v>10555.35</v>
       </c>
       <c r="O36" t="n">
-        <v>10842.9</v>
+        <v>10733.2</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3511,12 +3509,14 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3535,77 +3535,81 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10409.3</v>
+        <v>10369.1</v>
       </c>
       <c r="C37" t="n">
-        <v>10415.7</v>
+        <v>10471.7</v>
       </c>
       <c r="D37" t="n">
-        <v>10238.6</v>
+        <v>10127.6</v>
       </c>
       <c r="E37" t="n">
-        <v>10368.1</v>
+        <v>10471.7</v>
       </c>
       <c r="F37" t="n">
-        <v>-41.2</v>
+        <v>103.6</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.01</v>
       </c>
       <c r="H37" t="n">
-        <v>177.1</v>
+        <v>344.1</v>
       </c>
       <c r="I37" t="n">
-        <v>10205.2</v>
+        <v>10061.5</v>
       </c>
       <c r="J37" t="n">
-        <v>10203.35</v>
+        <v>10211.47</v>
       </c>
       <c r="K37" t="n">
-        <v>10321.3</v>
+        <v>10279.55</v>
       </c>
       <c r="L37" t="n">
-        <v>10439.25</v>
+        <v>10347.62</v>
       </c>
       <c r="M37" t="n">
-        <v>10497.3</v>
+        <v>10456.65</v>
       </c>
       <c r="N37" t="n">
-        <v>10555.35</v>
+        <v>10565.68</v>
       </c>
       <c r="O37" t="n">
-        <v>10733.2</v>
+        <v>10592.8</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3619,80 +3623,74 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10369.1</v>
+        <v>10471.4</v>
       </c>
       <c r="C38" t="n">
-        <v>10471.7</v>
+        <v>10570.1</v>
       </c>
       <c r="D38" t="n">
-        <v>10127.6</v>
+        <v>10352.9</v>
       </c>
       <c r="E38" t="n">
-        <v>10471.7</v>
+        <v>10363.3</v>
       </c>
       <c r="F38" t="n">
-        <v>103.6</v>
+        <v>-108.4</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0104</v>
       </c>
       <c r="H38" t="n">
-        <v>344.1</v>
+        <v>217.2</v>
       </c>
       <c r="I38" t="n">
-        <v>10061.5</v>
+        <v>9783.5</v>
       </c>
       <c r="J38" t="n">
-        <v>10211.47</v>
+        <v>10213.62</v>
       </c>
       <c r="K38" t="n">
-        <v>10279.55</v>
+        <v>10299.65</v>
       </c>
       <c r="L38" t="n">
-        <v>10347.62</v>
+        <v>10385.68</v>
       </c>
       <c r="M38" t="n">
-        <v>10456.65</v>
+        <v>10643.75</v>
       </c>
       <c r="N38" t="n">
-        <v>10565.68</v>
+        <v>10901.83</v>
       </c>
       <c r="O38" t="n">
-        <v>10592.8</v>
+        <v>10815.8</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3714,50 +3712,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10471.4</v>
+        <v>10363.6</v>
       </c>
       <c r="C39" t="n">
-        <v>10570.1</v>
+        <v>10575.3</v>
       </c>
       <c r="D39" t="n">
-        <v>10352.9</v>
+        <v>10332.4</v>
       </c>
       <c r="E39" t="n">
-        <v>10363.3</v>
+        <v>10508</v>
       </c>
       <c r="F39" t="n">
-        <v>-108.4</v>
+        <v>144.7</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.014</v>
       </c>
       <c r="H39" t="n">
-        <v>217.2</v>
+        <v>242.9</v>
       </c>
       <c r="I39" t="n">
-        <v>9783.5</v>
+        <v>10135.7</v>
       </c>
       <c r="J39" t="n">
-        <v>10213.62</v>
+        <v>10097</v>
       </c>
       <c r="K39" t="n">
-        <v>10299.65</v>
+        <v>10254.7</v>
       </c>
       <c r="L39" t="n">
-        <v>10385.68</v>
+        <v>10412.4</v>
       </c>
       <c r="M39" t="n">
-        <v>10643.75</v>
+        <v>10471.9</v>
       </c>
       <c r="N39" t="n">
-        <v>10901.83</v>
+        <v>10531.4</v>
       </c>
       <c r="O39" t="n">
-        <v>10815.8</v>
+        <v>10787.3</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3770,14 +3768,18 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3796,50 +3798,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10363.6</v>
+        <v>10507.8</v>
       </c>
       <c r="C40" t="n">
-        <v>10575.3</v>
+        <v>10701.3</v>
       </c>
       <c r="D40" t="n">
-        <v>10332.4</v>
+        <v>10429.2</v>
       </c>
       <c r="E40" t="n">
-        <v>10508</v>
+        <v>10679</v>
       </c>
       <c r="F40" t="n">
-        <v>144.7</v>
+        <v>171</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0163</v>
       </c>
       <c r="H40" t="n">
-        <v>242.9</v>
+        <v>272.1</v>
       </c>
       <c r="I40" t="n">
-        <v>10135.7</v>
+        <v>10089.5</v>
       </c>
       <c r="J40" t="n">
-        <v>10097</v>
+        <v>10292.18</v>
       </c>
       <c r="K40" t="n">
-        <v>10254.7</v>
+        <v>10386.55</v>
       </c>
       <c r="L40" t="n">
-        <v>10412.4</v>
+        <v>10480.93</v>
       </c>
       <c r="M40" t="n">
-        <v>10471.9</v>
+        <v>10629.45</v>
       </c>
       <c r="N40" t="n">
-        <v>10531.4</v>
+        <v>10777.97</v>
       </c>
       <c r="O40" t="n">
-        <v>10787.3</v>
+        <v>10818.2</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3850,21 +3852,19 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3873,78 +3873,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10507.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C41" t="n">
-        <v>10701.3</v>
+        <v>10747</v>
       </c>
       <c r="D41" t="n">
-        <v>10429.2</v>
+        <v>10397.5</v>
       </c>
       <c r="E41" t="n">
-        <v>10679</v>
+        <v>10497.3</v>
       </c>
       <c r="F41" t="n">
-        <v>171</v>
+        <v>-181.7</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.017</v>
       </c>
       <c r="H41" t="n">
-        <v>272.1</v>
+        <v>349.5</v>
       </c>
       <c r="I41" t="n">
-        <v>10089.5</v>
+        <v>10157.1</v>
       </c>
       <c r="J41" t="n">
-        <v>10292.18</v>
+        <v>10463.78</v>
       </c>
       <c r="K41" t="n">
-        <v>10386.55</v>
+        <v>10542.95</v>
       </c>
       <c r="L41" t="n">
-        <v>10480.93</v>
+        <v>10622.12</v>
       </c>
       <c r="M41" t="n">
-        <v>10629.45</v>
+        <v>10815.05</v>
       </c>
       <c r="N41" t="n">
-        <v>10777.97</v>
+        <v>11007.97</v>
       </c>
       <c r="O41" t="n">
-        <v>10818.2</v>
+        <v>10973.4</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3957,72 +3955,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10679.4</v>
+        <v>10498.1</v>
       </c>
       <c r="C42" t="n">
-        <v>10747</v>
+        <v>10623.7</v>
       </c>
       <c r="D42" t="n">
-        <v>10397.5</v>
+        <v>10423</v>
       </c>
       <c r="E42" t="n">
-        <v>10497.3</v>
+        <v>10600.4</v>
       </c>
       <c r="F42" t="n">
-        <v>-181.7</v>
+        <v>103.1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.017</v>
+        <v>0.0098</v>
       </c>
       <c r="H42" t="n">
-        <v>349.5</v>
+        <v>200.7</v>
       </c>
       <c r="I42" t="n">
-        <v>10157.1</v>
+        <v>10048</v>
       </c>
       <c r="J42" t="n">
-        <v>10463.78</v>
+        <v>10110.32</v>
       </c>
       <c r="K42" t="n">
-        <v>10542.95</v>
+        <v>10322.55</v>
       </c>
       <c r="L42" t="n">
-        <v>10622.12</v>
+        <v>10534.77</v>
       </c>
       <c r="M42" t="n">
-        <v>10815.05</v>
+        <v>10672.05</v>
       </c>
       <c r="N42" t="n">
-        <v>11007.97</v>
+        <v>10809.32</v>
       </c>
       <c r="O42" t="n">
-        <v>10973.4</v>
+        <v>11096.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4041,57 +4039,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10498.1</v>
+        <v>10600.3</v>
       </c>
       <c r="C43" t="n">
-        <v>10623.7</v>
+        <v>10763.4</v>
       </c>
       <c r="D43" t="n">
-        <v>10423</v>
+        <v>10483.1</v>
       </c>
       <c r="E43" t="n">
-        <v>10600.4</v>
+        <v>10736.2</v>
       </c>
       <c r="F43" t="n">
-        <v>103.1</v>
+        <v>135.8</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0128</v>
       </c>
       <c r="H43" t="n">
-        <v>200.7</v>
+        <v>280.3</v>
       </c>
       <c r="I43" t="n">
-        <v>10048</v>
+        <v>10222.3</v>
       </c>
       <c r="J43" t="n">
-        <v>10110.32</v>
+        <v>10438.23</v>
       </c>
       <c r="K43" t="n">
-        <v>10322.55</v>
+        <v>10500.05</v>
       </c>
       <c r="L43" t="n">
-        <v>10534.77</v>
+        <v>10561.88</v>
       </c>
       <c r="M43" t="n">
-        <v>10672.05</v>
+        <v>10700.75</v>
       </c>
       <c r="N43" t="n">
-        <v>10809.32</v>
+        <v>10839.63</v>
       </c>
       <c r="O43" t="n">
-        <v>11096.5</v>
+        <v>10824.4</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4099,16 +4097,20 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4121,59 +4123,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10600.3</v>
+        <v>10736.1</v>
       </c>
       <c r="C44" t="n">
-        <v>10763.4</v>
+        <v>10989.5</v>
       </c>
       <c r="D44" t="n">
-        <v>10483.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E44" t="n">
-        <v>10736.2</v>
+        <v>10868.1</v>
       </c>
       <c r="F44" t="n">
-        <v>135.8</v>
+        <v>131.9</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0123</v>
       </c>
       <c r="H44" t="n">
-        <v>280.3</v>
+        <v>253.4</v>
       </c>
       <c r="I44" t="n">
-        <v>10222.3</v>
+        <v>10202.8</v>
       </c>
       <c r="J44" t="n">
-        <v>10438.23</v>
+        <v>10512.37</v>
       </c>
       <c r="K44" t="n">
-        <v>10500.05</v>
+        <v>10596.05</v>
       </c>
       <c r="L44" t="n">
-        <v>10561.88</v>
+        <v>10679.73</v>
       </c>
       <c r="M44" t="n">
-        <v>10700.75</v>
+        <v>10876.35</v>
       </c>
       <c r="N44" t="n">
-        <v>10839.63</v>
+        <v>11072.98</v>
       </c>
       <c r="O44" t="n">
-        <v>10824.4</v>
+        <v>11043.7</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4181,12 +4179,10 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4212,50 +4208,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10736.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C45" t="n">
-        <v>10989.5</v>
+        <v>10959.9</v>
       </c>
       <c r="D45" t="n">
-        <v>10736.1</v>
+        <v>10832.5</v>
       </c>
       <c r="E45" t="n">
-        <v>10868.1</v>
+        <v>10901.1</v>
       </c>
       <c r="F45" t="n">
-        <v>131.9</v>
+        <v>33</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0123</v>
+        <v>0.003</v>
       </c>
       <c r="H45" t="n">
-        <v>253.4</v>
+        <v>127.4</v>
       </c>
       <c r="I45" t="n">
-        <v>10202.8</v>
+        <v>10482.7</v>
       </c>
       <c r="J45" t="n">
-        <v>10512.37</v>
+        <v>10617.35</v>
       </c>
       <c r="K45" t="n">
-        <v>10596.05</v>
+        <v>10741.4</v>
       </c>
       <c r="L45" t="n">
-        <v>10679.73</v>
+        <v>10865.45</v>
       </c>
       <c r="M45" t="n">
-        <v>10876.35</v>
+        <v>10994.8</v>
       </c>
       <c r="N45" t="n">
-        <v>11072.98</v>
+        <v>11124.15</v>
       </c>
       <c r="O45" t="n">
-        <v>11043.7</v>
+        <v>11242.9</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4266,15 +4262,13 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4287,68 +4281,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10868.1</v>
+        <v>10901.1</v>
       </c>
       <c r="C46" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D46" t="n">
-        <v>10832.5</v>
+        <v>10723.7</v>
       </c>
       <c r="E46" t="n">
-        <v>10901.1</v>
+        <v>10750.1</v>
       </c>
       <c r="F46" t="n">
-        <v>33</v>
+        <v>-151</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0139</v>
       </c>
       <c r="H46" t="n">
-        <v>127.4</v>
+        <v>187.2</v>
       </c>
       <c r="I46" t="n">
-        <v>10482.7</v>
+        <v>10705.1</v>
       </c>
       <c r="J46" t="n">
-        <v>10617.35</v>
+        <v>10776.15</v>
       </c>
       <c r="K46" t="n">
-        <v>10741.4</v>
+        <v>10837.4</v>
       </c>
       <c r="L46" t="n">
-        <v>10865.45</v>
+        <v>10898.65</v>
       </c>
       <c r="M46" t="n">
-        <v>10994.8</v>
+        <v>10964.8</v>
       </c>
       <c r="N46" t="n">
-        <v>11124.15</v>
+        <v>11030.95</v>
       </c>
       <c r="O46" t="n">
-        <v>11242.9</v>
+        <v>11087.3</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4360,86 +4362,80 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10901.1</v>
+        <v>10750</v>
       </c>
       <c r="C47" t="n">
-        <v>10910.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D47" t="n">
-        <v>10723.7</v>
+        <v>10684.4</v>
       </c>
       <c r="E47" t="n">
-        <v>10750.1</v>
+        <v>10816.6</v>
       </c>
       <c r="F47" t="n">
-        <v>-151</v>
+        <v>66.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0139</v>
+        <v>0.0062</v>
       </c>
       <c r="H47" t="n">
-        <v>187.2</v>
+        <v>147.2</v>
       </c>
       <c r="I47" t="n">
-        <v>10705.1</v>
+        <v>10536.5</v>
       </c>
       <c r="J47" t="n">
-        <v>10776.15</v>
+        <v>10529.3</v>
       </c>
       <c r="K47" t="n">
-        <v>10837.4</v>
+        <v>10656.5</v>
       </c>
       <c r="L47" t="n">
-        <v>10898.65</v>
+        <v>10783.7</v>
       </c>
       <c r="M47" t="n">
-        <v>10964.8</v>
+        <v>10843.7</v>
       </c>
       <c r="N47" t="n">
-        <v>11030.95</v>
+        <v>10903.7</v>
       </c>
       <c r="O47" t="n">
-        <v>11087.3</v>
+        <v>11098.1</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4451,55 +4447,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10750</v>
+        <v>10816.3</v>
       </c>
       <c r="C48" t="n">
-        <v>10831.6</v>
+        <v>10920.5</v>
       </c>
       <c r="D48" t="n">
-        <v>10684.4</v>
+        <v>10772.6</v>
       </c>
       <c r="E48" t="n">
-        <v>10816.6</v>
+        <v>10824.3</v>
       </c>
       <c r="F48" t="n">
-        <v>66.5</v>
+        <v>7.7</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0007</v>
       </c>
       <c r="H48" t="n">
-        <v>147.2</v>
+        <v>147.9</v>
       </c>
       <c r="I48" t="n">
-        <v>10536.5</v>
+        <v>10537.2</v>
       </c>
       <c r="J48" t="n">
-        <v>10529.3</v>
+        <v>10698.7</v>
       </c>
       <c r="K48" t="n">
-        <v>10656.5</v>
+        <v>10743</v>
       </c>
       <c r="L48" t="n">
-        <v>10783.7</v>
+        <v>10787.3</v>
       </c>
       <c r="M48" t="n">
-        <v>10843.7</v>
+        <v>10890.2</v>
       </c>
       <c r="N48" t="n">
-        <v>10903.7</v>
+        <v>10993.1</v>
       </c>
       <c r="O48" t="n">
-        <v>11098.1</v>
+        <v>10978.8</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4510,14 +4510,14 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U48" s="8" t="n">
@@ -4533,57 +4533,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10816.3</v>
+        <v>10824.6</v>
       </c>
       <c r="C49" t="n">
-        <v>10920.5</v>
+        <v>10866.8</v>
       </c>
       <c r="D49" t="n">
-        <v>10772.6</v>
+        <v>10689.6</v>
       </c>
       <c r="E49" t="n">
-        <v>10824.3</v>
+        <v>10831.1</v>
       </c>
       <c r="F49" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>147.9</v>
+        <v>177.2</v>
       </c>
       <c r="I49" t="n">
-        <v>10537.2</v>
+        <v>10624.7</v>
       </c>
       <c r="J49" t="n">
-        <v>10698.7</v>
+        <v>10665.27</v>
       </c>
       <c r="K49" t="n">
-        <v>10743</v>
+        <v>10750.35</v>
       </c>
       <c r="L49" t="n">
-        <v>10787.3</v>
+        <v>10835.42</v>
       </c>
       <c r="M49" t="n">
-        <v>10890.2</v>
+        <v>10898.25</v>
       </c>
       <c r="N49" t="n">
-        <v>10993.1</v>
+        <v>10961.08</v>
       </c>
       <c r="O49" t="n">
-        <v>10978.8</v>
+        <v>11068.4</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4591,18 +4591,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4617,72 +4617,74 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10824.6</v>
+        <v>10831</v>
       </c>
       <c r="C50" t="n">
-        <v>10866.8</v>
+        <v>10868.3</v>
       </c>
       <c r="D50" t="n">
-        <v>10689.6</v>
+        <v>10594.3</v>
       </c>
       <c r="E50" t="n">
-        <v>10831.1</v>
+        <v>10650.4</v>
       </c>
       <c r="F50" t="n">
-        <v>6.8</v>
+        <v>-180.7</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0167</v>
       </c>
       <c r="H50" t="n">
-        <v>177.2</v>
+        <v>274</v>
       </c>
       <c r="I50" t="n">
-        <v>10624.7</v>
+        <v>10512.4</v>
       </c>
       <c r="J50" t="n">
-        <v>10665.27</v>
+        <v>10680.35</v>
       </c>
       <c r="K50" t="n">
-        <v>10750.35</v>
+        <v>10742.5</v>
       </c>
       <c r="L50" t="n">
-        <v>10835.42</v>
+        <v>10804.65</v>
       </c>
       <c r="M50" t="n">
-        <v>10898.25</v>
+        <v>10919.7</v>
       </c>
       <c r="N50" t="n">
-        <v>10961.08</v>
+        <v>11034.75</v>
       </c>
       <c r="O50" t="n">
-        <v>11068.4</v>
+        <v>11044</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4708,71 +4710,69 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10831</v>
+        <v>10650.9</v>
       </c>
       <c r="C51" t="n">
-        <v>10868.3</v>
+        <v>10823</v>
       </c>
       <c r="D51" t="n">
-        <v>10594.3</v>
+        <v>10586.4</v>
       </c>
       <c r="E51" t="n">
-        <v>10650.4</v>
+        <v>10659.1</v>
       </c>
       <c r="F51" t="n">
-        <v>-180.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0167</v>
+        <v>0.0008</v>
       </c>
       <c r="H51" t="n">
-        <v>274</v>
+        <v>236.6</v>
       </c>
       <c r="I51" t="n">
-        <v>10512.4</v>
+        <v>10320.3</v>
       </c>
       <c r="J51" t="n">
-        <v>10680.35</v>
+        <v>10335.95</v>
       </c>
       <c r="K51" t="n">
-        <v>10742.5</v>
+        <v>10513.4</v>
       </c>
       <c r="L51" t="n">
-        <v>10804.65</v>
+        <v>10690.85</v>
       </c>
       <c r="M51" t="n">
-        <v>10919.7</v>
+        <v>10787.4</v>
       </c>
       <c r="N51" t="n">
-        <v>11034.75</v>
+        <v>10883.95</v>
       </c>
       <c r="O51" t="n">
-        <v>11044</v>
+        <v>11142.3</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4794,50 +4794,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10650.9</v>
+        <v>10659.1</v>
       </c>
       <c r="C52" t="n">
-        <v>10823</v>
+        <v>10774.7</v>
       </c>
       <c r="D52" t="n">
-        <v>10586.4</v>
+        <v>10656.7</v>
       </c>
       <c r="E52" t="n">
-        <v>10659.1</v>
+        <v>10695.3</v>
       </c>
       <c r="F52" t="n">
-        <v>8.699999999999999</v>
+        <v>36.2</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0034</v>
       </c>
       <c r="H52" t="n">
-        <v>236.6</v>
+        <v>118</v>
       </c>
       <c r="I52" t="n">
-        <v>10320.3</v>
+        <v>10349.8</v>
       </c>
       <c r="J52" t="n">
-        <v>10335.95</v>
+        <v>10399.7</v>
       </c>
       <c r="K52" t="n">
-        <v>10513.4</v>
+        <v>10540.8</v>
       </c>
       <c r="L52" t="n">
-        <v>10690.85</v>
+        <v>10681.9</v>
       </c>
       <c r="M52" t="n">
-        <v>10787.4</v>
+        <v>10777.4</v>
       </c>
       <c r="N52" t="n">
-        <v>10883.95</v>
+        <v>10872.9</v>
       </c>
       <c r="O52" t="n">
-        <v>11142.3</v>
+        <v>11059.6</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4850,13 +4850,11 @@
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4871,74 +4869,82 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10659.1</v>
+        <v>10695.2</v>
       </c>
       <c r="C53" t="n">
-        <v>10774.7</v>
+        <v>10758.7</v>
       </c>
       <c r="D53" t="n">
-        <v>10656.7</v>
+        <v>10390.7</v>
       </c>
       <c r="E53" t="n">
-        <v>10695.3</v>
+        <v>10462</v>
       </c>
       <c r="F53" t="n">
-        <v>36.2</v>
+        <v>-233.3</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.0218</v>
       </c>
       <c r="H53" t="n">
-        <v>118</v>
+        <v>368</v>
       </c>
       <c r="I53" t="n">
-        <v>10349.8</v>
+        <v>10538.7</v>
       </c>
       <c r="J53" t="n">
-        <v>10399.7</v>
+        <v>10567.1</v>
       </c>
       <c r="K53" t="n">
-        <v>10540.8</v>
+        <v>10636.3</v>
       </c>
       <c r="L53" t="n">
-        <v>10681.9</v>
+        <v>10705.5</v>
       </c>
       <c r="M53" t="n">
-        <v>10777.4</v>
+        <v>10754.3</v>
       </c>
       <c r="N53" t="n">
-        <v>10872.9</v>
+        <v>10803.1</v>
       </c>
       <c r="O53" t="n">
-        <v>11059.6</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+        <v>10892.7</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4951,84 +4957,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10695.2</v>
+        <v>10462.4</v>
       </c>
       <c r="C54" t="n">
-        <v>10758.7</v>
+        <v>10602.6</v>
       </c>
       <c r="D54" t="n">
-        <v>10390.7</v>
+        <v>10367.3</v>
       </c>
       <c r="E54" t="n">
-        <v>10462</v>
+        <v>10552.1</v>
       </c>
       <c r="F54" t="n">
-        <v>-233.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0218</v>
+        <v>0.0086</v>
       </c>
       <c r="H54" t="n">
-        <v>368</v>
+        <v>235.3</v>
       </c>
       <c r="I54" t="n">
-        <v>10538.7</v>
+        <v>10022.7</v>
       </c>
       <c r="J54" t="n">
-        <v>10567.1</v>
+        <v>10037.65</v>
       </c>
       <c r="K54" t="n">
-        <v>10636.3</v>
+        <v>10278</v>
       </c>
       <c r="L54" t="n">
-        <v>10705.5</v>
+        <v>10518.35</v>
       </c>
       <c r="M54" t="n">
-        <v>10754.3</v>
+        <v>10646</v>
       </c>
       <c r="N54" t="n">
-        <v>10803.1</v>
+        <v>10773.65</v>
       </c>
       <c r="O54" t="n">
-        <v>10892.7</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>11126.7</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5041,55 +5035,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10462.4</v>
+        <v>10551.6</v>
       </c>
       <c r="C55" t="n">
-        <v>10602.6</v>
+        <v>10892.4</v>
       </c>
       <c r="D55" t="n">
-        <v>10367.3</v>
+        <v>10549.6</v>
       </c>
       <c r="E55" t="n">
-        <v>10552.1</v>
+        <v>10881.9</v>
       </c>
       <c r="F55" t="n">
-        <v>90.09999999999999</v>
+        <v>329.8</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0313</v>
       </c>
       <c r="H55" t="n">
-        <v>235.3</v>
+        <v>342.8</v>
       </c>
       <c r="I55" t="n">
-        <v>10022.7</v>
+        <v>10132</v>
       </c>
       <c r="J55" t="n">
-        <v>10037.65</v>
+        <v>10350.37</v>
       </c>
       <c r="K55" t="n">
-        <v>10278</v>
+        <v>10434.45</v>
       </c>
       <c r="L55" t="n">
-        <v>10518.35</v>
+        <v>10518.52</v>
       </c>
       <c r="M55" t="n">
-        <v>10646</v>
+        <v>10669.75</v>
       </c>
       <c r="N55" t="n">
-        <v>10773.65</v>
+        <v>10820.97</v>
       </c>
       <c r="O55" t="n">
-        <v>11126.7</v>
+        <v>10837.9</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5100,78 +5098,80 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10551.6</v>
+        <v>10882.3</v>
       </c>
       <c r="C56" t="n">
-        <v>10892.4</v>
+        <v>10889.9</v>
       </c>
       <c r="D56" t="n">
-        <v>10549.6</v>
+        <v>10630</v>
       </c>
       <c r="E56" t="n">
-        <v>10881.9</v>
+        <v>10690.4</v>
       </c>
       <c r="F56" t="n">
-        <v>329.8</v>
+        <v>-191.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0313</v>
+        <v>-0.0176</v>
       </c>
       <c r="H56" t="n">
-        <v>342.8</v>
+        <v>259.9</v>
       </c>
       <c r="I56" t="n">
-        <v>10132</v>
+        <v>10206.8</v>
       </c>
       <c r="J56" t="n">
-        <v>10350.37</v>
+        <v>10619.55</v>
       </c>
       <c r="K56" t="n">
-        <v>10434.45</v>
+        <v>10710.5</v>
       </c>
       <c r="L56" t="n">
-        <v>10518.52</v>
+        <v>10801.45</v>
       </c>
       <c r="M56" t="n">
-        <v>10669.75</v>
+        <v>11053.3</v>
       </c>
       <c r="N56" t="n">
-        <v>10820.97</v>
+        <v>11305.15</v>
       </c>
       <c r="O56" t="n">
-        <v>10837.9</v>
+        <v>11235.2</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5179,83 +5179,83 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10882.3</v>
+        <v>10690.9</v>
       </c>
       <c r="C57" t="n">
-        <v>10889.9</v>
+        <v>10778.72</v>
       </c>
       <c r="D57" t="n">
-        <v>10630</v>
+        <v>10643.3</v>
       </c>
       <c r="E57" t="n">
-        <v>10690.4</v>
+        <v>10729.78</v>
       </c>
       <c r="F57" t="n">
-        <v>-191.5</v>
+        <v>39.38</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0037</v>
       </c>
       <c r="H57" t="n">
-        <v>259.9</v>
+        <v>135.42</v>
       </c>
       <c r="I57" t="n">
-        <v>10206.8</v>
+        <v>10370.1</v>
       </c>
       <c r="J57" t="n">
-        <v>10619.55</v>
+        <v>10395.73</v>
       </c>
       <c r="K57" t="n">
-        <v>10710.5</v>
+        <v>10560.45</v>
       </c>
       <c r="L57" t="n">
-        <v>10801.45</v>
+        <v>10725.18</v>
       </c>
       <c r="M57" t="n">
-        <v>11053.3</v>
+        <v>10820.35</v>
       </c>
       <c r="N57" t="n">
-        <v>11305.15</v>
+        <v>10915.53</v>
       </c>
       <c r="O57" t="n">
-        <v>11235.2</v>
+        <v>11149.8</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5263,14 +5263,12 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5288,88 +5286,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>10690.9</v>
-      </c>
-      <c r="C58" t="n">
-        <v>10774.5</v>
-      </c>
-      <c r="D58" t="n">
-        <v>10643.3</v>
-      </c>
-      <c r="E58" t="n">
-        <v>10722.07</v>
-      </c>
-      <c r="F58" t="n">
-        <v>31.67</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="H58" t="n">
-        <v>131.2</v>
-      </c>
-      <c r="I58" t="n">
-        <v>10370.1</v>
-      </c>
-      <c r="J58" t="n">
-        <v>10395.73</v>
-      </c>
-      <c r="K58" t="n">
-        <v>10560.45</v>
-      </c>
-      <c r="L58" t="n">
-        <v>10725.18</v>
-      </c>
-      <c r="M58" t="n">
-        <v>10820.35</v>
-      </c>
-      <c r="N58" t="n">
-        <v>10915.53</v>
-      </c>
-      <c r="O58" t="n">
-        <v>11149.8</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>
